--- a/04-Bieu-Mau/08-FRM-800/FRM-801_Training_Plan.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-801_Training_Plan.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -102,8 +102,40 @@
       <color theme="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="001A2733"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="001565C0"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007A8FA6"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00BBCCCC"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -135,8 +167,33 @@
         <fgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002C9CD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4F0F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001565C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F7FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000C2D48"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="56">
+  <borders count="85">
     <border>
       <left/>
       <right/>
@@ -719,11 +776,317 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -960,6 +1323,227 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="72" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="76" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="78" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="79" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="80" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="79" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="81" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="37" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="83" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="73" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="71" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="74" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="78" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="81" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="70" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="73" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="74" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="76" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="78" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="82" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="37" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="82" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="70" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="73" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="70" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1034,6 +1618,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1792692" cy="517122"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1792692" cy="517122"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1792692" cy="517122"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1387,1558 +2061,1648 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="50" t="n"/>
-      <c r="B1" s="99" t="n"/>
-      <c r="C1" s="99" t="n"/>
-      <c r="D1" s="99" t="n"/>
-      <c r="E1" s="99" t="n"/>
-      <c r="F1" s="99" t="n"/>
-      <c r="G1" s="99" t="n"/>
-      <c r="H1" s="99" t="n"/>
-      <c r="I1" s="99" t="n"/>
-      <c r="J1" s="99" t="n"/>
-      <c r="K1" s="99" t="n"/>
-      <c r="L1" s="52" t="inlineStr">
+      <c r="A1" s="106" t="n"/>
+      <c r="B1" s="107" t="n"/>
+      <c r="C1" s="107" t="n"/>
+      <c r="D1" s="107" t="n"/>
+      <c r="E1" s="107" t="n"/>
+      <c r="F1" s="107" t="n"/>
+      <c r="G1" s="107" t="n"/>
+      <c r="H1" s="107" t="n"/>
+      <c r="I1" s="107" t="n"/>
+      <c r="J1" s="107" t="n"/>
+      <c r="K1" s="108" t="n"/>
+      <c r="L1" s="109" t="inlineStr">
         <is>
           <t>TRAINING PLAN</t>
         </is>
       </c>
-      <c r="M1" s="99" t="n"/>
-      <c r="N1" s="99" t="n"/>
-      <c r="O1" s="99" t="n"/>
-      <c r="P1" s="99" t="n"/>
-      <c r="Q1" s="99" t="n"/>
-      <c r="R1" s="99" t="n"/>
-      <c r="S1" s="99" t="n"/>
-      <c r="T1" s="99" t="n"/>
-      <c r="U1" s="99" t="n"/>
-      <c r="V1" s="99" t="n"/>
-      <c r="W1" s="99" t="n"/>
-      <c r="X1" s="99" t="n"/>
-      <c r="Y1" s="99" t="n"/>
-      <c r="Z1" s="99" t="n"/>
-      <c r="AA1" s="99" t="n"/>
-      <c r="AB1" s="99" t="n"/>
-      <c r="AC1" s="99" t="n"/>
-      <c r="AD1" s="99" t="n"/>
-      <c r="AE1" s="99" t="n"/>
-      <c r="AF1" s="99" t="n"/>
-      <c r="AG1" s="99" t="n"/>
-      <c r="AH1" s="99" t="n"/>
-      <c r="AI1" s="99" t="n"/>
-      <c r="AJ1" s="99" t="n"/>
-      <c r="AK1" s="99" t="n"/>
-      <c r="AL1" s="99" t="n"/>
-      <c r="AM1" s="99" t="n"/>
-      <c r="AN1" s="99" t="n"/>
-      <c r="AO1" s="99" t="n"/>
-      <c r="AP1" s="99" t="n"/>
-      <c r="AQ1" s="53" t="inlineStr">
+      <c r="M1" s="110" t="n"/>
+      <c r="N1" s="110" t="n"/>
+      <c r="O1" s="110" t="n"/>
+      <c r="P1" s="110" t="n"/>
+      <c r="Q1" s="110" t="n"/>
+      <c r="R1" s="110" t="n"/>
+      <c r="S1" s="110" t="n"/>
+      <c r="T1" s="110" t="n"/>
+      <c r="U1" s="110" t="n"/>
+      <c r="V1" s="110" t="n"/>
+      <c r="W1" s="110" t="n"/>
+      <c r="X1" s="110" t="n"/>
+      <c r="Y1" s="110" t="n"/>
+      <c r="Z1" s="110" t="n"/>
+      <c r="AA1" s="110" t="n"/>
+      <c r="AB1" s="110" t="n"/>
+      <c r="AC1" s="110" t="n"/>
+      <c r="AD1" s="110" t="n"/>
+      <c r="AE1" s="110" t="n"/>
+      <c r="AF1" s="110" t="n"/>
+      <c r="AG1" s="110" t="n"/>
+      <c r="AH1" s="110" t="n"/>
+      <c r="AI1" s="110" t="n"/>
+      <c r="AJ1" s="110" t="n"/>
+      <c r="AK1" s="110" t="n"/>
+      <c r="AL1" s="110" t="n"/>
+      <c r="AM1" s="110" t="n"/>
+      <c r="AN1" s="110" t="n"/>
+      <c r="AO1" s="110" t="n"/>
+      <c r="AP1" s="111" t="n"/>
+      <c r="AQ1" s="112" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="100" t="n"/>
-      <c r="AS1" s="100" t="n"/>
-      <c r="AT1" s="100" t="n"/>
-      <c r="AU1" s="100" t="n"/>
-      <c r="AV1" s="101" t="n"/>
-      <c r="AW1" s="56" t="inlineStr">
+      <c r="AR1" s="113" t="n"/>
+      <c r="AS1" s="113" t="n"/>
+      <c r="AT1" s="113" t="n"/>
+      <c r="AU1" s="113" t="n"/>
+      <c r="AV1" s="114" t="n"/>
+      <c r="AW1" s="115" t="inlineStr">
         <is>
           <t>FRM-801</t>
         </is>
       </c>
-      <c r="AX1" s="100" t="n"/>
-      <c r="AY1" s="100" t="n"/>
-      <c r="AZ1" s="100" t="n"/>
-      <c r="BA1" s="100" t="n"/>
-      <c r="BB1" s="100" t="n"/>
-      <c r="BC1" s="100" t="n"/>
-      <c r="BD1" s="101" t="n"/>
+      <c r="AX1" s="116" t="n"/>
+      <c r="AY1" s="116" t="n"/>
+      <c r="AZ1" s="116" t="n"/>
+      <c r="BA1" s="116" t="n"/>
+      <c r="BB1" s="116" t="n"/>
+      <c r="BC1" s="116" t="n"/>
+      <c r="BD1" s="117" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="102" t="n"/>
-      <c r="L2" s="102" t="n"/>
-      <c r="AQ2" s="59" t="inlineStr">
+      <c r="A2" s="118" t="n"/>
+      <c r="B2" s="46" t="n"/>
+      <c r="C2" s="46" t="n"/>
+      <c r="D2" s="46" t="n"/>
+      <c r="E2" s="46" t="n"/>
+      <c r="F2" s="46" t="n"/>
+      <c r="G2" s="46" t="n"/>
+      <c r="H2" s="46" t="n"/>
+      <c r="I2" s="46" t="n"/>
+      <c r="J2" s="46" t="n"/>
+      <c r="K2" s="119" t="n"/>
+      <c r="L2" s="120" t="n"/>
+      <c r="M2" s="121" t="n"/>
+      <c r="N2" s="121" t="n"/>
+      <c r="O2" s="121" t="n"/>
+      <c r="P2" s="121" t="n"/>
+      <c r="Q2" s="121" t="n"/>
+      <c r="R2" s="121" t="n"/>
+      <c r="S2" s="121" t="n"/>
+      <c r="T2" s="121" t="n"/>
+      <c r="U2" s="121" t="n"/>
+      <c r="V2" s="121" t="n"/>
+      <c r="W2" s="121" t="n"/>
+      <c r="X2" s="121" t="n"/>
+      <c r="Y2" s="121" t="n"/>
+      <c r="Z2" s="121" t="n"/>
+      <c r="AA2" s="121" t="n"/>
+      <c r="AB2" s="121" t="n"/>
+      <c r="AC2" s="121" t="n"/>
+      <c r="AD2" s="121" t="n"/>
+      <c r="AE2" s="121" t="n"/>
+      <c r="AF2" s="121" t="n"/>
+      <c r="AG2" s="121" t="n"/>
+      <c r="AH2" s="121" t="n"/>
+      <c r="AI2" s="121" t="n"/>
+      <c r="AJ2" s="121" t="n"/>
+      <c r="AK2" s="121" t="n"/>
+      <c r="AL2" s="121" t="n"/>
+      <c r="AM2" s="121" t="n"/>
+      <c r="AN2" s="121" t="n"/>
+      <c r="AO2" s="121" t="n"/>
+      <c r="AP2" s="122" t="n"/>
+      <c r="AQ2" s="123" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="103" t="n"/>
-      <c r="AS2" s="103" t="n"/>
-      <c r="AT2" s="103" t="n"/>
-      <c r="AU2" s="103" t="n"/>
-      <c r="AV2" s="104" t="n"/>
-      <c r="AW2" s="62" t="inlineStr">
+      <c r="AR2" s="124" t="n"/>
+      <c r="AS2" s="124" t="n"/>
+      <c r="AT2" s="124" t="n"/>
+      <c r="AU2" s="124" t="n"/>
+      <c r="AV2" s="125" t="n"/>
+      <c r="AW2" s="126" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="103" t="n"/>
-      <c r="AY2" s="103" t="n"/>
-      <c r="AZ2" s="103" t="n"/>
-      <c r="BA2" s="103" t="n"/>
-      <c r="BB2" s="103" t="n"/>
-      <c r="BC2" s="103" t="n"/>
-      <c r="BD2" s="104" t="n"/>
+      <c r="AX2" s="127" t="n"/>
+      <c r="AY2" s="127" t="n"/>
+      <c r="AZ2" s="127" t="n"/>
+      <c r="BA2" s="127" t="n"/>
+      <c r="BB2" s="127" t="n"/>
+      <c r="BC2" s="127" t="n"/>
+      <c r="BD2" s="128" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="102" t="n"/>
-      <c r="L3" s="105" t="n"/>
-      <c r="M3" s="103" t="n"/>
-      <c r="N3" s="103" t="n"/>
-      <c r="O3" s="103" t="n"/>
-      <c r="P3" s="103" t="n"/>
-      <c r="Q3" s="103" t="n"/>
-      <c r="R3" s="103" t="n"/>
-      <c r="S3" s="103" t="n"/>
-      <c r="T3" s="103" t="n"/>
-      <c r="U3" s="103" t="n"/>
-      <c r="V3" s="103" t="n"/>
-      <c r="W3" s="103" t="n"/>
-      <c r="X3" s="103" t="n"/>
-      <c r="Y3" s="103" t="n"/>
-      <c r="Z3" s="103" t="n"/>
-      <c r="AA3" s="103" t="n"/>
-      <c r="AB3" s="103" t="n"/>
-      <c r="AC3" s="103" t="n"/>
-      <c r="AD3" s="103" t="n"/>
-      <c r="AE3" s="103" t="n"/>
-      <c r="AF3" s="103" t="n"/>
-      <c r="AG3" s="103" t="n"/>
-      <c r="AH3" s="103" t="n"/>
-      <c r="AI3" s="103" t="n"/>
-      <c r="AJ3" s="103" t="n"/>
-      <c r="AK3" s="103" t="n"/>
-      <c r="AL3" s="103" t="n"/>
-      <c r="AM3" s="103" t="n"/>
-      <c r="AN3" s="103" t="n"/>
-      <c r="AO3" s="103" t="n"/>
-      <c r="AP3" s="103" t="n"/>
-      <c r="AQ3" s="59" t="inlineStr">
+      <c r="A3" s="118" t="n"/>
+      <c r="B3" s="46" t="n"/>
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="46" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="46" t="n"/>
+      <c r="G3" s="46" t="n"/>
+      <c r="H3" s="46" t="n"/>
+      <c r="I3" s="46" t="n"/>
+      <c r="J3" s="46" t="n"/>
+      <c r="K3" s="119" t="n"/>
+      <c r="L3" s="120" t="n"/>
+      <c r="M3" s="121" t="n"/>
+      <c r="N3" s="121" t="n"/>
+      <c r="O3" s="121" t="n"/>
+      <c r="P3" s="121" t="n"/>
+      <c r="Q3" s="121" t="n"/>
+      <c r="R3" s="121" t="n"/>
+      <c r="S3" s="121" t="n"/>
+      <c r="T3" s="121" t="n"/>
+      <c r="U3" s="121" t="n"/>
+      <c r="V3" s="121" t="n"/>
+      <c r="W3" s="121" t="n"/>
+      <c r="X3" s="121" t="n"/>
+      <c r="Y3" s="121" t="n"/>
+      <c r="Z3" s="121" t="n"/>
+      <c r="AA3" s="121" t="n"/>
+      <c r="AB3" s="121" t="n"/>
+      <c r="AC3" s="121" t="n"/>
+      <c r="AD3" s="121" t="n"/>
+      <c r="AE3" s="121" t="n"/>
+      <c r="AF3" s="121" t="n"/>
+      <c r="AG3" s="121" t="n"/>
+      <c r="AH3" s="121" t="n"/>
+      <c r="AI3" s="121" t="n"/>
+      <c r="AJ3" s="121" t="n"/>
+      <c r="AK3" s="121" t="n"/>
+      <c r="AL3" s="121" t="n"/>
+      <c r="AM3" s="121" t="n"/>
+      <c r="AN3" s="121" t="n"/>
+      <c r="AO3" s="121" t="n"/>
+      <c r="AP3" s="122" t="n"/>
+      <c r="AQ3" s="123" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="103" t="n"/>
-      <c r="AS3" s="103" t="n"/>
-      <c r="AT3" s="103" t="n"/>
-      <c r="AU3" s="103" t="n"/>
-      <c r="AV3" s="104" t="n"/>
-      <c r="AW3" s="62" t="inlineStr">
+      <c r="AR3" s="124" t="n"/>
+      <c r="AS3" s="124" t="n"/>
+      <c r="AT3" s="124" t="n"/>
+      <c r="AU3" s="124" t="n"/>
+      <c r="AV3" s="125" t="n"/>
+      <c r="AW3" s="126" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="103" t="n"/>
-      <c r="AY3" s="103" t="n"/>
-      <c r="AZ3" s="103" t="n"/>
-      <c r="BA3" s="103" t="n"/>
-      <c r="BB3" s="103" t="n"/>
-      <c r="BC3" s="103" t="n"/>
-      <c r="BD3" s="104" t="n"/>
+      <c r="AX3" s="127" t="n"/>
+      <c r="AY3" s="127" t="n"/>
+      <c r="AZ3" s="127" t="n"/>
+      <c r="BA3" s="127" t="n"/>
+      <c r="BB3" s="127" t="n"/>
+      <c r="BC3" s="127" t="n"/>
+      <c r="BD3" s="128" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="102" t="n"/>
-      <c r="L4" s="64" t="inlineStr">
+      <c r="A4" s="118" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
+      <c r="I4" s="46" t="n"/>
+      <c r="J4" s="46" t="n"/>
+      <c r="K4" s="119" t="n"/>
+      <c r="L4" s="129" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="59" t="inlineStr">
+      <c r="M4" s="130" t="n"/>
+      <c r="N4" s="130" t="n"/>
+      <c r="O4" s="130" t="n"/>
+      <c r="P4" s="130" t="n"/>
+      <c r="Q4" s="130" t="n"/>
+      <c r="R4" s="130" t="n"/>
+      <c r="S4" s="130" t="n"/>
+      <c r="T4" s="130" t="n"/>
+      <c r="U4" s="130" t="n"/>
+      <c r="V4" s="130" t="n"/>
+      <c r="W4" s="130" t="n"/>
+      <c r="X4" s="130" t="n"/>
+      <c r="Y4" s="130" t="n"/>
+      <c r="Z4" s="130" t="n"/>
+      <c r="AA4" s="130" t="n"/>
+      <c r="AB4" s="130" t="n"/>
+      <c r="AC4" s="130" t="n"/>
+      <c r="AD4" s="130" t="n"/>
+      <c r="AE4" s="130" t="n"/>
+      <c r="AF4" s="130" t="n"/>
+      <c r="AG4" s="130" t="n"/>
+      <c r="AH4" s="130" t="n"/>
+      <c r="AI4" s="130" t="n"/>
+      <c r="AJ4" s="130" t="n"/>
+      <c r="AK4" s="130" t="n"/>
+      <c r="AL4" s="130" t="n"/>
+      <c r="AM4" s="130" t="n"/>
+      <c r="AN4" s="130" t="n"/>
+      <c r="AO4" s="130" t="n"/>
+      <c r="AP4" s="131" t="n"/>
+      <c r="AQ4" s="123" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="103" t="n"/>
-      <c r="AS4" s="103" t="n"/>
-      <c r="AT4" s="103" t="n"/>
-      <c r="AU4" s="103" t="n"/>
-      <c r="AV4" s="104" t="n"/>
-      <c r="AW4" s="62" t="inlineStr">
+      <c r="AR4" s="124" t="n"/>
+      <c r="AS4" s="124" t="n"/>
+      <c r="AT4" s="124" t="n"/>
+      <c r="AU4" s="124" t="n"/>
+      <c r="AV4" s="125" t="n"/>
+      <c r="AW4" s="126" t="inlineStr">
         <is>
           <t>HR + Department Manager</t>
         </is>
       </c>
-      <c r="AX4" s="103" t="n"/>
-      <c r="AY4" s="103" t="n"/>
-      <c r="AZ4" s="103" t="n"/>
-      <c r="BA4" s="103" t="n"/>
-      <c r="BB4" s="103" t="n"/>
-      <c r="BC4" s="103" t="n"/>
-      <c r="BD4" s="104" t="n"/>
+      <c r="AX4" s="127" t="n"/>
+      <c r="AY4" s="127" t="n"/>
+      <c r="AZ4" s="127" t="n"/>
+      <c r="BA4" s="127" t="n"/>
+      <c r="BB4" s="127" t="n"/>
+      <c r="BC4" s="127" t="n"/>
+      <c r="BD4" s="128" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="105" t="n"/>
-      <c r="B5" s="103" t="n"/>
-      <c r="C5" s="103" t="n"/>
-      <c r="D5" s="103" t="n"/>
-      <c r="E5" s="103" t="n"/>
-      <c r="F5" s="103" t="n"/>
-      <c r="G5" s="103" t="n"/>
-      <c r="H5" s="103" t="n"/>
-      <c r="I5" s="103" t="n"/>
-      <c r="J5" s="103" t="n"/>
-      <c r="K5" s="103" t="n"/>
-      <c r="L5" s="65" t="inlineStr">
+      <c r="A5" s="132" t="n"/>
+      <c r="B5" s="133" t="n"/>
+      <c r="C5" s="133" t="n"/>
+      <c r="D5" s="133" t="n"/>
+      <c r="E5" s="133" t="n"/>
+      <c r="F5" s="133" t="n"/>
+      <c r="G5" s="133" t="n"/>
+      <c r="H5" s="133" t="n"/>
+      <c r="I5" s="133" t="n"/>
+      <c r="J5" s="133" t="n"/>
+      <c r="K5" s="134" t="n"/>
+      <c r="L5" s="135" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="103" t="n"/>
-      <c r="N5" s="103" t="n"/>
-      <c r="O5" s="103" t="n"/>
-      <c r="P5" s="103" t="n"/>
-      <c r="Q5" s="103" t="n"/>
-      <c r="R5" s="103" t="n"/>
-      <c r="S5" s="103" t="n"/>
-      <c r="T5" s="103" t="n"/>
-      <c r="U5" s="103" t="n"/>
-      <c r="V5" s="103" t="n"/>
-      <c r="W5" s="103" t="n"/>
-      <c r="X5" s="103" t="n"/>
-      <c r="Y5" s="103" t="n"/>
-      <c r="Z5" s="103" t="n"/>
-      <c r="AA5" s="103" t="n"/>
-      <c r="AB5" s="103" t="n"/>
-      <c r="AC5" s="103" t="n"/>
-      <c r="AD5" s="103" t="n"/>
-      <c r="AE5" s="103" t="n"/>
-      <c r="AF5" s="103" t="n"/>
-      <c r="AG5" s="103" t="n"/>
-      <c r="AH5" s="103" t="n"/>
-      <c r="AI5" s="103" t="n"/>
-      <c r="AJ5" s="103" t="n"/>
-      <c r="AK5" s="103" t="n"/>
-      <c r="AL5" s="103" t="n"/>
-      <c r="AM5" s="103" t="n"/>
-      <c r="AN5" s="103" t="n"/>
-      <c r="AO5" s="103" t="n"/>
-      <c r="AP5" s="103" t="n"/>
-      <c r="AQ5" s="59" t="inlineStr">
+      <c r="M5" s="136" t="n"/>
+      <c r="N5" s="136" t="n"/>
+      <c r="O5" s="136" t="n"/>
+      <c r="P5" s="136" t="n"/>
+      <c r="Q5" s="136" t="n"/>
+      <c r="R5" s="136" t="n"/>
+      <c r="S5" s="136" t="n"/>
+      <c r="T5" s="136" t="n"/>
+      <c r="U5" s="136" t="n"/>
+      <c r="V5" s="136" t="n"/>
+      <c r="W5" s="136" t="n"/>
+      <c r="X5" s="136" t="n"/>
+      <c r="Y5" s="136" t="n"/>
+      <c r="Z5" s="136" t="n"/>
+      <c r="AA5" s="136" t="n"/>
+      <c r="AB5" s="136" t="n"/>
+      <c r="AC5" s="136" t="n"/>
+      <c r="AD5" s="136" t="n"/>
+      <c r="AE5" s="136" t="n"/>
+      <c r="AF5" s="136" t="n"/>
+      <c r="AG5" s="136" t="n"/>
+      <c r="AH5" s="136" t="n"/>
+      <c r="AI5" s="136" t="n"/>
+      <c r="AJ5" s="136" t="n"/>
+      <c r="AK5" s="136" t="n"/>
+      <c r="AL5" s="136" t="n"/>
+      <c r="AM5" s="136" t="n"/>
+      <c r="AN5" s="136" t="n"/>
+      <c r="AO5" s="136" t="n"/>
+      <c r="AP5" s="137" t="n"/>
+      <c r="AQ5" s="138" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="103" t="n"/>
-      <c r="AS5" s="103" t="n"/>
-      <c r="AT5" s="103" t="n"/>
-      <c r="AU5" s="103" t="n"/>
-      <c r="AV5" s="104" t="n"/>
-      <c r="AW5" s="62" t="inlineStr">
+      <c r="AR5" s="139" t="n"/>
+      <c r="AS5" s="139" t="n"/>
+      <c r="AT5" s="139" t="n"/>
+      <c r="AU5" s="139" t="n"/>
+      <c r="AV5" s="140" t="n"/>
+      <c r="AW5" s="141" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="103" t="n"/>
-      <c r="AY5" s="103" t="n"/>
-      <c r="AZ5" s="103" t="n"/>
-      <c r="BA5" s="103" t="n"/>
-      <c r="BB5" s="103" t="n"/>
-      <c r="BC5" s="103" t="n"/>
-      <c r="BD5" s="104" t="n"/>
+      <c r="AX5" s="142" t="n"/>
+      <c r="AY5" s="142" t="n"/>
+      <c r="AZ5" s="142" t="n"/>
+      <c r="BA5" s="142" t="n"/>
+      <c r="BB5" s="142" t="n"/>
+      <c r="BC5" s="142" t="n"/>
+      <c r="BD5" s="143" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="66" t="n"/>
-      <c r="B6" s="98" t="n"/>
-      <c r="C6" s="98" t="n"/>
-      <c r="D6" s="98" t="n"/>
-      <c r="E6" s="98" t="n"/>
-      <c r="F6" s="98" t="n"/>
-      <c r="G6" s="98" t="n"/>
-      <c r="H6" s="98" t="n"/>
-      <c r="I6" s="98" t="n"/>
-      <c r="J6" s="98" t="n"/>
-      <c r="K6" s="98" t="n"/>
-      <c r="L6" s="98" t="n"/>
-      <c r="M6" s="98" t="n"/>
-      <c r="N6" s="98" t="n"/>
-      <c r="O6" s="98" t="n"/>
-      <c r="P6" s="98" t="n"/>
-      <c r="Q6" s="98" t="n"/>
-      <c r="R6" s="98" t="n"/>
-      <c r="S6" s="98" t="n"/>
-      <c r="T6" s="98" t="n"/>
-      <c r="U6" s="98" t="n"/>
-      <c r="V6" s="98" t="n"/>
-      <c r="W6" s="98" t="n"/>
-      <c r="X6" s="98" t="n"/>
-      <c r="Y6" s="98" t="n"/>
-      <c r="Z6" s="98" t="n"/>
-      <c r="AA6" s="98" t="n"/>
-      <c r="AB6" s="98" t="n"/>
-      <c r="AC6" s="98" t="n"/>
-      <c r="AD6" s="98" t="n"/>
-      <c r="AE6" s="98" t="n"/>
-      <c r="AF6" s="98" t="n"/>
-      <c r="AG6" s="98" t="n"/>
-      <c r="AH6" s="98" t="n"/>
-      <c r="AI6" s="98" t="n"/>
-      <c r="AJ6" s="98" t="n"/>
-      <c r="AK6" s="98" t="n"/>
-      <c r="AL6" s="98" t="n"/>
-      <c r="AM6" s="98" t="n"/>
-      <c r="AN6" s="98" t="n"/>
-      <c r="AO6" s="98" t="n"/>
-      <c r="AP6" s="98" t="n"/>
-      <c r="AQ6" s="98" t="n"/>
-      <c r="AR6" s="98" t="n"/>
-      <c r="AS6" s="98" t="n"/>
-      <c r="AT6" s="98" t="n"/>
-      <c r="AU6" s="98" t="n"/>
-      <c r="AV6" s="98" t="n"/>
-      <c r="AW6" s="98" t="n"/>
-      <c r="AX6" s="98" t="n"/>
-      <c r="AY6" s="98" t="n"/>
-      <c r="AZ6" s="98" t="n"/>
-      <c r="BA6" s="98" t="n"/>
-      <c r="BB6" s="98" t="n"/>
-      <c r="BC6" s="98" t="n"/>
-      <c r="BD6" s="98" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="144" t="n"/>
+      <c r="B6" s="144" t="n"/>
+      <c r="C6" s="144" t="n"/>
+      <c r="D6" s="144" t="n"/>
+      <c r="E6" s="144" t="n"/>
+      <c r="F6" s="144" t="n"/>
+      <c r="G6" s="144" t="n"/>
+      <c r="H6" s="144" t="n"/>
+      <c r="I6" s="144" t="n"/>
+      <c r="J6" s="144" t="n"/>
+      <c r="K6" s="144" t="n"/>
+      <c r="L6" s="144" t="n"/>
+      <c r="M6" s="144" t="n"/>
+      <c r="N6" s="144" t="n"/>
+      <c r="O6" s="144" t="n"/>
+      <c r="P6" s="144" t="n"/>
+      <c r="Q6" s="144" t="n"/>
+      <c r="R6" s="144" t="n"/>
+      <c r="S6" s="144" t="n"/>
+      <c r="T6" s="144" t="n"/>
+      <c r="U6" s="144" t="n"/>
+      <c r="V6" s="144" t="n"/>
+      <c r="W6" s="144" t="n"/>
+      <c r="X6" s="144" t="n"/>
+      <c r="Y6" s="144" t="n"/>
+      <c r="Z6" s="144" t="n"/>
+      <c r="AA6" s="144" t="n"/>
+      <c r="AB6" s="144" t="n"/>
+      <c r="AC6" s="144" t="n"/>
+      <c r="AD6" s="144" t="n"/>
+      <c r="AE6" s="144" t="n"/>
+      <c r="AF6" s="144" t="n"/>
+      <c r="AG6" s="144" t="n"/>
+      <c r="AH6" s="144" t="n"/>
+      <c r="AI6" s="144" t="n"/>
+      <c r="AJ6" s="144" t="n"/>
+      <c r="AK6" s="144" t="n"/>
+      <c r="AL6" s="144" t="n"/>
+      <c r="AM6" s="144" t="n"/>
+      <c r="AN6" s="144" t="n"/>
+      <c r="AO6" s="144" t="n"/>
+      <c r="AP6" s="144" t="n"/>
+      <c r="AQ6" s="144" t="n"/>
+      <c r="AR6" s="144" t="n"/>
+      <c r="AS6" s="144" t="n"/>
+      <c r="AT6" s="144" t="n"/>
+      <c r="AU6" s="144" t="n"/>
+      <c r="AV6" s="144" t="n"/>
+      <c r="AW6" s="144" t="n"/>
+      <c r="AX6" s="144" t="n"/>
+      <c r="AY6" s="144" t="n"/>
+      <c r="AZ6" s="144" t="n"/>
+      <c r="BA6" s="144" t="n"/>
+      <c r="BB6" s="144" t="n"/>
+      <c r="BC6" s="144" t="n"/>
+      <c r="BD6" s="144" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="67" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="145" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="100" t="n"/>
-      <c r="C7" s="100" t="n"/>
-      <c r="D7" s="100" t="n"/>
-      <c r="E7" s="100" t="n"/>
-      <c r="F7" s="100" t="n"/>
-      <c r="G7" s="100" t="n"/>
-      <c r="H7" s="100" t="n"/>
-      <c r="I7" s="100" t="n"/>
-      <c r="J7" s="100" t="n"/>
-      <c r="K7" s="100" t="n"/>
-      <c r="L7" s="100" t="n"/>
-      <c r="M7" s="100" t="n"/>
-      <c r="N7" s="100" t="n"/>
-      <c r="O7" s="100" t="n"/>
-      <c r="P7" s="100" t="n"/>
-      <c r="Q7" s="100" t="n"/>
-      <c r="R7" s="100" t="n"/>
-      <c r="S7" s="100" t="n"/>
-      <c r="T7" s="100" t="n"/>
-      <c r="U7" s="100" t="n"/>
-      <c r="V7" s="100" t="n"/>
-      <c r="W7" s="100" t="n"/>
-      <c r="X7" s="100" t="n"/>
-      <c r="Y7" s="100" t="n"/>
-      <c r="Z7" s="100" t="n"/>
-      <c r="AA7" s="100" t="n"/>
-      <c r="AB7" s="100" t="n"/>
-      <c r="AC7" s="100" t="n"/>
-      <c r="AD7" s="100" t="n"/>
-      <c r="AE7" s="100" t="n"/>
-      <c r="AF7" s="100" t="n"/>
-      <c r="AG7" s="100" t="n"/>
-      <c r="AH7" s="100" t="n"/>
-      <c r="AI7" s="100" t="n"/>
-      <c r="AJ7" s="100" t="n"/>
-      <c r="AK7" s="100" t="n"/>
-      <c r="AL7" s="100" t="n"/>
-      <c r="AM7" s="100" t="n"/>
-      <c r="AN7" s="100" t="n"/>
-      <c r="AO7" s="100" t="n"/>
-      <c r="AP7" s="100" t="n"/>
-      <c r="AQ7" s="100" t="n"/>
-      <c r="AR7" s="100" t="n"/>
-      <c r="AS7" s="100" t="n"/>
-      <c r="AT7" s="100" t="n"/>
-      <c r="AU7" s="100" t="n"/>
-      <c r="AV7" s="100" t="n"/>
-      <c r="AW7" s="100" t="n"/>
-      <c r="AX7" s="100" t="n"/>
-      <c r="AY7" s="100" t="n"/>
-      <c r="AZ7" s="100" t="n"/>
-      <c r="BA7" s="100" t="n"/>
-      <c r="BB7" s="100" t="n"/>
-      <c r="BC7" s="100" t="n"/>
-      <c r="BD7" s="101" t="n"/>
+      <c r="B7" s="146" t="n"/>
+      <c r="C7" s="146" t="n"/>
+      <c r="D7" s="146" t="n"/>
+      <c r="E7" s="146" t="n"/>
+      <c r="F7" s="146" t="n"/>
+      <c r="G7" s="146" t="n"/>
+      <c r="H7" s="146" t="n"/>
+      <c r="I7" s="146" t="n"/>
+      <c r="J7" s="146" t="n"/>
+      <c r="K7" s="146" t="n"/>
+      <c r="L7" s="146" t="n"/>
+      <c r="M7" s="146" t="n"/>
+      <c r="N7" s="146" t="n"/>
+      <c r="O7" s="146" t="n"/>
+      <c r="P7" s="146" t="n"/>
+      <c r="Q7" s="146" t="n"/>
+      <c r="R7" s="146" t="n"/>
+      <c r="S7" s="146" t="n"/>
+      <c r="T7" s="146" t="n"/>
+      <c r="U7" s="146" t="n"/>
+      <c r="V7" s="146" t="n"/>
+      <c r="W7" s="146" t="n"/>
+      <c r="X7" s="146" t="n"/>
+      <c r="Y7" s="146" t="n"/>
+      <c r="Z7" s="146" t="n"/>
+      <c r="AA7" s="146" t="n"/>
+      <c r="AB7" s="146" t="n"/>
+      <c r="AC7" s="146" t="n"/>
+      <c r="AD7" s="146" t="n"/>
+      <c r="AE7" s="146" t="n"/>
+      <c r="AF7" s="146" t="n"/>
+      <c r="AG7" s="146" t="n"/>
+      <c r="AH7" s="146" t="n"/>
+      <c r="AI7" s="146" t="n"/>
+      <c r="AJ7" s="146" t="n"/>
+      <c r="AK7" s="146" t="n"/>
+      <c r="AL7" s="146" t="n"/>
+      <c r="AM7" s="146" t="n"/>
+      <c r="AN7" s="146" t="n"/>
+      <c r="AO7" s="146" t="n"/>
+      <c r="AP7" s="146" t="n"/>
+      <c r="AQ7" s="146" t="n"/>
+      <c r="AR7" s="146" t="n"/>
+      <c r="AS7" s="146" t="n"/>
+      <c r="AT7" s="146" t="n"/>
+      <c r="AU7" s="146" t="n"/>
+      <c r="AV7" s="146" t="n"/>
+      <c r="AW7" s="146" t="n"/>
+      <c r="AX7" s="146" t="n"/>
+      <c r="AY7" s="146" t="n"/>
+      <c r="AZ7" s="146" t="n"/>
+      <c r="BA7" s="146" t="n"/>
+      <c r="BB7" s="146" t="n"/>
+      <c r="BC7" s="146" t="n"/>
+      <c r="BD7" s="147" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="68" t="inlineStr">
+      <c r="A8" s="148" t="inlineStr">
         <is>
           <t>Training Plan ID</t>
         </is>
       </c>
-      <c r="B8" s="92" t="n"/>
-      <c r="C8" s="92" t="n"/>
-      <c r="D8" s="92" t="n"/>
-      <c r="E8" s="92" t="n"/>
-      <c r="F8" s="92" t="n"/>
-      <c r="G8" s="92" t="n"/>
-      <c r="H8" s="92" t="n"/>
-      <c r="I8" s="92" t="n"/>
-      <c r="J8" s="93" t="n"/>
-      <c r="K8" s="71" t="n"/>
-      <c r="L8" s="94" t="n"/>
-      <c r="M8" s="94" t="n"/>
-      <c r="N8" s="94" t="n"/>
-      <c r="O8" s="94" t="n"/>
-      <c r="P8" s="94" t="n"/>
-      <c r="Q8" s="94" t="n"/>
-      <c r="R8" s="94" t="n"/>
-      <c r="S8" s="94" t="n"/>
-      <c r="T8" s="94" t="n"/>
-      <c r="U8" s="94" t="n"/>
-      <c r="V8" s="94" t="n"/>
-      <c r="W8" s="94" t="n"/>
-      <c r="X8" s="94" t="n"/>
-      <c r="Y8" s="94" t="n"/>
-      <c r="Z8" s="94" t="n"/>
-      <c r="AA8" s="94" t="n"/>
-      <c r="AB8" s="95" t="n"/>
-      <c r="AC8" s="68" t="inlineStr">
+      <c r="B8" s="149" t="n"/>
+      <c r="C8" s="149" t="n"/>
+      <c r="D8" s="149" t="n"/>
+      <c r="E8" s="149" t="n"/>
+      <c r="F8" s="149" t="n"/>
+      <c r="G8" s="149" t="n"/>
+      <c r="H8" s="149" t="n"/>
+      <c r="I8" s="149" t="n"/>
+      <c r="J8" s="149" t="n"/>
+      <c r="K8" s="150" t="n"/>
+      <c r="L8" s="151" t="n"/>
+      <c r="M8" s="151" t="n"/>
+      <c r="N8" s="151" t="n"/>
+      <c r="O8" s="151" t="n"/>
+      <c r="P8" s="151" t="n"/>
+      <c r="Q8" s="151" t="n"/>
+      <c r="R8" s="151" t="n"/>
+      <c r="S8" s="151" t="n"/>
+      <c r="T8" s="151" t="n"/>
+      <c r="U8" s="151" t="n"/>
+      <c r="V8" s="151" t="n"/>
+      <c r="W8" s="151" t="n"/>
+      <c r="X8" s="151" t="n"/>
+      <c r="Y8" s="151" t="n"/>
+      <c r="Z8" s="151" t="n"/>
+      <c r="AA8" s="151" t="n"/>
+      <c r="AB8" s="151" t="n"/>
+      <c r="AC8" s="152" t="inlineStr">
         <is>
           <t>Plan Status</t>
         </is>
       </c>
-      <c r="AD8" s="92" t="n"/>
-      <c r="AE8" s="92" t="n"/>
-      <c r="AF8" s="92" t="n"/>
-      <c r="AG8" s="92" t="n"/>
-      <c r="AH8" s="92" t="n"/>
-      <c r="AI8" s="92" t="n"/>
-      <c r="AJ8" s="92" t="n"/>
-      <c r="AK8" s="92" t="n"/>
-      <c r="AL8" s="93" t="n"/>
-      <c r="AM8" s="71" t="n"/>
-      <c r="AN8" s="94" t="n"/>
-      <c r="AO8" s="94" t="n"/>
-      <c r="AP8" s="94" t="n"/>
-      <c r="AQ8" s="94" t="n"/>
-      <c r="AR8" s="94" t="n"/>
-      <c r="AS8" s="94" t="n"/>
-      <c r="AT8" s="94" t="n"/>
-      <c r="AU8" s="94" t="n"/>
-      <c r="AV8" s="94" t="n"/>
-      <c r="AW8" s="94" t="n"/>
-      <c r="AX8" s="94" t="n"/>
-      <c r="AY8" s="94" t="n"/>
-      <c r="AZ8" s="94" t="n"/>
-      <c r="BA8" s="94" t="n"/>
-      <c r="BB8" s="94" t="n"/>
-      <c r="BC8" s="94" t="n"/>
-      <c r="BD8" s="95" t="n"/>
+      <c r="AD8" s="149" t="n"/>
+      <c r="AE8" s="149" t="n"/>
+      <c r="AF8" s="149" t="n"/>
+      <c r="AG8" s="149" t="n"/>
+      <c r="AH8" s="149" t="n"/>
+      <c r="AI8" s="149" t="n"/>
+      <c r="AJ8" s="149" t="n"/>
+      <c r="AK8" s="149" t="n"/>
+      <c r="AL8" s="149" t="n"/>
+      <c r="AM8" s="150" t="n"/>
+      <c r="AN8" s="151" t="n"/>
+      <c r="AO8" s="151" t="n"/>
+      <c r="AP8" s="151" t="n"/>
+      <c r="AQ8" s="151" t="n"/>
+      <c r="AR8" s="151" t="n"/>
+      <c r="AS8" s="151" t="n"/>
+      <c r="AT8" s="151" t="n"/>
+      <c r="AU8" s="151" t="n"/>
+      <c r="AV8" s="151" t="n"/>
+      <c r="AW8" s="151" t="n"/>
+      <c r="AX8" s="151" t="n"/>
+      <c r="AY8" s="151" t="n"/>
+      <c r="AZ8" s="151" t="n"/>
+      <c r="BA8" s="151" t="n"/>
+      <c r="BB8" s="151" t="n"/>
+      <c r="BC8" s="151" t="n"/>
+      <c r="BD8" s="153" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="68" t="inlineStr">
+      <c r="A9" s="154" t="inlineStr">
         <is>
           <t>Department / Role</t>
         </is>
       </c>
-      <c r="B9" s="92" t="n"/>
-      <c r="C9" s="92" t="n"/>
-      <c r="D9" s="92" t="n"/>
-      <c r="E9" s="92" t="n"/>
-      <c r="F9" s="92" t="n"/>
-      <c r="G9" s="92" t="n"/>
-      <c r="H9" s="92" t="n"/>
-      <c r="I9" s="92" t="n"/>
-      <c r="J9" s="93" t="n"/>
-      <c r="K9" s="71" t="n"/>
-      <c r="L9" s="94" t="n"/>
-      <c r="M9" s="94" t="n"/>
-      <c r="N9" s="94" t="n"/>
-      <c r="O9" s="94" t="n"/>
-      <c r="P9" s="94" t="n"/>
-      <c r="Q9" s="94" t="n"/>
-      <c r="R9" s="94" t="n"/>
-      <c r="S9" s="94" t="n"/>
-      <c r="T9" s="94" t="n"/>
-      <c r="U9" s="94" t="n"/>
-      <c r="V9" s="94" t="n"/>
-      <c r="W9" s="94" t="n"/>
-      <c r="X9" s="94" t="n"/>
-      <c r="Y9" s="94" t="n"/>
-      <c r="Z9" s="94" t="n"/>
-      <c r="AA9" s="94" t="n"/>
-      <c r="AB9" s="95" t="n"/>
-      <c r="AC9" s="68" t="inlineStr">
+      <c r="B9" s="54" t="n"/>
+      <c r="C9" s="54" t="n"/>
+      <c r="D9" s="54" t="n"/>
+      <c r="E9" s="54" t="n"/>
+      <c r="F9" s="54" t="n"/>
+      <c r="G9" s="54" t="n"/>
+      <c r="H9" s="54" t="n"/>
+      <c r="I9" s="54" t="n"/>
+      <c r="J9" s="54" t="n"/>
+      <c r="K9" s="155" t="n"/>
+      <c r="L9" s="74" t="n"/>
+      <c r="M9" s="74" t="n"/>
+      <c r="N9" s="74" t="n"/>
+      <c r="O9" s="74" t="n"/>
+      <c r="P9" s="74" t="n"/>
+      <c r="Q9" s="74" t="n"/>
+      <c r="R9" s="74" t="n"/>
+      <c r="S9" s="74" t="n"/>
+      <c r="T9" s="74" t="n"/>
+      <c r="U9" s="74" t="n"/>
+      <c r="V9" s="74" t="n"/>
+      <c r="W9" s="74" t="n"/>
+      <c r="X9" s="74" t="n"/>
+      <c r="Y9" s="74" t="n"/>
+      <c r="Z9" s="74" t="n"/>
+      <c r="AA9" s="74" t="n"/>
+      <c r="AB9" s="74" t="n"/>
+      <c r="AC9" s="156" t="inlineStr">
         <is>
           <t>Owner / Manager</t>
         </is>
       </c>
-      <c r="AD9" s="92" t="n"/>
-      <c r="AE9" s="92" t="n"/>
-      <c r="AF9" s="92" t="n"/>
-      <c r="AG9" s="92" t="n"/>
-      <c r="AH9" s="92" t="n"/>
-      <c r="AI9" s="92" t="n"/>
-      <c r="AJ9" s="92" t="n"/>
-      <c r="AK9" s="92" t="n"/>
-      <c r="AL9" s="93" t="n"/>
-      <c r="AM9" s="71" t="n"/>
-      <c r="AN9" s="94" t="n"/>
-      <c r="AO9" s="94" t="n"/>
-      <c r="AP9" s="94" t="n"/>
-      <c r="AQ9" s="94" t="n"/>
-      <c r="AR9" s="94" t="n"/>
-      <c r="AS9" s="94" t="n"/>
-      <c r="AT9" s="94" t="n"/>
-      <c r="AU9" s="94" t="n"/>
-      <c r="AV9" s="94" t="n"/>
-      <c r="AW9" s="94" t="n"/>
-      <c r="AX9" s="94" t="n"/>
-      <c r="AY9" s="94" t="n"/>
-      <c r="AZ9" s="94" t="n"/>
-      <c r="BA9" s="94" t="n"/>
-      <c r="BB9" s="94" t="n"/>
-      <c r="BC9" s="94" t="n"/>
-      <c r="BD9" s="95" t="n"/>
+      <c r="AD9" s="54" t="n"/>
+      <c r="AE9" s="54" t="n"/>
+      <c r="AF9" s="54" t="n"/>
+      <c r="AG9" s="54" t="n"/>
+      <c r="AH9" s="54" t="n"/>
+      <c r="AI9" s="54" t="n"/>
+      <c r="AJ9" s="54" t="n"/>
+      <c r="AK9" s="54" t="n"/>
+      <c r="AL9" s="54" t="n"/>
+      <c r="AM9" s="155" t="n"/>
+      <c r="AN9" s="74" t="n"/>
+      <c r="AO9" s="74" t="n"/>
+      <c r="AP9" s="74" t="n"/>
+      <c r="AQ9" s="74" t="n"/>
+      <c r="AR9" s="74" t="n"/>
+      <c r="AS9" s="74" t="n"/>
+      <c r="AT9" s="74" t="n"/>
+      <c r="AU9" s="74" t="n"/>
+      <c r="AV9" s="74" t="n"/>
+      <c r="AW9" s="74" t="n"/>
+      <c r="AX9" s="74" t="n"/>
+      <c r="AY9" s="74" t="n"/>
+      <c r="AZ9" s="74" t="n"/>
+      <c r="BA9" s="74" t="n"/>
+      <c r="BB9" s="74" t="n"/>
+      <c r="BC9" s="74" t="n"/>
+      <c r="BD9" s="157" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="68" t="inlineStr">
+      <c r="A10" s="154" t="inlineStr">
         <is>
           <t>Target Population</t>
         </is>
       </c>
-      <c r="B10" s="92" t="n"/>
-      <c r="C10" s="92" t="n"/>
-      <c r="D10" s="92" t="n"/>
-      <c r="E10" s="92" t="n"/>
-      <c r="F10" s="92" t="n"/>
-      <c r="G10" s="92" t="n"/>
-      <c r="H10" s="92" t="n"/>
-      <c r="I10" s="92" t="n"/>
-      <c r="J10" s="93" t="n"/>
-      <c r="K10" s="71" t="n"/>
-      <c r="L10" s="94" t="n"/>
-      <c r="M10" s="94" t="n"/>
-      <c r="N10" s="94" t="n"/>
-      <c r="O10" s="94" t="n"/>
-      <c r="P10" s="94" t="n"/>
-      <c r="Q10" s="94" t="n"/>
-      <c r="R10" s="94" t="n"/>
-      <c r="S10" s="94" t="n"/>
-      <c r="T10" s="94" t="n"/>
-      <c r="U10" s="94" t="n"/>
-      <c r="V10" s="94" t="n"/>
-      <c r="W10" s="94" t="n"/>
-      <c r="X10" s="94" t="n"/>
-      <c r="Y10" s="94" t="n"/>
-      <c r="Z10" s="94" t="n"/>
-      <c r="AA10" s="94" t="n"/>
-      <c r="AB10" s="95" t="n"/>
-      <c r="AC10" s="68" t="inlineStr">
+      <c r="B10" s="54" t="n"/>
+      <c r="C10" s="54" t="n"/>
+      <c r="D10" s="54" t="n"/>
+      <c r="E10" s="54" t="n"/>
+      <c r="F10" s="54" t="n"/>
+      <c r="G10" s="54" t="n"/>
+      <c r="H10" s="54" t="n"/>
+      <c r="I10" s="54" t="n"/>
+      <c r="J10" s="54" t="n"/>
+      <c r="K10" s="155" t="n"/>
+      <c r="L10" s="74" t="n"/>
+      <c r="M10" s="74" t="n"/>
+      <c r="N10" s="74" t="n"/>
+      <c r="O10" s="74" t="n"/>
+      <c r="P10" s="74" t="n"/>
+      <c r="Q10" s="74" t="n"/>
+      <c r="R10" s="74" t="n"/>
+      <c r="S10" s="74" t="n"/>
+      <c r="T10" s="74" t="n"/>
+      <c r="U10" s="74" t="n"/>
+      <c r="V10" s="74" t="n"/>
+      <c r="W10" s="74" t="n"/>
+      <c r="X10" s="74" t="n"/>
+      <c r="Y10" s="74" t="n"/>
+      <c r="Z10" s="74" t="n"/>
+      <c r="AA10" s="74" t="n"/>
+      <c r="AB10" s="74" t="n"/>
+      <c r="AC10" s="156" t="inlineStr">
         <is>
           <t>Cycle</t>
         </is>
       </c>
-      <c r="AD10" s="92" t="n"/>
-      <c r="AE10" s="92" t="n"/>
-      <c r="AF10" s="92" t="n"/>
-      <c r="AG10" s="92" t="n"/>
-      <c r="AH10" s="92" t="n"/>
-      <c r="AI10" s="92" t="n"/>
-      <c r="AJ10" s="92" t="n"/>
-      <c r="AK10" s="92" t="n"/>
-      <c r="AL10" s="93" t="n"/>
-      <c r="AM10" s="71" t="n"/>
-      <c r="AN10" s="94" t="n"/>
-      <c r="AO10" s="94" t="n"/>
-      <c r="AP10" s="94" t="n"/>
-      <c r="AQ10" s="94" t="n"/>
-      <c r="AR10" s="94" t="n"/>
-      <c r="AS10" s="94" t="n"/>
-      <c r="AT10" s="94" t="n"/>
-      <c r="AU10" s="94" t="n"/>
-      <c r="AV10" s="94" t="n"/>
-      <c r="AW10" s="94" t="n"/>
-      <c r="AX10" s="94" t="n"/>
-      <c r="AY10" s="94" t="n"/>
-      <c r="AZ10" s="94" t="n"/>
-      <c r="BA10" s="94" t="n"/>
-      <c r="BB10" s="94" t="n"/>
-      <c r="BC10" s="94" t="n"/>
-      <c r="BD10" s="95" t="n"/>
+      <c r="AD10" s="54" t="n"/>
+      <c r="AE10" s="54" t="n"/>
+      <c r="AF10" s="54" t="n"/>
+      <c r="AG10" s="54" t="n"/>
+      <c r="AH10" s="54" t="n"/>
+      <c r="AI10" s="54" t="n"/>
+      <c r="AJ10" s="54" t="n"/>
+      <c r="AK10" s="54" t="n"/>
+      <c r="AL10" s="54" t="n"/>
+      <c r="AM10" s="155" t="n"/>
+      <c r="AN10" s="74" t="n"/>
+      <c r="AO10" s="74" t="n"/>
+      <c r="AP10" s="74" t="n"/>
+      <c r="AQ10" s="74" t="n"/>
+      <c r="AR10" s="74" t="n"/>
+      <c r="AS10" s="74" t="n"/>
+      <c r="AT10" s="74" t="n"/>
+      <c r="AU10" s="74" t="n"/>
+      <c r="AV10" s="74" t="n"/>
+      <c r="AW10" s="74" t="n"/>
+      <c r="AX10" s="74" t="n"/>
+      <c r="AY10" s="74" t="n"/>
+      <c r="AZ10" s="74" t="n"/>
+      <c r="BA10" s="74" t="n"/>
+      <c r="BB10" s="74" t="n"/>
+      <c r="BC10" s="74" t="n"/>
+      <c r="BD10" s="157" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="68" t="inlineStr">
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="158" t="inlineStr">
         <is>
           <t>Prepared Date</t>
         </is>
       </c>
-      <c r="B11" s="86" t="n"/>
-      <c r="C11" s="86" t="n"/>
-      <c r="D11" s="86" t="n"/>
-      <c r="E11" s="86" t="n"/>
-      <c r="F11" s="86" t="n"/>
-      <c r="G11" s="86" t="n"/>
-      <c r="H11" s="86" t="n"/>
-      <c r="I11" s="86" t="n"/>
-      <c r="J11" s="87" t="n"/>
-      <c r="K11" s="71" t="n"/>
-      <c r="L11" s="96" t="n"/>
-      <c r="M11" s="96" t="n"/>
-      <c r="N11" s="96" t="n"/>
-      <c r="O11" s="96" t="n"/>
-      <c r="P11" s="96" t="n"/>
-      <c r="Q11" s="96" t="n"/>
-      <c r="R11" s="96" t="n"/>
-      <c r="S11" s="96" t="n"/>
-      <c r="T11" s="96" t="n"/>
-      <c r="U11" s="96" t="n"/>
-      <c r="V11" s="96" t="n"/>
-      <c r="W11" s="96" t="n"/>
-      <c r="X11" s="96" t="n"/>
-      <c r="Y11" s="96" t="n"/>
-      <c r="Z11" s="96" t="n"/>
-      <c r="AA11" s="96" t="n"/>
-      <c r="AB11" s="97" t="n"/>
-      <c r="AC11" s="68" t="inlineStr">
+      <c r="B11" s="159" t="n"/>
+      <c r="C11" s="159" t="n"/>
+      <c r="D11" s="159" t="n"/>
+      <c r="E11" s="159" t="n"/>
+      <c r="F11" s="159" t="n"/>
+      <c r="G11" s="159" t="n"/>
+      <c r="H11" s="159" t="n"/>
+      <c r="I11" s="159" t="n"/>
+      <c r="J11" s="159" t="n"/>
+      <c r="K11" s="160" t="n"/>
+      <c r="L11" s="161" t="n"/>
+      <c r="M11" s="161" t="n"/>
+      <c r="N11" s="161" t="n"/>
+      <c r="O11" s="161" t="n"/>
+      <c r="P11" s="161" t="n"/>
+      <c r="Q11" s="161" t="n"/>
+      <c r="R11" s="161" t="n"/>
+      <c r="S11" s="161" t="n"/>
+      <c r="T11" s="161" t="n"/>
+      <c r="U11" s="161" t="n"/>
+      <c r="V11" s="161" t="n"/>
+      <c r="W11" s="161" t="n"/>
+      <c r="X11" s="161" t="n"/>
+      <c r="Y11" s="161" t="n"/>
+      <c r="Z11" s="161" t="n"/>
+      <c r="AA11" s="161" t="n"/>
+      <c r="AB11" s="161" t="n"/>
+      <c r="AC11" s="162" t="inlineStr">
         <is>
           <t>Evidence Folder Ref</t>
         </is>
       </c>
-      <c r="AD11" s="86" t="n"/>
-      <c r="AE11" s="86" t="n"/>
-      <c r="AF11" s="86" t="n"/>
-      <c r="AG11" s="86" t="n"/>
-      <c r="AH11" s="86" t="n"/>
-      <c r="AI11" s="86" t="n"/>
-      <c r="AJ11" s="86" t="n"/>
-      <c r="AK11" s="86" t="n"/>
-      <c r="AL11" s="87" t="n"/>
-      <c r="AM11" s="71" t="n"/>
-      <c r="AN11" s="96" t="n"/>
-      <c r="AO11" s="96" t="n"/>
-      <c r="AP11" s="96" t="n"/>
-      <c r="AQ11" s="96" t="n"/>
-      <c r="AR11" s="96" t="n"/>
-      <c r="AS11" s="96" t="n"/>
-      <c r="AT11" s="96" t="n"/>
-      <c r="AU11" s="96" t="n"/>
-      <c r="AV11" s="96" t="n"/>
-      <c r="AW11" s="96" t="n"/>
-      <c r="AX11" s="96" t="n"/>
-      <c r="AY11" s="96" t="n"/>
-      <c r="AZ11" s="96" t="n"/>
-      <c r="BA11" s="96" t="n"/>
-      <c r="BB11" s="96" t="n"/>
-      <c r="BC11" s="96" t="n"/>
-      <c r="BD11" s="97" t="n"/>
+      <c r="AD11" s="159" t="n"/>
+      <c r="AE11" s="159" t="n"/>
+      <c r="AF11" s="159" t="n"/>
+      <c r="AG11" s="159" t="n"/>
+      <c r="AH11" s="159" t="n"/>
+      <c r="AI11" s="159" t="n"/>
+      <c r="AJ11" s="159" t="n"/>
+      <c r="AK11" s="159" t="n"/>
+      <c r="AL11" s="159" t="n"/>
+      <c r="AM11" s="160" t="n"/>
+      <c r="AN11" s="161" t="n"/>
+      <c r="AO11" s="161" t="n"/>
+      <c r="AP11" s="161" t="n"/>
+      <c r="AQ11" s="161" t="n"/>
+      <c r="AR11" s="161" t="n"/>
+      <c r="AS11" s="161" t="n"/>
+      <c r="AT11" s="161" t="n"/>
+      <c r="AU11" s="161" t="n"/>
+      <c r="AV11" s="161" t="n"/>
+      <c r="AW11" s="161" t="n"/>
+      <c r="AX11" s="161" t="n"/>
+      <c r="AY11" s="161" t="n"/>
+      <c r="AZ11" s="161" t="n"/>
+      <c r="BA11" s="161" t="n"/>
+      <c r="BB11" s="161" t="n"/>
+      <c r="BC11" s="161" t="n"/>
+      <c r="BD11" s="163" t="n"/>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="67" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="145" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. COMPETENCE GAP / TARGET</t>
         </is>
       </c>
-      <c r="B12" s="92" t="n"/>
-      <c r="C12" s="92" t="n"/>
-      <c r="D12" s="92" t="n"/>
-      <c r="E12" s="92" t="n"/>
-      <c r="F12" s="92" t="n"/>
-      <c r="G12" s="92" t="n"/>
-      <c r="H12" s="92" t="n"/>
-      <c r="I12" s="92" t="n"/>
-      <c r="J12" s="92" t="n"/>
-      <c r="K12" s="92" t="n"/>
-      <c r="L12" s="92" t="n"/>
-      <c r="M12" s="92" t="n"/>
-      <c r="N12" s="92" t="n"/>
-      <c r="O12" s="92" t="n"/>
-      <c r="P12" s="92" t="n"/>
-      <c r="Q12" s="92" t="n"/>
-      <c r="R12" s="92" t="n"/>
-      <c r="S12" s="92" t="n"/>
-      <c r="T12" s="92" t="n"/>
-      <c r="U12" s="92" t="n"/>
-      <c r="V12" s="92" t="n"/>
-      <c r="W12" s="92" t="n"/>
-      <c r="X12" s="92" t="n"/>
-      <c r="Y12" s="92" t="n"/>
-      <c r="Z12" s="92" t="n"/>
-      <c r="AA12" s="92" t="n"/>
-      <c r="AB12" s="92" t="n"/>
-      <c r="AC12" s="92" t="n"/>
-      <c r="AD12" s="92" t="n"/>
-      <c r="AE12" s="92" t="n"/>
-      <c r="AF12" s="92" t="n"/>
-      <c r="AG12" s="92" t="n"/>
-      <c r="AH12" s="92" t="n"/>
-      <c r="AI12" s="92" t="n"/>
-      <c r="AJ12" s="92" t="n"/>
-      <c r="AK12" s="92" t="n"/>
-      <c r="AL12" s="92" t="n"/>
-      <c r="AM12" s="92" t="n"/>
-      <c r="AN12" s="92" t="n"/>
-      <c r="AO12" s="92" t="n"/>
-      <c r="AP12" s="92" t="n"/>
-      <c r="AQ12" s="92" t="n"/>
-      <c r="AR12" s="92" t="n"/>
-      <c r="AS12" s="92" t="n"/>
-      <c r="AT12" s="92" t="n"/>
-      <c r="AU12" s="92" t="n"/>
-      <c r="AV12" s="92" t="n"/>
-      <c r="AW12" s="92" t="n"/>
-      <c r="AX12" s="92" t="n"/>
-      <c r="AY12" s="92" t="n"/>
-      <c r="AZ12" s="92" t="n"/>
-      <c r="BA12" s="92" t="n"/>
-      <c r="BB12" s="92" t="n"/>
-      <c r="BC12" s="92" t="n"/>
-      <c r="BD12" s="93" t="n"/>
+      <c r="B12" s="146" t="n"/>
+      <c r="C12" s="146" t="n"/>
+      <c r="D12" s="146" t="n"/>
+      <c r="E12" s="146" t="n"/>
+      <c r="F12" s="146" t="n"/>
+      <c r="G12" s="146" t="n"/>
+      <c r="H12" s="146" t="n"/>
+      <c r="I12" s="146" t="n"/>
+      <c r="J12" s="146" t="n"/>
+      <c r="K12" s="146" t="n"/>
+      <c r="L12" s="146" t="n"/>
+      <c r="M12" s="146" t="n"/>
+      <c r="N12" s="146" t="n"/>
+      <c r="O12" s="146" t="n"/>
+      <c r="P12" s="146" t="n"/>
+      <c r="Q12" s="146" t="n"/>
+      <c r="R12" s="146" t="n"/>
+      <c r="S12" s="146" t="n"/>
+      <c r="T12" s="146" t="n"/>
+      <c r="U12" s="146" t="n"/>
+      <c r="V12" s="146" t="n"/>
+      <c r="W12" s="146" t="n"/>
+      <c r="X12" s="146" t="n"/>
+      <c r="Y12" s="146" t="n"/>
+      <c r="Z12" s="146" t="n"/>
+      <c r="AA12" s="146" t="n"/>
+      <c r="AB12" s="146" t="n"/>
+      <c r="AC12" s="146" t="n"/>
+      <c r="AD12" s="146" t="n"/>
+      <c r="AE12" s="146" t="n"/>
+      <c r="AF12" s="146" t="n"/>
+      <c r="AG12" s="146" t="n"/>
+      <c r="AH12" s="146" t="n"/>
+      <c r="AI12" s="146" t="n"/>
+      <c r="AJ12" s="146" t="n"/>
+      <c r="AK12" s="146" t="n"/>
+      <c r="AL12" s="146" t="n"/>
+      <c r="AM12" s="146" t="n"/>
+      <c r="AN12" s="146" t="n"/>
+      <c r="AO12" s="146" t="n"/>
+      <c r="AP12" s="146" t="n"/>
+      <c r="AQ12" s="146" t="n"/>
+      <c r="AR12" s="146" t="n"/>
+      <c r="AS12" s="146" t="n"/>
+      <c r="AT12" s="146" t="n"/>
+      <c r="AU12" s="146" t="n"/>
+      <c r="AV12" s="146" t="n"/>
+      <c r="AW12" s="146" t="n"/>
+      <c r="AX12" s="146" t="n"/>
+      <c r="AY12" s="146" t="n"/>
+      <c r="AZ12" s="146" t="n"/>
+      <c r="BA12" s="146" t="n"/>
+      <c r="BB12" s="146" t="n"/>
+      <c r="BC12" s="146" t="n"/>
+      <c r="BD12" s="147" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="68" t="inlineStr">
+      <c r="A13" s="148" t="inlineStr">
         <is>
           <t>Required Skill</t>
         </is>
       </c>
-      <c r="B13" s="92" t="n"/>
-      <c r="C13" s="92" t="n"/>
-      <c r="D13" s="92" t="n"/>
-      <c r="E13" s="92" t="n"/>
-      <c r="F13" s="92" t="n"/>
-      <c r="G13" s="92" t="n"/>
-      <c r="H13" s="92" t="n"/>
-      <c r="I13" s="92" t="n"/>
-      <c r="J13" s="93" t="n"/>
-      <c r="K13" s="71" t="n"/>
-      <c r="L13" s="94" t="n"/>
-      <c r="M13" s="94" t="n"/>
-      <c r="N13" s="94" t="n"/>
-      <c r="O13" s="94" t="n"/>
-      <c r="P13" s="94" t="n"/>
-      <c r="Q13" s="94" t="n"/>
-      <c r="R13" s="94" t="n"/>
-      <c r="S13" s="94" t="n"/>
-      <c r="T13" s="94" t="n"/>
-      <c r="U13" s="94" t="n"/>
-      <c r="V13" s="94" t="n"/>
-      <c r="W13" s="94" t="n"/>
-      <c r="X13" s="94" t="n"/>
-      <c r="Y13" s="94" t="n"/>
-      <c r="Z13" s="94" t="n"/>
-      <c r="AA13" s="94" t="n"/>
-      <c r="AB13" s="95" t="n"/>
-      <c r="AC13" s="68" t="inlineStr">
+      <c r="B13" s="149" t="n"/>
+      <c r="C13" s="149" t="n"/>
+      <c r="D13" s="149" t="n"/>
+      <c r="E13" s="149" t="n"/>
+      <c r="F13" s="149" t="n"/>
+      <c r="G13" s="149" t="n"/>
+      <c r="H13" s="149" t="n"/>
+      <c r="I13" s="149" t="n"/>
+      <c r="J13" s="149" t="n"/>
+      <c r="K13" s="150" t="n"/>
+      <c r="L13" s="151" t="n"/>
+      <c r="M13" s="151" t="n"/>
+      <c r="N13" s="151" t="n"/>
+      <c r="O13" s="151" t="n"/>
+      <c r="P13" s="151" t="n"/>
+      <c r="Q13" s="151" t="n"/>
+      <c r="R13" s="151" t="n"/>
+      <c r="S13" s="151" t="n"/>
+      <c r="T13" s="151" t="n"/>
+      <c r="U13" s="151" t="n"/>
+      <c r="V13" s="151" t="n"/>
+      <c r="W13" s="151" t="n"/>
+      <c r="X13" s="151" t="n"/>
+      <c r="Y13" s="151" t="n"/>
+      <c r="Z13" s="151" t="n"/>
+      <c r="AA13" s="151" t="n"/>
+      <c r="AB13" s="151" t="n"/>
+      <c r="AC13" s="152" t="inlineStr">
         <is>
           <t>Current Gap</t>
         </is>
       </c>
-      <c r="AD13" s="92" t="n"/>
-      <c r="AE13" s="92" t="n"/>
-      <c r="AF13" s="92" t="n"/>
-      <c r="AG13" s="92" t="n"/>
-      <c r="AH13" s="92" t="n"/>
-      <c r="AI13" s="92" t="n"/>
-      <c r="AJ13" s="92" t="n"/>
-      <c r="AK13" s="92" t="n"/>
-      <c r="AL13" s="93" t="n"/>
-      <c r="AM13" s="71" t="n"/>
-      <c r="AN13" s="94" t="n"/>
-      <c r="AO13" s="94" t="n"/>
-      <c r="AP13" s="94" t="n"/>
-      <c r="AQ13" s="94" t="n"/>
-      <c r="AR13" s="94" t="n"/>
-      <c r="AS13" s="94" t="n"/>
-      <c r="AT13" s="94" t="n"/>
-      <c r="AU13" s="94" t="n"/>
-      <c r="AV13" s="94" t="n"/>
-      <c r="AW13" s="94" t="n"/>
-      <c r="AX13" s="94" t="n"/>
-      <c r="AY13" s="94" t="n"/>
-      <c r="AZ13" s="94" t="n"/>
-      <c r="BA13" s="94" t="n"/>
-      <c r="BB13" s="94" t="n"/>
-      <c r="BC13" s="94" t="n"/>
-      <c r="BD13" s="95" t="n"/>
+      <c r="AD13" s="149" t="n"/>
+      <c r="AE13" s="149" t="n"/>
+      <c r="AF13" s="149" t="n"/>
+      <c r="AG13" s="149" t="n"/>
+      <c r="AH13" s="149" t="n"/>
+      <c r="AI13" s="149" t="n"/>
+      <c r="AJ13" s="149" t="n"/>
+      <c r="AK13" s="149" t="n"/>
+      <c r="AL13" s="149" t="n"/>
+      <c r="AM13" s="150" t="n"/>
+      <c r="AN13" s="151" t="n"/>
+      <c r="AO13" s="151" t="n"/>
+      <c r="AP13" s="151" t="n"/>
+      <c r="AQ13" s="151" t="n"/>
+      <c r="AR13" s="151" t="n"/>
+      <c r="AS13" s="151" t="n"/>
+      <c r="AT13" s="151" t="n"/>
+      <c r="AU13" s="151" t="n"/>
+      <c r="AV13" s="151" t="n"/>
+      <c r="AW13" s="151" t="n"/>
+      <c r="AX13" s="151" t="n"/>
+      <c r="AY13" s="151" t="n"/>
+      <c r="AZ13" s="151" t="n"/>
+      <c r="BA13" s="151" t="n"/>
+      <c r="BB13" s="151" t="n"/>
+      <c r="BC13" s="151" t="n"/>
+      <c r="BD13" s="153" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="68" t="inlineStr">
+      <c r="A14" s="154" t="inlineStr">
         <is>
           <t>Target Level</t>
         </is>
       </c>
-      <c r="B14" s="92" t="n"/>
-      <c r="C14" s="92" t="n"/>
-      <c r="D14" s="92" t="n"/>
-      <c r="E14" s="92" t="n"/>
-      <c r="F14" s="92" t="n"/>
-      <c r="G14" s="92" t="n"/>
-      <c r="H14" s="92" t="n"/>
-      <c r="I14" s="92" t="n"/>
-      <c r="J14" s="93" t="n"/>
-      <c r="K14" s="71" t="n"/>
-      <c r="L14" s="94" t="n"/>
-      <c r="M14" s="94" t="n"/>
-      <c r="N14" s="94" t="n"/>
-      <c r="O14" s="94" t="n"/>
-      <c r="P14" s="94" t="n"/>
-      <c r="Q14" s="94" t="n"/>
-      <c r="R14" s="94" t="n"/>
-      <c r="S14" s="94" t="n"/>
-      <c r="T14" s="94" t="n"/>
-      <c r="U14" s="94" t="n"/>
-      <c r="V14" s="94" t="n"/>
-      <c r="W14" s="94" t="n"/>
-      <c r="X14" s="94" t="n"/>
-      <c r="Y14" s="94" t="n"/>
-      <c r="Z14" s="94" t="n"/>
-      <c r="AA14" s="94" t="n"/>
-      <c r="AB14" s="95" t="n"/>
-      <c r="AC14" s="68" t="inlineStr">
+      <c r="B14" s="54" t="n"/>
+      <c r="C14" s="54" t="n"/>
+      <c r="D14" s="54" t="n"/>
+      <c r="E14" s="54" t="n"/>
+      <c r="F14" s="54" t="n"/>
+      <c r="G14" s="54" t="n"/>
+      <c r="H14" s="54" t="n"/>
+      <c r="I14" s="54" t="n"/>
+      <c r="J14" s="54" t="n"/>
+      <c r="K14" s="155" t="n"/>
+      <c r="L14" s="74" t="n"/>
+      <c r="M14" s="74" t="n"/>
+      <c r="N14" s="74" t="n"/>
+      <c r="O14" s="74" t="n"/>
+      <c r="P14" s="74" t="n"/>
+      <c r="Q14" s="74" t="n"/>
+      <c r="R14" s="74" t="n"/>
+      <c r="S14" s="74" t="n"/>
+      <c r="T14" s="74" t="n"/>
+      <c r="U14" s="74" t="n"/>
+      <c r="V14" s="74" t="n"/>
+      <c r="W14" s="74" t="n"/>
+      <c r="X14" s="74" t="n"/>
+      <c r="Y14" s="74" t="n"/>
+      <c r="Z14" s="74" t="n"/>
+      <c r="AA14" s="74" t="n"/>
+      <c r="AB14" s="74" t="n"/>
+      <c r="AC14" s="156" t="inlineStr">
         <is>
           <t>Training Method</t>
         </is>
       </c>
-      <c r="AD14" s="92" t="n"/>
-      <c r="AE14" s="92" t="n"/>
-      <c r="AF14" s="92" t="n"/>
-      <c r="AG14" s="92" t="n"/>
-      <c r="AH14" s="92" t="n"/>
-      <c r="AI14" s="92" t="n"/>
-      <c r="AJ14" s="92" t="n"/>
-      <c r="AK14" s="92" t="n"/>
-      <c r="AL14" s="93" t="n"/>
-      <c r="AM14" s="71" t="n"/>
-      <c r="AN14" s="94" t="n"/>
-      <c r="AO14" s="94" t="n"/>
-      <c r="AP14" s="94" t="n"/>
-      <c r="AQ14" s="94" t="n"/>
-      <c r="AR14" s="94" t="n"/>
-      <c r="AS14" s="94" t="n"/>
-      <c r="AT14" s="94" t="n"/>
-      <c r="AU14" s="94" t="n"/>
-      <c r="AV14" s="94" t="n"/>
-      <c r="AW14" s="94" t="n"/>
-      <c r="AX14" s="94" t="n"/>
-      <c r="AY14" s="94" t="n"/>
-      <c r="AZ14" s="94" t="n"/>
-      <c r="BA14" s="94" t="n"/>
-      <c r="BB14" s="94" t="n"/>
-      <c r="BC14" s="94" t="n"/>
-      <c r="BD14" s="95" t="n"/>
+      <c r="AD14" s="54" t="n"/>
+      <c r="AE14" s="54" t="n"/>
+      <c r="AF14" s="54" t="n"/>
+      <c r="AG14" s="54" t="n"/>
+      <c r="AH14" s="54" t="n"/>
+      <c r="AI14" s="54" t="n"/>
+      <c r="AJ14" s="54" t="n"/>
+      <c r="AK14" s="54" t="n"/>
+      <c r="AL14" s="54" t="n"/>
+      <c r="AM14" s="155" t="n"/>
+      <c r="AN14" s="74" t="n"/>
+      <c r="AO14" s="74" t="n"/>
+      <c r="AP14" s="74" t="n"/>
+      <c r="AQ14" s="74" t="n"/>
+      <c r="AR14" s="74" t="n"/>
+      <c r="AS14" s="74" t="n"/>
+      <c r="AT14" s="74" t="n"/>
+      <c r="AU14" s="74" t="n"/>
+      <c r="AV14" s="74" t="n"/>
+      <c r="AW14" s="74" t="n"/>
+      <c r="AX14" s="74" t="n"/>
+      <c r="AY14" s="74" t="n"/>
+      <c r="AZ14" s="74" t="n"/>
+      <c r="BA14" s="74" t="n"/>
+      <c r="BB14" s="74" t="n"/>
+      <c r="BC14" s="74" t="n"/>
+      <c r="BD14" s="157" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="68" t="inlineStr">
+      <c r="A15" s="158" t="inlineStr">
         <is>
           <t>Expected Evidence</t>
         </is>
       </c>
-      <c r="B15" s="92" t="n"/>
-      <c r="C15" s="92" t="n"/>
-      <c r="D15" s="92" t="n"/>
-      <c r="E15" s="92" t="n"/>
-      <c r="F15" s="92" t="n"/>
-      <c r="G15" s="92" t="n"/>
-      <c r="H15" s="92" t="n"/>
-      <c r="I15" s="92" t="n"/>
-      <c r="J15" s="93" t="n"/>
-      <c r="K15" s="71" t="n"/>
-      <c r="L15" s="94" t="n"/>
-      <c r="M15" s="94" t="n"/>
-      <c r="N15" s="94" t="n"/>
-      <c r="O15" s="94" t="n"/>
-      <c r="P15" s="94" t="n"/>
-      <c r="Q15" s="94" t="n"/>
-      <c r="R15" s="94" t="n"/>
-      <c r="S15" s="94" t="n"/>
-      <c r="T15" s="94" t="n"/>
-      <c r="U15" s="94" t="n"/>
-      <c r="V15" s="94" t="n"/>
-      <c r="W15" s="94" t="n"/>
-      <c r="X15" s="94" t="n"/>
-      <c r="Y15" s="94" t="n"/>
-      <c r="Z15" s="94" t="n"/>
-      <c r="AA15" s="94" t="n"/>
-      <c r="AB15" s="95" t="n"/>
-      <c r="AC15" s="68" t="inlineStr">
+      <c r="B15" s="159" t="n"/>
+      <c r="C15" s="159" t="n"/>
+      <c r="D15" s="159" t="n"/>
+      <c r="E15" s="159" t="n"/>
+      <c r="F15" s="159" t="n"/>
+      <c r="G15" s="159" t="n"/>
+      <c r="H15" s="159" t="n"/>
+      <c r="I15" s="159" t="n"/>
+      <c r="J15" s="159" t="n"/>
+      <c r="K15" s="160" t="n"/>
+      <c r="L15" s="161" t="n"/>
+      <c r="M15" s="161" t="n"/>
+      <c r="N15" s="161" t="n"/>
+      <c r="O15" s="161" t="n"/>
+      <c r="P15" s="161" t="n"/>
+      <c r="Q15" s="161" t="n"/>
+      <c r="R15" s="161" t="n"/>
+      <c r="S15" s="161" t="n"/>
+      <c r="T15" s="161" t="n"/>
+      <c r="U15" s="161" t="n"/>
+      <c r="V15" s="161" t="n"/>
+      <c r="W15" s="161" t="n"/>
+      <c r="X15" s="161" t="n"/>
+      <c r="Y15" s="161" t="n"/>
+      <c r="Z15" s="161" t="n"/>
+      <c r="AA15" s="161" t="n"/>
+      <c r="AB15" s="161" t="n"/>
+      <c r="AC15" s="162" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="AD15" s="92" t="n"/>
-      <c r="AE15" s="92" t="n"/>
-      <c r="AF15" s="92" t="n"/>
-      <c r="AG15" s="92" t="n"/>
-      <c r="AH15" s="92" t="n"/>
-      <c r="AI15" s="92" t="n"/>
-      <c r="AJ15" s="92" t="n"/>
-      <c r="AK15" s="92" t="n"/>
-      <c r="AL15" s="93" t="n"/>
-      <c r="AM15" s="71" t="n"/>
-      <c r="AN15" s="94" t="n"/>
-      <c r="AO15" s="94" t="n"/>
-      <c r="AP15" s="94" t="n"/>
-      <c r="AQ15" s="94" t="n"/>
-      <c r="AR15" s="94" t="n"/>
-      <c r="AS15" s="94" t="n"/>
-      <c r="AT15" s="94" t="n"/>
-      <c r="AU15" s="94" t="n"/>
-      <c r="AV15" s="94" t="n"/>
-      <c r="AW15" s="94" t="n"/>
-      <c r="AX15" s="94" t="n"/>
-      <c r="AY15" s="94" t="n"/>
-      <c r="AZ15" s="94" t="n"/>
-      <c r="BA15" s="94" t="n"/>
-      <c r="BB15" s="94" t="n"/>
-      <c r="BC15" s="94" t="n"/>
-      <c r="BD15" s="95" t="n"/>
+      <c r="AD15" s="159" t="n"/>
+      <c r="AE15" s="159" t="n"/>
+      <c r="AF15" s="159" t="n"/>
+      <c r="AG15" s="159" t="n"/>
+      <c r="AH15" s="159" t="n"/>
+      <c r="AI15" s="159" t="n"/>
+      <c r="AJ15" s="159" t="n"/>
+      <c r="AK15" s="159" t="n"/>
+      <c r="AL15" s="159" t="n"/>
+      <c r="AM15" s="160" t="n"/>
+      <c r="AN15" s="161" t="n"/>
+      <c r="AO15" s="161" t="n"/>
+      <c r="AP15" s="161" t="n"/>
+      <c r="AQ15" s="161" t="n"/>
+      <c r="AR15" s="161" t="n"/>
+      <c r="AS15" s="161" t="n"/>
+      <c r="AT15" s="161" t="n"/>
+      <c r="AU15" s="161" t="n"/>
+      <c r="AV15" s="161" t="n"/>
+      <c r="AW15" s="161" t="n"/>
+      <c r="AX15" s="161" t="n"/>
+      <c r="AY15" s="161" t="n"/>
+      <c r="AZ15" s="161" t="n"/>
+      <c r="BA15" s="161" t="n"/>
+      <c r="BB15" s="161" t="n"/>
+      <c r="BC15" s="161" t="n"/>
+      <c r="BD15" s="163" t="n"/>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="67" t="inlineStr">
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="145" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. SCHEDULE / RESOURCE</t>
         </is>
       </c>
-      <c r="B16" s="92" t="n"/>
-      <c r="C16" s="92" t="n"/>
-      <c r="D16" s="92" t="n"/>
-      <c r="E16" s="92" t="n"/>
-      <c r="F16" s="92" t="n"/>
-      <c r="G16" s="92" t="n"/>
-      <c r="H16" s="92" t="n"/>
-      <c r="I16" s="92" t="n"/>
-      <c r="J16" s="92" t="n"/>
-      <c r="K16" s="92" t="n"/>
-      <c r="L16" s="92" t="n"/>
-      <c r="M16" s="92" t="n"/>
-      <c r="N16" s="92" t="n"/>
-      <c r="O16" s="92" t="n"/>
-      <c r="P16" s="92" t="n"/>
-      <c r="Q16" s="92" t="n"/>
-      <c r="R16" s="92" t="n"/>
-      <c r="S16" s="92" t="n"/>
-      <c r="T16" s="92" t="n"/>
-      <c r="U16" s="92" t="n"/>
-      <c r="V16" s="92" t="n"/>
-      <c r="W16" s="92" t="n"/>
-      <c r="X16" s="92" t="n"/>
-      <c r="Y16" s="92" t="n"/>
-      <c r="Z16" s="92" t="n"/>
-      <c r="AA16" s="92" t="n"/>
-      <c r="AB16" s="92" t="n"/>
-      <c r="AC16" s="92" t="n"/>
-      <c r="AD16" s="92" t="n"/>
-      <c r="AE16" s="92" t="n"/>
-      <c r="AF16" s="92" t="n"/>
-      <c r="AG16" s="92" t="n"/>
-      <c r="AH16" s="92" t="n"/>
-      <c r="AI16" s="92" t="n"/>
-      <c r="AJ16" s="92" t="n"/>
-      <c r="AK16" s="92" t="n"/>
-      <c r="AL16" s="92" t="n"/>
-      <c r="AM16" s="92" t="n"/>
-      <c r="AN16" s="92" t="n"/>
-      <c r="AO16" s="92" t="n"/>
-      <c r="AP16" s="92" t="n"/>
-      <c r="AQ16" s="92" t="n"/>
-      <c r="AR16" s="92" t="n"/>
-      <c r="AS16" s="92" t="n"/>
-      <c r="AT16" s="92" t="n"/>
-      <c r="AU16" s="92" t="n"/>
-      <c r="AV16" s="92" t="n"/>
-      <c r="AW16" s="92" t="n"/>
-      <c r="AX16" s="92" t="n"/>
-      <c r="AY16" s="92" t="n"/>
-      <c r="AZ16" s="92" t="n"/>
-      <c r="BA16" s="92" t="n"/>
-      <c r="BB16" s="92" t="n"/>
-      <c r="BC16" s="92" t="n"/>
-      <c r="BD16" s="93" t="n"/>
+      <c r="B16" s="146" t="n"/>
+      <c r="C16" s="146" t="n"/>
+      <c r="D16" s="146" t="n"/>
+      <c r="E16" s="146" t="n"/>
+      <c r="F16" s="146" t="n"/>
+      <c r="G16" s="146" t="n"/>
+      <c r="H16" s="146" t="n"/>
+      <c r="I16" s="146" t="n"/>
+      <c r="J16" s="146" t="n"/>
+      <c r="K16" s="146" t="n"/>
+      <c r="L16" s="146" t="n"/>
+      <c r="M16" s="146" t="n"/>
+      <c r="N16" s="146" t="n"/>
+      <c r="O16" s="146" t="n"/>
+      <c r="P16" s="146" t="n"/>
+      <c r="Q16" s="146" t="n"/>
+      <c r="R16" s="146" t="n"/>
+      <c r="S16" s="146" t="n"/>
+      <c r="T16" s="146" t="n"/>
+      <c r="U16" s="146" t="n"/>
+      <c r="V16" s="146" t="n"/>
+      <c r="W16" s="146" t="n"/>
+      <c r="X16" s="146" t="n"/>
+      <c r="Y16" s="146" t="n"/>
+      <c r="Z16" s="146" t="n"/>
+      <c r="AA16" s="146" t="n"/>
+      <c r="AB16" s="146" t="n"/>
+      <c r="AC16" s="146" t="n"/>
+      <c r="AD16" s="146" t="n"/>
+      <c r="AE16" s="146" t="n"/>
+      <c r="AF16" s="146" t="n"/>
+      <c r="AG16" s="146" t="n"/>
+      <c r="AH16" s="146" t="n"/>
+      <c r="AI16" s="146" t="n"/>
+      <c r="AJ16" s="146" t="n"/>
+      <c r="AK16" s="146" t="n"/>
+      <c r="AL16" s="146" t="n"/>
+      <c r="AM16" s="146" t="n"/>
+      <c r="AN16" s="146" t="n"/>
+      <c r="AO16" s="146" t="n"/>
+      <c r="AP16" s="146" t="n"/>
+      <c r="AQ16" s="146" t="n"/>
+      <c r="AR16" s="146" t="n"/>
+      <c r="AS16" s="146" t="n"/>
+      <c r="AT16" s="146" t="n"/>
+      <c r="AU16" s="146" t="n"/>
+      <c r="AV16" s="146" t="n"/>
+      <c r="AW16" s="146" t="n"/>
+      <c r="AX16" s="146" t="n"/>
+      <c r="AY16" s="146" t="n"/>
+      <c r="AZ16" s="146" t="n"/>
+      <c r="BA16" s="146" t="n"/>
+      <c r="BB16" s="146" t="n"/>
+      <c r="BC16" s="146" t="n"/>
+      <c r="BD16" s="147" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="68" t="inlineStr">
+      <c r="A17" s="148" t="inlineStr">
         <is>
           <t>Trainer</t>
         </is>
       </c>
-      <c r="B17" s="92" t="n"/>
-      <c r="C17" s="92" t="n"/>
-      <c r="D17" s="92" t="n"/>
-      <c r="E17" s="92" t="n"/>
-      <c r="F17" s="92" t="n"/>
-      <c r="G17" s="92" t="n"/>
-      <c r="H17" s="92" t="n"/>
-      <c r="I17" s="92" t="n"/>
-      <c r="J17" s="93" t="n"/>
-      <c r="K17" s="71" t="n"/>
-      <c r="L17" s="94" t="n"/>
-      <c r="M17" s="94" t="n"/>
-      <c r="N17" s="94" t="n"/>
-      <c r="O17" s="94" t="n"/>
-      <c r="P17" s="94" t="n"/>
-      <c r="Q17" s="94" t="n"/>
-      <c r="R17" s="94" t="n"/>
-      <c r="S17" s="94" t="n"/>
-      <c r="T17" s="94" t="n"/>
-      <c r="U17" s="94" t="n"/>
-      <c r="V17" s="94" t="n"/>
-      <c r="W17" s="94" t="n"/>
-      <c r="X17" s="94" t="n"/>
-      <c r="Y17" s="94" t="n"/>
-      <c r="Z17" s="94" t="n"/>
-      <c r="AA17" s="94" t="n"/>
-      <c r="AB17" s="95" t="n"/>
-      <c r="AC17" s="68" t="inlineStr">
+      <c r="B17" s="149" t="n"/>
+      <c r="C17" s="149" t="n"/>
+      <c r="D17" s="149" t="n"/>
+      <c r="E17" s="149" t="n"/>
+      <c r="F17" s="149" t="n"/>
+      <c r="G17" s="149" t="n"/>
+      <c r="H17" s="149" t="n"/>
+      <c r="I17" s="149" t="n"/>
+      <c r="J17" s="149" t="n"/>
+      <c r="K17" s="150" t="n"/>
+      <c r="L17" s="151" t="n"/>
+      <c r="M17" s="151" t="n"/>
+      <c r="N17" s="151" t="n"/>
+      <c r="O17" s="151" t="n"/>
+      <c r="P17" s="151" t="n"/>
+      <c r="Q17" s="151" t="n"/>
+      <c r="R17" s="151" t="n"/>
+      <c r="S17" s="151" t="n"/>
+      <c r="T17" s="151" t="n"/>
+      <c r="U17" s="151" t="n"/>
+      <c r="V17" s="151" t="n"/>
+      <c r="W17" s="151" t="n"/>
+      <c r="X17" s="151" t="n"/>
+      <c r="Y17" s="151" t="n"/>
+      <c r="Z17" s="151" t="n"/>
+      <c r="AA17" s="151" t="n"/>
+      <c r="AB17" s="151" t="n"/>
+      <c r="AC17" s="152" t="inlineStr">
         <is>
           <t>Scheduled Date</t>
         </is>
       </c>
-      <c r="AD17" s="92" t="n"/>
-      <c r="AE17" s="92" t="n"/>
-      <c r="AF17" s="92" t="n"/>
-      <c r="AG17" s="92" t="n"/>
-      <c r="AH17" s="92" t="n"/>
-      <c r="AI17" s="92" t="n"/>
-      <c r="AJ17" s="92" t="n"/>
-      <c r="AK17" s="92" t="n"/>
-      <c r="AL17" s="93" t="n"/>
-      <c r="AM17" s="71" t="n"/>
-      <c r="AN17" s="94" t="n"/>
-      <c r="AO17" s="94" t="n"/>
-      <c r="AP17" s="94" t="n"/>
-      <c r="AQ17" s="94" t="n"/>
-      <c r="AR17" s="94" t="n"/>
-      <c r="AS17" s="94" t="n"/>
-      <c r="AT17" s="94" t="n"/>
-      <c r="AU17" s="94" t="n"/>
-      <c r="AV17" s="94" t="n"/>
-      <c r="AW17" s="94" t="n"/>
-      <c r="AX17" s="94" t="n"/>
-      <c r="AY17" s="94" t="n"/>
-      <c r="AZ17" s="94" t="n"/>
-      <c r="BA17" s="94" t="n"/>
-      <c r="BB17" s="94" t="n"/>
-      <c r="BC17" s="94" t="n"/>
-      <c r="BD17" s="95" t="n"/>
+      <c r="AD17" s="149" t="n"/>
+      <c r="AE17" s="149" t="n"/>
+      <c r="AF17" s="149" t="n"/>
+      <c r="AG17" s="149" t="n"/>
+      <c r="AH17" s="149" t="n"/>
+      <c r="AI17" s="149" t="n"/>
+      <c r="AJ17" s="149" t="n"/>
+      <c r="AK17" s="149" t="n"/>
+      <c r="AL17" s="149" t="n"/>
+      <c r="AM17" s="150" t="n"/>
+      <c r="AN17" s="151" t="n"/>
+      <c r="AO17" s="151" t="n"/>
+      <c r="AP17" s="151" t="n"/>
+      <c r="AQ17" s="151" t="n"/>
+      <c r="AR17" s="151" t="n"/>
+      <c r="AS17" s="151" t="n"/>
+      <c r="AT17" s="151" t="n"/>
+      <c r="AU17" s="151" t="n"/>
+      <c r="AV17" s="151" t="n"/>
+      <c r="AW17" s="151" t="n"/>
+      <c r="AX17" s="151" t="n"/>
+      <c r="AY17" s="151" t="n"/>
+      <c r="AZ17" s="151" t="n"/>
+      <c r="BA17" s="151" t="n"/>
+      <c r="BB17" s="151" t="n"/>
+      <c r="BC17" s="151" t="n"/>
+      <c r="BD17" s="153" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="68" t="inlineStr">
+      <c r="A18" s="154" t="inlineStr">
         <is>
           <t>Material / Resource</t>
         </is>
       </c>
-      <c r="B18" s="92" t="n"/>
-      <c r="C18" s="92" t="n"/>
-      <c r="D18" s="92" t="n"/>
-      <c r="E18" s="92" t="n"/>
-      <c r="F18" s="92" t="n"/>
-      <c r="G18" s="92" t="n"/>
-      <c r="H18" s="92" t="n"/>
-      <c r="I18" s="92" t="n"/>
-      <c r="J18" s="93" t="n"/>
-      <c r="K18" s="71" t="n"/>
-      <c r="L18" s="94" t="n"/>
-      <c r="M18" s="94" t="n"/>
-      <c r="N18" s="94" t="n"/>
-      <c r="O18" s="94" t="n"/>
-      <c r="P18" s="94" t="n"/>
-      <c r="Q18" s="94" t="n"/>
-      <c r="R18" s="94" t="n"/>
-      <c r="S18" s="94" t="n"/>
-      <c r="T18" s="94" t="n"/>
-      <c r="U18" s="94" t="n"/>
-      <c r="V18" s="94" t="n"/>
-      <c r="W18" s="94" t="n"/>
-      <c r="X18" s="94" t="n"/>
-      <c r="Y18" s="94" t="n"/>
-      <c r="Z18" s="94" t="n"/>
-      <c r="AA18" s="94" t="n"/>
-      <c r="AB18" s="95" t="n"/>
-      <c r="AC18" s="68" t="inlineStr">
+      <c r="B18" s="54" t="n"/>
+      <c r="C18" s="54" t="n"/>
+      <c r="D18" s="54" t="n"/>
+      <c r="E18" s="54" t="n"/>
+      <c r="F18" s="54" t="n"/>
+      <c r="G18" s="54" t="n"/>
+      <c r="H18" s="54" t="n"/>
+      <c r="I18" s="54" t="n"/>
+      <c r="J18" s="54" t="n"/>
+      <c r="K18" s="155" t="n"/>
+      <c r="L18" s="74" t="n"/>
+      <c r="M18" s="74" t="n"/>
+      <c r="N18" s="74" t="n"/>
+      <c r="O18" s="74" t="n"/>
+      <c r="P18" s="74" t="n"/>
+      <c r="Q18" s="74" t="n"/>
+      <c r="R18" s="74" t="n"/>
+      <c r="S18" s="74" t="n"/>
+      <c r="T18" s="74" t="n"/>
+      <c r="U18" s="74" t="n"/>
+      <c r="V18" s="74" t="n"/>
+      <c r="W18" s="74" t="n"/>
+      <c r="X18" s="74" t="n"/>
+      <c r="Y18" s="74" t="n"/>
+      <c r="Z18" s="74" t="n"/>
+      <c r="AA18" s="74" t="n"/>
+      <c r="AB18" s="74" t="n"/>
+      <c r="AC18" s="156" t="inlineStr">
         <is>
           <t>OJT / Test / Observation Method</t>
         </is>
       </c>
-      <c r="AD18" s="92" t="n"/>
-      <c r="AE18" s="92" t="n"/>
-      <c r="AF18" s="92" t="n"/>
-      <c r="AG18" s="92" t="n"/>
-      <c r="AH18" s="92" t="n"/>
-      <c r="AI18" s="92" t="n"/>
-      <c r="AJ18" s="92" t="n"/>
-      <c r="AK18" s="92" t="n"/>
-      <c r="AL18" s="93" t="n"/>
-      <c r="AM18" s="71" t="n"/>
-      <c r="AN18" s="94" t="n"/>
-      <c r="AO18" s="94" t="n"/>
-      <c r="AP18" s="94" t="n"/>
-      <c r="AQ18" s="94" t="n"/>
-      <c r="AR18" s="94" t="n"/>
-      <c r="AS18" s="94" t="n"/>
-      <c r="AT18" s="94" t="n"/>
-      <c r="AU18" s="94" t="n"/>
-      <c r="AV18" s="94" t="n"/>
-      <c r="AW18" s="94" t="n"/>
-      <c r="AX18" s="94" t="n"/>
-      <c r="AY18" s="94" t="n"/>
-      <c r="AZ18" s="94" t="n"/>
-      <c r="BA18" s="94" t="n"/>
-      <c r="BB18" s="94" t="n"/>
-      <c r="BC18" s="94" t="n"/>
-      <c r="BD18" s="95" t="n"/>
+      <c r="AD18" s="54" t="n"/>
+      <c r="AE18" s="54" t="n"/>
+      <c r="AF18" s="54" t="n"/>
+      <c r="AG18" s="54" t="n"/>
+      <c r="AH18" s="54" t="n"/>
+      <c r="AI18" s="54" t="n"/>
+      <c r="AJ18" s="54" t="n"/>
+      <c r="AK18" s="54" t="n"/>
+      <c r="AL18" s="54" t="n"/>
+      <c r="AM18" s="155" t="n"/>
+      <c r="AN18" s="74" t="n"/>
+      <c r="AO18" s="74" t="n"/>
+      <c r="AP18" s="74" t="n"/>
+      <c r="AQ18" s="74" t="n"/>
+      <c r="AR18" s="74" t="n"/>
+      <c r="AS18" s="74" t="n"/>
+      <c r="AT18" s="74" t="n"/>
+      <c r="AU18" s="74" t="n"/>
+      <c r="AV18" s="74" t="n"/>
+      <c r="AW18" s="74" t="n"/>
+      <c r="AX18" s="74" t="n"/>
+      <c r="AY18" s="74" t="n"/>
+      <c r="AZ18" s="74" t="n"/>
+      <c r="BA18" s="74" t="n"/>
+      <c r="BB18" s="74" t="n"/>
+      <c r="BC18" s="74" t="n"/>
+      <c r="BD18" s="157" t="n"/>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="68" t="inlineStr">
+      <c r="A19" s="158" t="inlineStr">
         <is>
           <t>Follow-Up Date</t>
         </is>
       </c>
-      <c r="B19" s="86" t="n"/>
-      <c r="C19" s="86" t="n"/>
-      <c r="D19" s="86" t="n"/>
-      <c r="E19" s="86" t="n"/>
-      <c r="F19" s="86" t="n"/>
-      <c r="G19" s="86" t="n"/>
-      <c r="H19" s="86" t="n"/>
-      <c r="I19" s="86" t="n"/>
-      <c r="J19" s="87" t="n"/>
-      <c r="K19" s="71" t="n"/>
-      <c r="L19" s="96" t="n"/>
-      <c r="M19" s="96" t="n"/>
-      <c r="N19" s="96" t="n"/>
-      <c r="O19" s="96" t="n"/>
-      <c r="P19" s="96" t="n"/>
-      <c r="Q19" s="96" t="n"/>
-      <c r="R19" s="96" t="n"/>
-      <c r="S19" s="96" t="n"/>
-      <c r="T19" s="96" t="n"/>
-      <c r="U19" s="96" t="n"/>
-      <c r="V19" s="96" t="n"/>
-      <c r="W19" s="96" t="n"/>
-      <c r="X19" s="96" t="n"/>
-      <c r="Y19" s="96" t="n"/>
-      <c r="Z19" s="96" t="n"/>
-      <c r="AA19" s="96" t="n"/>
-      <c r="AB19" s="97" t="n"/>
-      <c r="AC19" s="68" t="inlineStr">
+      <c r="B19" s="159" t="n"/>
+      <c r="C19" s="159" t="n"/>
+      <c r="D19" s="159" t="n"/>
+      <c r="E19" s="159" t="n"/>
+      <c r="F19" s="159" t="n"/>
+      <c r="G19" s="159" t="n"/>
+      <c r="H19" s="159" t="n"/>
+      <c r="I19" s="159" t="n"/>
+      <c r="J19" s="159" t="n"/>
+      <c r="K19" s="160" t="n"/>
+      <c r="L19" s="161" t="n"/>
+      <c r="M19" s="161" t="n"/>
+      <c r="N19" s="161" t="n"/>
+      <c r="O19" s="161" t="n"/>
+      <c r="P19" s="161" t="n"/>
+      <c r="Q19" s="161" t="n"/>
+      <c r="R19" s="161" t="n"/>
+      <c r="S19" s="161" t="n"/>
+      <c r="T19" s="161" t="n"/>
+      <c r="U19" s="161" t="n"/>
+      <c r="V19" s="161" t="n"/>
+      <c r="W19" s="161" t="n"/>
+      <c r="X19" s="161" t="n"/>
+      <c r="Y19" s="161" t="n"/>
+      <c r="Z19" s="161" t="n"/>
+      <c r="AA19" s="161" t="n"/>
+      <c r="AB19" s="161" t="n"/>
+      <c r="AC19" s="162" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AD19" s="86" t="n"/>
-      <c r="AE19" s="86" t="n"/>
-      <c r="AF19" s="86" t="n"/>
-      <c r="AG19" s="86" t="n"/>
-      <c r="AH19" s="86" t="n"/>
-      <c r="AI19" s="86" t="n"/>
-      <c r="AJ19" s="86" t="n"/>
-      <c r="AK19" s="86" t="n"/>
-      <c r="AL19" s="87" t="n"/>
-      <c r="AM19" s="71" t="n"/>
-      <c r="AN19" s="96" t="n"/>
-      <c r="AO19" s="96" t="n"/>
-      <c r="AP19" s="96" t="n"/>
-      <c r="AQ19" s="96" t="n"/>
-      <c r="AR19" s="96" t="n"/>
-      <c r="AS19" s="96" t="n"/>
-      <c r="AT19" s="96" t="n"/>
-      <c r="AU19" s="96" t="n"/>
-      <c r="AV19" s="96" t="n"/>
-      <c r="AW19" s="96" t="n"/>
-      <c r="AX19" s="96" t="n"/>
-      <c r="AY19" s="96" t="n"/>
-      <c r="AZ19" s="96" t="n"/>
-      <c r="BA19" s="96" t="n"/>
-      <c r="BB19" s="96" t="n"/>
-      <c r="BC19" s="96" t="n"/>
-      <c r="BD19" s="97" t="n"/>
+      <c r="AD19" s="159" t="n"/>
+      <c r="AE19" s="159" t="n"/>
+      <c r="AF19" s="159" t="n"/>
+      <c r="AG19" s="159" t="n"/>
+      <c r="AH19" s="159" t="n"/>
+      <c r="AI19" s="159" t="n"/>
+      <c r="AJ19" s="159" t="n"/>
+      <c r="AK19" s="159" t="n"/>
+      <c r="AL19" s="159" t="n"/>
+      <c r="AM19" s="160" t="n"/>
+      <c r="AN19" s="161" t="n"/>
+      <c r="AO19" s="161" t="n"/>
+      <c r="AP19" s="161" t="n"/>
+      <c r="AQ19" s="161" t="n"/>
+      <c r="AR19" s="161" t="n"/>
+      <c r="AS19" s="161" t="n"/>
+      <c r="AT19" s="161" t="n"/>
+      <c r="AU19" s="161" t="n"/>
+      <c r="AV19" s="161" t="n"/>
+      <c r="AW19" s="161" t="n"/>
+      <c r="AX19" s="161" t="n"/>
+      <c r="AY19" s="161" t="n"/>
+      <c r="AZ19" s="161" t="n"/>
+      <c r="BA19" s="161" t="n"/>
+      <c r="BB19" s="161" t="n"/>
+      <c r="BC19" s="161" t="n"/>
+      <c r="BD19" s="163" t="n"/>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="67" t="inlineStr">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="145" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. DECISION / REVIEW</t>
         </is>
       </c>
-      <c r="B20" s="92" t="n"/>
-      <c r="C20" s="92" t="n"/>
-      <c r="D20" s="92" t="n"/>
-      <c r="E20" s="92" t="n"/>
-      <c r="F20" s="92" t="n"/>
-      <c r="G20" s="92" t="n"/>
-      <c r="H20" s="92" t="n"/>
-      <c r="I20" s="92" t="n"/>
-      <c r="J20" s="92" t="n"/>
-      <c r="K20" s="92" t="n"/>
-      <c r="L20" s="92" t="n"/>
-      <c r="M20" s="92" t="n"/>
-      <c r="N20" s="92" t="n"/>
-      <c r="O20" s="92" t="n"/>
-      <c r="P20" s="92" t="n"/>
-      <c r="Q20" s="92" t="n"/>
-      <c r="R20" s="92" t="n"/>
-      <c r="S20" s="92" t="n"/>
-      <c r="T20" s="92" t="n"/>
-      <c r="U20" s="92" t="n"/>
-      <c r="V20" s="92" t="n"/>
-      <c r="W20" s="92" t="n"/>
-      <c r="X20" s="92" t="n"/>
-      <c r="Y20" s="92" t="n"/>
-      <c r="Z20" s="92" t="n"/>
-      <c r="AA20" s="92" t="n"/>
-      <c r="AB20" s="92" t="n"/>
-      <c r="AC20" s="92" t="n"/>
-      <c r="AD20" s="92" t="n"/>
-      <c r="AE20" s="92" t="n"/>
-      <c r="AF20" s="92" t="n"/>
-      <c r="AG20" s="92" t="n"/>
-      <c r="AH20" s="92" t="n"/>
-      <c r="AI20" s="92" t="n"/>
-      <c r="AJ20" s="92" t="n"/>
-      <c r="AK20" s="92" t="n"/>
-      <c r="AL20" s="92" t="n"/>
-      <c r="AM20" s="92" t="n"/>
-      <c r="AN20" s="92" t="n"/>
-      <c r="AO20" s="92" t="n"/>
-      <c r="AP20" s="92" t="n"/>
-      <c r="AQ20" s="92" t="n"/>
-      <c r="AR20" s="92" t="n"/>
-      <c r="AS20" s="92" t="n"/>
-      <c r="AT20" s="92" t="n"/>
-      <c r="AU20" s="92" t="n"/>
-      <c r="AV20" s="92" t="n"/>
-      <c r="AW20" s="92" t="n"/>
-      <c r="AX20" s="92" t="n"/>
-      <c r="AY20" s="92" t="n"/>
-      <c r="AZ20" s="92" t="n"/>
-      <c r="BA20" s="92" t="n"/>
-      <c r="BB20" s="92" t="n"/>
-      <c r="BC20" s="92" t="n"/>
-      <c r="BD20" s="93" t="n"/>
+      <c r="B20" s="146" t="n"/>
+      <c r="C20" s="146" t="n"/>
+      <c r="D20" s="146" t="n"/>
+      <c r="E20" s="146" t="n"/>
+      <c r="F20" s="146" t="n"/>
+      <c r="G20" s="146" t="n"/>
+      <c r="H20" s="146" t="n"/>
+      <c r="I20" s="146" t="n"/>
+      <c r="J20" s="146" t="n"/>
+      <c r="K20" s="146" t="n"/>
+      <c r="L20" s="146" t="n"/>
+      <c r="M20" s="146" t="n"/>
+      <c r="N20" s="146" t="n"/>
+      <c r="O20" s="146" t="n"/>
+      <c r="P20" s="146" t="n"/>
+      <c r="Q20" s="146" t="n"/>
+      <c r="R20" s="146" t="n"/>
+      <c r="S20" s="146" t="n"/>
+      <c r="T20" s="146" t="n"/>
+      <c r="U20" s="146" t="n"/>
+      <c r="V20" s="146" t="n"/>
+      <c r="W20" s="146" t="n"/>
+      <c r="X20" s="146" t="n"/>
+      <c r="Y20" s="146" t="n"/>
+      <c r="Z20" s="146" t="n"/>
+      <c r="AA20" s="146" t="n"/>
+      <c r="AB20" s="146" t="n"/>
+      <c r="AC20" s="146" t="n"/>
+      <c r="AD20" s="146" t="n"/>
+      <c r="AE20" s="146" t="n"/>
+      <c r="AF20" s="146" t="n"/>
+      <c r="AG20" s="146" t="n"/>
+      <c r="AH20" s="146" t="n"/>
+      <c r="AI20" s="146" t="n"/>
+      <c r="AJ20" s="146" t="n"/>
+      <c r="AK20" s="146" t="n"/>
+      <c r="AL20" s="146" t="n"/>
+      <c r="AM20" s="146" t="n"/>
+      <c r="AN20" s="146" t="n"/>
+      <c r="AO20" s="146" t="n"/>
+      <c r="AP20" s="146" t="n"/>
+      <c r="AQ20" s="146" t="n"/>
+      <c r="AR20" s="146" t="n"/>
+      <c r="AS20" s="146" t="n"/>
+      <c r="AT20" s="146" t="n"/>
+      <c r="AU20" s="146" t="n"/>
+      <c r="AV20" s="146" t="n"/>
+      <c r="AW20" s="146" t="n"/>
+      <c r="AX20" s="146" t="n"/>
+      <c r="AY20" s="146" t="n"/>
+      <c r="AZ20" s="146" t="n"/>
+      <c r="BA20" s="146" t="n"/>
+      <c r="BB20" s="146" t="n"/>
+      <c r="BC20" s="146" t="n"/>
+      <c r="BD20" s="147" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="68" t="inlineStr">
+      <c r="A21" s="148" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="B21" s="92" t="n"/>
-      <c r="C21" s="92" t="n"/>
-      <c r="D21" s="92" t="n"/>
-      <c r="E21" s="92" t="n"/>
-      <c r="F21" s="92" t="n"/>
-      <c r="G21" s="92" t="n"/>
-      <c r="H21" s="92" t="n"/>
-      <c r="I21" s="92" t="n"/>
-      <c r="J21" s="93" t="n"/>
-      <c r="K21" s="71" t="n"/>
-      <c r="L21" s="94" t="n"/>
-      <c r="M21" s="94" t="n"/>
-      <c r="N21" s="94" t="n"/>
-      <c r="O21" s="94" t="n"/>
-      <c r="P21" s="94" t="n"/>
-      <c r="Q21" s="94" t="n"/>
-      <c r="R21" s="94" t="n"/>
-      <c r="S21" s="94" t="n"/>
-      <c r="T21" s="94" t="n"/>
-      <c r="U21" s="94" t="n"/>
-      <c r="V21" s="94" t="n"/>
-      <c r="W21" s="94" t="n"/>
-      <c r="X21" s="94" t="n"/>
-      <c r="Y21" s="94" t="n"/>
-      <c r="Z21" s="94" t="n"/>
-      <c r="AA21" s="94" t="n"/>
-      <c r="AB21" s="95" t="n"/>
-      <c r="AC21" s="68" t="inlineStr">
+      <c r="B21" s="149" t="n"/>
+      <c r="C21" s="149" t="n"/>
+      <c r="D21" s="149" t="n"/>
+      <c r="E21" s="149" t="n"/>
+      <c r="F21" s="149" t="n"/>
+      <c r="G21" s="149" t="n"/>
+      <c r="H21" s="149" t="n"/>
+      <c r="I21" s="149" t="n"/>
+      <c r="J21" s="149" t="n"/>
+      <c r="K21" s="150" t="n"/>
+      <c r="L21" s="151" t="n"/>
+      <c r="M21" s="151" t="n"/>
+      <c r="N21" s="151" t="n"/>
+      <c r="O21" s="151" t="n"/>
+      <c r="P21" s="151" t="n"/>
+      <c r="Q21" s="151" t="n"/>
+      <c r="R21" s="151" t="n"/>
+      <c r="S21" s="151" t="n"/>
+      <c r="T21" s="151" t="n"/>
+      <c r="U21" s="151" t="n"/>
+      <c r="V21" s="151" t="n"/>
+      <c r="W21" s="151" t="n"/>
+      <c r="X21" s="151" t="n"/>
+      <c r="Y21" s="151" t="n"/>
+      <c r="Z21" s="151" t="n"/>
+      <c r="AA21" s="151" t="n"/>
+      <c r="AB21" s="151" t="n"/>
+      <c r="AC21" s="152" t="inlineStr">
         <is>
           <t>Review Status</t>
         </is>
       </c>
-      <c r="AD21" s="92" t="n"/>
-      <c r="AE21" s="92" t="n"/>
-      <c r="AF21" s="92" t="n"/>
-      <c r="AG21" s="92" t="n"/>
-      <c r="AH21" s="92" t="n"/>
-      <c r="AI21" s="92" t="n"/>
-      <c r="AJ21" s="92" t="n"/>
-      <c r="AK21" s="92" t="n"/>
-      <c r="AL21" s="93" t="n"/>
-      <c r="AM21" s="71" t="n"/>
-      <c r="AN21" s="94" t="n"/>
-      <c r="AO21" s="94" t="n"/>
-      <c r="AP21" s="94" t="n"/>
-      <c r="AQ21" s="94" t="n"/>
-      <c r="AR21" s="94" t="n"/>
-      <c r="AS21" s="94" t="n"/>
-      <c r="AT21" s="94" t="n"/>
-      <c r="AU21" s="94" t="n"/>
-      <c r="AV21" s="94" t="n"/>
-      <c r="AW21" s="94" t="n"/>
-      <c r="AX21" s="94" t="n"/>
-      <c r="AY21" s="94" t="n"/>
-      <c r="AZ21" s="94" t="n"/>
-      <c r="BA21" s="94" t="n"/>
-      <c r="BB21" s="94" t="n"/>
-      <c r="BC21" s="94" t="n"/>
-      <c r="BD21" s="95" t="n"/>
+      <c r="AD21" s="149" t="n"/>
+      <c r="AE21" s="149" t="n"/>
+      <c r="AF21" s="149" t="n"/>
+      <c r="AG21" s="149" t="n"/>
+      <c r="AH21" s="149" t="n"/>
+      <c r="AI21" s="149" t="n"/>
+      <c r="AJ21" s="149" t="n"/>
+      <c r="AK21" s="149" t="n"/>
+      <c r="AL21" s="149" t="n"/>
+      <c r="AM21" s="150" t="n"/>
+      <c r="AN21" s="151" t="n"/>
+      <c r="AO21" s="151" t="n"/>
+      <c r="AP21" s="151" t="n"/>
+      <c r="AQ21" s="151" t="n"/>
+      <c r="AR21" s="151" t="n"/>
+      <c r="AS21" s="151" t="n"/>
+      <c r="AT21" s="151" t="n"/>
+      <c r="AU21" s="151" t="n"/>
+      <c r="AV21" s="151" t="n"/>
+      <c r="AW21" s="151" t="n"/>
+      <c r="AX21" s="151" t="n"/>
+      <c r="AY21" s="151" t="n"/>
+      <c r="AZ21" s="151" t="n"/>
+      <c r="BA21" s="151" t="n"/>
+      <c r="BB21" s="151" t="n"/>
+      <c r="BC21" s="151" t="n"/>
+      <c r="BD21" s="153" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="68" t="inlineStr">
+      <c r="A22" s="158" t="inlineStr">
         <is>
           <t>Authorized By</t>
         </is>
       </c>
-      <c r="B22" s="92" t="n"/>
-      <c r="C22" s="92" t="n"/>
-      <c r="D22" s="92" t="n"/>
-      <c r="E22" s="92" t="n"/>
-      <c r="F22" s="92" t="n"/>
-      <c r="G22" s="92" t="n"/>
-      <c r="H22" s="92" t="n"/>
-      <c r="I22" s="92" t="n"/>
-      <c r="J22" s="93" t="n"/>
-      <c r="K22" s="71" t="n"/>
-      <c r="L22" s="94" t="n"/>
-      <c r="M22" s="94" t="n"/>
-      <c r="N22" s="94" t="n"/>
-      <c r="O22" s="94" t="n"/>
-      <c r="P22" s="94" t="n"/>
-      <c r="Q22" s="94" t="n"/>
-      <c r="R22" s="94" t="n"/>
-      <c r="S22" s="94" t="n"/>
-      <c r="T22" s="94" t="n"/>
-      <c r="U22" s="94" t="n"/>
-      <c r="V22" s="94" t="n"/>
-      <c r="W22" s="94" t="n"/>
-      <c r="X22" s="94" t="n"/>
-      <c r="Y22" s="94" t="n"/>
-      <c r="Z22" s="94" t="n"/>
-      <c r="AA22" s="94" t="n"/>
-      <c r="AB22" s="95" t="n"/>
-      <c r="AC22" s="68" t="inlineStr">
+      <c r="B22" s="159" t="n"/>
+      <c r="C22" s="159" t="n"/>
+      <c r="D22" s="159" t="n"/>
+      <c r="E22" s="159" t="n"/>
+      <c r="F22" s="159" t="n"/>
+      <c r="G22" s="159" t="n"/>
+      <c r="H22" s="159" t="n"/>
+      <c r="I22" s="159" t="n"/>
+      <c r="J22" s="159" t="n"/>
+      <c r="K22" s="160" t="n"/>
+      <c r="L22" s="161" t="n"/>
+      <c r="M22" s="161" t="n"/>
+      <c r="N22" s="161" t="n"/>
+      <c r="O22" s="161" t="n"/>
+      <c r="P22" s="161" t="n"/>
+      <c r="Q22" s="161" t="n"/>
+      <c r="R22" s="161" t="n"/>
+      <c r="S22" s="161" t="n"/>
+      <c r="T22" s="161" t="n"/>
+      <c r="U22" s="161" t="n"/>
+      <c r="V22" s="161" t="n"/>
+      <c r="W22" s="161" t="n"/>
+      <c r="X22" s="161" t="n"/>
+      <c r="Y22" s="161" t="n"/>
+      <c r="Z22" s="161" t="n"/>
+      <c r="AA22" s="161" t="n"/>
+      <c r="AB22" s="161" t="n"/>
+      <c r="AC22" s="162" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
-      <c r="AD22" s="92" t="n"/>
-      <c r="AE22" s="92" t="n"/>
-      <c r="AF22" s="92" t="n"/>
-      <c r="AG22" s="92" t="n"/>
-      <c r="AH22" s="92" t="n"/>
-      <c r="AI22" s="92" t="n"/>
-      <c r="AJ22" s="92" t="n"/>
-      <c r="AK22" s="92" t="n"/>
-      <c r="AL22" s="93" t="n"/>
-      <c r="AM22" s="71" t="n"/>
-      <c r="AN22" s="94" t="n"/>
-      <c r="AO22" s="94" t="n"/>
-      <c r="AP22" s="94" t="n"/>
-      <c r="AQ22" s="94" t="n"/>
-      <c r="AR22" s="94" t="n"/>
-      <c r="AS22" s="94" t="n"/>
-      <c r="AT22" s="94" t="n"/>
-      <c r="AU22" s="94" t="n"/>
-      <c r="AV22" s="94" t="n"/>
-      <c r="AW22" s="94" t="n"/>
-      <c r="AX22" s="94" t="n"/>
-      <c r="AY22" s="94" t="n"/>
-      <c r="AZ22" s="94" t="n"/>
-      <c r="BA22" s="94" t="n"/>
-      <c r="BB22" s="94" t="n"/>
-      <c r="BC22" s="94" t="n"/>
-      <c r="BD22" s="95" t="n"/>
+      <c r="AD22" s="159" t="n"/>
+      <c r="AE22" s="159" t="n"/>
+      <c r="AF22" s="159" t="n"/>
+      <c r="AG22" s="159" t="n"/>
+      <c r="AH22" s="159" t="n"/>
+      <c r="AI22" s="159" t="n"/>
+      <c r="AJ22" s="159" t="n"/>
+      <c r="AK22" s="159" t="n"/>
+      <c r="AL22" s="159" t="n"/>
+      <c r="AM22" s="160" t="n"/>
+      <c r="AN22" s="161" t="n"/>
+      <c r="AO22" s="161" t="n"/>
+      <c r="AP22" s="161" t="n"/>
+      <c r="AQ22" s="161" t="n"/>
+      <c r="AR22" s="161" t="n"/>
+      <c r="AS22" s="161" t="n"/>
+      <c r="AT22" s="161" t="n"/>
+      <c r="AU22" s="161" t="n"/>
+      <c r="AV22" s="161" t="n"/>
+      <c r="AW22" s="161" t="n"/>
+      <c r="AX22" s="161" t="n"/>
+      <c r="AY22" s="161" t="n"/>
+      <c r="AZ22" s="161" t="n"/>
+      <c r="BA22" s="161" t="n"/>
+      <c r="BB22" s="161" t="n"/>
+      <c r="BC22" s="161" t="n"/>
+      <c r="BD22" s="163" t="n"/>
     </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="67" t="inlineStr">
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="145" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B23" s="92" t="n"/>
-      <c r="C23" s="92" t="n"/>
-      <c r="D23" s="92" t="n"/>
-      <c r="E23" s="92" t="n"/>
-      <c r="F23" s="92" t="n"/>
-      <c r="G23" s="92" t="n"/>
-      <c r="H23" s="92" t="n"/>
-      <c r="I23" s="92" t="n"/>
-      <c r="J23" s="92" t="n"/>
-      <c r="K23" s="92" t="n"/>
-      <c r="L23" s="92" t="n"/>
-      <c r="M23" s="92" t="n"/>
-      <c r="N23" s="92" t="n"/>
-      <c r="O23" s="92" t="n"/>
-      <c r="P23" s="92" t="n"/>
-      <c r="Q23" s="92" t="n"/>
-      <c r="R23" s="92" t="n"/>
-      <c r="S23" s="92" t="n"/>
-      <c r="T23" s="92" t="n"/>
-      <c r="U23" s="92" t="n"/>
-      <c r="V23" s="92" t="n"/>
-      <c r="W23" s="92" t="n"/>
-      <c r="X23" s="92" t="n"/>
-      <c r="Y23" s="92" t="n"/>
-      <c r="Z23" s="92" t="n"/>
-      <c r="AA23" s="92" t="n"/>
-      <c r="AB23" s="92" t="n"/>
-      <c r="AC23" s="92" t="n"/>
-      <c r="AD23" s="92" t="n"/>
-      <c r="AE23" s="92" t="n"/>
-      <c r="AF23" s="92" t="n"/>
-      <c r="AG23" s="92" t="n"/>
-      <c r="AH23" s="92" t="n"/>
-      <c r="AI23" s="92" t="n"/>
-      <c r="AJ23" s="92" t="n"/>
-      <c r="AK23" s="92" t="n"/>
-      <c r="AL23" s="92" t="n"/>
-      <c r="AM23" s="92" t="n"/>
-      <c r="AN23" s="92" t="n"/>
-      <c r="AO23" s="92" t="n"/>
-      <c r="AP23" s="92" t="n"/>
-      <c r="AQ23" s="92" t="n"/>
-      <c r="AR23" s="92" t="n"/>
-      <c r="AS23" s="92" t="n"/>
-      <c r="AT23" s="92" t="n"/>
-      <c r="AU23" s="92" t="n"/>
-      <c r="AV23" s="92" t="n"/>
-      <c r="AW23" s="92" t="n"/>
-      <c r="AX23" s="92" t="n"/>
-      <c r="AY23" s="92" t="n"/>
-      <c r="AZ23" s="92" t="n"/>
-      <c r="BA23" s="92" t="n"/>
-      <c r="BB23" s="92" t="n"/>
-      <c r="BC23" s="92" t="n"/>
-      <c r="BD23" s="93" t="n"/>
+      <c r="B23" s="146" t="n"/>
+      <c r="C23" s="146" t="n"/>
+      <c r="D23" s="146" t="n"/>
+      <c r="E23" s="146" t="n"/>
+      <c r="F23" s="146" t="n"/>
+      <c r="G23" s="146" t="n"/>
+      <c r="H23" s="146" t="n"/>
+      <c r="I23" s="146" t="n"/>
+      <c r="J23" s="146" t="n"/>
+      <c r="K23" s="146" t="n"/>
+      <c r="L23" s="146" t="n"/>
+      <c r="M23" s="146" t="n"/>
+      <c r="N23" s="146" t="n"/>
+      <c r="O23" s="146" t="n"/>
+      <c r="P23" s="146" t="n"/>
+      <c r="Q23" s="146" t="n"/>
+      <c r="R23" s="146" t="n"/>
+      <c r="S23" s="146" t="n"/>
+      <c r="T23" s="146" t="n"/>
+      <c r="U23" s="146" t="n"/>
+      <c r="V23" s="146" t="n"/>
+      <c r="W23" s="146" t="n"/>
+      <c r="X23" s="146" t="n"/>
+      <c r="Y23" s="146" t="n"/>
+      <c r="Z23" s="146" t="n"/>
+      <c r="AA23" s="146" t="n"/>
+      <c r="AB23" s="146" t="n"/>
+      <c r="AC23" s="146" t="n"/>
+      <c r="AD23" s="146" t="n"/>
+      <c r="AE23" s="146" t="n"/>
+      <c r="AF23" s="146" t="n"/>
+      <c r="AG23" s="146" t="n"/>
+      <c r="AH23" s="146" t="n"/>
+      <c r="AI23" s="146" t="n"/>
+      <c r="AJ23" s="146" t="n"/>
+      <c r="AK23" s="146" t="n"/>
+      <c r="AL23" s="146" t="n"/>
+      <c r="AM23" s="146" t="n"/>
+      <c r="AN23" s="146" t="n"/>
+      <c r="AO23" s="146" t="n"/>
+      <c r="AP23" s="146" t="n"/>
+      <c r="AQ23" s="146" t="n"/>
+      <c r="AR23" s="146" t="n"/>
+      <c r="AS23" s="146" t="n"/>
+      <c r="AT23" s="146" t="n"/>
+      <c r="AU23" s="146" t="n"/>
+      <c r="AV23" s="146" t="n"/>
+      <c r="AW23" s="146" t="n"/>
+      <c r="AX23" s="146" t="n"/>
+      <c r="AY23" s="146" t="n"/>
+      <c r="AZ23" s="146" t="n"/>
+      <c r="BA23" s="146" t="n"/>
+      <c r="BB23" s="146" t="n"/>
+      <c r="BC23" s="146" t="n"/>
+      <c r="BD23" s="147" t="n"/>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="76" t="inlineStr">
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="164" t="inlineStr">
         <is>
           <t>Prepared By</t>
         </is>
       </c>
-      <c r="B24" s="86" t="n"/>
-      <c r="C24" s="86" t="n"/>
-      <c r="D24" s="86" t="n"/>
-      <c r="E24" s="86" t="n"/>
-      <c r="F24" s="86" t="n"/>
-      <c r="G24" s="86" t="n"/>
-      <c r="H24" s="86" t="n"/>
-      <c r="I24" s="86" t="n"/>
-      <c r="J24" s="86" t="n"/>
-      <c r="K24" s="86" t="n"/>
-      <c r="L24" s="86" t="n"/>
-      <c r="M24" s="86" t="n"/>
-      <c r="N24" s="86" t="n"/>
-      <c r="O24" s="86" t="n"/>
-      <c r="P24" s="86" t="n"/>
-      <c r="Q24" s="86" t="n"/>
-      <c r="R24" s="87" t="n"/>
-      <c r="S24" s="76" t="inlineStr">
+      <c r="B24" s="149" t="n"/>
+      <c r="C24" s="149" t="n"/>
+      <c r="D24" s="149" t="n"/>
+      <c r="E24" s="149" t="n"/>
+      <c r="F24" s="149" t="n"/>
+      <c r="G24" s="149" t="n"/>
+      <c r="H24" s="149" t="n"/>
+      <c r="I24" s="149" t="n"/>
+      <c r="J24" s="149" t="n"/>
+      <c r="K24" s="149" t="n"/>
+      <c r="L24" s="149" t="n"/>
+      <c r="M24" s="149" t="n"/>
+      <c r="N24" s="149" t="n"/>
+      <c r="O24" s="149" t="n"/>
+      <c r="P24" s="149" t="n"/>
+      <c r="Q24" s="149" t="n"/>
+      <c r="R24" s="149" t="n"/>
+      <c r="S24" s="165" t="inlineStr">
         <is>
           <t>Reviewed By</t>
         </is>
       </c>
-      <c r="T24" s="86" t="n"/>
-      <c r="U24" s="86" t="n"/>
-      <c r="V24" s="86" t="n"/>
-      <c r="W24" s="86" t="n"/>
-      <c r="X24" s="86" t="n"/>
-      <c r="Y24" s="86" t="n"/>
-      <c r="Z24" s="86" t="n"/>
-      <c r="AA24" s="86" t="n"/>
-      <c r="AB24" s="86" t="n"/>
-      <c r="AC24" s="86" t="n"/>
-      <c r="AD24" s="86" t="n"/>
-      <c r="AE24" s="86" t="n"/>
-      <c r="AF24" s="86" t="n"/>
-      <c r="AG24" s="86" t="n"/>
-      <c r="AH24" s="86" t="n"/>
-      <c r="AI24" s="86" t="n"/>
-      <c r="AJ24" s="86" t="n"/>
-      <c r="AK24" s="87" t="n"/>
-      <c r="AL24" s="76" t="inlineStr">
+      <c r="T24" s="149" t="n"/>
+      <c r="U24" s="149" t="n"/>
+      <c r="V24" s="149" t="n"/>
+      <c r="W24" s="149" t="n"/>
+      <c r="X24" s="149" t="n"/>
+      <c r="Y24" s="149" t="n"/>
+      <c r="Z24" s="149" t="n"/>
+      <c r="AA24" s="149" t="n"/>
+      <c r="AB24" s="149" t="n"/>
+      <c r="AC24" s="149" t="n"/>
+      <c r="AD24" s="149" t="n"/>
+      <c r="AE24" s="149" t="n"/>
+      <c r="AF24" s="149" t="n"/>
+      <c r="AG24" s="149" t="n"/>
+      <c r="AH24" s="149" t="n"/>
+      <c r="AI24" s="149" t="n"/>
+      <c r="AJ24" s="149" t="n"/>
+      <c r="AK24" s="149" t="n"/>
+      <c r="AL24" s="165" t="inlineStr">
         <is>
           <t>Approved By</t>
         </is>
       </c>
-      <c r="AM24" s="86" t="n"/>
-      <c r="AN24" s="86" t="n"/>
-      <c r="AO24" s="86" t="n"/>
-      <c r="AP24" s="86" t="n"/>
-      <c r="AQ24" s="86" t="n"/>
-      <c r="AR24" s="86" t="n"/>
-      <c r="AS24" s="86" t="n"/>
-      <c r="AT24" s="86" t="n"/>
-      <c r="AU24" s="86" t="n"/>
-      <c r="AV24" s="86" t="n"/>
-      <c r="AW24" s="86" t="n"/>
-      <c r="AX24" s="86" t="n"/>
-      <c r="AY24" s="86" t="n"/>
-      <c r="AZ24" s="86" t="n"/>
-      <c r="BA24" s="86" t="n"/>
-      <c r="BB24" s="86" t="n"/>
-      <c r="BC24" s="86" t="n"/>
-      <c r="BD24" s="87" t="n"/>
+      <c r="AM24" s="149" t="n"/>
+      <c r="AN24" s="149" t="n"/>
+      <c r="AO24" s="149" t="n"/>
+      <c r="AP24" s="149" t="n"/>
+      <c r="AQ24" s="149" t="n"/>
+      <c r="AR24" s="149" t="n"/>
+      <c r="AS24" s="149" t="n"/>
+      <c r="AT24" s="149" t="n"/>
+      <c r="AU24" s="149" t="n"/>
+      <c r="AV24" s="149" t="n"/>
+      <c r="AW24" s="149" t="n"/>
+      <c r="AX24" s="149" t="n"/>
+      <c r="AY24" s="149" t="n"/>
+      <c r="AZ24" s="149" t="n"/>
+      <c r="BA24" s="149" t="n"/>
+      <c r="BB24" s="149" t="n"/>
+      <c r="BC24" s="149" t="n"/>
+      <c r="BD24" s="166" t="n"/>
     </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="77" t="inlineStr">
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="167" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B25" s="96" t="n"/>
-      <c r="C25" s="96" t="n"/>
-      <c r="D25" s="96" t="n"/>
-      <c r="E25" s="96" t="n"/>
-      <c r="F25" s="96" t="n"/>
-      <c r="G25" s="96" t="n"/>
-      <c r="H25" s="96" t="n"/>
-      <c r="I25" s="96" t="n"/>
-      <c r="J25" s="96" t="n"/>
-      <c r="K25" s="96" t="n"/>
-      <c r="L25" s="96" t="n"/>
-      <c r="M25" s="96" t="n"/>
-      <c r="N25" s="96" t="n"/>
-      <c r="O25" s="96" t="n"/>
-      <c r="P25" s="96" t="n"/>
-      <c r="Q25" s="96" t="n"/>
-      <c r="R25" s="97" t="n"/>
-      <c r="S25" s="77" t="inlineStr">
+      <c r="B25" s="161" t="n"/>
+      <c r="C25" s="161" t="n"/>
+      <c r="D25" s="161" t="n"/>
+      <c r="E25" s="161" t="n"/>
+      <c r="F25" s="161" t="n"/>
+      <c r="G25" s="161" t="n"/>
+      <c r="H25" s="161" t="n"/>
+      <c r="I25" s="161" t="n"/>
+      <c r="J25" s="161" t="n"/>
+      <c r="K25" s="161" t="n"/>
+      <c r="L25" s="161" t="n"/>
+      <c r="M25" s="161" t="n"/>
+      <c r="N25" s="161" t="n"/>
+      <c r="O25" s="161" t="n"/>
+      <c r="P25" s="161" t="n"/>
+      <c r="Q25" s="161" t="n"/>
+      <c r="R25" s="161" t="n"/>
+      <c r="S25" s="168" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="T25" s="96" t="n"/>
-      <c r="U25" s="96" t="n"/>
-      <c r="V25" s="96" t="n"/>
-      <c r="W25" s="96" t="n"/>
-      <c r="X25" s="96" t="n"/>
-      <c r="Y25" s="96" t="n"/>
-      <c r="Z25" s="96" t="n"/>
-      <c r="AA25" s="96" t="n"/>
-      <c r="AB25" s="96" t="n"/>
-      <c r="AC25" s="96" t="n"/>
-      <c r="AD25" s="96" t="n"/>
-      <c r="AE25" s="96" t="n"/>
-      <c r="AF25" s="96" t="n"/>
-      <c r="AG25" s="96" t="n"/>
-      <c r="AH25" s="96" t="n"/>
-      <c r="AI25" s="96" t="n"/>
-      <c r="AJ25" s="96" t="n"/>
-      <c r="AK25" s="97" t="n"/>
-      <c r="AL25" s="77" t="inlineStr">
+      <c r="T25" s="161" t="n"/>
+      <c r="U25" s="161" t="n"/>
+      <c r="V25" s="161" t="n"/>
+      <c r="W25" s="161" t="n"/>
+      <c r="X25" s="161" t="n"/>
+      <c r="Y25" s="161" t="n"/>
+      <c r="Z25" s="161" t="n"/>
+      <c r="AA25" s="161" t="n"/>
+      <c r="AB25" s="161" t="n"/>
+      <c r="AC25" s="161" t="n"/>
+      <c r="AD25" s="161" t="n"/>
+      <c r="AE25" s="161" t="n"/>
+      <c r="AF25" s="161" t="n"/>
+      <c r="AG25" s="161" t="n"/>
+      <c r="AH25" s="161" t="n"/>
+      <c r="AI25" s="161" t="n"/>
+      <c r="AJ25" s="161" t="n"/>
+      <c r="AK25" s="161" t="n"/>
+      <c r="AL25" s="168" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AM25" s="96" t="n"/>
-      <c r="AN25" s="96" t="n"/>
-      <c r="AO25" s="96" t="n"/>
-      <c r="AP25" s="96" t="n"/>
-      <c r="AQ25" s="96" t="n"/>
-      <c r="AR25" s="96" t="n"/>
-      <c r="AS25" s="96" t="n"/>
-      <c r="AT25" s="96" t="n"/>
-      <c r="AU25" s="96" t="n"/>
-      <c r="AV25" s="96" t="n"/>
-      <c r="AW25" s="96" t="n"/>
-      <c r="AX25" s="96" t="n"/>
-      <c r="AY25" s="96" t="n"/>
-      <c r="AZ25" s="96" t="n"/>
-      <c r="BA25" s="96" t="n"/>
-      <c r="BB25" s="96" t="n"/>
-      <c r="BC25" s="96" t="n"/>
-      <c r="BD25" s="97" t="n"/>
+      <c r="AM25" s="161" t="n"/>
+      <c r="AN25" s="161" t="n"/>
+      <c r="AO25" s="161" t="n"/>
+      <c r="AP25" s="161" t="n"/>
+      <c r="AQ25" s="161" t="n"/>
+      <c r="AR25" s="161" t="n"/>
+      <c r="AS25" s="161" t="n"/>
+      <c r="AT25" s="161" t="n"/>
+      <c r="AU25" s="161" t="n"/>
+      <c r="AV25" s="161" t="n"/>
+      <c r="AW25" s="161" t="n"/>
+      <c r="AX25" s="161" t="n"/>
+      <c r="AY25" s="161" t="n"/>
+      <c r="AZ25" s="161" t="n"/>
+      <c r="BA25" s="161" t="n"/>
+      <c r="BB25" s="161" t="n"/>
+      <c r="BC25" s="161" t="n"/>
+      <c r="BD25" s="163" t="n"/>
     </row>
-    <row r="26" ht="4" customHeight="1">
+    <row r="26" ht="3" customHeight="1">
       <c r="A26" s="66" t="n"/>
       <c r="B26" s="66" t="n"/>
       <c r="C26" s="66" t="n"/>
@@ -2996,67 +3760,67 @@
       <c r="BC26" s="66" t="n"/>
       <c r="BD26" s="66" t="n"/>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="78" t="inlineStr">
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="145" t="inlineStr">
         <is>
           <t>NOTICE: Training plans shall state the required skill, current gap, target level, method, trainer, schedule, expected evidence and follow-up date; do not plan training without a clear competence outcome.</t>
         </is>
       </c>
-      <c r="B27" s="86" t="n"/>
-      <c r="C27" s="86" t="n"/>
-      <c r="D27" s="86" t="n"/>
-      <c r="E27" s="86" t="n"/>
-      <c r="F27" s="86" t="n"/>
-      <c r="G27" s="86" t="n"/>
-      <c r="H27" s="86" t="n"/>
-      <c r="I27" s="86" t="n"/>
-      <c r="J27" s="86" t="n"/>
-      <c r="K27" s="86" t="n"/>
-      <c r="L27" s="86" t="n"/>
-      <c r="M27" s="86" t="n"/>
-      <c r="N27" s="86" t="n"/>
-      <c r="O27" s="86" t="n"/>
-      <c r="P27" s="86" t="n"/>
-      <c r="Q27" s="86" t="n"/>
-      <c r="R27" s="86" t="n"/>
-      <c r="S27" s="86" t="n"/>
-      <c r="T27" s="86" t="n"/>
-      <c r="U27" s="86" t="n"/>
-      <c r="V27" s="86" t="n"/>
-      <c r="W27" s="86" t="n"/>
-      <c r="X27" s="86" t="n"/>
-      <c r="Y27" s="86" t="n"/>
-      <c r="Z27" s="86" t="n"/>
-      <c r="AA27" s="86" t="n"/>
-      <c r="AB27" s="86" t="n"/>
-      <c r="AC27" s="86" t="n"/>
-      <c r="AD27" s="86" t="n"/>
-      <c r="AE27" s="86" t="n"/>
-      <c r="AF27" s="86" t="n"/>
-      <c r="AG27" s="86" t="n"/>
-      <c r="AH27" s="86" t="n"/>
-      <c r="AI27" s="86" t="n"/>
-      <c r="AJ27" s="86" t="n"/>
-      <c r="AK27" s="86" t="n"/>
-      <c r="AL27" s="86" t="n"/>
-      <c r="AM27" s="86" t="n"/>
-      <c r="AN27" s="86" t="n"/>
-      <c r="AO27" s="86" t="n"/>
-      <c r="AP27" s="86" t="n"/>
-      <c r="AQ27" s="86" t="n"/>
-      <c r="AR27" s="86" t="n"/>
-      <c r="AS27" s="86" t="n"/>
-      <c r="AT27" s="86" t="n"/>
-      <c r="AU27" s="86" t="n"/>
-      <c r="AV27" s="86" t="n"/>
-      <c r="AW27" s="86" t="n"/>
-      <c r="AX27" s="86" t="n"/>
-      <c r="AY27" s="86" t="n"/>
-      <c r="AZ27" s="86" t="n"/>
-      <c r="BA27" s="86" t="n"/>
-      <c r="BB27" s="86" t="n"/>
-      <c r="BC27" s="86" t="n"/>
-      <c r="BD27" s="87" t="n"/>
+      <c r="B27" s="146" t="n"/>
+      <c r="C27" s="146" t="n"/>
+      <c r="D27" s="146" t="n"/>
+      <c r="E27" s="146" t="n"/>
+      <c r="F27" s="146" t="n"/>
+      <c r="G27" s="146" t="n"/>
+      <c r="H27" s="146" t="n"/>
+      <c r="I27" s="146" t="n"/>
+      <c r="J27" s="146" t="n"/>
+      <c r="K27" s="146" t="n"/>
+      <c r="L27" s="146" t="n"/>
+      <c r="M27" s="146" t="n"/>
+      <c r="N27" s="146" t="n"/>
+      <c r="O27" s="146" t="n"/>
+      <c r="P27" s="146" t="n"/>
+      <c r="Q27" s="146" t="n"/>
+      <c r="R27" s="146" t="n"/>
+      <c r="S27" s="146" t="n"/>
+      <c r="T27" s="146" t="n"/>
+      <c r="U27" s="146" t="n"/>
+      <c r="V27" s="146" t="n"/>
+      <c r="W27" s="146" t="n"/>
+      <c r="X27" s="146" t="n"/>
+      <c r="Y27" s="146" t="n"/>
+      <c r="Z27" s="146" t="n"/>
+      <c r="AA27" s="146" t="n"/>
+      <c r="AB27" s="146" t="n"/>
+      <c r="AC27" s="146" t="n"/>
+      <c r="AD27" s="146" t="n"/>
+      <c r="AE27" s="146" t="n"/>
+      <c r="AF27" s="146" t="n"/>
+      <c r="AG27" s="146" t="n"/>
+      <c r="AH27" s="146" t="n"/>
+      <c r="AI27" s="146" t="n"/>
+      <c r="AJ27" s="146" t="n"/>
+      <c r="AK27" s="146" t="n"/>
+      <c r="AL27" s="146" t="n"/>
+      <c r="AM27" s="146" t="n"/>
+      <c r="AN27" s="146" t="n"/>
+      <c r="AO27" s="146" t="n"/>
+      <c r="AP27" s="146" t="n"/>
+      <c r="AQ27" s="146" t="n"/>
+      <c r="AR27" s="146" t="n"/>
+      <c r="AS27" s="146" t="n"/>
+      <c r="AT27" s="146" t="n"/>
+      <c r="AU27" s="146" t="n"/>
+      <c r="AV27" s="146" t="n"/>
+      <c r="AW27" s="146" t="n"/>
+      <c r="AX27" s="146" t="n"/>
+      <c r="AY27" s="146" t="n"/>
+      <c r="AZ27" s="146" t="n"/>
+      <c r="BA27" s="146" t="n"/>
+      <c r="BB27" s="146" t="n"/>
+      <c r="BC27" s="146" t="n"/>
+      <c r="BD27" s="147" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1"/>
     <row r="29" ht="20" customHeight="1"/>
@@ -3232,7 +3996,7 @@
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="75">
+  <mergeCells count="74">
     <mergeCell ref="L4:AP4"/>
     <mergeCell ref="AC10:AL10"/>
     <mergeCell ref="K11:AB11"/>
@@ -3274,7 +4038,6 @@
     <mergeCell ref="K17:AB17"/>
     <mergeCell ref="A11:J11"/>
     <mergeCell ref="S25:AK25"/>
-    <mergeCell ref="A6:BD6"/>
     <mergeCell ref="AW5:BD5"/>
     <mergeCell ref="AC13:AL13"/>
     <mergeCell ref="AC18:AL18"/>
@@ -3341,6 +4104,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3412,1196 +4176,1286 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="50" t="n"/>
-      <c r="B1" s="99" t="n"/>
-      <c r="C1" s="99" t="n"/>
-      <c r="D1" s="99" t="n"/>
-      <c r="E1" s="99" t="n"/>
-      <c r="F1" s="99" t="n"/>
-      <c r="G1" s="99" t="n"/>
-      <c r="H1" s="99" t="n"/>
-      <c r="I1" s="99" t="n"/>
-      <c r="J1" s="99" t="n"/>
-      <c r="K1" s="99" t="n"/>
-      <c r="L1" s="52" t="inlineStr">
+      <c r="A1" s="106" t="n"/>
+      <c r="B1" s="107" t="n"/>
+      <c r="C1" s="107" t="n"/>
+      <c r="D1" s="107" t="n"/>
+      <c r="E1" s="107" t="n"/>
+      <c r="F1" s="107" t="n"/>
+      <c r="G1" s="107" t="n"/>
+      <c r="H1" s="107" t="n"/>
+      <c r="I1" s="107" t="n"/>
+      <c r="J1" s="107" t="n"/>
+      <c r="K1" s="108" t="n"/>
+      <c r="L1" s="109" t="inlineStr">
         <is>
           <t>TRAINING PLAN — TARGETS / RESOURCES</t>
         </is>
       </c>
-      <c r="M1" s="99" t="n"/>
-      <c r="N1" s="99" t="n"/>
-      <c r="O1" s="99" t="n"/>
-      <c r="P1" s="99" t="n"/>
-      <c r="Q1" s="99" t="n"/>
-      <c r="R1" s="99" t="n"/>
-      <c r="S1" s="99" t="n"/>
-      <c r="T1" s="99" t="n"/>
-      <c r="U1" s="99" t="n"/>
-      <c r="V1" s="99" t="n"/>
-      <c r="W1" s="99" t="n"/>
-      <c r="X1" s="99" t="n"/>
-      <c r="Y1" s="99" t="n"/>
-      <c r="Z1" s="99" t="n"/>
-      <c r="AA1" s="99" t="n"/>
-      <c r="AB1" s="99" t="n"/>
-      <c r="AC1" s="99" t="n"/>
-      <c r="AD1" s="99" t="n"/>
-      <c r="AE1" s="99" t="n"/>
-      <c r="AF1" s="99" t="n"/>
-      <c r="AG1" s="99" t="n"/>
-      <c r="AH1" s="99" t="n"/>
-      <c r="AI1" s="99" t="n"/>
-      <c r="AJ1" s="99" t="n"/>
-      <c r="AK1" s="99" t="n"/>
-      <c r="AL1" s="99" t="n"/>
-      <c r="AM1" s="99" t="n"/>
-      <c r="AN1" s="99" t="n"/>
-      <c r="AO1" s="99" t="n"/>
-      <c r="AP1" s="99" t="n"/>
-      <c r="AQ1" s="53" t="inlineStr">
+      <c r="M1" s="110" t="n"/>
+      <c r="N1" s="110" t="n"/>
+      <c r="O1" s="110" t="n"/>
+      <c r="P1" s="110" t="n"/>
+      <c r="Q1" s="110" t="n"/>
+      <c r="R1" s="110" t="n"/>
+      <c r="S1" s="110" t="n"/>
+      <c r="T1" s="110" t="n"/>
+      <c r="U1" s="110" t="n"/>
+      <c r="V1" s="110" t="n"/>
+      <c r="W1" s="110" t="n"/>
+      <c r="X1" s="110" t="n"/>
+      <c r="Y1" s="110" t="n"/>
+      <c r="Z1" s="110" t="n"/>
+      <c r="AA1" s="110" t="n"/>
+      <c r="AB1" s="110" t="n"/>
+      <c r="AC1" s="110" t="n"/>
+      <c r="AD1" s="110" t="n"/>
+      <c r="AE1" s="110" t="n"/>
+      <c r="AF1" s="110" t="n"/>
+      <c r="AG1" s="110" t="n"/>
+      <c r="AH1" s="110" t="n"/>
+      <c r="AI1" s="110" t="n"/>
+      <c r="AJ1" s="110" t="n"/>
+      <c r="AK1" s="110" t="n"/>
+      <c r="AL1" s="110" t="n"/>
+      <c r="AM1" s="110" t="n"/>
+      <c r="AN1" s="110" t="n"/>
+      <c r="AO1" s="110" t="n"/>
+      <c r="AP1" s="111" t="n"/>
+      <c r="AQ1" s="112" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="100" t="n"/>
-      <c r="AS1" s="100" t="n"/>
-      <c r="AT1" s="100" t="n"/>
-      <c r="AU1" s="100" t="n"/>
-      <c r="AV1" s="101" t="n"/>
-      <c r="AW1" s="56" t="inlineStr">
+      <c r="AR1" s="113" t="n"/>
+      <c r="AS1" s="113" t="n"/>
+      <c r="AT1" s="113" t="n"/>
+      <c r="AU1" s="113" t="n"/>
+      <c r="AV1" s="114" t="n"/>
+      <c r="AW1" s="115" t="inlineStr">
         <is>
           <t>FRM-801</t>
         </is>
       </c>
-      <c r="AX1" s="100" t="n"/>
-      <c r="AY1" s="100" t="n"/>
-      <c r="AZ1" s="100" t="n"/>
-      <c r="BA1" s="100" t="n"/>
-      <c r="BB1" s="100" t="n"/>
-      <c r="BC1" s="100" t="n"/>
-      <c r="BD1" s="101" t="n"/>
+      <c r="AX1" s="116" t="n"/>
+      <c r="AY1" s="116" t="n"/>
+      <c r="AZ1" s="116" t="n"/>
+      <c r="BA1" s="116" t="n"/>
+      <c r="BB1" s="116" t="n"/>
+      <c r="BC1" s="116" t="n"/>
+      <c r="BD1" s="117" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="102" t="n"/>
-      <c r="L2" s="102" t="n"/>
-      <c r="AQ2" s="59" t="inlineStr">
+      <c r="A2" s="118" t="n"/>
+      <c r="B2" s="46" t="n"/>
+      <c r="C2" s="46" t="n"/>
+      <c r="D2" s="46" t="n"/>
+      <c r="E2" s="46" t="n"/>
+      <c r="F2" s="46" t="n"/>
+      <c r="G2" s="46" t="n"/>
+      <c r="H2" s="46" t="n"/>
+      <c r="I2" s="46" t="n"/>
+      <c r="J2" s="46" t="n"/>
+      <c r="K2" s="119" t="n"/>
+      <c r="L2" s="120" t="n"/>
+      <c r="M2" s="121" t="n"/>
+      <c r="N2" s="121" t="n"/>
+      <c r="O2" s="121" t="n"/>
+      <c r="P2" s="121" t="n"/>
+      <c r="Q2" s="121" t="n"/>
+      <c r="R2" s="121" t="n"/>
+      <c r="S2" s="121" t="n"/>
+      <c r="T2" s="121" t="n"/>
+      <c r="U2" s="121" t="n"/>
+      <c r="V2" s="121" t="n"/>
+      <c r="W2" s="121" t="n"/>
+      <c r="X2" s="121" t="n"/>
+      <c r="Y2" s="121" t="n"/>
+      <c r="Z2" s="121" t="n"/>
+      <c r="AA2" s="121" t="n"/>
+      <c r="AB2" s="121" t="n"/>
+      <c r="AC2" s="121" t="n"/>
+      <c r="AD2" s="121" t="n"/>
+      <c r="AE2" s="121" t="n"/>
+      <c r="AF2" s="121" t="n"/>
+      <c r="AG2" s="121" t="n"/>
+      <c r="AH2" s="121" t="n"/>
+      <c r="AI2" s="121" t="n"/>
+      <c r="AJ2" s="121" t="n"/>
+      <c r="AK2" s="121" t="n"/>
+      <c r="AL2" s="121" t="n"/>
+      <c r="AM2" s="121" t="n"/>
+      <c r="AN2" s="121" t="n"/>
+      <c r="AO2" s="121" t="n"/>
+      <c r="AP2" s="122" t="n"/>
+      <c r="AQ2" s="123" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="103" t="n"/>
-      <c r="AS2" s="103" t="n"/>
-      <c r="AT2" s="103" t="n"/>
-      <c r="AU2" s="103" t="n"/>
-      <c r="AV2" s="104" t="n"/>
-      <c r="AW2" s="62" t="inlineStr">
+      <c r="AR2" s="124" t="n"/>
+      <c r="AS2" s="124" t="n"/>
+      <c r="AT2" s="124" t="n"/>
+      <c r="AU2" s="124" t="n"/>
+      <c r="AV2" s="125" t="n"/>
+      <c r="AW2" s="126" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="103" t="n"/>
-      <c r="AY2" s="103" t="n"/>
-      <c r="AZ2" s="103" t="n"/>
-      <c r="BA2" s="103" t="n"/>
-      <c r="BB2" s="103" t="n"/>
-      <c r="BC2" s="103" t="n"/>
-      <c r="BD2" s="104" t="n"/>
+      <c r="AX2" s="127" t="n"/>
+      <c r="AY2" s="127" t="n"/>
+      <c r="AZ2" s="127" t="n"/>
+      <c r="BA2" s="127" t="n"/>
+      <c r="BB2" s="127" t="n"/>
+      <c r="BC2" s="127" t="n"/>
+      <c r="BD2" s="128" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="102" t="n"/>
-      <c r="L3" s="105" t="n"/>
-      <c r="M3" s="103" t="n"/>
-      <c r="N3" s="103" t="n"/>
-      <c r="O3" s="103" t="n"/>
-      <c r="P3" s="103" t="n"/>
-      <c r="Q3" s="103" t="n"/>
-      <c r="R3" s="103" t="n"/>
-      <c r="S3" s="103" t="n"/>
-      <c r="T3" s="103" t="n"/>
-      <c r="U3" s="103" t="n"/>
-      <c r="V3" s="103" t="n"/>
-      <c r="W3" s="103" t="n"/>
-      <c r="X3" s="103" t="n"/>
-      <c r="Y3" s="103" t="n"/>
-      <c r="Z3" s="103" t="n"/>
-      <c r="AA3" s="103" t="n"/>
-      <c r="AB3" s="103" t="n"/>
-      <c r="AC3" s="103" t="n"/>
-      <c r="AD3" s="103" t="n"/>
-      <c r="AE3" s="103" t="n"/>
-      <c r="AF3" s="103" t="n"/>
-      <c r="AG3" s="103" t="n"/>
-      <c r="AH3" s="103" t="n"/>
-      <c r="AI3" s="103" t="n"/>
-      <c r="AJ3" s="103" t="n"/>
-      <c r="AK3" s="103" t="n"/>
-      <c r="AL3" s="103" t="n"/>
-      <c r="AM3" s="103" t="n"/>
-      <c r="AN3" s="103" t="n"/>
-      <c r="AO3" s="103" t="n"/>
-      <c r="AP3" s="103" t="n"/>
-      <c r="AQ3" s="59" t="inlineStr">
+      <c r="A3" s="118" t="n"/>
+      <c r="B3" s="46" t="n"/>
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="46" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="46" t="n"/>
+      <c r="G3" s="46" t="n"/>
+      <c r="H3" s="46" t="n"/>
+      <c r="I3" s="46" t="n"/>
+      <c r="J3" s="46" t="n"/>
+      <c r="K3" s="119" t="n"/>
+      <c r="L3" s="120" t="n"/>
+      <c r="M3" s="121" t="n"/>
+      <c r="N3" s="121" t="n"/>
+      <c r="O3" s="121" t="n"/>
+      <c r="P3" s="121" t="n"/>
+      <c r="Q3" s="121" t="n"/>
+      <c r="R3" s="121" t="n"/>
+      <c r="S3" s="121" t="n"/>
+      <c r="T3" s="121" t="n"/>
+      <c r="U3" s="121" t="n"/>
+      <c r="V3" s="121" t="n"/>
+      <c r="W3" s="121" t="n"/>
+      <c r="X3" s="121" t="n"/>
+      <c r="Y3" s="121" t="n"/>
+      <c r="Z3" s="121" t="n"/>
+      <c r="AA3" s="121" t="n"/>
+      <c r="AB3" s="121" t="n"/>
+      <c r="AC3" s="121" t="n"/>
+      <c r="AD3" s="121" t="n"/>
+      <c r="AE3" s="121" t="n"/>
+      <c r="AF3" s="121" t="n"/>
+      <c r="AG3" s="121" t="n"/>
+      <c r="AH3" s="121" t="n"/>
+      <c r="AI3" s="121" t="n"/>
+      <c r="AJ3" s="121" t="n"/>
+      <c r="AK3" s="121" t="n"/>
+      <c r="AL3" s="121" t="n"/>
+      <c r="AM3" s="121" t="n"/>
+      <c r="AN3" s="121" t="n"/>
+      <c r="AO3" s="121" t="n"/>
+      <c r="AP3" s="122" t="n"/>
+      <c r="AQ3" s="123" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="103" t="n"/>
-      <c r="AS3" s="103" t="n"/>
-      <c r="AT3" s="103" t="n"/>
-      <c r="AU3" s="103" t="n"/>
-      <c r="AV3" s="104" t="n"/>
-      <c r="AW3" s="62" t="inlineStr">
+      <c r="AR3" s="124" t="n"/>
+      <c r="AS3" s="124" t="n"/>
+      <c r="AT3" s="124" t="n"/>
+      <c r="AU3" s="124" t="n"/>
+      <c r="AV3" s="125" t="n"/>
+      <c r="AW3" s="126" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="103" t="n"/>
-      <c r="AY3" s="103" t="n"/>
-      <c r="AZ3" s="103" t="n"/>
-      <c r="BA3" s="103" t="n"/>
-      <c r="BB3" s="103" t="n"/>
-      <c r="BC3" s="103" t="n"/>
-      <c r="BD3" s="104" t="n"/>
+      <c r="AX3" s="127" t="n"/>
+      <c r="AY3" s="127" t="n"/>
+      <c r="AZ3" s="127" t="n"/>
+      <c r="BA3" s="127" t="n"/>
+      <c r="BB3" s="127" t="n"/>
+      <c r="BC3" s="127" t="n"/>
+      <c r="BD3" s="128" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="102" t="n"/>
-      <c r="L4" s="64" t="inlineStr">
+      <c r="A4" s="118" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
+      <c r="I4" s="46" t="n"/>
+      <c r="J4" s="46" t="n"/>
+      <c r="K4" s="119" t="n"/>
+      <c r="L4" s="129" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="59" t="inlineStr">
+      <c r="M4" s="130" t="n"/>
+      <c r="N4" s="130" t="n"/>
+      <c r="O4" s="130" t="n"/>
+      <c r="P4" s="130" t="n"/>
+      <c r="Q4" s="130" t="n"/>
+      <c r="R4" s="130" t="n"/>
+      <c r="S4" s="130" t="n"/>
+      <c r="T4" s="130" t="n"/>
+      <c r="U4" s="130" t="n"/>
+      <c r="V4" s="130" t="n"/>
+      <c r="W4" s="130" t="n"/>
+      <c r="X4" s="130" t="n"/>
+      <c r="Y4" s="130" t="n"/>
+      <c r="Z4" s="130" t="n"/>
+      <c r="AA4" s="130" t="n"/>
+      <c r="AB4" s="130" t="n"/>
+      <c r="AC4" s="130" t="n"/>
+      <c r="AD4" s="130" t="n"/>
+      <c r="AE4" s="130" t="n"/>
+      <c r="AF4" s="130" t="n"/>
+      <c r="AG4" s="130" t="n"/>
+      <c r="AH4" s="130" t="n"/>
+      <c r="AI4" s="130" t="n"/>
+      <c r="AJ4" s="130" t="n"/>
+      <c r="AK4" s="130" t="n"/>
+      <c r="AL4" s="130" t="n"/>
+      <c r="AM4" s="130" t="n"/>
+      <c r="AN4" s="130" t="n"/>
+      <c r="AO4" s="130" t="n"/>
+      <c r="AP4" s="131" t="n"/>
+      <c r="AQ4" s="123" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="103" t="n"/>
-      <c r="AS4" s="103" t="n"/>
-      <c r="AT4" s="103" t="n"/>
-      <c r="AU4" s="103" t="n"/>
-      <c r="AV4" s="104" t="n"/>
-      <c r="AW4" s="62" t="inlineStr">
+      <c r="AR4" s="124" t="n"/>
+      <c r="AS4" s="124" t="n"/>
+      <c r="AT4" s="124" t="n"/>
+      <c r="AU4" s="124" t="n"/>
+      <c r="AV4" s="125" t="n"/>
+      <c r="AW4" s="126" t="inlineStr">
         <is>
           <t>HR + Department Manager</t>
         </is>
       </c>
-      <c r="AX4" s="103" t="n"/>
-      <c r="AY4" s="103" t="n"/>
-      <c r="AZ4" s="103" t="n"/>
-      <c r="BA4" s="103" t="n"/>
-      <c r="BB4" s="103" t="n"/>
-      <c r="BC4" s="103" t="n"/>
-      <c r="BD4" s="104" t="n"/>
+      <c r="AX4" s="127" t="n"/>
+      <c r="AY4" s="127" t="n"/>
+      <c r="AZ4" s="127" t="n"/>
+      <c r="BA4" s="127" t="n"/>
+      <c r="BB4" s="127" t="n"/>
+      <c r="BC4" s="127" t="n"/>
+      <c r="BD4" s="128" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="105" t="n"/>
-      <c r="B5" s="103" t="n"/>
-      <c r="C5" s="103" t="n"/>
-      <c r="D5" s="103" t="n"/>
-      <c r="E5" s="103" t="n"/>
-      <c r="F5" s="103" t="n"/>
-      <c r="G5" s="103" t="n"/>
-      <c r="H5" s="103" t="n"/>
-      <c r="I5" s="103" t="n"/>
-      <c r="J5" s="103" t="n"/>
-      <c r="K5" s="103" t="n"/>
-      <c r="L5" s="65" t="inlineStr">
+      <c r="A5" s="132" t="n"/>
+      <c r="B5" s="133" t="n"/>
+      <c r="C5" s="133" t="n"/>
+      <c r="D5" s="133" t="n"/>
+      <c r="E5" s="133" t="n"/>
+      <c r="F5" s="133" t="n"/>
+      <c r="G5" s="133" t="n"/>
+      <c r="H5" s="133" t="n"/>
+      <c r="I5" s="133" t="n"/>
+      <c r="J5" s="133" t="n"/>
+      <c r="K5" s="134" t="n"/>
+      <c r="L5" s="135" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="103" t="n"/>
-      <c r="N5" s="103" t="n"/>
-      <c r="O5" s="103" t="n"/>
-      <c r="P5" s="103" t="n"/>
-      <c r="Q5" s="103" t="n"/>
-      <c r="R5" s="103" t="n"/>
-      <c r="S5" s="103" t="n"/>
-      <c r="T5" s="103" t="n"/>
-      <c r="U5" s="103" t="n"/>
-      <c r="V5" s="103" t="n"/>
-      <c r="W5" s="103" t="n"/>
-      <c r="X5" s="103" t="n"/>
-      <c r="Y5" s="103" t="n"/>
-      <c r="Z5" s="103" t="n"/>
-      <c r="AA5" s="103" t="n"/>
-      <c r="AB5" s="103" t="n"/>
-      <c r="AC5" s="103" t="n"/>
-      <c r="AD5" s="103" t="n"/>
-      <c r="AE5" s="103" t="n"/>
-      <c r="AF5" s="103" t="n"/>
-      <c r="AG5" s="103" t="n"/>
-      <c r="AH5" s="103" t="n"/>
-      <c r="AI5" s="103" t="n"/>
-      <c r="AJ5" s="103" t="n"/>
-      <c r="AK5" s="103" t="n"/>
-      <c r="AL5" s="103" t="n"/>
-      <c r="AM5" s="103" t="n"/>
-      <c r="AN5" s="103" t="n"/>
-      <c r="AO5" s="103" t="n"/>
-      <c r="AP5" s="103" t="n"/>
-      <c r="AQ5" s="59" t="inlineStr">
+      <c r="M5" s="136" t="n"/>
+      <c r="N5" s="136" t="n"/>
+      <c r="O5" s="136" t="n"/>
+      <c r="P5" s="136" t="n"/>
+      <c r="Q5" s="136" t="n"/>
+      <c r="R5" s="136" t="n"/>
+      <c r="S5" s="136" t="n"/>
+      <c r="T5" s="136" t="n"/>
+      <c r="U5" s="136" t="n"/>
+      <c r="V5" s="136" t="n"/>
+      <c r="W5" s="136" t="n"/>
+      <c r="X5" s="136" t="n"/>
+      <c r="Y5" s="136" t="n"/>
+      <c r="Z5" s="136" t="n"/>
+      <c r="AA5" s="136" t="n"/>
+      <c r="AB5" s="136" t="n"/>
+      <c r="AC5" s="136" t="n"/>
+      <c r="AD5" s="136" t="n"/>
+      <c r="AE5" s="136" t="n"/>
+      <c r="AF5" s="136" t="n"/>
+      <c r="AG5" s="136" t="n"/>
+      <c r="AH5" s="136" t="n"/>
+      <c r="AI5" s="136" t="n"/>
+      <c r="AJ5" s="136" t="n"/>
+      <c r="AK5" s="136" t="n"/>
+      <c r="AL5" s="136" t="n"/>
+      <c r="AM5" s="136" t="n"/>
+      <c r="AN5" s="136" t="n"/>
+      <c r="AO5" s="136" t="n"/>
+      <c r="AP5" s="137" t="n"/>
+      <c r="AQ5" s="138" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="103" t="n"/>
-      <c r="AS5" s="103" t="n"/>
-      <c r="AT5" s="103" t="n"/>
-      <c r="AU5" s="103" t="n"/>
-      <c r="AV5" s="104" t="n"/>
-      <c r="AW5" s="62" t="inlineStr">
+      <c r="AR5" s="139" t="n"/>
+      <c r="AS5" s="139" t="n"/>
+      <c r="AT5" s="139" t="n"/>
+      <c r="AU5" s="139" t="n"/>
+      <c r="AV5" s="140" t="n"/>
+      <c r="AW5" s="141" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="103" t="n"/>
-      <c r="AY5" s="103" t="n"/>
-      <c r="AZ5" s="103" t="n"/>
-      <c r="BA5" s="103" t="n"/>
-      <c r="BB5" s="103" t="n"/>
-      <c r="BC5" s="103" t="n"/>
-      <c r="BD5" s="104" t="n"/>
+      <c r="AX5" s="142" t="n"/>
+      <c r="AY5" s="142" t="n"/>
+      <c r="AZ5" s="142" t="n"/>
+      <c r="BA5" s="142" t="n"/>
+      <c r="BB5" s="142" t="n"/>
+      <c r="BC5" s="142" t="n"/>
+      <c r="BD5" s="143" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="66" t="n"/>
-      <c r="B6" s="98" t="n"/>
-      <c r="C6" s="98" t="n"/>
-      <c r="D6" s="98" t="n"/>
-      <c r="E6" s="98" t="n"/>
-      <c r="F6" s="98" t="n"/>
-      <c r="G6" s="98" t="n"/>
-      <c r="H6" s="98" t="n"/>
-      <c r="I6" s="98" t="n"/>
-      <c r="J6" s="98" t="n"/>
-      <c r="K6" s="98" t="n"/>
-      <c r="L6" s="98" t="n"/>
-      <c r="M6" s="98" t="n"/>
-      <c r="N6" s="98" t="n"/>
-      <c r="O6" s="98" t="n"/>
-      <c r="P6" s="98" t="n"/>
-      <c r="Q6" s="98" t="n"/>
-      <c r="R6" s="98" t="n"/>
-      <c r="S6" s="98" t="n"/>
-      <c r="T6" s="98" t="n"/>
-      <c r="U6" s="98" t="n"/>
-      <c r="V6" s="98" t="n"/>
-      <c r="W6" s="98" t="n"/>
-      <c r="X6" s="98" t="n"/>
-      <c r="Y6" s="98" t="n"/>
-      <c r="Z6" s="98" t="n"/>
-      <c r="AA6" s="98" t="n"/>
-      <c r="AB6" s="98" t="n"/>
-      <c r="AC6" s="98" t="n"/>
-      <c r="AD6" s="98" t="n"/>
-      <c r="AE6" s="98" t="n"/>
-      <c r="AF6" s="98" t="n"/>
-      <c r="AG6" s="98" t="n"/>
-      <c r="AH6" s="98" t="n"/>
-      <c r="AI6" s="98" t="n"/>
-      <c r="AJ6" s="98" t="n"/>
-      <c r="AK6" s="98" t="n"/>
-      <c r="AL6" s="98" t="n"/>
-      <c r="AM6" s="98" t="n"/>
-      <c r="AN6" s="98" t="n"/>
-      <c r="AO6" s="98" t="n"/>
-      <c r="AP6" s="98" t="n"/>
-      <c r="AQ6" s="98" t="n"/>
-      <c r="AR6" s="98" t="n"/>
-      <c r="AS6" s="98" t="n"/>
-      <c r="AT6" s="98" t="n"/>
-      <c r="AU6" s="98" t="n"/>
-      <c r="AV6" s="98" t="n"/>
-      <c r="AW6" s="98" t="n"/>
-      <c r="AX6" s="98" t="n"/>
-      <c r="AY6" s="98" t="n"/>
-      <c r="AZ6" s="98" t="n"/>
-      <c r="BA6" s="98" t="n"/>
-      <c r="BB6" s="98" t="n"/>
-      <c r="BC6" s="98" t="n"/>
-      <c r="BD6" s="98" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="144" t="n"/>
+      <c r="B6" s="144" t="n"/>
+      <c r="C6" s="144" t="n"/>
+      <c r="D6" s="144" t="n"/>
+      <c r="E6" s="144" t="n"/>
+      <c r="F6" s="144" t="n"/>
+      <c r="G6" s="144" t="n"/>
+      <c r="H6" s="144" t="n"/>
+      <c r="I6" s="144" t="n"/>
+      <c r="J6" s="144" t="n"/>
+      <c r="K6" s="144" t="n"/>
+      <c r="L6" s="144" t="n"/>
+      <c r="M6" s="144" t="n"/>
+      <c r="N6" s="144" t="n"/>
+      <c r="O6" s="144" t="n"/>
+      <c r="P6" s="144" t="n"/>
+      <c r="Q6" s="144" t="n"/>
+      <c r="R6" s="144" t="n"/>
+      <c r="S6" s="144" t="n"/>
+      <c r="T6" s="144" t="n"/>
+      <c r="U6" s="144" t="n"/>
+      <c r="V6" s="144" t="n"/>
+      <c r="W6" s="144" t="n"/>
+      <c r="X6" s="144" t="n"/>
+      <c r="Y6" s="144" t="n"/>
+      <c r="Z6" s="144" t="n"/>
+      <c r="AA6" s="144" t="n"/>
+      <c r="AB6" s="144" t="n"/>
+      <c r="AC6" s="144" t="n"/>
+      <c r="AD6" s="144" t="n"/>
+      <c r="AE6" s="144" t="n"/>
+      <c r="AF6" s="144" t="n"/>
+      <c r="AG6" s="144" t="n"/>
+      <c r="AH6" s="144" t="n"/>
+      <c r="AI6" s="144" t="n"/>
+      <c r="AJ6" s="144" t="n"/>
+      <c r="AK6" s="144" t="n"/>
+      <c r="AL6" s="144" t="n"/>
+      <c r="AM6" s="144" t="n"/>
+      <c r="AN6" s="144" t="n"/>
+      <c r="AO6" s="144" t="n"/>
+      <c r="AP6" s="144" t="n"/>
+      <c r="AQ6" s="144" t="n"/>
+      <c r="AR6" s="144" t="n"/>
+      <c r="AS6" s="144" t="n"/>
+      <c r="AT6" s="144" t="n"/>
+      <c r="AU6" s="144" t="n"/>
+      <c r="AV6" s="144" t="n"/>
+      <c r="AW6" s="144" t="n"/>
+      <c r="AX6" s="144" t="n"/>
+      <c r="AY6" s="144" t="n"/>
+      <c r="AZ6" s="144" t="n"/>
+      <c r="BA6" s="144" t="n"/>
+      <c r="BB6" s="144" t="n"/>
+      <c r="BC6" s="144" t="n"/>
+      <c r="BD6" s="144" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="67" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="145" t="inlineStr">
         <is>
           <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
         </is>
       </c>
-      <c r="B7" s="100" t="n"/>
-      <c r="C7" s="100" t="n"/>
-      <c r="D7" s="100" t="n"/>
-      <c r="E7" s="100" t="n"/>
-      <c r="F7" s="100" t="n"/>
-      <c r="G7" s="100" t="n"/>
-      <c r="H7" s="100" t="n"/>
-      <c r="I7" s="100" t="n"/>
-      <c r="J7" s="100" t="n"/>
-      <c r="K7" s="100" t="n"/>
-      <c r="L7" s="100" t="n"/>
-      <c r="M7" s="100" t="n"/>
-      <c r="N7" s="100" t="n"/>
-      <c r="O7" s="100" t="n"/>
-      <c r="P7" s="100" t="n"/>
-      <c r="Q7" s="100" t="n"/>
-      <c r="R7" s="100" t="n"/>
-      <c r="S7" s="100" t="n"/>
-      <c r="T7" s="100" t="n"/>
-      <c r="U7" s="100" t="n"/>
-      <c r="V7" s="100" t="n"/>
-      <c r="W7" s="100" t="n"/>
-      <c r="X7" s="100" t="n"/>
-      <c r="Y7" s="100" t="n"/>
-      <c r="Z7" s="100" t="n"/>
-      <c r="AA7" s="100" t="n"/>
-      <c r="AB7" s="100" t="n"/>
-      <c r="AC7" s="100" t="n"/>
-      <c r="AD7" s="100" t="n"/>
-      <c r="AE7" s="100" t="n"/>
-      <c r="AF7" s="100" t="n"/>
-      <c r="AG7" s="100" t="n"/>
-      <c r="AH7" s="100" t="n"/>
-      <c r="AI7" s="100" t="n"/>
-      <c r="AJ7" s="100" t="n"/>
-      <c r="AK7" s="100" t="n"/>
-      <c r="AL7" s="100" t="n"/>
-      <c r="AM7" s="100" t="n"/>
-      <c r="AN7" s="100" t="n"/>
-      <c r="AO7" s="100" t="n"/>
-      <c r="AP7" s="100" t="n"/>
-      <c r="AQ7" s="100" t="n"/>
-      <c r="AR7" s="100" t="n"/>
-      <c r="AS7" s="100" t="n"/>
-      <c r="AT7" s="100" t="n"/>
-      <c r="AU7" s="100" t="n"/>
-      <c r="AV7" s="100" t="n"/>
-      <c r="AW7" s="100" t="n"/>
-      <c r="AX7" s="100" t="n"/>
-      <c r="AY7" s="100" t="n"/>
-      <c r="AZ7" s="100" t="n"/>
-      <c r="BA7" s="100" t="n"/>
-      <c r="BB7" s="100" t="n"/>
-      <c r="BC7" s="100" t="n"/>
-      <c r="BD7" s="101" t="n"/>
+      <c r="B7" s="146" t="n"/>
+      <c r="C7" s="146" t="n"/>
+      <c r="D7" s="146" t="n"/>
+      <c r="E7" s="146" t="n"/>
+      <c r="F7" s="146" t="n"/>
+      <c r="G7" s="146" t="n"/>
+      <c r="H7" s="146" t="n"/>
+      <c r="I7" s="146" t="n"/>
+      <c r="J7" s="146" t="n"/>
+      <c r="K7" s="146" t="n"/>
+      <c r="L7" s="146" t="n"/>
+      <c r="M7" s="146" t="n"/>
+      <c r="N7" s="146" t="n"/>
+      <c r="O7" s="146" t="n"/>
+      <c r="P7" s="146" t="n"/>
+      <c r="Q7" s="146" t="n"/>
+      <c r="R7" s="146" t="n"/>
+      <c r="S7" s="146" t="n"/>
+      <c r="T7" s="146" t="n"/>
+      <c r="U7" s="146" t="n"/>
+      <c r="V7" s="146" t="n"/>
+      <c r="W7" s="146" t="n"/>
+      <c r="X7" s="146" t="n"/>
+      <c r="Y7" s="146" t="n"/>
+      <c r="Z7" s="146" t="n"/>
+      <c r="AA7" s="146" t="n"/>
+      <c r="AB7" s="146" t="n"/>
+      <c r="AC7" s="146" t="n"/>
+      <c r="AD7" s="146" t="n"/>
+      <c r="AE7" s="146" t="n"/>
+      <c r="AF7" s="146" t="n"/>
+      <c r="AG7" s="146" t="n"/>
+      <c r="AH7" s="146" t="n"/>
+      <c r="AI7" s="146" t="n"/>
+      <c r="AJ7" s="146" t="n"/>
+      <c r="AK7" s="146" t="n"/>
+      <c r="AL7" s="146" t="n"/>
+      <c r="AM7" s="146" t="n"/>
+      <c r="AN7" s="146" t="n"/>
+      <c r="AO7" s="146" t="n"/>
+      <c r="AP7" s="146" t="n"/>
+      <c r="AQ7" s="146" t="n"/>
+      <c r="AR7" s="146" t="n"/>
+      <c r="AS7" s="146" t="n"/>
+      <c r="AT7" s="146" t="n"/>
+      <c r="AU7" s="146" t="n"/>
+      <c r="AV7" s="146" t="n"/>
+      <c r="AW7" s="146" t="n"/>
+      <c r="AX7" s="146" t="n"/>
+      <c r="AY7" s="146" t="n"/>
+      <c r="AZ7" s="146" t="n"/>
+      <c r="BA7" s="146" t="n"/>
+      <c r="BB7" s="146" t="n"/>
+      <c r="BC7" s="146" t="n"/>
+      <c r="BD7" s="147" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="68" t="inlineStr">
+      <c r="A8" s="148" t="inlineStr">
         <is>
           <t>Source Links</t>
         </is>
       </c>
-      <c r="B8" s="92" t="n"/>
-      <c r="C8" s="92" t="n"/>
-      <c r="D8" s="92" t="n"/>
-      <c r="E8" s="92" t="n"/>
-      <c r="F8" s="92" t="n"/>
-      <c r="G8" s="92" t="n"/>
-      <c r="H8" s="92" t="n"/>
-      <c r="I8" s="92" t="n"/>
-      <c r="J8" s="93" t="n"/>
-      <c r="K8" s="79" t="inlineStr">
+      <c r="B8" s="149" t="n"/>
+      <c r="C8" s="149" t="n"/>
+      <c r="D8" s="149" t="n"/>
+      <c r="E8" s="149" t="n"/>
+      <c r="F8" s="149" t="n"/>
+      <c r="G8" s="149" t="n"/>
+      <c r="H8" s="149" t="n"/>
+      <c r="I8" s="149" t="n"/>
+      <c r="J8" s="149" t="n"/>
+      <c r="K8" s="169" t="inlineStr">
         <is>
           <t>SOP-801; WI-801 / WI-804; ANNEX-HR-001 + ANNEX-QMS-027 / 028</t>
         </is>
       </c>
-      <c r="L8" s="92" t="n"/>
-      <c r="M8" s="92" t="n"/>
-      <c r="N8" s="92" t="n"/>
-      <c r="O8" s="92" t="n"/>
-      <c r="P8" s="92" t="n"/>
-      <c r="Q8" s="92" t="n"/>
-      <c r="R8" s="92" t="n"/>
-      <c r="S8" s="92" t="n"/>
-      <c r="T8" s="92" t="n"/>
-      <c r="U8" s="92" t="n"/>
-      <c r="V8" s="92" t="n"/>
-      <c r="W8" s="92" t="n"/>
-      <c r="X8" s="92" t="n"/>
-      <c r="Y8" s="92" t="n"/>
-      <c r="Z8" s="92" t="n"/>
-      <c r="AA8" s="92" t="n"/>
-      <c r="AB8" s="92" t="n"/>
-      <c r="AC8" s="92" t="n"/>
-      <c r="AD8" s="92" t="n"/>
-      <c r="AE8" s="92" t="n"/>
-      <c r="AF8" s="92" t="n"/>
-      <c r="AG8" s="92" t="n"/>
-      <c r="AH8" s="92" t="n"/>
-      <c r="AI8" s="92" t="n"/>
-      <c r="AJ8" s="92" t="n"/>
-      <c r="AK8" s="92" t="n"/>
-      <c r="AL8" s="92" t="n"/>
-      <c r="AM8" s="92" t="n"/>
-      <c r="AN8" s="92" t="n"/>
-      <c r="AO8" s="92" t="n"/>
-      <c r="AP8" s="92" t="n"/>
-      <c r="AQ8" s="92" t="n"/>
-      <c r="AR8" s="92" t="n"/>
-      <c r="AS8" s="92" t="n"/>
-      <c r="AT8" s="92" t="n"/>
-      <c r="AU8" s="92" t="n"/>
-      <c r="AV8" s="92" t="n"/>
-      <c r="AW8" s="92" t="n"/>
-      <c r="AX8" s="92" t="n"/>
-      <c r="AY8" s="92" t="n"/>
-      <c r="AZ8" s="92" t="n"/>
-      <c r="BA8" s="92" t="n"/>
-      <c r="BB8" s="92" t="n"/>
-      <c r="BC8" s="92" t="n"/>
-      <c r="BD8" s="93" t="n"/>
+      <c r="L8" s="149" t="n"/>
+      <c r="M8" s="149" t="n"/>
+      <c r="N8" s="149" t="n"/>
+      <c r="O8" s="149" t="n"/>
+      <c r="P8" s="149" t="n"/>
+      <c r="Q8" s="149" t="n"/>
+      <c r="R8" s="149" t="n"/>
+      <c r="S8" s="149" t="n"/>
+      <c r="T8" s="149" t="n"/>
+      <c r="U8" s="149" t="n"/>
+      <c r="V8" s="149" t="n"/>
+      <c r="W8" s="149" t="n"/>
+      <c r="X8" s="149" t="n"/>
+      <c r="Y8" s="149" t="n"/>
+      <c r="Z8" s="149" t="n"/>
+      <c r="AA8" s="149" t="n"/>
+      <c r="AB8" s="149" t="n"/>
+      <c r="AC8" s="149" t="n"/>
+      <c r="AD8" s="149" t="n"/>
+      <c r="AE8" s="149" t="n"/>
+      <c r="AF8" s="149" t="n"/>
+      <c r="AG8" s="149" t="n"/>
+      <c r="AH8" s="149" t="n"/>
+      <c r="AI8" s="149" t="n"/>
+      <c r="AJ8" s="149" t="n"/>
+      <c r="AK8" s="149" t="n"/>
+      <c r="AL8" s="149" t="n"/>
+      <c r="AM8" s="149" t="n"/>
+      <c r="AN8" s="149" t="n"/>
+      <c r="AO8" s="149" t="n"/>
+      <c r="AP8" s="149" t="n"/>
+      <c r="AQ8" s="149" t="n"/>
+      <c r="AR8" s="149" t="n"/>
+      <c r="AS8" s="149" t="n"/>
+      <c r="AT8" s="149" t="n"/>
+      <c r="AU8" s="149" t="n"/>
+      <c r="AV8" s="149" t="n"/>
+      <c r="AW8" s="149" t="n"/>
+      <c r="AX8" s="149" t="n"/>
+      <c r="AY8" s="149" t="n"/>
+      <c r="AZ8" s="149" t="n"/>
+      <c r="BA8" s="149" t="n"/>
+      <c r="BB8" s="149" t="n"/>
+      <c r="BC8" s="149" t="n"/>
+      <c r="BD8" s="166" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="68" t="inlineStr">
+      <c r="A9" s="154" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="B9" s="92" t="n"/>
-      <c r="C9" s="92" t="n"/>
-      <c r="D9" s="92" t="n"/>
-      <c r="E9" s="92" t="n"/>
-      <c r="F9" s="92" t="n"/>
-      <c r="G9" s="92" t="n"/>
-      <c r="H9" s="92" t="n"/>
-      <c r="I9" s="92" t="n"/>
-      <c r="J9" s="93" t="n"/>
-      <c r="K9" s="79" t="inlineStr">
+      <c r="B9" s="54" t="n"/>
+      <c r="C9" s="54" t="n"/>
+      <c r="D9" s="54" t="n"/>
+      <c r="E9" s="54" t="n"/>
+      <c r="F9" s="54" t="n"/>
+      <c r="G9" s="54" t="n"/>
+      <c r="H9" s="54" t="n"/>
+      <c r="I9" s="54" t="n"/>
+      <c r="J9" s="54" t="n"/>
+      <c r="K9" s="170" t="inlineStr">
         <is>
           <t>Structured training plan + schedule / resource table</t>
         </is>
       </c>
-      <c r="L9" s="92" t="n"/>
-      <c r="M9" s="92" t="n"/>
-      <c r="N9" s="92" t="n"/>
-      <c r="O9" s="92" t="n"/>
-      <c r="P9" s="92" t="n"/>
-      <c r="Q9" s="92" t="n"/>
-      <c r="R9" s="92" t="n"/>
-      <c r="S9" s="92" t="n"/>
-      <c r="T9" s="92" t="n"/>
-      <c r="U9" s="92" t="n"/>
-      <c r="V9" s="92" t="n"/>
-      <c r="W9" s="92" t="n"/>
-      <c r="X9" s="92" t="n"/>
-      <c r="Y9" s="92" t="n"/>
-      <c r="Z9" s="92" t="n"/>
-      <c r="AA9" s="92" t="n"/>
-      <c r="AB9" s="92" t="n"/>
-      <c r="AC9" s="92" t="n"/>
-      <c r="AD9" s="92" t="n"/>
-      <c r="AE9" s="92" t="n"/>
-      <c r="AF9" s="92" t="n"/>
-      <c r="AG9" s="92" t="n"/>
-      <c r="AH9" s="92" t="n"/>
-      <c r="AI9" s="92" t="n"/>
-      <c r="AJ9" s="92" t="n"/>
-      <c r="AK9" s="92" t="n"/>
-      <c r="AL9" s="92" t="n"/>
-      <c r="AM9" s="92" t="n"/>
-      <c r="AN9" s="92" t="n"/>
-      <c r="AO9" s="92" t="n"/>
-      <c r="AP9" s="92" t="n"/>
-      <c r="AQ9" s="92" t="n"/>
-      <c r="AR9" s="92" t="n"/>
-      <c r="AS9" s="92" t="n"/>
-      <c r="AT9" s="92" t="n"/>
-      <c r="AU9" s="92" t="n"/>
-      <c r="AV9" s="92" t="n"/>
-      <c r="AW9" s="92" t="n"/>
-      <c r="AX9" s="92" t="n"/>
-      <c r="AY9" s="92" t="n"/>
-      <c r="AZ9" s="92" t="n"/>
-      <c r="BA9" s="92" t="n"/>
-      <c r="BB9" s="92" t="n"/>
-      <c r="BC9" s="92" t="n"/>
-      <c r="BD9" s="93" t="n"/>
+      <c r="L9" s="54" t="n"/>
+      <c r="M9" s="54" t="n"/>
+      <c r="N9" s="54" t="n"/>
+      <c r="O9" s="54" t="n"/>
+      <c r="P9" s="54" t="n"/>
+      <c r="Q9" s="54" t="n"/>
+      <c r="R9" s="54" t="n"/>
+      <c r="S9" s="54" t="n"/>
+      <c r="T9" s="54" t="n"/>
+      <c r="U9" s="54" t="n"/>
+      <c r="V9" s="54" t="n"/>
+      <c r="W9" s="54" t="n"/>
+      <c r="X9" s="54" t="n"/>
+      <c r="Y9" s="54" t="n"/>
+      <c r="Z9" s="54" t="n"/>
+      <c r="AA9" s="54" t="n"/>
+      <c r="AB9" s="54" t="n"/>
+      <c r="AC9" s="54" t="n"/>
+      <c r="AD9" s="54" t="n"/>
+      <c r="AE9" s="54" t="n"/>
+      <c r="AF9" s="54" t="n"/>
+      <c r="AG9" s="54" t="n"/>
+      <c r="AH9" s="54" t="n"/>
+      <c r="AI9" s="54" t="n"/>
+      <c r="AJ9" s="54" t="n"/>
+      <c r="AK9" s="54" t="n"/>
+      <c r="AL9" s="54" t="n"/>
+      <c r="AM9" s="54" t="n"/>
+      <c r="AN9" s="54" t="n"/>
+      <c r="AO9" s="54" t="n"/>
+      <c r="AP9" s="54" t="n"/>
+      <c r="AQ9" s="54" t="n"/>
+      <c r="AR9" s="54" t="n"/>
+      <c r="AS9" s="54" t="n"/>
+      <c r="AT9" s="54" t="n"/>
+      <c r="AU9" s="54" t="n"/>
+      <c r="AV9" s="54" t="n"/>
+      <c r="AW9" s="54" t="n"/>
+      <c r="AX9" s="54" t="n"/>
+      <c r="AY9" s="54" t="n"/>
+      <c r="AZ9" s="54" t="n"/>
+      <c r="BA9" s="54" t="n"/>
+      <c r="BB9" s="54" t="n"/>
+      <c r="BC9" s="54" t="n"/>
+      <c r="BD9" s="171" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="68" t="inlineStr">
+      <c r="A10" s="158" t="inlineStr">
         <is>
           <t>Boundary / SoR</t>
         </is>
       </c>
-      <c r="B10" s="92" t="n"/>
-      <c r="C10" s="92" t="n"/>
-      <c r="D10" s="92" t="n"/>
-      <c r="E10" s="92" t="n"/>
-      <c r="F10" s="92" t="n"/>
-      <c r="G10" s="92" t="n"/>
-      <c r="H10" s="92" t="n"/>
-      <c r="I10" s="92" t="n"/>
-      <c r="J10" s="93" t="n"/>
-      <c r="K10" s="79" t="inlineStr">
+      <c r="B10" s="159" t="n"/>
+      <c r="C10" s="159" t="n"/>
+      <c r="D10" s="159" t="n"/>
+      <c r="E10" s="159" t="n"/>
+      <c r="F10" s="159" t="n"/>
+      <c r="G10" s="159" t="n"/>
+      <c r="H10" s="159" t="n"/>
+      <c r="I10" s="159" t="n"/>
+      <c r="J10" s="159" t="n"/>
+      <c r="K10" s="172" t="inlineStr">
         <is>
           <t>Training-plan event defines who must be trained and when; intentionally separate from attendance, OJT, competence, certification and skills matrices.</t>
         </is>
       </c>
-      <c r="L10" s="92" t="n"/>
-      <c r="M10" s="92" t="n"/>
-      <c r="N10" s="92" t="n"/>
-      <c r="O10" s="92" t="n"/>
-      <c r="P10" s="92" t="n"/>
-      <c r="Q10" s="92" t="n"/>
-      <c r="R10" s="92" t="n"/>
-      <c r="S10" s="92" t="n"/>
-      <c r="T10" s="92" t="n"/>
-      <c r="U10" s="92" t="n"/>
-      <c r="V10" s="92" t="n"/>
-      <c r="W10" s="92" t="n"/>
-      <c r="X10" s="92" t="n"/>
-      <c r="Y10" s="92" t="n"/>
-      <c r="Z10" s="92" t="n"/>
-      <c r="AA10" s="92" t="n"/>
-      <c r="AB10" s="92" t="n"/>
-      <c r="AC10" s="92" t="n"/>
-      <c r="AD10" s="92" t="n"/>
-      <c r="AE10" s="92" t="n"/>
-      <c r="AF10" s="92" t="n"/>
-      <c r="AG10" s="92" t="n"/>
-      <c r="AH10" s="92" t="n"/>
-      <c r="AI10" s="92" t="n"/>
-      <c r="AJ10" s="92" t="n"/>
-      <c r="AK10" s="92" t="n"/>
-      <c r="AL10" s="92" t="n"/>
-      <c r="AM10" s="92" t="n"/>
-      <c r="AN10" s="92" t="n"/>
-      <c r="AO10" s="92" t="n"/>
-      <c r="AP10" s="92" t="n"/>
-      <c r="AQ10" s="92" t="n"/>
-      <c r="AR10" s="92" t="n"/>
-      <c r="AS10" s="92" t="n"/>
-      <c r="AT10" s="92" t="n"/>
-      <c r="AU10" s="92" t="n"/>
-      <c r="AV10" s="92" t="n"/>
-      <c r="AW10" s="92" t="n"/>
-      <c r="AX10" s="92" t="n"/>
-      <c r="AY10" s="92" t="n"/>
-      <c r="AZ10" s="92" t="n"/>
-      <c r="BA10" s="92" t="n"/>
-      <c r="BB10" s="92" t="n"/>
-      <c r="BC10" s="92" t="n"/>
-      <c r="BD10" s="93" t="n"/>
+      <c r="L10" s="159" t="n"/>
+      <c r="M10" s="159" t="n"/>
+      <c r="N10" s="159" t="n"/>
+      <c r="O10" s="159" t="n"/>
+      <c r="P10" s="159" t="n"/>
+      <c r="Q10" s="159" t="n"/>
+      <c r="R10" s="159" t="n"/>
+      <c r="S10" s="159" t="n"/>
+      <c r="T10" s="159" t="n"/>
+      <c r="U10" s="159" t="n"/>
+      <c r="V10" s="159" t="n"/>
+      <c r="W10" s="159" t="n"/>
+      <c r="X10" s="159" t="n"/>
+      <c r="Y10" s="159" t="n"/>
+      <c r="Z10" s="159" t="n"/>
+      <c r="AA10" s="159" t="n"/>
+      <c r="AB10" s="159" t="n"/>
+      <c r="AC10" s="159" t="n"/>
+      <c r="AD10" s="159" t="n"/>
+      <c r="AE10" s="159" t="n"/>
+      <c r="AF10" s="159" t="n"/>
+      <c r="AG10" s="159" t="n"/>
+      <c r="AH10" s="159" t="n"/>
+      <c r="AI10" s="159" t="n"/>
+      <c r="AJ10" s="159" t="n"/>
+      <c r="AK10" s="159" t="n"/>
+      <c r="AL10" s="159" t="n"/>
+      <c r="AM10" s="159" t="n"/>
+      <c r="AN10" s="159" t="n"/>
+      <c r="AO10" s="159" t="n"/>
+      <c r="AP10" s="159" t="n"/>
+      <c r="AQ10" s="159" t="n"/>
+      <c r="AR10" s="159" t="n"/>
+      <c r="AS10" s="159" t="n"/>
+      <c r="AT10" s="159" t="n"/>
+      <c r="AU10" s="159" t="n"/>
+      <c r="AV10" s="159" t="n"/>
+      <c r="AW10" s="159" t="n"/>
+      <c r="AX10" s="159" t="n"/>
+      <c r="AY10" s="159" t="n"/>
+      <c r="AZ10" s="159" t="n"/>
+      <c r="BA10" s="159" t="n"/>
+      <c r="BB10" s="159" t="n"/>
+      <c r="BC10" s="159" t="n"/>
+      <c r="BD10" s="173" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="67" t="inlineStr">
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="145" t="inlineStr">
         <is>
           <t xml:space="preserve">  TARGET POPULATION / SKILL PLAN</t>
         </is>
       </c>
-      <c r="B11" s="92" t="n"/>
-      <c r="C11" s="92" t="n"/>
-      <c r="D11" s="92" t="n"/>
-      <c r="E11" s="92" t="n"/>
-      <c r="F11" s="92" t="n"/>
-      <c r="G11" s="92" t="n"/>
-      <c r="H11" s="92" t="n"/>
-      <c r="I11" s="92" t="n"/>
-      <c r="J11" s="92" t="n"/>
-      <c r="K11" s="92" t="n"/>
-      <c r="L11" s="92" t="n"/>
-      <c r="M11" s="92" t="n"/>
-      <c r="N11" s="92" t="n"/>
-      <c r="O11" s="92" t="n"/>
-      <c r="P11" s="92" t="n"/>
-      <c r="Q11" s="92" t="n"/>
-      <c r="R11" s="92" t="n"/>
-      <c r="S11" s="92" t="n"/>
-      <c r="T11" s="92" t="n"/>
-      <c r="U11" s="92" t="n"/>
-      <c r="V11" s="92" t="n"/>
-      <c r="W11" s="92" t="n"/>
-      <c r="X11" s="92" t="n"/>
-      <c r="Y11" s="92" t="n"/>
-      <c r="Z11" s="92" t="n"/>
-      <c r="AA11" s="92" t="n"/>
-      <c r="AB11" s="92" t="n"/>
-      <c r="AC11" s="92" t="n"/>
-      <c r="AD11" s="92" t="n"/>
-      <c r="AE11" s="92" t="n"/>
-      <c r="AF11" s="92" t="n"/>
-      <c r="AG11" s="92" t="n"/>
-      <c r="AH11" s="92" t="n"/>
-      <c r="AI11" s="92" t="n"/>
-      <c r="AJ11" s="92" t="n"/>
-      <c r="AK11" s="92" t="n"/>
-      <c r="AL11" s="92" t="n"/>
-      <c r="AM11" s="92" t="n"/>
-      <c r="AN11" s="92" t="n"/>
-      <c r="AO11" s="92" t="n"/>
-      <c r="AP11" s="92" t="n"/>
-      <c r="AQ11" s="92" t="n"/>
-      <c r="AR11" s="92" t="n"/>
-      <c r="AS11" s="92" t="n"/>
-      <c r="AT11" s="92" t="n"/>
-      <c r="AU11" s="92" t="n"/>
-      <c r="AV11" s="92" t="n"/>
-      <c r="AW11" s="92" t="n"/>
-      <c r="AX11" s="92" t="n"/>
-      <c r="AY11" s="92" t="n"/>
-      <c r="AZ11" s="92" t="n"/>
-      <c r="BA11" s="92" t="n"/>
-      <c r="BB11" s="92" t="n"/>
-      <c r="BC11" s="92" t="n"/>
-      <c r="BD11" s="93" t="n"/>
+      <c r="B11" s="146" t="n"/>
+      <c r="C11" s="146" t="n"/>
+      <c r="D11" s="146" t="n"/>
+      <c r="E11" s="146" t="n"/>
+      <c r="F11" s="146" t="n"/>
+      <c r="G11" s="146" t="n"/>
+      <c r="H11" s="146" t="n"/>
+      <c r="I11" s="146" t="n"/>
+      <c r="J11" s="146" t="n"/>
+      <c r="K11" s="146" t="n"/>
+      <c r="L11" s="146" t="n"/>
+      <c r="M11" s="146" t="n"/>
+      <c r="N11" s="146" t="n"/>
+      <c r="O11" s="146" t="n"/>
+      <c r="P11" s="146" t="n"/>
+      <c r="Q11" s="146" t="n"/>
+      <c r="R11" s="146" t="n"/>
+      <c r="S11" s="146" t="n"/>
+      <c r="T11" s="146" t="n"/>
+      <c r="U11" s="146" t="n"/>
+      <c r="V11" s="146" t="n"/>
+      <c r="W11" s="146" t="n"/>
+      <c r="X11" s="146" t="n"/>
+      <c r="Y11" s="146" t="n"/>
+      <c r="Z11" s="146" t="n"/>
+      <c r="AA11" s="146" t="n"/>
+      <c r="AB11" s="146" t="n"/>
+      <c r="AC11" s="146" t="n"/>
+      <c r="AD11" s="146" t="n"/>
+      <c r="AE11" s="146" t="n"/>
+      <c r="AF11" s="146" t="n"/>
+      <c r="AG11" s="146" t="n"/>
+      <c r="AH11" s="146" t="n"/>
+      <c r="AI11" s="146" t="n"/>
+      <c r="AJ11" s="146" t="n"/>
+      <c r="AK11" s="146" t="n"/>
+      <c r="AL11" s="146" t="n"/>
+      <c r="AM11" s="146" t="n"/>
+      <c r="AN11" s="146" t="n"/>
+      <c r="AO11" s="146" t="n"/>
+      <c r="AP11" s="146" t="n"/>
+      <c r="AQ11" s="146" t="n"/>
+      <c r="AR11" s="146" t="n"/>
+      <c r="AS11" s="146" t="n"/>
+      <c r="AT11" s="146" t="n"/>
+      <c r="AU11" s="146" t="n"/>
+      <c r="AV11" s="146" t="n"/>
+      <c r="AW11" s="146" t="n"/>
+      <c r="AX11" s="146" t="n"/>
+      <c r="AY11" s="146" t="n"/>
+      <c r="AZ11" s="146" t="n"/>
+      <c r="BA11" s="146" t="n"/>
+      <c r="BB11" s="146" t="n"/>
+      <c r="BC11" s="146" t="n"/>
+      <c r="BD11" s="147" t="n"/>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="80" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="174" t="inlineStr">
         <is>
           <t>Target ID</t>
         </is>
       </c>
-      <c r="B12" s="92" t="n"/>
-      <c r="C12" s="92" t="n"/>
-      <c r="D12" s="92" t="n"/>
-      <c r="E12" s="92" t="n"/>
-      <c r="F12" s="93" t="n"/>
-      <c r="G12" s="80" t="inlineStr">
+      <c r="B12" s="175" t="n"/>
+      <c r="C12" s="175" t="n"/>
+      <c r="D12" s="175" t="n"/>
+      <c r="E12" s="175" t="n"/>
+      <c r="F12" s="175" t="n"/>
+      <c r="G12" s="176" t="inlineStr">
         <is>
           <t>Person or Group</t>
         </is>
       </c>
-      <c r="H12" s="92" t="n"/>
-      <c r="I12" s="92" t="n"/>
-      <c r="J12" s="92" t="n"/>
-      <c r="K12" s="92" t="n"/>
-      <c r="L12" s="92" t="n"/>
-      <c r="M12" s="93" t="n"/>
-      <c r="N12" s="80" t="inlineStr">
+      <c r="H12" s="175" t="n"/>
+      <c r="I12" s="175" t="n"/>
+      <c r="J12" s="175" t="n"/>
+      <c r="K12" s="175" t="n"/>
+      <c r="L12" s="175" t="n"/>
+      <c r="M12" s="175" t="n"/>
+      <c r="N12" s="176" t="inlineStr">
         <is>
           <t>Required Skill</t>
         </is>
       </c>
-      <c r="O12" s="92" t="n"/>
-      <c r="P12" s="92" t="n"/>
-      <c r="Q12" s="92" t="n"/>
-      <c r="R12" s="92" t="n"/>
-      <c r="S12" s="93" t="n"/>
-      <c r="T12" s="80" t="inlineStr">
+      <c r="O12" s="175" t="n"/>
+      <c r="P12" s="175" t="n"/>
+      <c r="Q12" s="175" t="n"/>
+      <c r="R12" s="175" t="n"/>
+      <c r="S12" s="175" t="n"/>
+      <c r="T12" s="176" t="inlineStr">
         <is>
           <t>Current Level</t>
         </is>
       </c>
-      <c r="U12" s="92" t="n"/>
-      <c r="V12" s="92" t="n"/>
-      <c r="W12" s="92" t="n"/>
-      <c r="X12" s="92" t="n"/>
-      <c r="Y12" s="93" t="n"/>
-      <c r="Z12" s="80" t="inlineStr">
+      <c r="U12" s="175" t="n"/>
+      <c r="V12" s="175" t="n"/>
+      <c r="W12" s="175" t="n"/>
+      <c r="X12" s="175" t="n"/>
+      <c r="Y12" s="175" t="n"/>
+      <c r="Z12" s="176" t="inlineStr">
         <is>
           <t>Target Level</t>
         </is>
       </c>
-      <c r="AA12" s="92" t="n"/>
-      <c r="AB12" s="92" t="n"/>
-      <c r="AC12" s="92" t="n"/>
-      <c r="AD12" s="92" t="n"/>
-      <c r="AE12" s="93" t="n"/>
-      <c r="AF12" s="80" t="inlineStr">
+      <c r="AA12" s="175" t="n"/>
+      <c r="AB12" s="175" t="n"/>
+      <c r="AC12" s="175" t="n"/>
+      <c r="AD12" s="175" t="n"/>
+      <c r="AE12" s="175" t="n"/>
+      <c r="AF12" s="176" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="AG12" s="92" t="n"/>
-      <c r="AH12" s="92" t="n"/>
-      <c r="AI12" s="92" t="n"/>
-      <c r="AJ12" s="92" t="n"/>
-      <c r="AK12" s="92" t="n"/>
-      <c r="AL12" s="92" t="n"/>
-      <c r="AM12" s="92" t="n"/>
-      <c r="AN12" s="93" t="n"/>
-      <c r="AO12" s="80" t="inlineStr">
+      <c r="AG12" s="175" t="n"/>
+      <c r="AH12" s="175" t="n"/>
+      <c r="AI12" s="175" t="n"/>
+      <c r="AJ12" s="175" t="n"/>
+      <c r="AK12" s="175" t="n"/>
+      <c r="AL12" s="175" t="n"/>
+      <c r="AM12" s="175" t="n"/>
+      <c r="AN12" s="175" t="n"/>
+      <c r="AO12" s="176" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="AP12" s="92" t="n"/>
-      <c r="AQ12" s="92" t="n"/>
-      <c r="AR12" s="92" t="n"/>
-      <c r="AS12" s="93" t="n"/>
-      <c r="AT12" s="80" t="inlineStr">
+      <c r="AP12" s="175" t="n"/>
+      <c r="AQ12" s="175" t="n"/>
+      <c r="AR12" s="175" t="n"/>
+      <c r="AS12" s="175" t="n"/>
+      <c r="AT12" s="176" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="AU12" s="92" t="n"/>
-      <c r="AV12" s="92" t="n"/>
-      <c r="AW12" s="92" t="n"/>
-      <c r="AX12" s="93" t="n"/>
-      <c r="AY12" s="80" t="inlineStr">
+      <c r="AU12" s="175" t="n"/>
+      <c r="AV12" s="175" t="n"/>
+      <c r="AW12" s="175" t="n"/>
+      <c r="AX12" s="175" t="n"/>
+      <c r="AY12" s="176" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="AZ12" s="92" t="n"/>
-      <c r="BA12" s="92" t="n"/>
-      <c r="BB12" s="92" t="n"/>
-      <c r="BC12" s="92" t="n"/>
-      <c r="BD12" s="93" t="n"/>
+      <c r="AZ12" s="175" t="n"/>
+      <c r="BA12" s="175" t="n"/>
+      <c r="BB12" s="175" t="n"/>
+      <c r="BC12" s="175" t="n"/>
+      <c r="BD12" s="177" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="71" t="n"/>
-      <c r="B13" s="94" t="n"/>
-      <c r="C13" s="94" t="n"/>
-      <c r="D13" s="94" t="n"/>
-      <c r="E13" s="94" t="n"/>
-      <c r="F13" s="95" t="n"/>
-      <c r="G13" s="71" t="n"/>
-      <c r="H13" s="94" t="n"/>
-      <c r="I13" s="94" t="n"/>
-      <c r="J13" s="94" t="n"/>
-      <c r="K13" s="94" t="n"/>
-      <c r="L13" s="94" t="n"/>
-      <c r="M13" s="95" t="n"/>
-      <c r="N13" s="71" t="n"/>
-      <c r="O13" s="94" t="n"/>
-      <c r="P13" s="94" t="n"/>
-      <c r="Q13" s="94" t="n"/>
-      <c r="R13" s="94" t="n"/>
-      <c r="S13" s="95" t="n"/>
-      <c r="T13" s="71" t="n"/>
-      <c r="U13" s="94" t="n"/>
-      <c r="V13" s="94" t="n"/>
-      <c r="W13" s="94" t="n"/>
-      <c r="X13" s="94" t="n"/>
-      <c r="Y13" s="95" t="n"/>
-      <c r="Z13" s="71" t="n"/>
-      <c r="AA13" s="94" t="n"/>
-      <c r="AB13" s="94" t="n"/>
-      <c r="AC13" s="94" t="n"/>
-      <c r="AD13" s="94" t="n"/>
-      <c r="AE13" s="95" t="n"/>
-      <c r="AF13" s="71" t="n"/>
-      <c r="AG13" s="94" t="n"/>
-      <c r="AH13" s="94" t="n"/>
-      <c r="AI13" s="94" t="n"/>
-      <c r="AJ13" s="94" t="n"/>
-      <c r="AK13" s="94" t="n"/>
-      <c r="AL13" s="94" t="n"/>
-      <c r="AM13" s="94" t="n"/>
-      <c r="AN13" s="95" t="n"/>
-      <c r="AO13" s="71" t="n"/>
-      <c r="AP13" s="94" t="n"/>
-      <c r="AQ13" s="94" t="n"/>
-      <c r="AR13" s="94" t="n"/>
-      <c r="AS13" s="95" t="n"/>
-      <c r="AT13" s="71" t="n"/>
-      <c r="AU13" s="94" t="n"/>
-      <c r="AV13" s="94" t="n"/>
-      <c r="AW13" s="94" t="n"/>
-      <c r="AX13" s="95" t="n"/>
-      <c r="AY13" s="71" t="n"/>
-      <c r="AZ13" s="94" t="n"/>
-      <c r="BA13" s="94" t="n"/>
-      <c r="BB13" s="94" t="n"/>
-      <c r="BC13" s="94" t="n"/>
-      <c r="BD13" s="95" t="n"/>
+      <c r="A13" s="178" t="n"/>
+      <c r="B13" s="151" t="n"/>
+      <c r="C13" s="151" t="n"/>
+      <c r="D13" s="151" t="n"/>
+      <c r="E13" s="151" t="n"/>
+      <c r="F13" s="151" t="n"/>
+      <c r="G13" s="150" t="n"/>
+      <c r="H13" s="151" t="n"/>
+      <c r="I13" s="151" t="n"/>
+      <c r="J13" s="151" t="n"/>
+      <c r="K13" s="151" t="n"/>
+      <c r="L13" s="151" t="n"/>
+      <c r="M13" s="151" t="n"/>
+      <c r="N13" s="150" t="n"/>
+      <c r="O13" s="151" t="n"/>
+      <c r="P13" s="151" t="n"/>
+      <c r="Q13" s="151" t="n"/>
+      <c r="R13" s="151" t="n"/>
+      <c r="S13" s="151" t="n"/>
+      <c r="T13" s="150" t="n"/>
+      <c r="U13" s="151" t="n"/>
+      <c r="V13" s="151" t="n"/>
+      <c r="W13" s="151" t="n"/>
+      <c r="X13" s="151" t="n"/>
+      <c r="Y13" s="151" t="n"/>
+      <c r="Z13" s="150" t="n"/>
+      <c r="AA13" s="151" t="n"/>
+      <c r="AB13" s="151" t="n"/>
+      <c r="AC13" s="151" t="n"/>
+      <c r="AD13" s="151" t="n"/>
+      <c r="AE13" s="151" t="n"/>
+      <c r="AF13" s="150" t="n"/>
+      <c r="AG13" s="151" t="n"/>
+      <c r="AH13" s="151" t="n"/>
+      <c r="AI13" s="151" t="n"/>
+      <c r="AJ13" s="151" t="n"/>
+      <c r="AK13" s="151" t="n"/>
+      <c r="AL13" s="151" t="n"/>
+      <c r="AM13" s="151" t="n"/>
+      <c r="AN13" s="151" t="n"/>
+      <c r="AO13" s="150" t="n"/>
+      <c r="AP13" s="151" t="n"/>
+      <c r="AQ13" s="151" t="n"/>
+      <c r="AR13" s="151" t="n"/>
+      <c r="AS13" s="151" t="n"/>
+      <c r="AT13" s="150" t="n"/>
+      <c r="AU13" s="151" t="n"/>
+      <c r="AV13" s="151" t="n"/>
+      <c r="AW13" s="151" t="n"/>
+      <c r="AX13" s="151" t="n"/>
+      <c r="AY13" s="150" t="n"/>
+      <c r="AZ13" s="151" t="n"/>
+      <c r="BA13" s="151" t="n"/>
+      <c r="BB13" s="151" t="n"/>
+      <c r="BC13" s="151" t="n"/>
+      <c r="BD13" s="153" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="81" t="n"/>
-      <c r="B14" s="94" t="n"/>
-      <c r="C14" s="94" t="n"/>
-      <c r="D14" s="94" t="n"/>
-      <c r="E14" s="94" t="n"/>
-      <c r="F14" s="95" t="n"/>
-      <c r="G14" s="81" t="n"/>
-      <c r="H14" s="94" t="n"/>
-      <c r="I14" s="94" t="n"/>
-      <c r="J14" s="94" t="n"/>
-      <c r="K14" s="94" t="n"/>
-      <c r="L14" s="94" t="n"/>
-      <c r="M14" s="95" t="n"/>
-      <c r="N14" s="81" t="n"/>
-      <c r="O14" s="94" t="n"/>
-      <c r="P14" s="94" t="n"/>
-      <c r="Q14" s="94" t="n"/>
-      <c r="R14" s="94" t="n"/>
-      <c r="S14" s="95" t="n"/>
-      <c r="T14" s="81" t="n"/>
-      <c r="U14" s="94" t="n"/>
-      <c r="V14" s="94" t="n"/>
-      <c r="W14" s="94" t="n"/>
-      <c r="X14" s="94" t="n"/>
-      <c r="Y14" s="95" t="n"/>
-      <c r="Z14" s="81" t="n"/>
-      <c r="AA14" s="94" t="n"/>
-      <c r="AB14" s="94" t="n"/>
-      <c r="AC14" s="94" t="n"/>
-      <c r="AD14" s="94" t="n"/>
-      <c r="AE14" s="95" t="n"/>
-      <c r="AF14" s="81" t="n"/>
-      <c r="AG14" s="94" t="n"/>
-      <c r="AH14" s="94" t="n"/>
-      <c r="AI14" s="94" t="n"/>
-      <c r="AJ14" s="94" t="n"/>
-      <c r="AK14" s="94" t="n"/>
-      <c r="AL14" s="94" t="n"/>
-      <c r="AM14" s="94" t="n"/>
-      <c r="AN14" s="95" t="n"/>
-      <c r="AO14" s="81" t="n"/>
-      <c r="AP14" s="94" t="n"/>
-      <c r="AQ14" s="94" t="n"/>
-      <c r="AR14" s="94" t="n"/>
-      <c r="AS14" s="95" t="n"/>
-      <c r="AT14" s="81" t="n"/>
-      <c r="AU14" s="94" t="n"/>
-      <c r="AV14" s="94" t="n"/>
-      <c r="AW14" s="94" t="n"/>
-      <c r="AX14" s="95" t="n"/>
-      <c r="AY14" s="81" t="n"/>
-      <c r="AZ14" s="94" t="n"/>
-      <c r="BA14" s="94" t="n"/>
-      <c r="BB14" s="94" t="n"/>
-      <c r="BC14" s="94" t="n"/>
-      <c r="BD14" s="95" t="n"/>
+      <c r="A14" s="179" t="n"/>
+      <c r="B14" s="74" t="n"/>
+      <c r="C14" s="74" t="n"/>
+      <c r="D14" s="74" t="n"/>
+      <c r="E14" s="74" t="n"/>
+      <c r="F14" s="74" t="n"/>
+      <c r="G14" s="180" t="n"/>
+      <c r="H14" s="74" t="n"/>
+      <c r="I14" s="74" t="n"/>
+      <c r="J14" s="74" t="n"/>
+      <c r="K14" s="74" t="n"/>
+      <c r="L14" s="74" t="n"/>
+      <c r="M14" s="74" t="n"/>
+      <c r="N14" s="180" t="n"/>
+      <c r="O14" s="74" t="n"/>
+      <c r="P14" s="74" t="n"/>
+      <c r="Q14" s="74" t="n"/>
+      <c r="R14" s="74" t="n"/>
+      <c r="S14" s="74" t="n"/>
+      <c r="T14" s="180" t="n"/>
+      <c r="U14" s="74" t="n"/>
+      <c r="V14" s="74" t="n"/>
+      <c r="W14" s="74" t="n"/>
+      <c r="X14" s="74" t="n"/>
+      <c r="Y14" s="74" t="n"/>
+      <c r="Z14" s="180" t="n"/>
+      <c r="AA14" s="74" t="n"/>
+      <c r="AB14" s="74" t="n"/>
+      <c r="AC14" s="74" t="n"/>
+      <c r="AD14" s="74" t="n"/>
+      <c r="AE14" s="74" t="n"/>
+      <c r="AF14" s="180" t="n"/>
+      <c r="AG14" s="74" t="n"/>
+      <c r="AH14" s="74" t="n"/>
+      <c r="AI14" s="74" t="n"/>
+      <c r="AJ14" s="74" t="n"/>
+      <c r="AK14" s="74" t="n"/>
+      <c r="AL14" s="74" t="n"/>
+      <c r="AM14" s="74" t="n"/>
+      <c r="AN14" s="74" t="n"/>
+      <c r="AO14" s="180" t="n"/>
+      <c r="AP14" s="74" t="n"/>
+      <c r="AQ14" s="74" t="n"/>
+      <c r="AR14" s="74" t="n"/>
+      <c r="AS14" s="74" t="n"/>
+      <c r="AT14" s="180" t="n"/>
+      <c r="AU14" s="74" t="n"/>
+      <c r="AV14" s="74" t="n"/>
+      <c r="AW14" s="74" t="n"/>
+      <c r="AX14" s="74" t="n"/>
+      <c r="AY14" s="180" t="n"/>
+      <c r="AZ14" s="74" t="n"/>
+      <c r="BA14" s="74" t="n"/>
+      <c r="BB14" s="74" t="n"/>
+      <c r="BC14" s="74" t="n"/>
+      <c r="BD14" s="157" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="71" t="n"/>
-      <c r="B15" s="94" t="n"/>
-      <c r="C15" s="94" t="n"/>
-      <c r="D15" s="94" t="n"/>
-      <c r="E15" s="94" t="n"/>
-      <c r="F15" s="95" t="n"/>
-      <c r="G15" s="71" t="n"/>
-      <c r="H15" s="94" t="n"/>
-      <c r="I15" s="94" t="n"/>
-      <c r="J15" s="94" t="n"/>
-      <c r="K15" s="94" t="n"/>
-      <c r="L15" s="94" t="n"/>
-      <c r="M15" s="95" t="n"/>
-      <c r="N15" s="71" t="n"/>
-      <c r="O15" s="94" t="n"/>
-      <c r="P15" s="94" t="n"/>
-      <c r="Q15" s="94" t="n"/>
-      <c r="R15" s="94" t="n"/>
-      <c r="S15" s="95" t="n"/>
-      <c r="T15" s="71" t="n"/>
-      <c r="U15" s="94" t="n"/>
-      <c r="V15" s="94" t="n"/>
-      <c r="W15" s="94" t="n"/>
-      <c r="X15" s="94" t="n"/>
-      <c r="Y15" s="95" t="n"/>
-      <c r="Z15" s="71" t="n"/>
-      <c r="AA15" s="94" t="n"/>
-      <c r="AB15" s="94" t="n"/>
-      <c r="AC15" s="94" t="n"/>
-      <c r="AD15" s="94" t="n"/>
-      <c r="AE15" s="95" t="n"/>
-      <c r="AF15" s="71" t="n"/>
-      <c r="AG15" s="94" t="n"/>
-      <c r="AH15" s="94" t="n"/>
-      <c r="AI15" s="94" t="n"/>
-      <c r="AJ15" s="94" t="n"/>
-      <c r="AK15" s="94" t="n"/>
-      <c r="AL15" s="94" t="n"/>
-      <c r="AM15" s="94" t="n"/>
-      <c r="AN15" s="95" t="n"/>
-      <c r="AO15" s="71" t="n"/>
-      <c r="AP15" s="94" t="n"/>
-      <c r="AQ15" s="94" t="n"/>
-      <c r="AR15" s="94" t="n"/>
-      <c r="AS15" s="95" t="n"/>
-      <c r="AT15" s="71" t="n"/>
-      <c r="AU15" s="94" t="n"/>
-      <c r="AV15" s="94" t="n"/>
-      <c r="AW15" s="94" t="n"/>
-      <c r="AX15" s="95" t="n"/>
-      <c r="AY15" s="71" t="n"/>
-      <c r="AZ15" s="94" t="n"/>
-      <c r="BA15" s="94" t="n"/>
-      <c r="BB15" s="94" t="n"/>
-      <c r="BC15" s="94" t="n"/>
-      <c r="BD15" s="95" t="n"/>
+      <c r="A15" s="181" t="n"/>
+      <c r="B15" s="74" t="n"/>
+      <c r="C15" s="74" t="n"/>
+      <c r="D15" s="74" t="n"/>
+      <c r="E15" s="74" t="n"/>
+      <c r="F15" s="74" t="n"/>
+      <c r="G15" s="155" t="n"/>
+      <c r="H15" s="74" t="n"/>
+      <c r="I15" s="74" t="n"/>
+      <c r="J15" s="74" t="n"/>
+      <c r="K15" s="74" t="n"/>
+      <c r="L15" s="74" t="n"/>
+      <c r="M15" s="74" t="n"/>
+      <c r="N15" s="155" t="n"/>
+      <c r="O15" s="74" t="n"/>
+      <c r="P15" s="74" t="n"/>
+      <c r="Q15" s="74" t="n"/>
+      <c r="R15" s="74" t="n"/>
+      <c r="S15" s="74" t="n"/>
+      <c r="T15" s="155" t="n"/>
+      <c r="U15" s="74" t="n"/>
+      <c r="V15" s="74" t="n"/>
+      <c r="W15" s="74" t="n"/>
+      <c r="X15" s="74" t="n"/>
+      <c r="Y15" s="74" t="n"/>
+      <c r="Z15" s="155" t="n"/>
+      <c r="AA15" s="74" t="n"/>
+      <c r="AB15" s="74" t="n"/>
+      <c r="AC15" s="74" t="n"/>
+      <c r="AD15" s="74" t="n"/>
+      <c r="AE15" s="74" t="n"/>
+      <c r="AF15" s="155" t="n"/>
+      <c r="AG15" s="74" t="n"/>
+      <c r="AH15" s="74" t="n"/>
+      <c r="AI15" s="74" t="n"/>
+      <c r="AJ15" s="74" t="n"/>
+      <c r="AK15" s="74" t="n"/>
+      <c r="AL15" s="74" t="n"/>
+      <c r="AM15" s="74" t="n"/>
+      <c r="AN15" s="74" t="n"/>
+      <c r="AO15" s="155" t="n"/>
+      <c r="AP15" s="74" t="n"/>
+      <c r="AQ15" s="74" t="n"/>
+      <c r="AR15" s="74" t="n"/>
+      <c r="AS15" s="74" t="n"/>
+      <c r="AT15" s="155" t="n"/>
+      <c r="AU15" s="74" t="n"/>
+      <c r="AV15" s="74" t="n"/>
+      <c r="AW15" s="74" t="n"/>
+      <c r="AX15" s="74" t="n"/>
+      <c r="AY15" s="155" t="n"/>
+      <c r="AZ15" s="74" t="n"/>
+      <c r="BA15" s="74" t="n"/>
+      <c r="BB15" s="74" t="n"/>
+      <c r="BC15" s="74" t="n"/>
+      <c r="BD15" s="157" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="81" t="n"/>
-      <c r="B16" s="94" t="n"/>
-      <c r="C16" s="94" t="n"/>
-      <c r="D16" s="94" t="n"/>
-      <c r="E16" s="94" t="n"/>
-      <c r="F16" s="95" t="n"/>
-      <c r="G16" s="81" t="n"/>
-      <c r="H16" s="94" t="n"/>
-      <c r="I16" s="94" t="n"/>
-      <c r="J16" s="94" t="n"/>
-      <c r="K16" s="94" t="n"/>
-      <c r="L16" s="94" t="n"/>
-      <c r="M16" s="95" t="n"/>
-      <c r="N16" s="81" t="n"/>
-      <c r="O16" s="94" t="n"/>
-      <c r="P16" s="94" t="n"/>
-      <c r="Q16" s="94" t="n"/>
-      <c r="R16" s="94" t="n"/>
-      <c r="S16" s="95" t="n"/>
-      <c r="T16" s="81" t="n"/>
-      <c r="U16" s="94" t="n"/>
-      <c r="V16" s="94" t="n"/>
-      <c r="W16" s="94" t="n"/>
-      <c r="X16" s="94" t="n"/>
-      <c r="Y16" s="95" t="n"/>
-      <c r="Z16" s="81" t="n"/>
-      <c r="AA16" s="94" t="n"/>
-      <c r="AB16" s="94" t="n"/>
-      <c r="AC16" s="94" t="n"/>
-      <c r="AD16" s="94" t="n"/>
-      <c r="AE16" s="95" t="n"/>
-      <c r="AF16" s="81" t="n"/>
-      <c r="AG16" s="94" t="n"/>
-      <c r="AH16" s="94" t="n"/>
-      <c r="AI16" s="94" t="n"/>
-      <c r="AJ16" s="94" t="n"/>
-      <c r="AK16" s="94" t="n"/>
-      <c r="AL16" s="94" t="n"/>
-      <c r="AM16" s="94" t="n"/>
-      <c r="AN16" s="95" t="n"/>
-      <c r="AO16" s="81" t="n"/>
-      <c r="AP16" s="94" t="n"/>
-      <c r="AQ16" s="94" t="n"/>
-      <c r="AR16" s="94" t="n"/>
-      <c r="AS16" s="95" t="n"/>
-      <c r="AT16" s="81" t="n"/>
-      <c r="AU16" s="94" t="n"/>
-      <c r="AV16" s="94" t="n"/>
-      <c r="AW16" s="94" t="n"/>
-      <c r="AX16" s="95" t="n"/>
-      <c r="AY16" s="81" t="n"/>
-      <c r="AZ16" s="94" t="n"/>
-      <c r="BA16" s="94" t="n"/>
-      <c r="BB16" s="94" t="n"/>
-      <c r="BC16" s="94" t="n"/>
-      <c r="BD16" s="95" t="n"/>
+      <c r="A16" s="179" t="n"/>
+      <c r="B16" s="74" t="n"/>
+      <c r="C16" s="74" t="n"/>
+      <c r="D16" s="74" t="n"/>
+      <c r="E16" s="74" t="n"/>
+      <c r="F16" s="74" t="n"/>
+      <c r="G16" s="180" t="n"/>
+      <c r="H16" s="74" t="n"/>
+      <c r="I16" s="74" t="n"/>
+      <c r="J16" s="74" t="n"/>
+      <c r="K16" s="74" t="n"/>
+      <c r="L16" s="74" t="n"/>
+      <c r="M16" s="74" t="n"/>
+      <c r="N16" s="180" t="n"/>
+      <c r="O16" s="74" t="n"/>
+      <c r="P16" s="74" t="n"/>
+      <c r="Q16" s="74" t="n"/>
+      <c r="R16" s="74" t="n"/>
+      <c r="S16" s="74" t="n"/>
+      <c r="T16" s="180" t="n"/>
+      <c r="U16" s="74" t="n"/>
+      <c r="V16" s="74" t="n"/>
+      <c r="W16" s="74" t="n"/>
+      <c r="X16" s="74" t="n"/>
+      <c r="Y16" s="74" t="n"/>
+      <c r="Z16" s="180" t="n"/>
+      <c r="AA16" s="74" t="n"/>
+      <c r="AB16" s="74" t="n"/>
+      <c r="AC16" s="74" t="n"/>
+      <c r="AD16" s="74" t="n"/>
+      <c r="AE16" s="74" t="n"/>
+      <c r="AF16" s="180" t="n"/>
+      <c r="AG16" s="74" t="n"/>
+      <c r="AH16" s="74" t="n"/>
+      <c r="AI16" s="74" t="n"/>
+      <c r="AJ16" s="74" t="n"/>
+      <c r="AK16" s="74" t="n"/>
+      <c r="AL16" s="74" t="n"/>
+      <c r="AM16" s="74" t="n"/>
+      <c r="AN16" s="74" t="n"/>
+      <c r="AO16" s="180" t="n"/>
+      <c r="AP16" s="74" t="n"/>
+      <c r="AQ16" s="74" t="n"/>
+      <c r="AR16" s="74" t="n"/>
+      <c r="AS16" s="74" t="n"/>
+      <c r="AT16" s="180" t="n"/>
+      <c r="AU16" s="74" t="n"/>
+      <c r="AV16" s="74" t="n"/>
+      <c r="AW16" s="74" t="n"/>
+      <c r="AX16" s="74" t="n"/>
+      <c r="AY16" s="180" t="n"/>
+      <c r="AZ16" s="74" t="n"/>
+      <c r="BA16" s="74" t="n"/>
+      <c r="BB16" s="74" t="n"/>
+      <c r="BC16" s="74" t="n"/>
+      <c r="BD16" s="157" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="71" t="n"/>
-      <c r="B17" s="94" t="n"/>
-      <c r="C17" s="94" t="n"/>
-      <c r="D17" s="94" t="n"/>
-      <c r="E17" s="94" t="n"/>
-      <c r="F17" s="95" t="n"/>
-      <c r="G17" s="71" t="n"/>
-      <c r="H17" s="94" t="n"/>
-      <c r="I17" s="94" t="n"/>
-      <c r="J17" s="94" t="n"/>
-      <c r="K17" s="94" t="n"/>
-      <c r="L17" s="94" t="n"/>
-      <c r="M17" s="95" t="n"/>
-      <c r="N17" s="71" t="n"/>
-      <c r="O17" s="94" t="n"/>
-      <c r="P17" s="94" t="n"/>
-      <c r="Q17" s="94" t="n"/>
-      <c r="R17" s="94" t="n"/>
-      <c r="S17" s="95" t="n"/>
-      <c r="T17" s="71" t="n"/>
-      <c r="U17" s="94" t="n"/>
-      <c r="V17" s="94" t="n"/>
-      <c r="W17" s="94" t="n"/>
-      <c r="X17" s="94" t="n"/>
-      <c r="Y17" s="95" t="n"/>
-      <c r="Z17" s="71" t="n"/>
-      <c r="AA17" s="94" t="n"/>
-      <c r="AB17" s="94" t="n"/>
-      <c r="AC17" s="94" t="n"/>
-      <c r="AD17" s="94" t="n"/>
-      <c r="AE17" s="95" t="n"/>
-      <c r="AF17" s="71" t="n"/>
-      <c r="AG17" s="94" t="n"/>
-      <c r="AH17" s="94" t="n"/>
-      <c r="AI17" s="94" t="n"/>
-      <c r="AJ17" s="94" t="n"/>
-      <c r="AK17" s="94" t="n"/>
-      <c r="AL17" s="94" t="n"/>
-      <c r="AM17" s="94" t="n"/>
-      <c r="AN17" s="95" t="n"/>
-      <c r="AO17" s="71" t="n"/>
-      <c r="AP17" s="94" t="n"/>
-      <c r="AQ17" s="94" t="n"/>
-      <c r="AR17" s="94" t="n"/>
-      <c r="AS17" s="95" t="n"/>
-      <c r="AT17" s="71" t="n"/>
-      <c r="AU17" s="94" t="n"/>
-      <c r="AV17" s="94" t="n"/>
-      <c r="AW17" s="94" t="n"/>
-      <c r="AX17" s="95" t="n"/>
-      <c r="AY17" s="71" t="n"/>
-      <c r="AZ17" s="94" t="n"/>
-      <c r="BA17" s="94" t="n"/>
-      <c r="BB17" s="94" t="n"/>
-      <c r="BC17" s="94" t="n"/>
-      <c r="BD17" s="95" t="n"/>
+      <c r="A17" s="181" t="n"/>
+      <c r="B17" s="74" t="n"/>
+      <c r="C17" s="74" t="n"/>
+      <c r="D17" s="74" t="n"/>
+      <c r="E17" s="74" t="n"/>
+      <c r="F17" s="74" t="n"/>
+      <c r="G17" s="155" t="n"/>
+      <c r="H17" s="74" t="n"/>
+      <c r="I17" s="74" t="n"/>
+      <c r="J17" s="74" t="n"/>
+      <c r="K17" s="74" t="n"/>
+      <c r="L17" s="74" t="n"/>
+      <c r="M17" s="74" t="n"/>
+      <c r="N17" s="155" t="n"/>
+      <c r="O17" s="74" t="n"/>
+      <c r="P17" s="74" t="n"/>
+      <c r="Q17" s="74" t="n"/>
+      <c r="R17" s="74" t="n"/>
+      <c r="S17" s="74" t="n"/>
+      <c r="T17" s="155" t="n"/>
+      <c r="U17" s="74" t="n"/>
+      <c r="V17" s="74" t="n"/>
+      <c r="W17" s="74" t="n"/>
+      <c r="X17" s="74" t="n"/>
+      <c r="Y17" s="74" t="n"/>
+      <c r="Z17" s="155" t="n"/>
+      <c r="AA17" s="74" t="n"/>
+      <c r="AB17" s="74" t="n"/>
+      <c r="AC17" s="74" t="n"/>
+      <c r="AD17" s="74" t="n"/>
+      <c r="AE17" s="74" t="n"/>
+      <c r="AF17" s="155" t="n"/>
+      <c r="AG17" s="74" t="n"/>
+      <c r="AH17" s="74" t="n"/>
+      <c r="AI17" s="74" t="n"/>
+      <c r="AJ17" s="74" t="n"/>
+      <c r="AK17" s="74" t="n"/>
+      <c r="AL17" s="74" t="n"/>
+      <c r="AM17" s="74" t="n"/>
+      <c r="AN17" s="74" t="n"/>
+      <c r="AO17" s="155" t="n"/>
+      <c r="AP17" s="74" t="n"/>
+      <c r="AQ17" s="74" t="n"/>
+      <c r="AR17" s="74" t="n"/>
+      <c r="AS17" s="74" t="n"/>
+      <c r="AT17" s="155" t="n"/>
+      <c r="AU17" s="74" t="n"/>
+      <c r="AV17" s="74" t="n"/>
+      <c r="AW17" s="74" t="n"/>
+      <c r="AX17" s="74" t="n"/>
+      <c r="AY17" s="155" t="n"/>
+      <c r="AZ17" s="74" t="n"/>
+      <c r="BA17" s="74" t="n"/>
+      <c r="BB17" s="74" t="n"/>
+      <c r="BC17" s="74" t="n"/>
+      <c r="BD17" s="157" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="81" t="n"/>
-      <c r="B18" s="94" t="n"/>
-      <c r="C18" s="94" t="n"/>
-      <c r="D18" s="94" t="n"/>
-      <c r="E18" s="94" t="n"/>
-      <c r="F18" s="95" t="n"/>
-      <c r="G18" s="81" t="n"/>
-      <c r="H18" s="94" t="n"/>
-      <c r="I18" s="94" t="n"/>
-      <c r="J18" s="94" t="n"/>
-      <c r="K18" s="94" t="n"/>
-      <c r="L18" s="94" t="n"/>
-      <c r="M18" s="95" t="n"/>
-      <c r="N18" s="81" t="n"/>
-      <c r="O18" s="94" t="n"/>
-      <c r="P18" s="94" t="n"/>
-      <c r="Q18" s="94" t="n"/>
-      <c r="R18" s="94" t="n"/>
-      <c r="S18" s="95" t="n"/>
-      <c r="T18" s="81" t="n"/>
-      <c r="U18" s="94" t="n"/>
-      <c r="V18" s="94" t="n"/>
-      <c r="W18" s="94" t="n"/>
-      <c r="X18" s="94" t="n"/>
-      <c r="Y18" s="95" t="n"/>
-      <c r="Z18" s="81" t="n"/>
-      <c r="AA18" s="94" t="n"/>
-      <c r="AB18" s="94" t="n"/>
-      <c r="AC18" s="94" t="n"/>
-      <c r="AD18" s="94" t="n"/>
-      <c r="AE18" s="95" t="n"/>
-      <c r="AF18" s="81" t="n"/>
-      <c r="AG18" s="94" t="n"/>
-      <c r="AH18" s="94" t="n"/>
-      <c r="AI18" s="94" t="n"/>
-      <c r="AJ18" s="94" t="n"/>
-      <c r="AK18" s="94" t="n"/>
-      <c r="AL18" s="94" t="n"/>
-      <c r="AM18" s="94" t="n"/>
-      <c r="AN18" s="95" t="n"/>
-      <c r="AO18" s="81" t="n"/>
-      <c r="AP18" s="94" t="n"/>
-      <c r="AQ18" s="94" t="n"/>
-      <c r="AR18" s="94" t="n"/>
-      <c r="AS18" s="95" t="n"/>
-      <c r="AT18" s="81" t="n"/>
-      <c r="AU18" s="94" t="n"/>
-      <c r="AV18" s="94" t="n"/>
-      <c r="AW18" s="94" t="n"/>
-      <c r="AX18" s="95" t="n"/>
-      <c r="AY18" s="81" t="n"/>
-      <c r="AZ18" s="94" t="n"/>
-      <c r="BA18" s="94" t="n"/>
-      <c r="BB18" s="94" t="n"/>
-      <c r="BC18" s="94" t="n"/>
-      <c r="BD18" s="95" t="n"/>
+      <c r="A18" s="179" t="n"/>
+      <c r="B18" s="74" t="n"/>
+      <c r="C18" s="74" t="n"/>
+      <c r="D18" s="74" t="n"/>
+      <c r="E18" s="74" t="n"/>
+      <c r="F18" s="74" t="n"/>
+      <c r="G18" s="180" t="n"/>
+      <c r="H18" s="74" t="n"/>
+      <c r="I18" s="74" t="n"/>
+      <c r="J18" s="74" t="n"/>
+      <c r="K18" s="74" t="n"/>
+      <c r="L18" s="74" t="n"/>
+      <c r="M18" s="74" t="n"/>
+      <c r="N18" s="180" t="n"/>
+      <c r="O18" s="74" t="n"/>
+      <c r="P18" s="74" t="n"/>
+      <c r="Q18" s="74" t="n"/>
+      <c r="R18" s="74" t="n"/>
+      <c r="S18" s="74" t="n"/>
+      <c r="T18" s="180" t="n"/>
+      <c r="U18" s="74" t="n"/>
+      <c r="V18" s="74" t="n"/>
+      <c r="W18" s="74" t="n"/>
+      <c r="X18" s="74" t="n"/>
+      <c r="Y18" s="74" t="n"/>
+      <c r="Z18" s="180" t="n"/>
+      <c r="AA18" s="74" t="n"/>
+      <c r="AB18" s="74" t="n"/>
+      <c r="AC18" s="74" t="n"/>
+      <c r="AD18" s="74" t="n"/>
+      <c r="AE18" s="74" t="n"/>
+      <c r="AF18" s="180" t="n"/>
+      <c r="AG18" s="74" t="n"/>
+      <c r="AH18" s="74" t="n"/>
+      <c r="AI18" s="74" t="n"/>
+      <c r="AJ18" s="74" t="n"/>
+      <c r="AK18" s="74" t="n"/>
+      <c r="AL18" s="74" t="n"/>
+      <c r="AM18" s="74" t="n"/>
+      <c r="AN18" s="74" t="n"/>
+      <c r="AO18" s="180" t="n"/>
+      <c r="AP18" s="74" t="n"/>
+      <c r="AQ18" s="74" t="n"/>
+      <c r="AR18" s="74" t="n"/>
+      <c r="AS18" s="74" t="n"/>
+      <c r="AT18" s="180" t="n"/>
+      <c r="AU18" s="74" t="n"/>
+      <c r="AV18" s="74" t="n"/>
+      <c r="AW18" s="74" t="n"/>
+      <c r="AX18" s="74" t="n"/>
+      <c r="AY18" s="180" t="n"/>
+      <c r="AZ18" s="74" t="n"/>
+      <c r="BA18" s="74" t="n"/>
+      <c r="BB18" s="74" t="n"/>
+      <c r="BC18" s="74" t="n"/>
+      <c r="BD18" s="157" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="71" t="n"/>
-      <c r="B19" s="94" t="n"/>
-      <c r="C19" s="94" t="n"/>
-      <c r="D19" s="94" t="n"/>
-      <c r="E19" s="94" t="n"/>
-      <c r="F19" s="95" t="n"/>
-      <c r="G19" s="71" t="n"/>
-      <c r="H19" s="94" t="n"/>
-      <c r="I19" s="94" t="n"/>
-      <c r="J19" s="94" t="n"/>
-      <c r="K19" s="94" t="n"/>
-      <c r="L19" s="94" t="n"/>
-      <c r="M19" s="95" t="n"/>
-      <c r="N19" s="71" t="n"/>
-      <c r="O19" s="94" t="n"/>
-      <c r="P19" s="94" t="n"/>
-      <c r="Q19" s="94" t="n"/>
-      <c r="R19" s="94" t="n"/>
-      <c r="S19" s="95" t="n"/>
-      <c r="T19" s="71" t="n"/>
-      <c r="U19" s="94" t="n"/>
-      <c r="V19" s="94" t="n"/>
-      <c r="W19" s="94" t="n"/>
-      <c r="X19" s="94" t="n"/>
-      <c r="Y19" s="95" t="n"/>
-      <c r="Z19" s="71" t="n"/>
-      <c r="AA19" s="94" t="n"/>
-      <c r="AB19" s="94" t="n"/>
-      <c r="AC19" s="94" t="n"/>
-      <c r="AD19" s="94" t="n"/>
-      <c r="AE19" s="95" t="n"/>
-      <c r="AF19" s="71" t="n"/>
-      <c r="AG19" s="94" t="n"/>
-      <c r="AH19" s="94" t="n"/>
-      <c r="AI19" s="94" t="n"/>
-      <c r="AJ19" s="94" t="n"/>
-      <c r="AK19" s="94" t="n"/>
-      <c r="AL19" s="94" t="n"/>
-      <c r="AM19" s="94" t="n"/>
-      <c r="AN19" s="95" t="n"/>
-      <c r="AO19" s="71" t="n"/>
-      <c r="AP19" s="94" t="n"/>
-      <c r="AQ19" s="94" t="n"/>
-      <c r="AR19" s="94" t="n"/>
-      <c r="AS19" s="95" t="n"/>
-      <c r="AT19" s="71" t="n"/>
-      <c r="AU19" s="94" t="n"/>
-      <c r="AV19" s="94" t="n"/>
-      <c r="AW19" s="94" t="n"/>
-      <c r="AX19" s="95" t="n"/>
-      <c r="AY19" s="71" t="n"/>
-      <c r="AZ19" s="94" t="n"/>
-      <c r="BA19" s="94" t="n"/>
-      <c r="BB19" s="94" t="n"/>
-      <c r="BC19" s="94" t="n"/>
-      <c r="BD19" s="95" t="n"/>
+      <c r="A19" s="181" t="n"/>
+      <c r="B19" s="74" t="n"/>
+      <c r="C19" s="74" t="n"/>
+      <c r="D19" s="74" t="n"/>
+      <c r="E19" s="74" t="n"/>
+      <c r="F19" s="74" t="n"/>
+      <c r="G19" s="155" t="n"/>
+      <c r="H19" s="74" t="n"/>
+      <c r="I19" s="74" t="n"/>
+      <c r="J19" s="74" t="n"/>
+      <c r="K19" s="74" t="n"/>
+      <c r="L19" s="74" t="n"/>
+      <c r="M19" s="74" t="n"/>
+      <c r="N19" s="155" t="n"/>
+      <c r="O19" s="74" t="n"/>
+      <c r="P19" s="74" t="n"/>
+      <c r="Q19" s="74" t="n"/>
+      <c r="R19" s="74" t="n"/>
+      <c r="S19" s="74" t="n"/>
+      <c r="T19" s="155" t="n"/>
+      <c r="U19" s="74" t="n"/>
+      <c r="V19" s="74" t="n"/>
+      <c r="W19" s="74" t="n"/>
+      <c r="X19" s="74" t="n"/>
+      <c r="Y19" s="74" t="n"/>
+      <c r="Z19" s="155" t="n"/>
+      <c r="AA19" s="74" t="n"/>
+      <c r="AB19" s="74" t="n"/>
+      <c r="AC19" s="74" t="n"/>
+      <c r="AD19" s="74" t="n"/>
+      <c r="AE19" s="74" t="n"/>
+      <c r="AF19" s="155" t="n"/>
+      <c r="AG19" s="74" t="n"/>
+      <c r="AH19" s="74" t="n"/>
+      <c r="AI19" s="74" t="n"/>
+      <c r="AJ19" s="74" t="n"/>
+      <c r="AK19" s="74" t="n"/>
+      <c r="AL19" s="74" t="n"/>
+      <c r="AM19" s="74" t="n"/>
+      <c r="AN19" s="74" t="n"/>
+      <c r="AO19" s="155" t="n"/>
+      <c r="AP19" s="74" t="n"/>
+      <c r="AQ19" s="74" t="n"/>
+      <c r="AR19" s="74" t="n"/>
+      <c r="AS19" s="74" t="n"/>
+      <c r="AT19" s="155" t="n"/>
+      <c r="AU19" s="74" t="n"/>
+      <c r="AV19" s="74" t="n"/>
+      <c r="AW19" s="74" t="n"/>
+      <c r="AX19" s="74" t="n"/>
+      <c r="AY19" s="155" t="n"/>
+      <c r="AZ19" s="74" t="n"/>
+      <c r="BA19" s="74" t="n"/>
+      <c r="BB19" s="74" t="n"/>
+      <c r="BC19" s="74" t="n"/>
+      <c r="BD19" s="157" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="81" t="n"/>
-      <c r="B20" s="94" t="n"/>
-      <c r="C20" s="94" t="n"/>
-      <c r="D20" s="94" t="n"/>
-      <c r="E20" s="94" t="n"/>
-      <c r="F20" s="95" t="n"/>
-      <c r="G20" s="81" t="n"/>
-      <c r="H20" s="94" t="n"/>
-      <c r="I20" s="94" t="n"/>
-      <c r="J20" s="94" t="n"/>
-      <c r="K20" s="94" t="n"/>
-      <c r="L20" s="94" t="n"/>
-      <c r="M20" s="95" t="n"/>
-      <c r="N20" s="81" t="n"/>
-      <c r="O20" s="94" t="n"/>
-      <c r="P20" s="94" t="n"/>
-      <c r="Q20" s="94" t="n"/>
-      <c r="R20" s="94" t="n"/>
-      <c r="S20" s="95" t="n"/>
-      <c r="T20" s="81" t="n"/>
-      <c r="U20" s="94" t="n"/>
-      <c r="V20" s="94" t="n"/>
-      <c r="W20" s="94" t="n"/>
-      <c r="X20" s="94" t="n"/>
-      <c r="Y20" s="95" t="n"/>
-      <c r="Z20" s="81" t="n"/>
-      <c r="AA20" s="94" t="n"/>
-      <c r="AB20" s="94" t="n"/>
-      <c r="AC20" s="94" t="n"/>
-      <c r="AD20" s="94" t="n"/>
-      <c r="AE20" s="95" t="n"/>
-      <c r="AF20" s="81" t="n"/>
-      <c r="AG20" s="94" t="n"/>
-      <c r="AH20" s="94" t="n"/>
-      <c r="AI20" s="94" t="n"/>
-      <c r="AJ20" s="94" t="n"/>
-      <c r="AK20" s="94" t="n"/>
-      <c r="AL20" s="94" t="n"/>
-      <c r="AM20" s="94" t="n"/>
-      <c r="AN20" s="95" t="n"/>
-      <c r="AO20" s="81" t="n"/>
-      <c r="AP20" s="94" t="n"/>
-      <c r="AQ20" s="94" t="n"/>
-      <c r="AR20" s="94" t="n"/>
-      <c r="AS20" s="95" t="n"/>
-      <c r="AT20" s="81" t="n"/>
-      <c r="AU20" s="94" t="n"/>
-      <c r="AV20" s="94" t="n"/>
-      <c r="AW20" s="94" t="n"/>
-      <c r="AX20" s="95" t="n"/>
-      <c r="AY20" s="81" t="n"/>
-      <c r="AZ20" s="94" t="n"/>
-      <c r="BA20" s="94" t="n"/>
-      <c r="BB20" s="94" t="n"/>
-      <c r="BC20" s="94" t="n"/>
-      <c r="BD20" s="95" t="n"/>
+      <c r="A20" s="182" t="n"/>
+      <c r="B20" s="161" t="n"/>
+      <c r="C20" s="161" t="n"/>
+      <c r="D20" s="161" t="n"/>
+      <c r="E20" s="161" t="n"/>
+      <c r="F20" s="161" t="n"/>
+      <c r="G20" s="183" t="n"/>
+      <c r="H20" s="161" t="n"/>
+      <c r="I20" s="161" t="n"/>
+      <c r="J20" s="161" t="n"/>
+      <c r="K20" s="161" t="n"/>
+      <c r="L20" s="161" t="n"/>
+      <c r="M20" s="161" t="n"/>
+      <c r="N20" s="183" t="n"/>
+      <c r="O20" s="161" t="n"/>
+      <c r="P20" s="161" t="n"/>
+      <c r="Q20" s="161" t="n"/>
+      <c r="R20" s="161" t="n"/>
+      <c r="S20" s="161" t="n"/>
+      <c r="T20" s="183" t="n"/>
+      <c r="U20" s="161" t="n"/>
+      <c r="V20" s="161" t="n"/>
+      <c r="W20" s="161" t="n"/>
+      <c r="X20" s="161" t="n"/>
+      <c r="Y20" s="161" t="n"/>
+      <c r="Z20" s="183" t="n"/>
+      <c r="AA20" s="161" t="n"/>
+      <c r="AB20" s="161" t="n"/>
+      <c r="AC20" s="161" t="n"/>
+      <c r="AD20" s="161" t="n"/>
+      <c r="AE20" s="161" t="n"/>
+      <c r="AF20" s="183" t="n"/>
+      <c r="AG20" s="161" t="n"/>
+      <c r="AH20" s="161" t="n"/>
+      <c r="AI20" s="161" t="n"/>
+      <c r="AJ20" s="161" t="n"/>
+      <c r="AK20" s="161" t="n"/>
+      <c r="AL20" s="161" t="n"/>
+      <c r="AM20" s="161" t="n"/>
+      <c r="AN20" s="161" t="n"/>
+      <c r="AO20" s="183" t="n"/>
+      <c r="AP20" s="161" t="n"/>
+      <c r="AQ20" s="161" t="n"/>
+      <c r="AR20" s="161" t="n"/>
+      <c r="AS20" s="161" t="n"/>
+      <c r="AT20" s="183" t="n"/>
+      <c r="AU20" s="161" t="n"/>
+      <c r="AV20" s="161" t="n"/>
+      <c r="AW20" s="161" t="n"/>
+      <c r="AX20" s="161" t="n"/>
+      <c r="AY20" s="183" t="n"/>
+      <c r="AZ20" s="161" t="n"/>
+      <c r="BA20" s="161" t="n"/>
+      <c r="BB20" s="161" t="n"/>
+      <c r="BC20" s="161" t="n"/>
+      <c r="BD20" s="163" t="n"/>
     </row>
-    <row r="21" ht="4" customHeight="1">
+    <row r="21" ht="3" customHeight="1">
       <c r="A21" s="66" t="n"/>
       <c r="B21" s="66" t="n"/>
       <c r="C21" s="66" t="n"/>
@@ -4659,67 +5513,67 @@
       <c r="BC21" s="66" t="n"/>
       <c r="BD21" s="66" t="n"/>
     </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="78" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="145" t="inlineStr">
         <is>
           <t>NOTICE: Controlled support sheet. Keep one row per controlled reference item and maintain traceable owner, date and evidence linkage.</t>
         </is>
       </c>
-      <c r="B22" s="86" t="n"/>
-      <c r="C22" s="86" t="n"/>
-      <c r="D22" s="86" t="n"/>
-      <c r="E22" s="86" t="n"/>
-      <c r="F22" s="86" t="n"/>
-      <c r="G22" s="86" t="n"/>
-      <c r="H22" s="86" t="n"/>
-      <c r="I22" s="86" t="n"/>
-      <c r="J22" s="86" t="n"/>
-      <c r="K22" s="86" t="n"/>
-      <c r="L22" s="86" t="n"/>
-      <c r="M22" s="86" t="n"/>
-      <c r="N22" s="86" t="n"/>
-      <c r="O22" s="86" t="n"/>
-      <c r="P22" s="86" t="n"/>
-      <c r="Q22" s="86" t="n"/>
-      <c r="R22" s="86" t="n"/>
-      <c r="S22" s="86" t="n"/>
-      <c r="T22" s="86" t="n"/>
-      <c r="U22" s="86" t="n"/>
-      <c r="V22" s="86" t="n"/>
-      <c r="W22" s="86" t="n"/>
-      <c r="X22" s="86" t="n"/>
-      <c r="Y22" s="86" t="n"/>
-      <c r="Z22" s="86" t="n"/>
-      <c r="AA22" s="86" t="n"/>
-      <c r="AB22" s="86" t="n"/>
-      <c r="AC22" s="86" t="n"/>
-      <c r="AD22" s="86" t="n"/>
-      <c r="AE22" s="86" t="n"/>
-      <c r="AF22" s="86" t="n"/>
-      <c r="AG22" s="86" t="n"/>
-      <c r="AH22" s="86" t="n"/>
-      <c r="AI22" s="86" t="n"/>
-      <c r="AJ22" s="86" t="n"/>
-      <c r="AK22" s="86" t="n"/>
-      <c r="AL22" s="86" t="n"/>
-      <c r="AM22" s="86" t="n"/>
-      <c r="AN22" s="86" t="n"/>
-      <c r="AO22" s="86" t="n"/>
-      <c r="AP22" s="86" t="n"/>
-      <c r="AQ22" s="86" t="n"/>
-      <c r="AR22" s="86" t="n"/>
-      <c r="AS22" s="86" t="n"/>
-      <c r="AT22" s="86" t="n"/>
-      <c r="AU22" s="86" t="n"/>
-      <c r="AV22" s="86" t="n"/>
-      <c r="AW22" s="86" t="n"/>
-      <c r="AX22" s="86" t="n"/>
-      <c r="AY22" s="86" t="n"/>
-      <c r="AZ22" s="86" t="n"/>
-      <c r="BA22" s="86" t="n"/>
-      <c r="BB22" s="86" t="n"/>
-      <c r="BC22" s="86" t="n"/>
-      <c r="BD22" s="87" t="n"/>
+      <c r="B22" s="146" t="n"/>
+      <c r="C22" s="146" t="n"/>
+      <c r="D22" s="146" t="n"/>
+      <c r="E22" s="146" t="n"/>
+      <c r="F22" s="146" t="n"/>
+      <c r="G22" s="146" t="n"/>
+      <c r="H22" s="146" t="n"/>
+      <c r="I22" s="146" t="n"/>
+      <c r="J22" s="146" t="n"/>
+      <c r="K22" s="146" t="n"/>
+      <c r="L22" s="146" t="n"/>
+      <c r="M22" s="146" t="n"/>
+      <c r="N22" s="146" t="n"/>
+      <c r="O22" s="146" t="n"/>
+      <c r="P22" s="146" t="n"/>
+      <c r="Q22" s="146" t="n"/>
+      <c r="R22" s="146" t="n"/>
+      <c r="S22" s="146" t="n"/>
+      <c r="T22" s="146" t="n"/>
+      <c r="U22" s="146" t="n"/>
+      <c r="V22" s="146" t="n"/>
+      <c r="W22" s="146" t="n"/>
+      <c r="X22" s="146" t="n"/>
+      <c r="Y22" s="146" t="n"/>
+      <c r="Z22" s="146" t="n"/>
+      <c r="AA22" s="146" t="n"/>
+      <c r="AB22" s="146" t="n"/>
+      <c r="AC22" s="146" t="n"/>
+      <c r="AD22" s="146" t="n"/>
+      <c r="AE22" s="146" t="n"/>
+      <c r="AF22" s="146" t="n"/>
+      <c r="AG22" s="146" t="n"/>
+      <c r="AH22" s="146" t="n"/>
+      <c r="AI22" s="146" t="n"/>
+      <c r="AJ22" s="146" t="n"/>
+      <c r="AK22" s="146" t="n"/>
+      <c r="AL22" s="146" t="n"/>
+      <c r="AM22" s="146" t="n"/>
+      <c r="AN22" s="146" t="n"/>
+      <c r="AO22" s="146" t="n"/>
+      <c r="AP22" s="146" t="n"/>
+      <c r="AQ22" s="146" t="n"/>
+      <c r="AR22" s="146" t="n"/>
+      <c r="AS22" s="146" t="n"/>
+      <c r="AT22" s="146" t="n"/>
+      <c r="AU22" s="146" t="n"/>
+      <c r="AV22" s="146" t="n"/>
+      <c r="AW22" s="146" t="n"/>
+      <c r="AX22" s="146" t="n"/>
+      <c r="AY22" s="146" t="n"/>
+      <c r="AZ22" s="146" t="n"/>
+      <c r="BA22" s="146" t="n"/>
+      <c r="BB22" s="146" t="n"/>
+      <c r="BC22" s="146" t="n"/>
+      <c r="BD22" s="147" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1"/>
     <row r="24" ht="20" customHeight="1"/>
@@ -4900,7 +5754,7 @@
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="105">
+  <mergeCells count="104">
     <mergeCell ref="AT13:AX13"/>
     <mergeCell ref="AO17:AS17"/>
     <mergeCell ref="AW2:BD2"/>
@@ -4917,7 +5771,6 @@
     <mergeCell ref="T16:Y16"/>
     <mergeCell ref="AQ4:AV4"/>
     <mergeCell ref="AO14:AS14"/>
-    <mergeCell ref="A6:BD6"/>
     <mergeCell ref="AW5:BD5"/>
     <mergeCell ref="Z19:AE19"/>
     <mergeCell ref="A13:F13"/>
@@ -5047,6 +5900,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5118,1134 +5972,1224 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="50" t="n"/>
-      <c r="B1" s="99" t="n"/>
-      <c r="C1" s="99" t="n"/>
-      <c r="D1" s="99" t="n"/>
-      <c r="E1" s="99" t="n"/>
-      <c r="F1" s="99" t="n"/>
-      <c r="G1" s="99" t="n"/>
-      <c r="H1" s="99" t="n"/>
-      <c r="I1" s="99" t="n"/>
-      <c r="J1" s="99" t="n"/>
-      <c r="K1" s="99" t="n"/>
-      <c r="L1" s="52" t="inlineStr">
+      <c r="A1" s="106" t="n"/>
+      <c r="B1" s="107" t="n"/>
+      <c r="C1" s="107" t="n"/>
+      <c r="D1" s="107" t="n"/>
+      <c r="E1" s="107" t="n"/>
+      <c r="F1" s="107" t="n"/>
+      <c r="G1" s="107" t="n"/>
+      <c r="H1" s="107" t="n"/>
+      <c r="I1" s="107" t="n"/>
+      <c r="J1" s="107" t="n"/>
+      <c r="K1" s="108" t="n"/>
+      <c r="L1" s="109" t="inlineStr">
         <is>
           <t>TRAINING PLAN — EVIDENCE REFERENCE REGISTER</t>
         </is>
       </c>
-      <c r="M1" s="99" t="n"/>
-      <c r="N1" s="99" t="n"/>
-      <c r="O1" s="99" t="n"/>
-      <c r="P1" s="99" t="n"/>
-      <c r="Q1" s="99" t="n"/>
-      <c r="R1" s="99" t="n"/>
-      <c r="S1" s="99" t="n"/>
-      <c r="T1" s="99" t="n"/>
-      <c r="U1" s="99" t="n"/>
-      <c r="V1" s="99" t="n"/>
-      <c r="W1" s="99" t="n"/>
-      <c r="X1" s="99" t="n"/>
-      <c r="Y1" s="99" t="n"/>
-      <c r="Z1" s="99" t="n"/>
-      <c r="AA1" s="99" t="n"/>
-      <c r="AB1" s="99" t="n"/>
-      <c r="AC1" s="99" t="n"/>
-      <c r="AD1" s="99" t="n"/>
-      <c r="AE1" s="99" t="n"/>
-      <c r="AF1" s="99" t="n"/>
-      <c r="AG1" s="99" t="n"/>
-      <c r="AH1" s="99" t="n"/>
-      <c r="AI1" s="99" t="n"/>
-      <c r="AJ1" s="99" t="n"/>
-      <c r="AK1" s="99" t="n"/>
-      <c r="AL1" s="99" t="n"/>
-      <c r="AM1" s="99" t="n"/>
-      <c r="AN1" s="99" t="n"/>
-      <c r="AO1" s="99" t="n"/>
-      <c r="AP1" s="99" t="n"/>
-      <c r="AQ1" s="53" t="inlineStr">
+      <c r="M1" s="110" t="n"/>
+      <c r="N1" s="110" t="n"/>
+      <c r="O1" s="110" t="n"/>
+      <c r="P1" s="110" t="n"/>
+      <c r="Q1" s="110" t="n"/>
+      <c r="R1" s="110" t="n"/>
+      <c r="S1" s="110" t="n"/>
+      <c r="T1" s="110" t="n"/>
+      <c r="U1" s="110" t="n"/>
+      <c r="V1" s="110" t="n"/>
+      <c r="W1" s="110" t="n"/>
+      <c r="X1" s="110" t="n"/>
+      <c r="Y1" s="110" t="n"/>
+      <c r="Z1" s="110" t="n"/>
+      <c r="AA1" s="110" t="n"/>
+      <c r="AB1" s="110" t="n"/>
+      <c r="AC1" s="110" t="n"/>
+      <c r="AD1" s="110" t="n"/>
+      <c r="AE1" s="110" t="n"/>
+      <c r="AF1" s="110" t="n"/>
+      <c r="AG1" s="110" t="n"/>
+      <c r="AH1" s="110" t="n"/>
+      <c r="AI1" s="110" t="n"/>
+      <c r="AJ1" s="110" t="n"/>
+      <c r="AK1" s="110" t="n"/>
+      <c r="AL1" s="110" t="n"/>
+      <c r="AM1" s="110" t="n"/>
+      <c r="AN1" s="110" t="n"/>
+      <c r="AO1" s="110" t="n"/>
+      <c r="AP1" s="111" t="n"/>
+      <c r="AQ1" s="112" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="100" t="n"/>
-      <c r="AS1" s="100" t="n"/>
-      <c r="AT1" s="100" t="n"/>
-      <c r="AU1" s="100" t="n"/>
-      <c r="AV1" s="101" t="n"/>
-      <c r="AW1" s="56" t="inlineStr">
+      <c r="AR1" s="113" t="n"/>
+      <c r="AS1" s="113" t="n"/>
+      <c r="AT1" s="113" t="n"/>
+      <c r="AU1" s="113" t="n"/>
+      <c r="AV1" s="114" t="n"/>
+      <c r="AW1" s="115" t="inlineStr">
         <is>
           <t>FRM-801</t>
         </is>
       </c>
-      <c r="AX1" s="100" t="n"/>
-      <c r="AY1" s="100" t="n"/>
-      <c r="AZ1" s="100" t="n"/>
-      <c r="BA1" s="100" t="n"/>
-      <c r="BB1" s="100" t="n"/>
-      <c r="BC1" s="100" t="n"/>
-      <c r="BD1" s="101" t="n"/>
+      <c r="AX1" s="116" t="n"/>
+      <c r="AY1" s="116" t="n"/>
+      <c r="AZ1" s="116" t="n"/>
+      <c r="BA1" s="116" t="n"/>
+      <c r="BB1" s="116" t="n"/>
+      <c r="BC1" s="116" t="n"/>
+      <c r="BD1" s="117" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="102" t="n"/>
-      <c r="L2" s="102" t="n"/>
-      <c r="AQ2" s="59" t="inlineStr">
+      <c r="A2" s="118" t="n"/>
+      <c r="B2" s="46" t="n"/>
+      <c r="C2" s="46" t="n"/>
+      <c r="D2" s="46" t="n"/>
+      <c r="E2" s="46" t="n"/>
+      <c r="F2" s="46" t="n"/>
+      <c r="G2" s="46" t="n"/>
+      <c r="H2" s="46" t="n"/>
+      <c r="I2" s="46" t="n"/>
+      <c r="J2" s="46" t="n"/>
+      <c r="K2" s="119" t="n"/>
+      <c r="L2" s="120" t="n"/>
+      <c r="M2" s="121" t="n"/>
+      <c r="N2" s="121" t="n"/>
+      <c r="O2" s="121" t="n"/>
+      <c r="P2" s="121" t="n"/>
+      <c r="Q2" s="121" t="n"/>
+      <c r="R2" s="121" t="n"/>
+      <c r="S2" s="121" t="n"/>
+      <c r="T2" s="121" t="n"/>
+      <c r="U2" s="121" t="n"/>
+      <c r="V2" s="121" t="n"/>
+      <c r="W2" s="121" t="n"/>
+      <c r="X2" s="121" t="n"/>
+      <c r="Y2" s="121" t="n"/>
+      <c r="Z2" s="121" t="n"/>
+      <c r="AA2" s="121" t="n"/>
+      <c r="AB2" s="121" t="n"/>
+      <c r="AC2" s="121" t="n"/>
+      <c r="AD2" s="121" t="n"/>
+      <c r="AE2" s="121" t="n"/>
+      <c r="AF2" s="121" t="n"/>
+      <c r="AG2" s="121" t="n"/>
+      <c r="AH2" s="121" t="n"/>
+      <c r="AI2" s="121" t="n"/>
+      <c r="AJ2" s="121" t="n"/>
+      <c r="AK2" s="121" t="n"/>
+      <c r="AL2" s="121" t="n"/>
+      <c r="AM2" s="121" t="n"/>
+      <c r="AN2" s="121" t="n"/>
+      <c r="AO2" s="121" t="n"/>
+      <c r="AP2" s="122" t="n"/>
+      <c r="AQ2" s="123" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="103" t="n"/>
-      <c r="AS2" s="103" t="n"/>
-      <c r="AT2" s="103" t="n"/>
-      <c r="AU2" s="103" t="n"/>
-      <c r="AV2" s="104" t="n"/>
-      <c r="AW2" s="62" t="inlineStr">
+      <c r="AR2" s="124" t="n"/>
+      <c r="AS2" s="124" t="n"/>
+      <c r="AT2" s="124" t="n"/>
+      <c r="AU2" s="124" t="n"/>
+      <c r="AV2" s="125" t="n"/>
+      <c r="AW2" s="126" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="103" t="n"/>
-      <c r="AY2" s="103" t="n"/>
-      <c r="AZ2" s="103" t="n"/>
-      <c r="BA2" s="103" t="n"/>
-      <c r="BB2" s="103" t="n"/>
-      <c r="BC2" s="103" t="n"/>
-      <c r="BD2" s="104" t="n"/>
+      <c r="AX2" s="127" t="n"/>
+      <c r="AY2" s="127" t="n"/>
+      <c r="AZ2" s="127" t="n"/>
+      <c r="BA2" s="127" t="n"/>
+      <c r="BB2" s="127" t="n"/>
+      <c r="BC2" s="127" t="n"/>
+      <c r="BD2" s="128" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="102" t="n"/>
-      <c r="L3" s="105" t="n"/>
-      <c r="M3" s="103" t="n"/>
-      <c r="N3" s="103" t="n"/>
-      <c r="O3" s="103" t="n"/>
-      <c r="P3" s="103" t="n"/>
-      <c r="Q3" s="103" t="n"/>
-      <c r="R3" s="103" t="n"/>
-      <c r="S3" s="103" t="n"/>
-      <c r="T3" s="103" t="n"/>
-      <c r="U3" s="103" t="n"/>
-      <c r="V3" s="103" t="n"/>
-      <c r="W3" s="103" t="n"/>
-      <c r="X3" s="103" t="n"/>
-      <c r="Y3" s="103" t="n"/>
-      <c r="Z3" s="103" t="n"/>
-      <c r="AA3" s="103" t="n"/>
-      <c r="AB3" s="103" t="n"/>
-      <c r="AC3" s="103" t="n"/>
-      <c r="AD3" s="103" t="n"/>
-      <c r="AE3" s="103" t="n"/>
-      <c r="AF3" s="103" t="n"/>
-      <c r="AG3" s="103" t="n"/>
-      <c r="AH3" s="103" t="n"/>
-      <c r="AI3" s="103" t="n"/>
-      <c r="AJ3" s="103" t="n"/>
-      <c r="AK3" s="103" t="n"/>
-      <c r="AL3" s="103" t="n"/>
-      <c r="AM3" s="103" t="n"/>
-      <c r="AN3" s="103" t="n"/>
-      <c r="AO3" s="103" t="n"/>
-      <c r="AP3" s="103" t="n"/>
-      <c r="AQ3" s="59" t="inlineStr">
+      <c r="A3" s="118" t="n"/>
+      <c r="B3" s="46" t="n"/>
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="46" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="46" t="n"/>
+      <c r="G3" s="46" t="n"/>
+      <c r="H3" s="46" t="n"/>
+      <c r="I3" s="46" t="n"/>
+      <c r="J3" s="46" t="n"/>
+      <c r="K3" s="119" t="n"/>
+      <c r="L3" s="120" t="n"/>
+      <c r="M3" s="121" t="n"/>
+      <c r="N3" s="121" t="n"/>
+      <c r="O3" s="121" t="n"/>
+      <c r="P3" s="121" t="n"/>
+      <c r="Q3" s="121" t="n"/>
+      <c r="R3" s="121" t="n"/>
+      <c r="S3" s="121" t="n"/>
+      <c r="T3" s="121" t="n"/>
+      <c r="U3" s="121" t="n"/>
+      <c r="V3" s="121" t="n"/>
+      <c r="W3" s="121" t="n"/>
+      <c r="X3" s="121" t="n"/>
+      <c r="Y3" s="121" t="n"/>
+      <c r="Z3" s="121" t="n"/>
+      <c r="AA3" s="121" t="n"/>
+      <c r="AB3" s="121" t="n"/>
+      <c r="AC3" s="121" t="n"/>
+      <c r="AD3" s="121" t="n"/>
+      <c r="AE3" s="121" t="n"/>
+      <c r="AF3" s="121" t="n"/>
+      <c r="AG3" s="121" t="n"/>
+      <c r="AH3" s="121" t="n"/>
+      <c r="AI3" s="121" t="n"/>
+      <c r="AJ3" s="121" t="n"/>
+      <c r="AK3" s="121" t="n"/>
+      <c r="AL3" s="121" t="n"/>
+      <c r="AM3" s="121" t="n"/>
+      <c r="AN3" s="121" t="n"/>
+      <c r="AO3" s="121" t="n"/>
+      <c r="AP3" s="122" t="n"/>
+      <c r="AQ3" s="123" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="103" t="n"/>
-      <c r="AS3" s="103" t="n"/>
-      <c r="AT3" s="103" t="n"/>
-      <c r="AU3" s="103" t="n"/>
-      <c r="AV3" s="104" t="n"/>
-      <c r="AW3" s="62" t="inlineStr">
+      <c r="AR3" s="124" t="n"/>
+      <c r="AS3" s="124" t="n"/>
+      <c r="AT3" s="124" t="n"/>
+      <c r="AU3" s="124" t="n"/>
+      <c r="AV3" s="125" t="n"/>
+      <c r="AW3" s="126" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="103" t="n"/>
-      <c r="AY3" s="103" t="n"/>
-      <c r="AZ3" s="103" t="n"/>
-      <c r="BA3" s="103" t="n"/>
-      <c r="BB3" s="103" t="n"/>
-      <c r="BC3" s="103" t="n"/>
-      <c r="BD3" s="104" t="n"/>
+      <c r="AX3" s="127" t="n"/>
+      <c r="AY3" s="127" t="n"/>
+      <c r="AZ3" s="127" t="n"/>
+      <c r="BA3" s="127" t="n"/>
+      <c r="BB3" s="127" t="n"/>
+      <c r="BC3" s="127" t="n"/>
+      <c r="BD3" s="128" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="102" t="n"/>
-      <c r="L4" s="64" t="inlineStr">
+      <c r="A4" s="118" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
+      <c r="I4" s="46" t="n"/>
+      <c r="J4" s="46" t="n"/>
+      <c r="K4" s="119" t="n"/>
+      <c r="L4" s="129" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="59" t="inlineStr">
+      <c r="M4" s="130" t="n"/>
+      <c r="N4" s="130" t="n"/>
+      <c r="O4" s="130" t="n"/>
+      <c r="P4" s="130" t="n"/>
+      <c r="Q4" s="130" t="n"/>
+      <c r="R4" s="130" t="n"/>
+      <c r="S4" s="130" t="n"/>
+      <c r="T4" s="130" t="n"/>
+      <c r="U4" s="130" t="n"/>
+      <c r="V4" s="130" t="n"/>
+      <c r="W4" s="130" t="n"/>
+      <c r="X4" s="130" t="n"/>
+      <c r="Y4" s="130" t="n"/>
+      <c r="Z4" s="130" t="n"/>
+      <c r="AA4" s="130" t="n"/>
+      <c r="AB4" s="130" t="n"/>
+      <c r="AC4" s="130" t="n"/>
+      <c r="AD4" s="130" t="n"/>
+      <c r="AE4" s="130" t="n"/>
+      <c r="AF4" s="130" t="n"/>
+      <c r="AG4" s="130" t="n"/>
+      <c r="AH4" s="130" t="n"/>
+      <c r="AI4" s="130" t="n"/>
+      <c r="AJ4" s="130" t="n"/>
+      <c r="AK4" s="130" t="n"/>
+      <c r="AL4" s="130" t="n"/>
+      <c r="AM4" s="130" t="n"/>
+      <c r="AN4" s="130" t="n"/>
+      <c r="AO4" s="130" t="n"/>
+      <c r="AP4" s="131" t="n"/>
+      <c r="AQ4" s="123" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="103" t="n"/>
-      <c r="AS4" s="103" t="n"/>
-      <c r="AT4" s="103" t="n"/>
-      <c r="AU4" s="103" t="n"/>
-      <c r="AV4" s="104" t="n"/>
-      <c r="AW4" s="62" t="inlineStr">
+      <c r="AR4" s="124" t="n"/>
+      <c r="AS4" s="124" t="n"/>
+      <c r="AT4" s="124" t="n"/>
+      <c r="AU4" s="124" t="n"/>
+      <c r="AV4" s="125" t="n"/>
+      <c r="AW4" s="126" t="inlineStr">
         <is>
           <t>HR + Department Manager</t>
         </is>
       </c>
-      <c r="AX4" s="103" t="n"/>
-      <c r="AY4" s="103" t="n"/>
-      <c r="AZ4" s="103" t="n"/>
-      <c r="BA4" s="103" t="n"/>
-      <c r="BB4" s="103" t="n"/>
-      <c r="BC4" s="103" t="n"/>
-      <c r="BD4" s="104" t="n"/>
+      <c r="AX4" s="127" t="n"/>
+      <c r="AY4" s="127" t="n"/>
+      <c r="AZ4" s="127" t="n"/>
+      <c r="BA4" s="127" t="n"/>
+      <c r="BB4" s="127" t="n"/>
+      <c r="BC4" s="127" t="n"/>
+      <c r="BD4" s="128" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="105" t="n"/>
-      <c r="B5" s="103" t="n"/>
-      <c r="C5" s="103" t="n"/>
-      <c r="D5" s="103" t="n"/>
-      <c r="E5" s="103" t="n"/>
-      <c r="F5" s="103" t="n"/>
-      <c r="G5" s="103" t="n"/>
-      <c r="H5" s="103" t="n"/>
-      <c r="I5" s="103" t="n"/>
-      <c r="J5" s="103" t="n"/>
-      <c r="K5" s="103" t="n"/>
-      <c r="L5" s="65" t="inlineStr">
+      <c r="A5" s="132" t="n"/>
+      <c r="B5" s="133" t="n"/>
+      <c r="C5" s="133" t="n"/>
+      <c r="D5" s="133" t="n"/>
+      <c r="E5" s="133" t="n"/>
+      <c r="F5" s="133" t="n"/>
+      <c r="G5" s="133" t="n"/>
+      <c r="H5" s="133" t="n"/>
+      <c r="I5" s="133" t="n"/>
+      <c r="J5" s="133" t="n"/>
+      <c r="K5" s="134" t="n"/>
+      <c r="L5" s="135" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="103" t="n"/>
-      <c r="N5" s="103" t="n"/>
-      <c r="O5" s="103" t="n"/>
-      <c r="P5" s="103" t="n"/>
-      <c r="Q5" s="103" t="n"/>
-      <c r="R5" s="103" t="n"/>
-      <c r="S5" s="103" t="n"/>
-      <c r="T5" s="103" t="n"/>
-      <c r="U5" s="103" t="n"/>
-      <c r="V5" s="103" t="n"/>
-      <c r="W5" s="103" t="n"/>
-      <c r="X5" s="103" t="n"/>
-      <c r="Y5" s="103" t="n"/>
-      <c r="Z5" s="103" t="n"/>
-      <c r="AA5" s="103" t="n"/>
-      <c r="AB5" s="103" t="n"/>
-      <c r="AC5" s="103" t="n"/>
-      <c r="AD5" s="103" t="n"/>
-      <c r="AE5" s="103" t="n"/>
-      <c r="AF5" s="103" t="n"/>
-      <c r="AG5" s="103" t="n"/>
-      <c r="AH5" s="103" t="n"/>
-      <c r="AI5" s="103" t="n"/>
-      <c r="AJ5" s="103" t="n"/>
-      <c r="AK5" s="103" t="n"/>
-      <c r="AL5" s="103" t="n"/>
-      <c r="AM5" s="103" t="n"/>
-      <c r="AN5" s="103" t="n"/>
-      <c r="AO5" s="103" t="n"/>
-      <c r="AP5" s="103" t="n"/>
-      <c r="AQ5" s="59" t="inlineStr">
+      <c r="M5" s="136" t="n"/>
+      <c r="N5" s="136" t="n"/>
+      <c r="O5" s="136" t="n"/>
+      <c r="P5" s="136" t="n"/>
+      <c r="Q5" s="136" t="n"/>
+      <c r="R5" s="136" t="n"/>
+      <c r="S5" s="136" t="n"/>
+      <c r="T5" s="136" t="n"/>
+      <c r="U5" s="136" t="n"/>
+      <c r="V5" s="136" t="n"/>
+      <c r="W5" s="136" t="n"/>
+      <c r="X5" s="136" t="n"/>
+      <c r="Y5" s="136" t="n"/>
+      <c r="Z5" s="136" t="n"/>
+      <c r="AA5" s="136" t="n"/>
+      <c r="AB5" s="136" t="n"/>
+      <c r="AC5" s="136" t="n"/>
+      <c r="AD5" s="136" t="n"/>
+      <c r="AE5" s="136" t="n"/>
+      <c r="AF5" s="136" t="n"/>
+      <c r="AG5" s="136" t="n"/>
+      <c r="AH5" s="136" t="n"/>
+      <c r="AI5" s="136" t="n"/>
+      <c r="AJ5" s="136" t="n"/>
+      <c r="AK5" s="136" t="n"/>
+      <c r="AL5" s="136" t="n"/>
+      <c r="AM5" s="136" t="n"/>
+      <c r="AN5" s="136" t="n"/>
+      <c r="AO5" s="136" t="n"/>
+      <c r="AP5" s="137" t="n"/>
+      <c r="AQ5" s="138" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="103" t="n"/>
-      <c r="AS5" s="103" t="n"/>
-      <c r="AT5" s="103" t="n"/>
-      <c r="AU5" s="103" t="n"/>
-      <c r="AV5" s="104" t="n"/>
-      <c r="AW5" s="62" t="inlineStr">
+      <c r="AR5" s="139" t="n"/>
+      <c r="AS5" s="139" t="n"/>
+      <c r="AT5" s="139" t="n"/>
+      <c r="AU5" s="139" t="n"/>
+      <c r="AV5" s="140" t="n"/>
+      <c r="AW5" s="141" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="103" t="n"/>
-      <c r="AY5" s="103" t="n"/>
-      <c r="AZ5" s="103" t="n"/>
-      <c r="BA5" s="103" t="n"/>
-      <c r="BB5" s="103" t="n"/>
-      <c r="BC5" s="103" t="n"/>
-      <c r="BD5" s="104" t="n"/>
+      <c r="AX5" s="142" t="n"/>
+      <c r="AY5" s="142" t="n"/>
+      <c r="AZ5" s="142" t="n"/>
+      <c r="BA5" s="142" t="n"/>
+      <c r="BB5" s="142" t="n"/>
+      <c r="BC5" s="142" t="n"/>
+      <c r="BD5" s="143" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="66" t="n"/>
-      <c r="B6" s="98" t="n"/>
-      <c r="C6" s="98" t="n"/>
-      <c r="D6" s="98" t="n"/>
-      <c r="E6" s="98" t="n"/>
-      <c r="F6" s="98" t="n"/>
-      <c r="G6" s="98" t="n"/>
-      <c r="H6" s="98" t="n"/>
-      <c r="I6" s="98" t="n"/>
-      <c r="J6" s="98" t="n"/>
-      <c r="K6" s="98" t="n"/>
-      <c r="L6" s="98" t="n"/>
-      <c r="M6" s="98" t="n"/>
-      <c r="N6" s="98" t="n"/>
-      <c r="O6" s="98" t="n"/>
-      <c r="P6" s="98" t="n"/>
-      <c r="Q6" s="98" t="n"/>
-      <c r="R6" s="98" t="n"/>
-      <c r="S6" s="98" t="n"/>
-      <c r="T6" s="98" t="n"/>
-      <c r="U6" s="98" t="n"/>
-      <c r="V6" s="98" t="n"/>
-      <c r="W6" s="98" t="n"/>
-      <c r="X6" s="98" t="n"/>
-      <c r="Y6" s="98" t="n"/>
-      <c r="Z6" s="98" t="n"/>
-      <c r="AA6" s="98" t="n"/>
-      <c r="AB6" s="98" t="n"/>
-      <c r="AC6" s="98" t="n"/>
-      <c r="AD6" s="98" t="n"/>
-      <c r="AE6" s="98" t="n"/>
-      <c r="AF6" s="98" t="n"/>
-      <c r="AG6" s="98" t="n"/>
-      <c r="AH6" s="98" t="n"/>
-      <c r="AI6" s="98" t="n"/>
-      <c r="AJ6" s="98" t="n"/>
-      <c r="AK6" s="98" t="n"/>
-      <c r="AL6" s="98" t="n"/>
-      <c r="AM6" s="98" t="n"/>
-      <c r="AN6" s="98" t="n"/>
-      <c r="AO6" s="98" t="n"/>
-      <c r="AP6" s="98" t="n"/>
-      <c r="AQ6" s="98" t="n"/>
-      <c r="AR6" s="98" t="n"/>
-      <c r="AS6" s="98" t="n"/>
-      <c r="AT6" s="98" t="n"/>
-      <c r="AU6" s="98" t="n"/>
-      <c r="AV6" s="98" t="n"/>
-      <c r="AW6" s="98" t="n"/>
-      <c r="AX6" s="98" t="n"/>
-      <c r="AY6" s="98" t="n"/>
-      <c r="AZ6" s="98" t="n"/>
-      <c r="BA6" s="98" t="n"/>
-      <c r="BB6" s="98" t="n"/>
-      <c r="BC6" s="98" t="n"/>
-      <c r="BD6" s="98" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="144" t="n"/>
+      <c r="B6" s="144" t="n"/>
+      <c r="C6" s="144" t="n"/>
+      <c r="D6" s="144" t="n"/>
+      <c r="E6" s="144" t="n"/>
+      <c r="F6" s="144" t="n"/>
+      <c r="G6" s="144" t="n"/>
+      <c r="H6" s="144" t="n"/>
+      <c r="I6" s="144" t="n"/>
+      <c r="J6" s="144" t="n"/>
+      <c r="K6" s="144" t="n"/>
+      <c r="L6" s="144" t="n"/>
+      <c r="M6" s="144" t="n"/>
+      <c r="N6" s="144" t="n"/>
+      <c r="O6" s="144" t="n"/>
+      <c r="P6" s="144" t="n"/>
+      <c r="Q6" s="144" t="n"/>
+      <c r="R6" s="144" t="n"/>
+      <c r="S6" s="144" t="n"/>
+      <c r="T6" s="144" t="n"/>
+      <c r="U6" s="144" t="n"/>
+      <c r="V6" s="144" t="n"/>
+      <c r="W6" s="144" t="n"/>
+      <c r="X6" s="144" t="n"/>
+      <c r="Y6" s="144" t="n"/>
+      <c r="Z6" s="144" t="n"/>
+      <c r="AA6" s="144" t="n"/>
+      <c r="AB6" s="144" t="n"/>
+      <c r="AC6" s="144" t="n"/>
+      <c r="AD6" s="144" t="n"/>
+      <c r="AE6" s="144" t="n"/>
+      <c r="AF6" s="144" t="n"/>
+      <c r="AG6" s="144" t="n"/>
+      <c r="AH6" s="144" t="n"/>
+      <c r="AI6" s="144" t="n"/>
+      <c r="AJ6" s="144" t="n"/>
+      <c r="AK6" s="144" t="n"/>
+      <c r="AL6" s="144" t="n"/>
+      <c r="AM6" s="144" t="n"/>
+      <c r="AN6" s="144" t="n"/>
+      <c r="AO6" s="144" t="n"/>
+      <c r="AP6" s="144" t="n"/>
+      <c r="AQ6" s="144" t="n"/>
+      <c r="AR6" s="144" t="n"/>
+      <c r="AS6" s="144" t="n"/>
+      <c r="AT6" s="144" t="n"/>
+      <c r="AU6" s="144" t="n"/>
+      <c r="AV6" s="144" t="n"/>
+      <c r="AW6" s="144" t="n"/>
+      <c r="AX6" s="144" t="n"/>
+      <c r="AY6" s="144" t="n"/>
+      <c r="AZ6" s="144" t="n"/>
+      <c r="BA6" s="144" t="n"/>
+      <c r="BB6" s="144" t="n"/>
+      <c r="BC6" s="144" t="n"/>
+      <c r="BD6" s="144" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="67" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="145" t="inlineStr">
         <is>
           <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
         </is>
       </c>
-      <c r="B7" s="100" t="n"/>
-      <c r="C7" s="100" t="n"/>
-      <c r="D7" s="100" t="n"/>
-      <c r="E7" s="100" t="n"/>
-      <c r="F7" s="100" t="n"/>
-      <c r="G7" s="100" t="n"/>
-      <c r="H7" s="100" t="n"/>
-      <c r="I7" s="100" t="n"/>
-      <c r="J7" s="100" t="n"/>
-      <c r="K7" s="100" t="n"/>
-      <c r="L7" s="100" t="n"/>
-      <c r="M7" s="100" t="n"/>
-      <c r="N7" s="100" t="n"/>
-      <c r="O7" s="100" t="n"/>
-      <c r="P7" s="100" t="n"/>
-      <c r="Q7" s="100" t="n"/>
-      <c r="R7" s="100" t="n"/>
-      <c r="S7" s="100" t="n"/>
-      <c r="T7" s="100" t="n"/>
-      <c r="U7" s="100" t="n"/>
-      <c r="V7" s="100" t="n"/>
-      <c r="W7" s="100" t="n"/>
-      <c r="X7" s="100" t="n"/>
-      <c r="Y7" s="100" t="n"/>
-      <c r="Z7" s="100" t="n"/>
-      <c r="AA7" s="100" t="n"/>
-      <c r="AB7" s="100" t="n"/>
-      <c r="AC7" s="100" t="n"/>
-      <c r="AD7" s="100" t="n"/>
-      <c r="AE7" s="100" t="n"/>
-      <c r="AF7" s="100" t="n"/>
-      <c r="AG7" s="100" t="n"/>
-      <c r="AH7" s="100" t="n"/>
-      <c r="AI7" s="100" t="n"/>
-      <c r="AJ7" s="100" t="n"/>
-      <c r="AK7" s="100" t="n"/>
-      <c r="AL7" s="100" t="n"/>
-      <c r="AM7" s="100" t="n"/>
-      <c r="AN7" s="100" t="n"/>
-      <c r="AO7" s="100" t="n"/>
-      <c r="AP7" s="100" t="n"/>
-      <c r="AQ7" s="100" t="n"/>
-      <c r="AR7" s="100" t="n"/>
-      <c r="AS7" s="100" t="n"/>
-      <c r="AT7" s="100" t="n"/>
-      <c r="AU7" s="100" t="n"/>
-      <c r="AV7" s="100" t="n"/>
-      <c r="AW7" s="100" t="n"/>
-      <c r="AX7" s="100" t="n"/>
-      <c r="AY7" s="100" t="n"/>
-      <c r="AZ7" s="100" t="n"/>
-      <c r="BA7" s="100" t="n"/>
-      <c r="BB7" s="100" t="n"/>
-      <c r="BC7" s="100" t="n"/>
-      <c r="BD7" s="101" t="n"/>
+      <c r="B7" s="146" t="n"/>
+      <c r="C7" s="146" t="n"/>
+      <c r="D7" s="146" t="n"/>
+      <c r="E7" s="146" t="n"/>
+      <c r="F7" s="146" t="n"/>
+      <c r="G7" s="146" t="n"/>
+      <c r="H7" s="146" t="n"/>
+      <c r="I7" s="146" t="n"/>
+      <c r="J7" s="146" t="n"/>
+      <c r="K7" s="146" t="n"/>
+      <c r="L7" s="146" t="n"/>
+      <c r="M7" s="146" t="n"/>
+      <c r="N7" s="146" t="n"/>
+      <c r="O7" s="146" t="n"/>
+      <c r="P7" s="146" t="n"/>
+      <c r="Q7" s="146" t="n"/>
+      <c r="R7" s="146" t="n"/>
+      <c r="S7" s="146" t="n"/>
+      <c r="T7" s="146" t="n"/>
+      <c r="U7" s="146" t="n"/>
+      <c r="V7" s="146" t="n"/>
+      <c r="W7" s="146" t="n"/>
+      <c r="X7" s="146" t="n"/>
+      <c r="Y7" s="146" t="n"/>
+      <c r="Z7" s="146" t="n"/>
+      <c r="AA7" s="146" t="n"/>
+      <c r="AB7" s="146" t="n"/>
+      <c r="AC7" s="146" t="n"/>
+      <c r="AD7" s="146" t="n"/>
+      <c r="AE7" s="146" t="n"/>
+      <c r="AF7" s="146" t="n"/>
+      <c r="AG7" s="146" t="n"/>
+      <c r="AH7" s="146" t="n"/>
+      <c r="AI7" s="146" t="n"/>
+      <c r="AJ7" s="146" t="n"/>
+      <c r="AK7" s="146" t="n"/>
+      <c r="AL7" s="146" t="n"/>
+      <c r="AM7" s="146" t="n"/>
+      <c r="AN7" s="146" t="n"/>
+      <c r="AO7" s="146" t="n"/>
+      <c r="AP7" s="146" t="n"/>
+      <c r="AQ7" s="146" t="n"/>
+      <c r="AR7" s="146" t="n"/>
+      <c r="AS7" s="146" t="n"/>
+      <c r="AT7" s="146" t="n"/>
+      <c r="AU7" s="146" t="n"/>
+      <c r="AV7" s="146" t="n"/>
+      <c r="AW7" s="146" t="n"/>
+      <c r="AX7" s="146" t="n"/>
+      <c r="AY7" s="146" t="n"/>
+      <c r="AZ7" s="146" t="n"/>
+      <c r="BA7" s="146" t="n"/>
+      <c r="BB7" s="146" t="n"/>
+      <c r="BC7" s="146" t="n"/>
+      <c r="BD7" s="147" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="68" t="inlineStr">
+      <c r="A8" s="148" t="inlineStr">
         <is>
           <t>Source Links</t>
         </is>
       </c>
-      <c r="B8" s="92" t="n"/>
-      <c r="C8" s="92" t="n"/>
-      <c r="D8" s="92" t="n"/>
-      <c r="E8" s="92" t="n"/>
-      <c r="F8" s="92" t="n"/>
-      <c r="G8" s="92" t="n"/>
-      <c r="H8" s="92" t="n"/>
-      <c r="I8" s="92" t="n"/>
-      <c r="J8" s="93" t="n"/>
-      <c r="K8" s="79" t="inlineStr">
+      <c r="B8" s="149" t="n"/>
+      <c r="C8" s="149" t="n"/>
+      <c r="D8" s="149" t="n"/>
+      <c r="E8" s="149" t="n"/>
+      <c r="F8" s="149" t="n"/>
+      <c r="G8" s="149" t="n"/>
+      <c r="H8" s="149" t="n"/>
+      <c r="I8" s="149" t="n"/>
+      <c r="J8" s="149" t="n"/>
+      <c r="K8" s="169" t="inlineStr">
         <is>
           <t>SOP-801; WI-801 / WI-804; ANNEX-HR-001 + ANNEX-QMS-027 / 028</t>
         </is>
       </c>
-      <c r="L8" s="92" t="n"/>
-      <c r="M8" s="92" t="n"/>
-      <c r="N8" s="92" t="n"/>
-      <c r="O8" s="92" t="n"/>
-      <c r="P8" s="92" t="n"/>
-      <c r="Q8" s="92" t="n"/>
-      <c r="R8" s="92" t="n"/>
-      <c r="S8" s="92" t="n"/>
-      <c r="T8" s="92" t="n"/>
-      <c r="U8" s="92" t="n"/>
-      <c r="V8" s="92" t="n"/>
-      <c r="W8" s="92" t="n"/>
-      <c r="X8" s="92" t="n"/>
-      <c r="Y8" s="92" t="n"/>
-      <c r="Z8" s="92" t="n"/>
-      <c r="AA8" s="92" t="n"/>
-      <c r="AB8" s="92" t="n"/>
-      <c r="AC8" s="92" t="n"/>
-      <c r="AD8" s="92" t="n"/>
-      <c r="AE8" s="92" t="n"/>
-      <c r="AF8" s="92" t="n"/>
-      <c r="AG8" s="92" t="n"/>
-      <c r="AH8" s="92" t="n"/>
-      <c r="AI8" s="92" t="n"/>
-      <c r="AJ8" s="92" t="n"/>
-      <c r="AK8" s="92" t="n"/>
-      <c r="AL8" s="92" t="n"/>
-      <c r="AM8" s="92" t="n"/>
-      <c r="AN8" s="92" t="n"/>
-      <c r="AO8" s="92" t="n"/>
-      <c r="AP8" s="92" t="n"/>
-      <c r="AQ8" s="92" t="n"/>
-      <c r="AR8" s="92" t="n"/>
-      <c r="AS8" s="92" t="n"/>
-      <c r="AT8" s="92" t="n"/>
-      <c r="AU8" s="92" t="n"/>
-      <c r="AV8" s="92" t="n"/>
-      <c r="AW8" s="92" t="n"/>
-      <c r="AX8" s="92" t="n"/>
-      <c r="AY8" s="92" t="n"/>
-      <c r="AZ8" s="92" t="n"/>
-      <c r="BA8" s="92" t="n"/>
-      <c r="BB8" s="92" t="n"/>
-      <c r="BC8" s="92" t="n"/>
-      <c r="BD8" s="93" t="n"/>
+      <c r="L8" s="149" t="n"/>
+      <c r="M8" s="149" t="n"/>
+      <c r="N8" s="149" t="n"/>
+      <c r="O8" s="149" t="n"/>
+      <c r="P8" s="149" t="n"/>
+      <c r="Q8" s="149" t="n"/>
+      <c r="R8" s="149" t="n"/>
+      <c r="S8" s="149" t="n"/>
+      <c r="T8" s="149" t="n"/>
+      <c r="U8" s="149" t="n"/>
+      <c r="V8" s="149" t="n"/>
+      <c r="W8" s="149" t="n"/>
+      <c r="X8" s="149" t="n"/>
+      <c r="Y8" s="149" t="n"/>
+      <c r="Z8" s="149" t="n"/>
+      <c r="AA8" s="149" t="n"/>
+      <c r="AB8" s="149" t="n"/>
+      <c r="AC8" s="149" t="n"/>
+      <c r="AD8" s="149" t="n"/>
+      <c r="AE8" s="149" t="n"/>
+      <c r="AF8" s="149" t="n"/>
+      <c r="AG8" s="149" t="n"/>
+      <c r="AH8" s="149" t="n"/>
+      <c r="AI8" s="149" t="n"/>
+      <c r="AJ8" s="149" t="n"/>
+      <c r="AK8" s="149" t="n"/>
+      <c r="AL8" s="149" t="n"/>
+      <c r="AM8" s="149" t="n"/>
+      <c r="AN8" s="149" t="n"/>
+      <c r="AO8" s="149" t="n"/>
+      <c r="AP8" s="149" t="n"/>
+      <c r="AQ8" s="149" t="n"/>
+      <c r="AR8" s="149" t="n"/>
+      <c r="AS8" s="149" t="n"/>
+      <c r="AT8" s="149" t="n"/>
+      <c r="AU8" s="149" t="n"/>
+      <c r="AV8" s="149" t="n"/>
+      <c r="AW8" s="149" t="n"/>
+      <c r="AX8" s="149" t="n"/>
+      <c r="AY8" s="149" t="n"/>
+      <c r="AZ8" s="149" t="n"/>
+      <c r="BA8" s="149" t="n"/>
+      <c r="BB8" s="149" t="n"/>
+      <c r="BC8" s="149" t="n"/>
+      <c r="BD8" s="166" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="68" t="inlineStr">
+      <c r="A9" s="154" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="B9" s="92" t="n"/>
-      <c r="C9" s="92" t="n"/>
-      <c r="D9" s="92" t="n"/>
-      <c r="E9" s="92" t="n"/>
-      <c r="F9" s="92" t="n"/>
-      <c r="G9" s="92" t="n"/>
-      <c r="H9" s="92" t="n"/>
-      <c r="I9" s="92" t="n"/>
-      <c r="J9" s="93" t="n"/>
-      <c r="K9" s="79" t="inlineStr">
+      <c r="B9" s="54" t="n"/>
+      <c r="C9" s="54" t="n"/>
+      <c r="D9" s="54" t="n"/>
+      <c r="E9" s="54" t="n"/>
+      <c r="F9" s="54" t="n"/>
+      <c r="G9" s="54" t="n"/>
+      <c r="H9" s="54" t="n"/>
+      <c r="I9" s="54" t="n"/>
+      <c r="J9" s="54" t="n"/>
+      <c r="K9" s="170" t="inlineStr">
         <is>
           <t>Record traceable evidence references only; do not duplicate system-owned master data.</t>
         </is>
       </c>
-      <c r="L9" s="92" t="n"/>
-      <c r="M9" s="92" t="n"/>
-      <c r="N9" s="92" t="n"/>
-      <c r="O9" s="92" t="n"/>
-      <c r="P9" s="92" t="n"/>
-      <c r="Q9" s="92" t="n"/>
-      <c r="R9" s="92" t="n"/>
-      <c r="S9" s="92" t="n"/>
-      <c r="T9" s="92" t="n"/>
-      <c r="U9" s="92" t="n"/>
-      <c r="V9" s="92" t="n"/>
-      <c r="W9" s="92" t="n"/>
-      <c r="X9" s="92" t="n"/>
-      <c r="Y9" s="92" t="n"/>
-      <c r="Z9" s="92" t="n"/>
-      <c r="AA9" s="92" t="n"/>
-      <c r="AB9" s="92" t="n"/>
-      <c r="AC9" s="92" t="n"/>
-      <c r="AD9" s="92" t="n"/>
-      <c r="AE9" s="92" t="n"/>
-      <c r="AF9" s="92" t="n"/>
-      <c r="AG9" s="92" t="n"/>
-      <c r="AH9" s="92" t="n"/>
-      <c r="AI9" s="92" t="n"/>
-      <c r="AJ9" s="92" t="n"/>
-      <c r="AK9" s="92" t="n"/>
-      <c r="AL9" s="92" t="n"/>
-      <c r="AM9" s="92" t="n"/>
-      <c r="AN9" s="92" t="n"/>
-      <c r="AO9" s="92" t="n"/>
-      <c r="AP9" s="92" t="n"/>
-      <c r="AQ9" s="92" t="n"/>
-      <c r="AR9" s="92" t="n"/>
-      <c r="AS9" s="92" t="n"/>
-      <c r="AT9" s="92" t="n"/>
-      <c r="AU9" s="92" t="n"/>
-      <c r="AV9" s="92" t="n"/>
-      <c r="AW9" s="92" t="n"/>
-      <c r="AX9" s="92" t="n"/>
-      <c r="AY9" s="92" t="n"/>
-      <c r="AZ9" s="92" t="n"/>
-      <c r="BA9" s="92" t="n"/>
-      <c r="BB9" s="92" t="n"/>
-      <c r="BC9" s="92" t="n"/>
-      <c r="BD9" s="93" t="n"/>
+      <c r="L9" s="54" t="n"/>
+      <c r="M9" s="54" t="n"/>
+      <c r="N9" s="54" t="n"/>
+      <c r="O9" s="54" t="n"/>
+      <c r="P9" s="54" t="n"/>
+      <c r="Q9" s="54" t="n"/>
+      <c r="R9" s="54" t="n"/>
+      <c r="S9" s="54" t="n"/>
+      <c r="T9" s="54" t="n"/>
+      <c r="U9" s="54" t="n"/>
+      <c r="V9" s="54" t="n"/>
+      <c r="W9" s="54" t="n"/>
+      <c r="X9" s="54" t="n"/>
+      <c r="Y9" s="54" t="n"/>
+      <c r="Z9" s="54" t="n"/>
+      <c r="AA9" s="54" t="n"/>
+      <c r="AB9" s="54" t="n"/>
+      <c r="AC9" s="54" t="n"/>
+      <c r="AD9" s="54" t="n"/>
+      <c r="AE9" s="54" t="n"/>
+      <c r="AF9" s="54" t="n"/>
+      <c r="AG9" s="54" t="n"/>
+      <c r="AH9" s="54" t="n"/>
+      <c r="AI9" s="54" t="n"/>
+      <c r="AJ9" s="54" t="n"/>
+      <c r="AK9" s="54" t="n"/>
+      <c r="AL9" s="54" t="n"/>
+      <c r="AM9" s="54" t="n"/>
+      <c r="AN9" s="54" t="n"/>
+      <c r="AO9" s="54" t="n"/>
+      <c r="AP9" s="54" t="n"/>
+      <c r="AQ9" s="54" t="n"/>
+      <c r="AR9" s="54" t="n"/>
+      <c r="AS9" s="54" t="n"/>
+      <c r="AT9" s="54" t="n"/>
+      <c r="AU9" s="54" t="n"/>
+      <c r="AV9" s="54" t="n"/>
+      <c r="AW9" s="54" t="n"/>
+      <c r="AX9" s="54" t="n"/>
+      <c r="AY9" s="54" t="n"/>
+      <c r="AZ9" s="54" t="n"/>
+      <c r="BA9" s="54" t="n"/>
+      <c r="BB9" s="54" t="n"/>
+      <c r="BC9" s="54" t="n"/>
+      <c r="BD9" s="171" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="68" t="inlineStr">
+      <c r="A10" s="158" t="inlineStr">
         <is>
           <t>Boundary / SoR</t>
         </is>
       </c>
-      <c r="B10" s="92" t="n"/>
-      <c r="C10" s="92" t="n"/>
-      <c r="D10" s="92" t="n"/>
-      <c r="E10" s="92" t="n"/>
-      <c r="F10" s="92" t="n"/>
-      <c r="G10" s="92" t="n"/>
-      <c r="H10" s="92" t="n"/>
-      <c r="I10" s="92" t="n"/>
-      <c r="J10" s="93" t="n"/>
-      <c r="K10" s="79" t="inlineStr">
+      <c r="B10" s="159" t="n"/>
+      <c r="C10" s="159" t="n"/>
+      <c r="D10" s="159" t="n"/>
+      <c r="E10" s="159" t="n"/>
+      <c r="F10" s="159" t="n"/>
+      <c r="G10" s="159" t="n"/>
+      <c r="H10" s="159" t="n"/>
+      <c r="I10" s="159" t="n"/>
+      <c r="J10" s="159" t="n"/>
+      <c r="K10" s="172" t="inlineStr">
         <is>
           <t>M365 evidence / shared workbook</t>
         </is>
       </c>
-      <c r="L10" s="92" t="n"/>
-      <c r="M10" s="92" t="n"/>
-      <c r="N10" s="92" t="n"/>
-      <c r="O10" s="92" t="n"/>
-      <c r="P10" s="92" t="n"/>
-      <c r="Q10" s="92" t="n"/>
-      <c r="R10" s="92" t="n"/>
-      <c r="S10" s="92" t="n"/>
-      <c r="T10" s="92" t="n"/>
-      <c r="U10" s="92" t="n"/>
-      <c r="V10" s="92" t="n"/>
-      <c r="W10" s="92" t="n"/>
-      <c r="X10" s="92" t="n"/>
-      <c r="Y10" s="92" t="n"/>
-      <c r="Z10" s="92" t="n"/>
-      <c r="AA10" s="92" t="n"/>
-      <c r="AB10" s="92" t="n"/>
-      <c r="AC10" s="92" t="n"/>
-      <c r="AD10" s="92" t="n"/>
-      <c r="AE10" s="92" t="n"/>
-      <c r="AF10" s="92" t="n"/>
-      <c r="AG10" s="92" t="n"/>
-      <c r="AH10" s="92" t="n"/>
-      <c r="AI10" s="92" t="n"/>
-      <c r="AJ10" s="92" t="n"/>
-      <c r="AK10" s="92" t="n"/>
-      <c r="AL10" s="92" t="n"/>
-      <c r="AM10" s="92" t="n"/>
-      <c r="AN10" s="92" t="n"/>
-      <c r="AO10" s="92" t="n"/>
-      <c r="AP10" s="92" t="n"/>
-      <c r="AQ10" s="92" t="n"/>
-      <c r="AR10" s="92" t="n"/>
-      <c r="AS10" s="92" t="n"/>
-      <c r="AT10" s="92" t="n"/>
-      <c r="AU10" s="92" t="n"/>
-      <c r="AV10" s="92" t="n"/>
-      <c r="AW10" s="92" t="n"/>
-      <c r="AX10" s="92" t="n"/>
-      <c r="AY10" s="92" t="n"/>
-      <c r="AZ10" s="92" t="n"/>
-      <c r="BA10" s="92" t="n"/>
-      <c r="BB10" s="92" t="n"/>
-      <c r="BC10" s="92" t="n"/>
-      <c r="BD10" s="93" t="n"/>
+      <c r="L10" s="159" t="n"/>
+      <c r="M10" s="159" t="n"/>
+      <c r="N10" s="159" t="n"/>
+      <c r="O10" s="159" t="n"/>
+      <c r="P10" s="159" t="n"/>
+      <c r="Q10" s="159" t="n"/>
+      <c r="R10" s="159" t="n"/>
+      <c r="S10" s="159" t="n"/>
+      <c r="T10" s="159" t="n"/>
+      <c r="U10" s="159" t="n"/>
+      <c r="V10" s="159" t="n"/>
+      <c r="W10" s="159" t="n"/>
+      <c r="X10" s="159" t="n"/>
+      <c r="Y10" s="159" t="n"/>
+      <c r="Z10" s="159" t="n"/>
+      <c r="AA10" s="159" t="n"/>
+      <c r="AB10" s="159" t="n"/>
+      <c r="AC10" s="159" t="n"/>
+      <c r="AD10" s="159" t="n"/>
+      <c r="AE10" s="159" t="n"/>
+      <c r="AF10" s="159" t="n"/>
+      <c r="AG10" s="159" t="n"/>
+      <c r="AH10" s="159" t="n"/>
+      <c r="AI10" s="159" t="n"/>
+      <c r="AJ10" s="159" t="n"/>
+      <c r="AK10" s="159" t="n"/>
+      <c r="AL10" s="159" t="n"/>
+      <c r="AM10" s="159" t="n"/>
+      <c r="AN10" s="159" t="n"/>
+      <c r="AO10" s="159" t="n"/>
+      <c r="AP10" s="159" t="n"/>
+      <c r="AQ10" s="159" t="n"/>
+      <c r="AR10" s="159" t="n"/>
+      <c r="AS10" s="159" t="n"/>
+      <c r="AT10" s="159" t="n"/>
+      <c r="AU10" s="159" t="n"/>
+      <c r="AV10" s="159" t="n"/>
+      <c r="AW10" s="159" t="n"/>
+      <c r="AX10" s="159" t="n"/>
+      <c r="AY10" s="159" t="n"/>
+      <c r="AZ10" s="159" t="n"/>
+      <c r="BA10" s="159" t="n"/>
+      <c r="BB10" s="159" t="n"/>
+      <c r="BC10" s="159" t="n"/>
+      <c r="BD10" s="173" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="67" t="inlineStr">
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="145" t="inlineStr">
         <is>
           <t xml:space="preserve">  SUPPORT TABLE</t>
         </is>
       </c>
-      <c r="B11" s="92" t="n"/>
-      <c r="C11" s="92" t="n"/>
-      <c r="D11" s="92" t="n"/>
-      <c r="E11" s="92" t="n"/>
-      <c r="F11" s="92" t="n"/>
-      <c r="G11" s="92" t="n"/>
-      <c r="H11" s="92" t="n"/>
-      <c r="I11" s="92" t="n"/>
-      <c r="J11" s="92" t="n"/>
-      <c r="K11" s="92" t="n"/>
-      <c r="L11" s="92" t="n"/>
-      <c r="M11" s="92" t="n"/>
-      <c r="N11" s="92" t="n"/>
-      <c r="O11" s="92" t="n"/>
-      <c r="P11" s="92" t="n"/>
-      <c r="Q11" s="92" t="n"/>
-      <c r="R11" s="92" t="n"/>
-      <c r="S11" s="92" t="n"/>
-      <c r="T11" s="92" t="n"/>
-      <c r="U11" s="92" t="n"/>
-      <c r="V11" s="92" t="n"/>
-      <c r="W11" s="92" t="n"/>
-      <c r="X11" s="92" t="n"/>
-      <c r="Y11" s="92" t="n"/>
-      <c r="Z11" s="92" t="n"/>
-      <c r="AA11" s="92" t="n"/>
-      <c r="AB11" s="92" t="n"/>
-      <c r="AC11" s="92" t="n"/>
-      <c r="AD11" s="92" t="n"/>
-      <c r="AE11" s="92" t="n"/>
-      <c r="AF11" s="92" t="n"/>
-      <c r="AG11" s="92" t="n"/>
-      <c r="AH11" s="92" t="n"/>
-      <c r="AI11" s="92" t="n"/>
-      <c r="AJ11" s="92" t="n"/>
-      <c r="AK11" s="92" t="n"/>
-      <c r="AL11" s="92" t="n"/>
-      <c r="AM11" s="92" t="n"/>
-      <c r="AN11" s="92" t="n"/>
-      <c r="AO11" s="92" t="n"/>
-      <c r="AP11" s="92" t="n"/>
-      <c r="AQ11" s="92" t="n"/>
-      <c r="AR11" s="92" t="n"/>
-      <c r="AS11" s="92" t="n"/>
-      <c r="AT11" s="92" t="n"/>
-      <c r="AU11" s="92" t="n"/>
-      <c r="AV11" s="92" t="n"/>
-      <c r="AW11" s="92" t="n"/>
-      <c r="AX11" s="92" t="n"/>
-      <c r="AY11" s="92" t="n"/>
-      <c r="AZ11" s="92" t="n"/>
-      <c r="BA11" s="92" t="n"/>
-      <c r="BB11" s="92" t="n"/>
-      <c r="BC11" s="92" t="n"/>
-      <c r="BD11" s="93" t="n"/>
+      <c r="B11" s="146" t="n"/>
+      <c r="C11" s="146" t="n"/>
+      <c r="D11" s="146" t="n"/>
+      <c r="E11" s="146" t="n"/>
+      <c r="F11" s="146" t="n"/>
+      <c r="G11" s="146" t="n"/>
+      <c r="H11" s="146" t="n"/>
+      <c r="I11" s="146" t="n"/>
+      <c r="J11" s="146" t="n"/>
+      <c r="K11" s="146" t="n"/>
+      <c r="L11" s="146" t="n"/>
+      <c r="M11" s="146" t="n"/>
+      <c r="N11" s="146" t="n"/>
+      <c r="O11" s="146" t="n"/>
+      <c r="P11" s="146" t="n"/>
+      <c r="Q11" s="146" t="n"/>
+      <c r="R11" s="146" t="n"/>
+      <c r="S11" s="146" t="n"/>
+      <c r="T11" s="146" t="n"/>
+      <c r="U11" s="146" t="n"/>
+      <c r="V11" s="146" t="n"/>
+      <c r="W11" s="146" t="n"/>
+      <c r="X11" s="146" t="n"/>
+      <c r="Y11" s="146" t="n"/>
+      <c r="Z11" s="146" t="n"/>
+      <c r="AA11" s="146" t="n"/>
+      <c r="AB11" s="146" t="n"/>
+      <c r="AC11" s="146" t="n"/>
+      <c r="AD11" s="146" t="n"/>
+      <c r="AE11" s="146" t="n"/>
+      <c r="AF11" s="146" t="n"/>
+      <c r="AG11" s="146" t="n"/>
+      <c r="AH11" s="146" t="n"/>
+      <c r="AI11" s="146" t="n"/>
+      <c r="AJ11" s="146" t="n"/>
+      <c r="AK11" s="146" t="n"/>
+      <c r="AL11" s="146" t="n"/>
+      <c r="AM11" s="146" t="n"/>
+      <c r="AN11" s="146" t="n"/>
+      <c r="AO11" s="146" t="n"/>
+      <c r="AP11" s="146" t="n"/>
+      <c r="AQ11" s="146" t="n"/>
+      <c r="AR11" s="146" t="n"/>
+      <c r="AS11" s="146" t="n"/>
+      <c r="AT11" s="146" t="n"/>
+      <c r="AU11" s="146" t="n"/>
+      <c r="AV11" s="146" t="n"/>
+      <c r="AW11" s="146" t="n"/>
+      <c r="AX11" s="146" t="n"/>
+      <c r="AY11" s="146" t="n"/>
+      <c r="AZ11" s="146" t="n"/>
+      <c r="BA11" s="146" t="n"/>
+      <c r="BB11" s="146" t="n"/>
+      <c r="BC11" s="146" t="n"/>
+      <c r="BD11" s="147" t="n"/>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="80" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="174" t="inlineStr">
         <is>
           <t>Evidence ID</t>
         </is>
       </c>
-      <c r="B12" s="92" t="n"/>
-      <c r="C12" s="92" t="n"/>
-      <c r="D12" s="92" t="n"/>
-      <c r="E12" s="92" t="n"/>
-      <c r="F12" s="93" t="n"/>
-      <c r="G12" s="80" t="inlineStr">
+      <c r="B12" s="175" t="n"/>
+      <c r="C12" s="175" t="n"/>
+      <c r="D12" s="175" t="n"/>
+      <c r="E12" s="175" t="n"/>
+      <c r="F12" s="175" t="n"/>
+      <c r="G12" s="176" t="inlineStr">
         <is>
           <t>Related Record</t>
         </is>
       </c>
-      <c r="H12" s="92" t="n"/>
-      <c r="I12" s="92" t="n"/>
-      <c r="J12" s="92" t="n"/>
-      <c r="K12" s="92" t="n"/>
-      <c r="L12" s="92" t="n"/>
-      <c r="M12" s="93" t="n"/>
-      <c r="N12" s="80" t="inlineStr">
+      <c r="H12" s="175" t="n"/>
+      <c r="I12" s="175" t="n"/>
+      <c r="J12" s="175" t="n"/>
+      <c r="K12" s="175" t="n"/>
+      <c r="L12" s="175" t="n"/>
+      <c r="M12" s="175" t="n"/>
+      <c r="N12" s="176" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="O12" s="92" t="n"/>
-      <c r="P12" s="92" t="n"/>
-      <c r="Q12" s="92" t="n"/>
-      <c r="R12" s="92" t="n"/>
-      <c r="S12" s="92" t="n"/>
-      <c r="T12" s="92" t="n"/>
-      <c r="U12" s="92" t="n"/>
-      <c r="V12" s="92" t="n"/>
-      <c r="W12" s="93" t="n"/>
-      <c r="X12" s="80" t="inlineStr">
+      <c r="O12" s="175" t="n"/>
+      <c r="P12" s="175" t="n"/>
+      <c r="Q12" s="175" t="n"/>
+      <c r="R12" s="175" t="n"/>
+      <c r="S12" s="175" t="n"/>
+      <c r="T12" s="175" t="n"/>
+      <c r="U12" s="175" t="n"/>
+      <c r="V12" s="175" t="n"/>
+      <c r="W12" s="175" t="n"/>
+      <c r="X12" s="176" t="inlineStr">
         <is>
           <t>Source System</t>
         </is>
       </c>
-      <c r="Y12" s="92" t="n"/>
-      <c r="Z12" s="92" t="n"/>
-      <c r="AA12" s="92" t="n"/>
-      <c r="AB12" s="92" t="n"/>
-      <c r="AC12" s="92" t="n"/>
-      <c r="AD12" s="93" t="n"/>
-      <c r="AE12" s="80" t="inlineStr">
+      <c r="Y12" s="175" t="n"/>
+      <c r="Z12" s="175" t="n"/>
+      <c r="AA12" s="175" t="n"/>
+      <c r="AB12" s="175" t="n"/>
+      <c r="AC12" s="175" t="n"/>
+      <c r="AD12" s="175" t="n"/>
+      <c r="AE12" s="176" t="inlineStr">
         <is>
           <t>Reference Path or Link</t>
         </is>
       </c>
-      <c r="AF12" s="92" t="n"/>
-      <c r="AG12" s="92" t="n"/>
-      <c r="AH12" s="92" t="n"/>
-      <c r="AI12" s="92" t="n"/>
-      <c r="AJ12" s="92" t="n"/>
-      <c r="AK12" s="92" t="n"/>
-      <c r="AL12" s="93" t="n"/>
-      <c r="AM12" s="80" t="inlineStr">
+      <c r="AF12" s="175" t="n"/>
+      <c r="AG12" s="175" t="n"/>
+      <c r="AH12" s="175" t="n"/>
+      <c r="AI12" s="175" t="n"/>
+      <c r="AJ12" s="175" t="n"/>
+      <c r="AK12" s="175" t="n"/>
+      <c r="AL12" s="175" t="n"/>
+      <c r="AM12" s="176" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AN12" s="92" t="n"/>
-      <c r="AO12" s="92" t="n"/>
-      <c r="AP12" s="92" t="n"/>
-      <c r="AQ12" s="92" t="n"/>
-      <c r="AR12" s="93" t="n"/>
-      <c r="AS12" s="80" t="inlineStr">
+      <c r="AN12" s="175" t="n"/>
+      <c r="AO12" s="175" t="n"/>
+      <c r="AP12" s="175" t="n"/>
+      <c r="AQ12" s="175" t="n"/>
+      <c r="AR12" s="175" t="n"/>
+      <c r="AS12" s="176" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="AT12" s="92" t="n"/>
-      <c r="AU12" s="92" t="n"/>
-      <c r="AV12" s="92" t="n"/>
-      <c r="AW12" s="93" t="n"/>
-      <c r="AX12" s="80" t="inlineStr">
+      <c r="AT12" s="175" t="n"/>
+      <c r="AU12" s="175" t="n"/>
+      <c r="AV12" s="175" t="n"/>
+      <c r="AW12" s="175" t="n"/>
+      <c r="AX12" s="176" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AY12" s="92" t="n"/>
-      <c r="AZ12" s="92" t="n"/>
-      <c r="BA12" s="92" t="n"/>
-      <c r="BB12" s="92" t="n"/>
-      <c r="BC12" s="92" t="n"/>
-      <c r="BD12" s="93" t="n"/>
+      <c r="AY12" s="175" t="n"/>
+      <c r="AZ12" s="175" t="n"/>
+      <c r="BA12" s="175" t="n"/>
+      <c r="BB12" s="175" t="n"/>
+      <c r="BC12" s="175" t="n"/>
+      <c r="BD12" s="177" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="71" t="n"/>
-      <c r="B13" s="94" t="n"/>
-      <c r="C13" s="94" t="n"/>
-      <c r="D13" s="94" t="n"/>
-      <c r="E13" s="94" t="n"/>
-      <c r="F13" s="95" t="n"/>
-      <c r="G13" s="71" t="n"/>
-      <c r="H13" s="94" t="n"/>
-      <c r="I13" s="94" t="n"/>
-      <c r="J13" s="94" t="n"/>
-      <c r="K13" s="94" t="n"/>
-      <c r="L13" s="94" t="n"/>
-      <c r="M13" s="95" t="n"/>
-      <c r="N13" s="71" t="n"/>
-      <c r="O13" s="94" t="n"/>
-      <c r="P13" s="94" t="n"/>
-      <c r="Q13" s="94" t="n"/>
-      <c r="R13" s="94" t="n"/>
-      <c r="S13" s="94" t="n"/>
-      <c r="T13" s="94" t="n"/>
-      <c r="U13" s="94" t="n"/>
-      <c r="V13" s="94" t="n"/>
-      <c r="W13" s="95" t="n"/>
-      <c r="X13" s="71" t="n"/>
-      <c r="Y13" s="94" t="n"/>
-      <c r="Z13" s="94" t="n"/>
-      <c r="AA13" s="94" t="n"/>
-      <c r="AB13" s="94" t="n"/>
-      <c r="AC13" s="94" t="n"/>
-      <c r="AD13" s="95" t="n"/>
-      <c r="AE13" s="71" t="n"/>
-      <c r="AF13" s="94" t="n"/>
-      <c r="AG13" s="94" t="n"/>
-      <c r="AH13" s="94" t="n"/>
-      <c r="AI13" s="94" t="n"/>
-      <c r="AJ13" s="94" t="n"/>
-      <c r="AK13" s="94" t="n"/>
-      <c r="AL13" s="95" t="n"/>
-      <c r="AM13" s="71" t="n"/>
-      <c r="AN13" s="94" t="n"/>
-      <c r="AO13" s="94" t="n"/>
-      <c r="AP13" s="94" t="n"/>
-      <c r="AQ13" s="94" t="n"/>
-      <c r="AR13" s="95" t="n"/>
-      <c r="AS13" s="71" t="n"/>
-      <c r="AT13" s="94" t="n"/>
-      <c r="AU13" s="94" t="n"/>
-      <c r="AV13" s="94" t="n"/>
-      <c r="AW13" s="95" t="n"/>
-      <c r="AX13" s="71" t="n"/>
-      <c r="AY13" s="94" t="n"/>
-      <c r="AZ13" s="94" t="n"/>
-      <c r="BA13" s="94" t="n"/>
-      <c r="BB13" s="94" t="n"/>
-      <c r="BC13" s="94" t="n"/>
-      <c r="BD13" s="95" t="n"/>
+      <c r="A13" s="178" t="n"/>
+      <c r="B13" s="151" t="n"/>
+      <c r="C13" s="151" t="n"/>
+      <c r="D13" s="151" t="n"/>
+      <c r="E13" s="151" t="n"/>
+      <c r="F13" s="151" t="n"/>
+      <c r="G13" s="150" t="n"/>
+      <c r="H13" s="151" t="n"/>
+      <c r="I13" s="151" t="n"/>
+      <c r="J13" s="151" t="n"/>
+      <c r="K13" s="151" t="n"/>
+      <c r="L13" s="151" t="n"/>
+      <c r="M13" s="151" t="n"/>
+      <c r="N13" s="150" t="n"/>
+      <c r="O13" s="151" t="n"/>
+      <c r="P13" s="151" t="n"/>
+      <c r="Q13" s="151" t="n"/>
+      <c r="R13" s="151" t="n"/>
+      <c r="S13" s="151" t="n"/>
+      <c r="T13" s="151" t="n"/>
+      <c r="U13" s="151" t="n"/>
+      <c r="V13" s="151" t="n"/>
+      <c r="W13" s="151" t="n"/>
+      <c r="X13" s="150" t="n"/>
+      <c r="Y13" s="151" t="n"/>
+      <c r="Z13" s="151" t="n"/>
+      <c r="AA13" s="151" t="n"/>
+      <c r="AB13" s="151" t="n"/>
+      <c r="AC13" s="151" t="n"/>
+      <c r="AD13" s="151" t="n"/>
+      <c r="AE13" s="150" t="n"/>
+      <c r="AF13" s="151" t="n"/>
+      <c r="AG13" s="151" t="n"/>
+      <c r="AH13" s="151" t="n"/>
+      <c r="AI13" s="151" t="n"/>
+      <c r="AJ13" s="151" t="n"/>
+      <c r="AK13" s="151" t="n"/>
+      <c r="AL13" s="151" t="n"/>
+      <c r="AM13" s="150" t="n"/>
+      <c r="AN13" s="151" t="n"/>
+      <c r="AO13" s="151" t="n"/>
+      <c r="AP13" s="151" t="n"/>
+      <c r="AQ13" s="151" t="n"/>
+      <c r="AR13" s="151" t="n"/>
+      <c r="AS13" s="150" t="n"/>
+      <c r="AT13" s="151" t="n"/>
+      <c r="AU13" s="151" t="n"/>
+      <c r="AV13" s="151" t="n"/>
+      <c r="AW13" s="151" t="n"/>
+      <c r="AX13" s="150" t="n"/>
+      <c r="AY13" s="151" t="n"/>
+      <c r="AZ13" s="151" t="n"/>
+      <c r="BA13" s="151" t="n"/>
+      <c r="BB13" s="151" t="n"/>
+      <c r="BC13" s="151" t="n"/>
+      <c r="BD13" s="153" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="81" t="n"/>
-      <c r="B14" s="94" t="n"/>
-      <c r="C14" s="94" t="n"/>
-      <c r="D14" s="94" t="n"/>
-      <c r="E14" s="94" t="n"/>
-      <c r="F14" s="95" t="n"/>
-      <c r="G14" s="81" t="n"/>
-      <c r="H14" s="94" t="n"/>
-      <c r="I14" s="94" t="n"/>
-      <c r="J14" s="94" t="n"/>
-      <c r="K14" s="94" t="n"/>
-      <c r="L14" s="94" t="n"/>
-      <c r="M14" s="95" t="n"/>
-      <c r="N14" s="81" t="n"/>
-      <c r="O14" s="94" t="n"/>
-      <c r="P14" s="94" t="n"/>
-      <c r="Q14" s="94" t="n"/>
-      <c r="R14" s="94" t="n"/>
-      <c r="S14" s="94" t="n"/>
-      <c r="T14" s="94" t="n"/>
-      <c r="U14" s="94" t="n"/>
-      <c r="V14" s="94" t="n"/>
-      <c r="W14" s="95" t="n"/>
-      <c r="X14" s="81" t="n"/>
-      <c r="Y14" s="94" t="n"/>
-      <c r="Z14" s="94" t="n"/>
-      <c r="AA14" s="94" t="n"/>
-      <c r="AB14" s="94" t="n"/>
-      <c r="AC14" s="94" t="n"/>
-      <c r="AD14" s="95" t="n"/>
-      <c r="AE14" s="81" t="n"/>
-      <c r="AF14" s="94" t="n"/>
-      <c r="AG14" s="94" t="n"/>
-      <c r="AH14" s="94" t="n"/>
-      <c r="AI14" s="94" t="n"/>
-      <c r="AJ14" s="94" t="n"/>
-      <c r="AK14" s="94" t="n"/>
-      <c r="AL14" s="95" t="n"/>
-      <c r="AM14" s="81" t="n"/>
-      <c r="AN14" s="94" t="n"/>
-      <c r="AO14" s="94" t="n"/>
-      <c r="AP14" s="94" t="n"/>
-      <c r="AQ14" s="94" t="n"/>
-      <c r="AR14" s="95" t="n"/>
-      <c r="AS14" s="81" t="n"/>
-      <c r="AT14" s="94" t="n"/>
-      <c r="AU14" s="94" t="n"/>
-      <c r="AV14" s="94" t="n"/>
-      <c r="AW14" s="95" t="n"/>
-      <c r="AX14" s="81" t="n"/>
-      <c r="AY14" s="94" t="n"/>
-      <c r="AZ14" s="94" t="n"/>
-      <c r="BA14" s="94" t="n"/>
-      <c r="BB14" s="94" t="n"/>
-      <c r="BC14" s="94" t="n"/>
-      <c r="BD14" s="95" t="n"/>
+      <c r="A14" s="179" t="n"/>
+      <c r="B14" s="74" t="n"/>
+      <c r="C14" s="74" t="n"/>
+      <c r="D14" s="74" t="n"/>
+      <c r="E14" s="74" t="n"/>
+      <c r="F14" s="74" t="n"/>
+      <c r="G14" s="180" t="n"/>
+      <c r="H14" s="74" t="n"/>
+      <c r="I14" s="74" t="n"/>
+      <c r="J14" s="74" t="n"/>
+      <c r="K14" s="74" t="n"/>
+      <c r="L14" s="74" t="n"/>
+      <c r="M14" s="74" t="n"/>
+      <c r="N14" s="180" t="n"/>
+      <c r="O14" s="74" t="n"/>
+      <c r="P14" s="74" t="n"/>
+      <c r="Q14" s="74" t="n"/>
+      <c r="R14" s="74" t="n"/>
+      <c r="S14" s="74" t="n"/>
+      <c r="T14" s="74" t="n"/>
+      <c r="U14" s="74" t="n"/>
+      <c r="V14" s="74" t="n"/>
+      <c r="W14" s="74" t="n"/>
+      <c r="X14" s="180" t="n"/>
+      <c r="Y14" s="74" t="n"/>
+      <c r="Z14" s="74" t="n"/>
+      <c r="AA14" s="74" t="n"/>
+      <c r="AB14" s="74" t="n"/>
+      <c r="AC14" s="74" t="n"/>
+      <c r="AD14" s="74" t="n"/>
+      <c r="AE14" s="180" t="n"/>
+      <c r="AF14" s="74" t="n"/>
+      <c r="AG14" s="74" t="n"/>
+      <c r="AH14" s="74" t="n"/>
+      <c r="AI14" s="74" t="n"/>
+      <c r="AJ14" s="74" t="n"/>
+      <c r="AK14" s="74" t="n"/>
+      <c r="AL14" s="74" t="n"/>
+      <c r="AM14" s="180" t="n"/>
+      <c r="AN14" s="74" t="n"/>
+      <c r="AO14" s="74" t="n"/>
+      <c r="AP14" s="74" t="n"/>
+      <c r="AQ14" s="74" t="n"/>
+      <c r="AR14" s="74" t="n"/>
+      <c r="AS14" s="180" t="n"/>
+      <c r="AT14" s="74" t="n"/>
+      <c r="AU14" s="74" t="n"/>
+      <c r="AV14" s="74" t="n"/>
+      <c r="AW14" s="74" t="n"/>
+      <c r="AX14" s="180" t="n"/>
+      <c r="AY14" s="74" t="n"/>
+      <c r="AZ14" s="74" t="n"/>
+      <c r="BA14" s="74" t="n"/>
+      <c r="BB14" s="74" t="n"/>
+      <c r="BC14" s="74" t="n"/>
+      <c r="BD14" s="157" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="71" t="n"/>
-      <c r="B15" s="94" t="n"/>
-      <c r="C15" s="94" t="n"/>
-      <c r="D15" s="94" t="n"/>
-      <c r="E15" s="94" t="n"/>
-      <c r="F15" s="95" t="n"/>
-      <c r="G15" s="71" t="n"/>
-      <c r="H15" s="94" t="n"/>
-      <c r="I15" s="94" t="n"/>
-      <c r="J15" s="94" t="n"/>
-      <c r="K15" s="94" t="n"/>
-      <c r="L15" s="94" t="n"/>
-      <c r="M15" s="95" t="n"/>
-      <c r="N15" s="71" t="n"/>
-      <c r="O15" s="94" t="n"/>
-      <c r="P15" s="94" t="n"/>
-      <c r="Q15" s="94" t="n"/>
-      <c r="R15" s="94" t="n"/>
-      <c r="S15" s="94" t="n"/>
-      <c r="T15" s="94" t="n"/>
-      <c r="U15" s="94" t="n"/>
-      <c r="V15" s="94" t="n"/>
-      <c r="W15" s="95" t="n"/>
-      <c r="X15" s="71" t="n"/>
-      <c r="Y15" s="94" t="n"/>
-      <c r="Z15" s="94" t="n"/>
-      <c r="AA15" s="94" t="n"/>
-      <c r="AB15" s="94" t="n"/>
-      <c r="AC15" s="94" t="n"/>
-      <c r="AD15" s="95" t="n"/>
-      <c r="AE15" s="71" t="n"/>
-      <c r="AF15" s="94" t="n"/>
-      <c r="AG15" s="94" t="n"/>
-      <c r="AH15" s="94" t="n"/>
-      <c r="AI15" s="94" t="n"/>
-      <c r="AJ15" s="94" t="n"/>
-      <c r="AK15" s="94" t="n"/>
-      <c r="AL15" s="95" t="n"/>
-      <c r="AM15" s="71" t="n"/>
-      <c r="AN15" s="94" t="n"/>
-      <c r="AO15" s="94" t="n"/>
-      <c r="AP15" s="94" t="n"/>
-      <c r="AQ15" s="94" t="n"/>
-      <c r="AR15" s="95" t="n"/>
-      <c r="AS15" s="71" t="n"/>
-      <c r="AT15" s="94" t="n"/>
-      <c r="AU15" s="94" t="n"/>
-      <c r="AV15" s="94" t="n"/>
-      <c r="AW15" s="95" t="n"/>
-      <c r="AX15" s="71" t="n"/>
-      <c r="AY15" s="94" t="n"/>
-      <c r="AZ15" s="94" t="n"/>
-      <c r="BA15" s="94" t="n"/>
-      <c r="BB15" s="94" t="n"/>
-      <c r="BC15" s="94" t="n"/>
-      <c r="BD15" s="95" t="n"/>
+      <c r="A15" s="181" t="n"/>
+      <c r="B15" s="74" t="n"/>
+      <c r="C15" s="74" t="n"/>
+      <c r="D15" s="74" t="n"/>
+      <c r="E15" s="74" t="n"/>
+      <c r="F15" s="74" t="n"/>
+      <c r="G15" s="155" t="n"/>
+      <c r="H15" s="74" t="n"/>
+      <c r="I15" s="74" t="n"/>
+      <c r="J15" s="74" t="n"/>
+      <c r="K15" s="74" t="n"/>
+      <c r="L15" s="74" t="n"/>
+      <c r="M15" s="74" t="n"/>
+      <c r="N15" s="155" t="n"/>
+      <c r="O15" s="74" t="n"/>
+      <c r="P15" s="74" t="n"/>
+      <c r="Q15" s="74" t="n"/>
+      <c r="R15" s="74" t="n"/>
+      <c r="S15" s="74" t="n"/>
+      <c r="T15" s="74" t="n"/>
+      <c r="U15" s="74" t="n"/>
+      <c r="V15" s="74" t="n"/>
+      <c r="W15" s="74" t="n"/>
+      <c r="X15" s="155" t="n"/>
+      <c r="Y15" s="74" t="n"/>
+      <c r="Z15" s="74" t="n"/>
+      <c r="AA15" s="74" t="n"/>
+      <c r="AB15" s="74" t="n"/>
+      <c r="AC15" s="74" t="n"/>
+      <c r="AD15" s="74" t="n"/>
+      <c r="AE15" s="155" t="n"/>
+      <c r="AF15" s="74" t="n"/>
+      <c r="AG15" s="74" t="n"/>
+      <c r="AH15" s="74" t="n"/>
+      <c r="AI15" s="74" t="n"/>
+      <c r="AJ15" s="74" t="n"/>
+      <c r="AK15" s="74" t="n"/>
+      <c r="AL15" s="74" t="n"/>
+      <c r="AM15" s="155" t="n"/>
+      <c r="AN15" s="74" t="n"/>
+      <c r="AO15" s="74" t="n"/>
+      <c r="AP15" s="74" t="n"/>
+      <c r="AQ15" s="74" t="n"/>
+      <c r="AR15" s="74" t="n"/>
+      <c r="AS15" s="155" t="n"/>
+      <c r="AT15" s="74" t="n"/>
+      <c r="AU15" s="74" t="n"/>
+      <c r="AV15" s="74" t="n"/>
+      <c r="AW15" s="74" t="n"/>
+      <c r="AX15" s="155" t="n"/>
+      <c r="AY15" s="74" t="n"/>
+      <c r="AZ15" s="74" t="n"/>
+      <c r="BA15" s="74" t="n"/>
+      <c r="BB15" s="74" t="n"/>
+      <c r="BC15" s="74" t="n"/>
+      <c r="BD15" s="157" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="81" t="n"/>
-      <c r="B16" s="94" t="n"/>
-      <c r="C16" s="94" t="n"/>
-      <c r="D16" s="94" t="n"/>
-      <c r="E16" s="94" t="n"/>
-      <c r="F16" s="95" t="n"/>
-      <c r="G16" s="81" t="n"/>
-      <c r="H16" s="94" t="n"/>
-      <c r="I16" s="94" t="n"/>
-      <c r="J16" s="94" t="n"/>
-      <c r="K16" s="94" t="n"/>
-      <c r="L16" s="94" t="n"/>
-      <c r="M16" s="95" t="n"/>
-      <c r="N16" s="81" t="n"/>
-      <c r="O16" s="94" t="n"/>
-      <c r="P16" s="94" t="n"/>
-      <c r="Q16" s="94" t="n"/>
-      <c r="R16" s="94" t="n"/>
-      <c r="S16" s="94" t="n"/>
-      <c r="T16" s="94" t="n"/>
-      <c r="U16" s="94" t="n"/>
-      <c r="V16" s="94" t="n"/>
-      <c r="W16" s="95" t="n"/>
-      <c r="X16" s="81" t="n"/>
-      <c r="Y16" s="94" t="n"/>
-      <c r="Z16" s="94" t="n"/>
-      <c r="AA16" s="94" t="n"/>
-      <c r="AB16" s="94" t="n"/>
-      <c r="AC16" s="94" t="n"/>
-      <c r="AD16" s="95" t="n"/>
-      <c r="AE16" s="81" t="n"/>
-      <c r="AF16" s="94" t="n"/>
-      <c r="AG16" s="94" t="n"/>
-      <c r="AH16" s="94" t="n"/>
-      <c r="AI16" s="94" t="n"/>
-      <c r="AJ16" s="94" t="n"/>
-      <c r="AK16" s="94" t="n"/>
-      <c r="AL16" s="95" t="n"/>
-      <c r="AM16" s="81" t="n"/>
-      <c r="AN16" s="94" t="n"/>
-      <c r="AO16" s="94" t="n"/>
-      <c r="AP16" s="94" t="n"/>
-      <c r="AQ16" s="94" t="n"/>
-      <c r="AR16" s="95" t="n"/>
-      <c r="AS16" s="81" t="n"/>
-      <c r="AT16" s="94" t="n"/>
-      <c r="AU16" s="94" t="n"/>
-      <c r="AV16" s="94" t="n"/>
-      <c r="AW16" s="95" t="n"/>
-      <c r="AX16" s="81" t="n"/>
-      <c r="AY16" s="94" t="n"/>
-      <c r="AZ16" s="94" t="n"/>
-      <c r="BA16" s="94" t="n"/>
-      <c r="BB16" s="94" t="n"/>
-      <c r="BC16" s="94" t="n"/>
-      <c r="BD16" s="95" t="n"/>
+      <c r="A16" s="179" t="n"/>
+      <c r="B16" s="74" t="n"/>
+      <c r="C16" s="74" t="n"/>
+      <c r="D16" s="74" t="n"/>
+      <c r="E16" s="74" t="n"/>
+      <c r="F16" s="74" t="n"/>
+      <c r="G16" s="180" t="n"/>
+      <c r="H16" s="74" t="n"/>
+      <c r="I16" s="74" t="n"/>
+      <c r="J16" s="74" t="n"/>
+      <c r="K16" s="74" t="n"/>
+      <c r="L16" s="74" t="n"/>
+      <c r="M16" s="74" t="n"/>
+      <c r="N16" s="180" t="n"/>
+      <c r="O16" s="74" t="n"/>
+      <c r="P16" s="74" t="n"/>
+      <c r="Q16" s="74" t="n"/>
+      <c r="R16" s="74" t="n"/>
+      <c r="S16" s="74" t="n"/>
+      <c r="T16" s="74" t="n"/>
+      <c r="U16" s="74" t="n"/>
+      <c r="V16" s="74" t="n"/>
+      <c r="W16" s="74" t="n"/>
+      <c r="X16" s="180" t="n"/>
+      <c r="Y16" s="74" t="n"/>
+      <c r="Z16" s="74" t="n"/>
+      <c r="AA16" s="74" t="n"/>
+      <c r="AB16" s="74" t="n"/>
+      <c r="AC16" s="74" t="n"/>
+      <c r="AD16" s="74" t="n"/>
+      <c r="AE16" s="180" t="n"/>
+      <c r="AF16" s="74" t="n"/>
+      <c r="AG16" s="74" t="n"/>
+      <c r="AH16" s="74" t="n"/>
+      <c r="AI16" s="74" t="n"/>
+      <c r="AJ16" s="74" t="n"/>
+      <c r="AK16" s="74" t="n"/>
+      <c r="AL16" s="74" t="n"/>
+      <c r="AM16" s="180" t="n"/>
+      <c r="AN16" s="74" t="n"/>
+      <c r="AO16" s="74" t="n"/>
+      <c r="AP16" s="74" t="n"/>
+      <c r="AQ16" s="74" t="n"/>
+      <c r="AR16" s="74" t="n"/>
+      <c r="AS16" s="180" t="n"/>
+      <c r="AT16" s="74" t="n"/>
+      <c r="AU16" s="74" t="n"/>
+      <c r="AV16" s="74" t="n"/>
+      <c r="AW16" s="74" t="n"/>
+      <c r="AX16" s="180" t="n"/>
+      <c r="AY16" s="74" t="n"/>
+      <c r="AZ16" s="74" t="n"/>
+      <c r="BA16" s="74" t="n"/>
+      <c r="BB16" s="74" t="n"/>
+      <c r="BC16" s="74" t="n"/>
+      <c r="BD16" s="157" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="71" t="n"/>
-      <c r="B17" s="94" t="n"/>
-      <c r="C17" s="94" t="n"/>
-      <c r="D17" s="94" t="n"/>
-      <c r="E17" s="94" t="n"/>
-      <c r="F17" s="95" t="n"/>
-      <c r="G17" s="71" t="n"/>
-      <c r="H17" s="94" t="n"/>
-      <c r="I17" s="94" t="n"/>
-      <c r="J17" s="94" t="n"/>
-      <c r="K17" s="94" t="n"/>
-      <c r="L17" s="94" t="n"/>
-      <c r="M17" s="95" t="n"/>
-      <c r="N17" s="71" t="n"/>
-      <c r="O17" s="94" t="n"/>
-      <c r="P17" s="94" t="n"/>
-      <c r="Q17" s="94" t="n"/>
-      <c r="R17" s="94" t="n"/>
-      <c r="S17" s="94" t="n"/>
-      <c r="T17" s="94" t="n"/>
-      <c r="U17" s="94" t="n"/>
-      <c r="V17" s="94" t="n"/>
-      <c r="W17" s="95" t="n"/>
-      <c r="X17" s="71" t="n"/>
-      <c r="Y17" s="94" t="n"/>
-      <c r="Z17" s="94" t="n"/>
-      <c r="AA17" s="94" t="n"/>
-      <c r="AB17" s="94" t="n"/>
-      <c r="AC17" s="94" t="n"/>
-      <c r="AD17" s="95" t="n"/>
-      <c r="AE17" s="71" t="n"/>
-      <c r="AF17" s="94" t="n"/>
-      <c r="AG17" s="94" t="n"/>
-      <c r="AH17" s="94" t="n"/>
-      <c r="AI17" s="94" t="n"/>
-      <c r="AJ17" s="94" t="n"/>
-      <c r="AK17" s="94" t="n"/>
-      <c r="AL17" s="95" t="n"/>
-      <c r="AM17" s="71" t="n"/>
-      <c r="AN17" s="94" t="n"/>
-      <c r="AO17" s="94" t="n"/>
-      <c r="AP17" s="94" t="n"/>
-      <c r="AQ17" s="94" t="n"/>
-      <c r="AR17" s="95" t="n"/>
-      <c r="AS17" s="71" t="n"/>
-      <c r="AT17" s="94" t="n"/>
-      <c r="AU17" s="94" t="n"/>
-      <c r="AV17" s="94" t="n"/>
-      <c r="AW17" s="95" t="n"/>
-      <c r="AX17" s="71" t="n"/>
-      <c r="AY17" s="94" t="n"/>
-      <c r="AZ17" s="94" t="n"/>
-      <c r="BA17" s="94" t="n"/>
-      <c r="BB17" s="94" t="n"/>
-      <c r="BC17" s="94" t="n"/>
-      <c r="BD17" s="95" t="n"/>
+      <c r="A17" s="181" t="n"/>
+      <c r="B17" s="74" t="n"/>
+      <c r="C17" s="74" t="n"/>
+      <c r="D17" s="74" t="n"/>
+      <c r="E17" s="74" t="n"/>
+      <c r="F17" s="74" t="n"/>
+      <c r="G17" s="155" t="n"/>
+      <c r="H17" s="74" t="n"/>
+      <c r="I17" s="74" t="n"/>
+      <c r="J17" s="74" t="n"/>
+      <c r="K17" s="74" t="n"/>
+      <c r="L17" s="74" t="n"/>
+      <c r="M17" s="74" t="n"/>
+      <c r="N17" s="155" t="n"/>
+      <c r="O17" s="74" t="n"/>
+      <c r="P17" s="74" t="n"/>
+      <c r="Q17" s="74" t="n"/>
+      <c r="R17" s="74" t="n"/>
+      <c r="S17" s="74" t="n"/>
+      <c r="T17" s="74" t="n"/>
+      <c r="U17" s="74" t="n"/>
+      <c r="V17" s="74" t="n"/>
+      <c r="W17" s="74" t="n"/>
+      <c r="X17" s="155" t="n"/>
+      <c r="Y17" s="74" t="n"/>
+      <c r="Z17" s="74" t="n"/>
+      <c r="AA17" s="74" t="n"/>
+      <c r="AB17" s="74" t="n"/>
+      <c r="AC17" s="74" t="n"/>
+      <c r="AD17" s="74" t="n"/>
+      <c r="AE17" s="155" t="n"/>
+      <c r="AF17" s="74" t="n"/>
+      <c r="AG17" s="74" t="n"/>
+      <c r="AH17" s="74" t="n"/>
+      <c r="AI17" s="74" t="n"/>
+      <c r="AJ17" s="74" t="n"/>
+      <c r="AK17" s="74" t="n"/>
+      <c r="AL17" s="74" t="n"/>
+      <c r="AM17" s="155" t="n"/>
+      <c r="AN17" s="74" t="n"/>
+      <c r="AO17" s="74" t="n"/>
+      <c r="AP17" s="74" t="n"/>
+      <c r="AQ17" s="74" t="n"/>
+      <c r="AR17" s="74" t="n"/>
+      <c r="AS17" s="155" t="n"/>
+      <c r="AT17" s="74" t="n"/>
+      <c r="AU17" s="74" t="n"/>
+      <c r="AV17" s="74" t="n"/>
+      <c r="AW17" s="74" t="n"/>
+      <c r="AX17" s="155" t="n"/>
+      <c r="AY17" s="74" t="n"/>
+      <c r="AZ17" s="74" t="n"/>
+      <c r="BA17" s="74" t="n"/>
+      <c r="BB17" s="74" t="n"/>
+      <c r="BC17" s="74" t="n"/>
+      <c r="BD17" s="157" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="81" t="n"/>
-      <c r="B18" s="94" t="n"/>
-      <c r="C18" s="94" t="n"/>
-      <c r="D18" s="94" t="n"/>
-      <c r="E18" s="94" t="n"/>
-      <c r="F18" s="95" t="n"/>
-      <c r="G18" s="81" t="n"/>
-      <c r="H18" s="94" t="n"/>
-      <c r="I18" s="94" t="n"/>
-      <c r="J18" s="94" t="n"/>
-      <c r="K18" s="94" t="n"/>
-      <c r="L18" s="94" t="n"/>
-      <c r="M18" s="95" t="n"/>
-      <c r="N18" s="81" t="n"/>
-      <c r="O18" s="94" t="n"/>
-      <c r="P18" s="94" t="n"/>
-      <c r="Q18" s="94" t="n"/>
-      <c r="R18" s="94" t="n"/>
-      <c r="S18" s="94" t="n"/>
-      <c r="T18" s="94" t="n"/>
-      <c r="U18" s="94" t="n"/>
-      <c r="V18" s="94" t="n"/>
-      <c r="W18" s="95" t="n"/>
-      <c r="X18" s="81" t="n"/>
-      <c r="Y18" s="94" t="n"/>
-      <c r="Z18" s="94" t="n"/>
-      <c r="AA18" s="94" t="n"/>
-      <c r="AB18" s="94" t="n"/>
-      <c r="AC18" s="94" t="n"/>
-      <c r="AD18" s="95" t="n"/>
-      <c r="AE18" s="81" t="n"/>
-      <c r="AF18" s="94" t="n"/>
-      <c r="AG18" s="94" t="n"/>
-      <c r="AH18" s="94" t="n"/>
-      <c r="AI18" s="94" t="n"/>
-      <c r="AJ18" s="94" t="n"/>
-      <c r="AK18" s="94" t="n"/>
-      <c r="AL18" s="95" t="n"/>
-      <c r="AM18" s="81" t="n"/>
-      <c r="AN18" s="94" t="n"/>
-      <c r="AO18" s="94" t="n"/>
-      <c r="AP18" s="94" t="n"/>
-      <c r="AQ18" s="94" t="n"/>
-      <c r="AR18" s="95" t="n"/>
-      <c r="AS18" s="81" t="n"/>
-      <c r="AT18" s="94" t="n"/>
-      <c r="AU18" s="94" t="n"/>
-      <c r="AV18" s="94" t="n"/>
-      <c r="AW18" s="95" t="n"/>
-      <c r="AX18" s="81" t="n"/>
-      <c r="AY18" s="94" t="n"/>
-      <c r="AZ18" s="94" t="n"/>
-      <c r="BA18" s="94" t="n"/>
-      <c r="BB18" s="94" t="n"/>
-      <c r="BC18" s="94" t="n"/>
-      <c r="BD18" s="95" t="n"/>
+      <c r="A18" s="179" t="n"/>
+      <c r="B18" s="74" t="n"/>
+      <c r="C18" s="74" t="n"/>
+      <c r="D18" s="74" t="n"/>
+      <c r="E18" s="74" t="n"/>
+      <c r="F18" s="74" t="n"/>
+      <c r="G18" s="180" t="n"/>
+      <c r="H18" s="74" t="n"/>
+      <c r="I18" s="74" t="n"/>
+      <c r="J18" s="74" t="n"/>
+      <c r="K18" s="74" t="n"/>
+      <c r="L18" s="74" t="n"/>
+      <c r="M18" s="74" t="n"/>
+      <c r="N18" s="180" t="n"/>
+      <c r="O18" s="74" t="n"/>
+      <c r="P18" s="74" t="n"/>
+      <c r="Q18" s="74" t="n"/>
+      <c r="R18" s="74" t="n"/>
+      <c r="S18" s="74" t="n"/>
+      <c r="T18" s="74" t="n"/>
+      <c r="U18" s="74" t="n"/>
+      <c r="V18" s="74" t="n"/>
+      <c r="W18" s="74" t="n"/>
+      <c r="X18" s="180" t="n"/>
+      <c r="Y18" s="74" t="n"/>
+      <c r="Z18" s="74" t="n"/>
+      <c r="AA18" s="74" t="n"/>
+      <c r="AB18" s="74" t="n"/>
+      <c r="AC18" s="74" t="n"/>
+      <c r="AD18" s="74" t="n"/>
+      <c r="AE18" s="180" t="n"/>
+      <c r="AF18" s="74" t="n"/>
+      <c r="AG18" s="74" t="n"/>
+      <c r="AH18" s="74" t="n"/>
+      <c r="AI18" s="74" t="n"/>
+      <c r="AJ18" s="74" t="n"/>
+      <c r="AK18" s="74" t="n"/>
+      <c r="AL18" s="74" t="n"/>
+      <c r="AM18" s="180" t="n"/>
+      <c r="AN18" s="74" t="n"/>
+      <c r="AO18" s="74" t="n"/>
+      <c r="AP18" s="74" t="n"/>
+      <c r="AQ18" s="74" t="n"/>
+      <c r="AR18" s="74" t="n"/>
+      <c r="AS18" s="180" t="n"/>
+      <c r="AT18" s="74" t="n"/>
+      <c r="AU18" s="74" t="n"/>
+      <c r="AV18" s="74" t="n"/>
+      <c r="AW18" s="74" t="n"/>
+      <c r="AX18" s="180" t="n"/>
+      <c r="AY18" s="74" t="n"/>
+      <c r="AZ18" s="74" t="n"/>
+      <c r="BA18" s="74" t="n"/>
+      <c r="BB18" s="74" t="n"/>
+      <c r="BC18" s="74" t="n"/>
+      <c r="BD18" s="157" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="71" t="n"/>
-      <c r="B19" s="94" t="n"/>
-      <c r="C19" s="94" t="n"/>
-      <c r="D19" s="94" t="n"/>
-      <c r="E19" s="94" t="n"/>
-      <c r="F19" s="95" t="n"/>
-      <c r="G19" s="71" t="n"/>
-      <c r="H19" s="94" t="n"/>
-      <c r="I19" s="94" t="n"/>
-      <c r="J19" s="94" t="n"/>
-      <c r="K19" s="94" t="n"/>
-      <c r="L19" s="94" t="n"/>
-      <c r="M19" s="95" t="n"/>
-      <c r="N19" s="71" t="n"/>
-      <c r="O19" s="94" t="n"/>
-      <c r="P19" s="94" t="n"/>
-      <c r="Q19" s="94" t="n"/>
-      <c r="R19" s="94" t="n"/>
-      <c r="S19" s="94" t="n"/>
-      <c r="T19" s="94" t="n"/>
-      <c r="U19" s="94" t="n"/>
-      <c r="V19" s="94" t="n"/>
-      <c r="W19" s="95" t="n"/>
-      <c r="X19" s="71" t="n"/>
-      <c r="Y19" s="94" t="n"/>
-      <c r="Z19" s="94" t="n"/>
-      <c r="AA19" s="94" t="n"/>
-      <c r="AB19" s="94" t="n"/>
-      <c r="AC19" s="94" t="n"/>
-      <c r="AD19" s="95" t="n"/>
-      <c r="AE19" s="71" t="n"/>
-      <c r="AF19" s="94" t="n"/>
-      <c r="AG19" s="94" t="n"/>
-      <c r="AH19" s="94" t="n"/>
-      <c r="AI19" s="94" t="n"/>
-      <c r="AJ19" s="94" t="n"/>
-      <c r="AK19" s="94" t="n"/>
-      <c r="AL19" s="95" t="n"/>
-      <c r="AM19" s="71" t="n"/>
-      <c r="AN19" s="94" t="n"/>
-      <c r="AO19" s="94" t="n"/>
-      <c r="AP19" s="94" t="n"/>
-      <c r="AQ19" s="94" t="n"/>
-      <c r="AR19" s="95" t="n"/>
-      <c r="AS19" s="71" t="n"/>
-      <c r="AT19" s="94" t="n"/>
-      <c r="AU19" s="94" t="n"/>
-      <c r="AV19" s="94" t="n"/>
-      <c r="AW19" s="95" t="n"/>
-      <c r="AX19" s="71" t="n"/>
-      <c r="AY19" s="94" t="n"/>
-      <c r="AZ19" s="94" t="n"/>
-      <c r="BA19" s="94" t="n"/>
-      <c r="BB19" s="94" t="n"/>
-      <c r="BC19" s="94" t="n"/>
-      <c r="BD19" s="95" t="n"/>
+      <c r="A19" s="184" t="n"/>
+      <c r="B19" s="161" t="n"/>
+      <c r="C19" s="161" t="n"/>
+      <c r="D19" s="161" t="n"/>
+      <c r="E19" s="161" t="n"/>
+      <c r="F19" s="161" t="n"/>
+      <c r="G19" s="160" t="n"/>
+      <c r="H19" s="161" t="n"/>
+      <c r="I19" s="161" t="n"/>
+      <c r="J19" s="161" t="n"/>
+      <c r="K19" s="161" t="n"/>
+      <c r="L19" s="161" t="n"/>
+      <c r="M19" s="161" t="n"/>
+      <c r="N19" s="160" t="n"/>
+      <c r="O19" s="161" t="n"/>
+      <c r="P19" s="161" t="n"/>
+      <c r="Q19" s="161" t="n"/>
+      <c r="R19" s="161" t="n"/>
+      <c r="S19" s="161" t="n"/>
+      <c r="T19" s="161" t="n"/>
+      <c r="U19" s="161" t="n"/>
+      <c r="V19" s="161" t="n"/>
+      <c r="W19" s="161" t="n"/>
+      <c r="X19" s="160" t="n"/>
+      <c r="Y19" s="161" t="n"/>
+      <c r="Z19" s="161" t="n"/>
+      <c r="AA19" s="161" t="n"/>
+      <c r="AB19" s="161" t="n"/>
+      <c r="AC19" s="161" t="n"/>
+      <c r="AD19" s="161" t="n"/>
+      <c r="AE19" s="160" t="n"/>
+      <c r="AF19" s="161" t="n"/>
+      <c r="AG19" s="161" t="n"/>
+      <c r="AH19" s="161" t="n"/>
+      <c r="AI19" s="161" t="n"/>
+      <c r="AJ19" s="161" t="n"/>
+      <c r="AK19" s="161" t="n"/>
+      <c r="AL19" s="161" t="n"/>
+      <c r="AM19" s="160" t="n"/>
+      <c r="AN19" s="161" t="n"/>
+      <c r="AO19" s="161" t="n"/>
+      <c r="AP19" s="161" t="n"/>
+      <c r="AQ19" s="161" t="n"/>
+      <c r="AR19" s="161" t="n"/>
+      <c r="AS19" s="160" t="n"/>
+      <c r="AT19" s="161" t="n"/>
+      <c r="AU19" s="161" t="n"/>
+      <c r="AV19" s="161" t="n"/>
+      <c r="AW19" s="161" t="n"/>
+      <c r="AX19" s="160" t="n"/>
+      <c r="AY19" s="161" t="n"/>
+      <c r="AZ19" s="161" t="n"/>
+      <c r="BA19" s="161" t="n"/>
+      <c r="BB19" s="161" t="n"/>
+      <c r="BC19" s="161" t="n"/>
+      <c r="BD19" s="163" t="n"/>
     </row>
-    <row r="20" ht="4" customHeight="1">
+    <row r="20" ht="3" customHeight="1">
       <c r="A20" s="66" t="n"/>
       <c r="B20" s="66" t="n"/>
       <c r="C20" s="66" t="n"/>
@@ -6303,67 +7247,67 @@
       <c r="BC20" s="66" t="n"/>
       <c r="BD20" s="66" t="n"/>
     </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="78" t="inlineStr">
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="145" t="inlineStr">
         <is>
           <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
         </is>
       </c>
-      <c r="B21" s="86" t="n"/>
-      <c r="C21" s="86" t="n"/>
-      <c r="D21" s="86" t="n"/>
-      <c r="E21" s="86" t="n"/>
-      <c r="F21" s="86" t="n"/>
-      <c r="G21" s="86" t="n"/>
-      <c r="H21" s="86" t="n"/>
-      <c r="I21" s="86" t="n"/>
-      <c r="J21" s="86" t="n"/>
-      <c r="K21" s="86" t="n"/>
-      <c r="L21" s="86" t="n"/>
-      <c r="M21" s="86" t="n"/>
-      <c r="N21" s="86" t="n"/>
-      <c r="O21" s="86" t="n"/>
-      <c r="P21" s="86" t="n"/>
-      <c r="Q21" s="86" t="n"/>
-      <c r="R21" s="86" t="n"/>
-      <c r="S21" s="86" t="n"/>
-      <c r="T21" s="86" t="n"/>
-      <c r="U21" s="86" t="n"/>
-      <c r="V21" s="86" t="n"/>
-      <c r="W21" s="86" t="n"/>
-      <c r="X21" s="86" t="n"/>
-      <c r="Y21" s="86" t="n"/>
-      <c r="Z21" s="86" t="n"/>
-      <c r="AA21" s="86" t="n"/>
-      <c r="AB21" s="86" t="n"/>
-      <c r="AC21" s="86" t="n"/>
-      <c r="AD21" s="86" t="n"/>
-      <c r="AE21" s="86" t="n"/>
-      <c r="AF21" s="86" t="n"/>
-      <c r="AG21" s="86" t="n"/>
-      <c r="AH21" s="86" t="n"/>
-      <c r="AI21" s="86" t="n"/>
-      <c r="AJ21" s="86" t="n"/>
-      <c r="AK21" s="86" t="n"/>
-      <c r="AL21" s="86" t="n"/>
-      <c r="AM21" s="86" t="n"/>
-      <c r="AN21" s="86" t="n"/>
-      <c r="AO21" s="86" t="n"/>
-      <c r="AP21" s="86" t="n"/>
-      <c r="AQ21" s="86" t="n"/>
-      <c r="AR21" s="86" t="n"/>
-      <c r="AS21" s="86" t="n"/>
-      <c r="AT21" s="86" t="n"/>
-      <c r="AU21" s="86" t="n"/>
-      <c r="AV21" s="86" t="n"/>
-      <c r="AW21" s="86" t="n"/>
-      <c r="AX21" s="86" t="n"/>
-      <c r="AY21" s="86" t="n"/>
-      <c r="AZ21" s="86" t="n"/>
-      <c r="BA21" s="86" t="n"/>
-      <c r="BB21" s="86" t="n"/>
-      <c r="BC21" s="86" t="n"/>
-      <c r="BD21" s="87" t="n"/>
+      <c r="B21" s="146" t="n"/>
+      <c r="C21" s="146" t="n"/>
+      <c r="D21" s="146" t="n"/>
+      <c r="E21" s="146" t="n"/>
+      <c r="F21" s="146" t="n"/>
+      <c r="G21" s="146" t="n"/>
+      <c r="H21" s="146" t="n"/>
+      <c r="I21" s="146" t="n"/>
+      <c r="J21" s="146" t="n"/>
+      <c r="K21" s="146" t="n"/>
+      <c r="L21" s="146" t="n"/>
+      <c r="M21" s="146" t="n"/>
+      <c r="N21" s="146" t="n"/>
+      <c r="O21" s="146" t="n"/>
+      <c r="P21" s="146" t="n"/>
+      <c r="Q21" s="146" t="n"/>
+      <c r="R21" s="146" t="n"/>
+      <c r="S21" s="146" t="n"/>
+      <c r="T21" s="146" t="n"/>
+      <c r="U21" s="146" t="n"/>
+      <c r="V21" s="146" t="n"/>
+      <c r="W21" s="146" t="n"/>
+      <c r="X21" s="146" t="n"/>
+      <c r="Y21" s="146" t="n"/>
+      <c r="Z21" s="146" t="n"/>
+      <c r="AA21" s="146" t="n"/>
+      <c r="AB21" s="146" t="n"/>
+      <c r="AC21" s="146" t="n"/>
+      <c r="AD21" s="146" t="n"/>
+      <c r="AE21" s="146" t="n"/>
+      <c r="AF21" s="146" t="n"/>
+      <c r="AG21" s="146" t="n"/>
+      <c r="AH21" s="146" t="n"/>
+      <c r="AI21" s="146" t="n"/>
+      <c r="AJ21" s="146" t="n"/>
+      <c r="AK21" s="146" t="n"/>
+      <c r="AL21" s="146" t="n"/>
+      <c r="AM21" s="146" t="n"/>
+      <c r="AN21" s="146" t="n"/>
+      <c r="AO21" s="146" t="n"/>
+      <c r="AP21" s="146" t="n"/>
+      <c r="AQ21" s="146" t="n"/>
+      <c r="AR21" s="146" t="n"/>
+      <c r="AS21" s="146" t="n"/>
+      <c r="AT21" s="146" t="n"/>
+      <c r="AU21" s="146" t="n"/>
+      <c r="AV21" s="146" t="n"/>
+      <c r="AW21" s="146" t="n"/>
+      <c r="AX21" s="146" t="n"/>
+      <c r="AY21" s="146" t="n"/>
+      <c r="AZ21" s="146" t="n"/>
+      <c r="BA21" s="146" t="n"/>
+      <c r="BB21" s="146" t="n"/>
+      <c r="BC21" s="146" t="n"/>
+      <c r="BD21" s="147" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1"/>
     <row r="23" ht="20" customHeight="1"/>
@@ -6545,7 +7489,7 @@
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="88">
+  <mergeCells count="87">
     <mergeCell ref="N19:W19"/>
     <mergeCell ref="AW2:BD2"/>
     <mergeCell ref="AE16:AL16"/>
@@ -6556,7 +7500,6 @@
     <mergeCell ref="AS12:AW12"/>
     <mergeCell ref="G12:M12"/>
     <mergeCell ref="AQ4:AV4"/>
-    <mergeCell ref="A6:BD6"/>
     <mergeCell ref="AM15:AR15"/>
     <mergeCell ref="AW5:BD5"/>
     <mergeCell ref="AM12:AR12"/>
@@ -6645,6 +7588,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6969,61 +7913,6 @@
     </row>
     <row r="6" ht="4" customHeight="1">
       <c r="A6" s="66" t="n"/>
-      <c r="B6" s="98" t="n"/>
-      <c r="C6" s="98" t="n"/>
-      <c r="D6" s="98" t="n"/>
-      <c r="E6" s="98" t="n"/>
-      <c r="F6" s="98" t="n"/>
-      <c r="G6" s="98" t="n"/>
-      <c r="H6" s="98" t="n"/>
-      <c r="I6" s="98" t="n"/>
-      <c r="J6" s="98" t="n"/>
-      <c r="K6" s="98" t="n"/>
-      <c r="L6" s="98" t="n"/>
-      <c r="M6" s="98" t="n"/>
-      <c r="N6" s="98" t="n"/>
-      <c r="O6" s="98" t="n"/>
-      <c r="P6" s="98" t="n"/>
-      <c r="Q6" s="98" t="n"/>
-      <c r="R6" s="98" t="n"/>
-      <c r="S6" s="98" t="n"/>
-      <c r="T6" s="98" t="n"/>
-      <c r="U6" s="98" t="n"/>
-      <c r="V6" s="98" t="n"/>
-      <c r="W6" s="98" t="n"/>
-      <c r="X6" s="98" t="n"/>
-      <c r="Y6" s="98" t="n"/>
-      <c r="Z6" s="98" t="n"/>
-      <c r="AA6" s="98" t="n"/>
-      <c r="AB6" s="98" t="n"/>
-      <c r="AC6" s="98" t="n"/>
-      <c r="AD6" s="98" t="n"/>
-      <c r="AE6" s="98" t="n"/>
-      <c r="AF6" s="98" t="n"/>
-      <c r="AG6" s="98" t="n"/>
-      <c r="AH6" s="98" t="n"/>
-      <c r="AI6" s="98" t="n"/>
-      <c r="AJ6" s="98" t="n"/>
-      <c r="AK6" s="98" t="n"/>
-      <c r="AL6" s="98" t="n"/>
-      <c r="AM6" s="98" t="n"/>
-      <c r="AN6" s="98" t="n"/>
-      <c r="AO6" s="98" t="n"/>
-      <c r="AP6" s="98" t="n"/>
-      <c r="AQ6" s="98" t="n"/>
-      <c r="AR6" s="98" t="n"/>
-      <c r="AS6" s="98" t="n"/>
-      <c r="AT6" s="98" t="n"/>
-      <c r="AU6" s="98" t="n"/>
-      <c r="AV6" s="98" t="n"/>
-      <c r="AW6" s="98" t="n"/>
-      <c r="AX6" s="98" t="n"/>
-      <c r="AY6" s="98" t="n"/>
-      <c r="AZ6" s="98" t="n"/>
-      <c r="BA6" s="98" t="n"/>
-      <c r="BB6" s="98" t="n"/>
-      <c r="BC6" s="98" t="n"/>
-      <c r="BD6" s="98" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="82" t="inlineStr">
@@ -7093,61 +7982,61 @@
           <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
         </is>
       </c>
-      <c r="B8" s="92" t="n"/>
-      <c r="C8" s="92" t="n"/>
-      <c r="D8" s="92" t="n"/>
-      <c r="E8" s="92" t="n"/>
-      <c r="F8" s="92" t="n"/>
-      <c r="G8" s="92" t="n"/>
-      <c r="H8" s="92" t="n"/>
-      <c r="I8" s="92" t="n"/>
-      <c r="J8" s="92" t="n"/>
-      <c r="K8" s="92" t="n"/>
-      <c r="L8" s="92" t="n"/>
-      <c r="M8" s="92" t="n"/>
-      <c r="N8" s="92" t="n"/>
-      <c r="O8" s="92" t="n"/>
-      <c r="P8" s="92" t="n"/>
-      <c r="Q8" s="92" t="n"/>
-      <c r="R8" s="92" t="n"/>
-      <c r="S8" s="92" t="n"/>
-      <c r="T8" s="92" t="n"/>
-      <c r="U8" s="92" t="n"/>
-      <c r="V8" s="92" t="n"/>
-      <c r="W8" s="92" t="n"/>
-      <c r="X8" s="92" t="n"/>
-      <c r="Y8" s="92" t="n"/>
-      <c r="Z8" s="92" t="n"/>
-      <c r="AA8" s="92" t="n"/>
-      <c r="AB8" s="92" t="n"/>
-      <c r="AC8" s="92" t="n"/>
-      <c r="AD8" s="92" t="n"/>
-      <c r="AE8" s="92" t="n"/>
-      <c r="AF8" s="92" t="n"/>
-      <c r="AG8" s="92" t="n"/>
-      <c r="AH8" s="92" t="n"/>
-      <c r="AI8" s="92" t="n"/>
-      <c r="AJ8" s="92" t="n"/>
-      <c r="AK8" s="92" t="n"/>
-      <c r="AL8" s="92" t="n"/>
-      <c r="AM8" s="92" t="n"/>
-      <c r="AN8" s="92" t="n"/>
-      <c r="AO8" s="92" t="n"/>
-      <c r="AP8" s="92" t="n"/>
-      <c r="AQ8" s="92" t="n"/>
-      <c r="AR8" s="92" t="n"/>
-      <c r="AS8" s="92" t="n"/>
-      <c r="AT8" s="92" t="n"/>
-      <c r="AU8" s="92" t="n"/>
-      <c r="AV8" s="92" t="n"/>
-      <c r="AW8" s="92" t="n"/>
-      <c r="AX8" s="92" t="n"/>
-      <c r="AY8" s="92" t="n"/>
-      <c r="AZ8" s="92" t="n"/>
-      <c r="BA8" s="92" t="n"/>
-      <c r="BB8" s="92" t="n"/>
-      <c r="BC8" s="92" t="n"/>
-      <c r="BD8" s="93" t="n"/>
+      <c r="B8" s="100" t="n"/>
+      <c r="C8" s="100" t="n"/>
+      <c r="D8" s="100" t="n"/>
+      <c r="E8" s="100" t="n"/>
+      <c r="F8" s="100" t="n"/>
+      <c r="G8" s="100" t="n"/>
+      <c r="H8" s="100" t="n"/>
+      <c r="I8" s="100" t="n"/>
+      <c r="J8" s="100" t="n"/>
+      <c r="K8" s="100" t="n"/>
+      <c r="L8" s="100" t="n"/>
+      <c r="M8" s="100" t="n"/>
+      <c r="N8" s="100" t="n"/>
+      <c r="O8" s="100" t="n"/>
+      <c r="P8" s="100" t="n"/>
+      <c r="Q8" s="100" t="n"/>
+      <c r="R8" s="100" t="n"/>
+      <c r="S8" s="100" t="n"/>
+      <c r="T8" s="100" t="n"/>
+      <c r="U8" s="100" t="n"/>
+      <c r="V8" s="100" t="n"/>
+      <c r="W8" s="100" t="n"/>
+      <c r="X8" s="100" t="n"/>
+      <c r="Y8" s="100" t="n"/>
+      <c r="Z8" s="100" t="n"/>
+      <c r="AA8" s="100" t="n"/>
+      <c r="AB8" s="100" t="n"/>
+      <c r="AC8" s="100" t="n"/>
+      <c r="AD8" s="100" t="n"/>
+      <c r="AE8" s="100" t="n"/>
+      <c r="AF8" s="100" t="n"/>
+      <c r="AG8" s="100" t="n"/>
+      <c r="AH8" s="100" t="n"/>
+      <c r="AI8" s="100" t="n"/>
+      <c r="AJ8" s="100" t="n"/>
+      <c r="AK8" s="100" t="n"/>
+      <c r="AL8" s="100" t="n"/>
+      <c r="AM8" s="100" t="n"/>
+      <c r="AN8" s="100" t="n"/>
+      <c r="AO8" s="100" t="n"/>
+      <c r="AP8" s="100" t="n"/>
+      <c r="AQ8" s="100" t="n"/>
+      <c r="AR8" s="100" t="n"/>
+      <c r="AS8" s="100" t="n"/>
+      <c r="AT8" s="100" t="n"/>
+      <c r="AU8" s="100" t="n"/>
+      <c r="AV8" s="100" t="n"/>
+      <c r="AW8" s="100" t="n"/>
+      <c r="AX8" s="100" t="n"/>
+      <c r="AY8" s="100" t="n"/>
+      <c r="AZ8" s="100" t="n"/>
+      <c r="BA8" s="100" t="n"/>
+      <c r="BB8" s="100" t="n"/>
+      <c r="BC8" s="100" t="n"/>
+      <c r="BD8" s="101" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="80" t="inlineStr">
@@ -8525,61 +9414,61 @@
           <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
         </is>
       </c>
-      <c r="B22" s="92" t="n"/>
-      <c r="C22" s="92" t="n"/>
-      <c r="D22" s="92" t="n"/>
-      <c r="E22" s="92" t="n"/>
-      <c r="F22" s="92" t="n"/>
-      <c r="G22" s="92" t="n"/>
-      <c r="H22" s="92" t="n"/>
-      <c r="I22" s="92" t="n"/>
-      <c r="J22" s="92" t="n"/>
-      <c r="K22" s="92" t="n"/>
-      <c r="L22" s="92" t="n"/>
-      <c r="M22" s="92" t="n"/>
-      <c r="N22" s="92" t="n"/>
-      <c r="O22" s="92" t="n"/>
-      <c r="P22" s="92" t="n"/>
-      <c r="Q22" s="92" t="n"/>
-      <c r="R22" s="92" t="n"/>
-      <c r="S22" s="92" t="n"/>
-      <c r="T22" s="92" t="n"/>
-      <c r="U22" s="92" t="n"/>
-      <c r="V22" s="92" t="n"/>
-      <c r="W22" s="92" t="n"/>
-      <c r="X22" s="92" t="n"/>
-      <c r="Y22" s="92" t="n"/>
-      <c r="Z22" s="92" t="n"/>
-      <c r="AA22" s="92" t="n"/>
-      <c r="AB22" s="92" t="n"/>
-      <c r="AC22" s="92" t="n"/>
-      <c r="AD22" s="92" t="n"/>
-      <c r="AE22" s="92" t="n"/>
-      <c r="AF22" s="92" t="n"/>
-      <c r="AG22" s="92" t="n"/>
-      <c r="AH22" s="92" t="n"/>
-      <c r="AI22" s="92" t="n"/>
-      <c r="AJ22" s="92" t="n"/>
-      <c r="AK22" s="92" t="n"/>
-      <c r="AL22" s="92" t="n"/>
-      <c r="AM22" s="92" t="n"/>
-      <c r="AN22" s="92" t="n"/>
-      <c r="AO22" s="92" t="n"/>
-      <c r="AP22" s="92" t="n"/>
-      <c r="AQ22" s="92" t="n"/>
-      <c r="AR22" s="92" t="n"/>
-      <c r="AS22" s="92" t="n"/>
-      <c r="AT22" s="92" t="n"/>
-      <c r="AU22" s="92" t="n"/>
-      <c r="AV22" s="92" t="n"/>
-      <c r="AW22" s="92" t="n"/>
-      <c r="AX22" s="92" t="n"/>
-      <c r="AY22" s="92" t="n"/>
-      <c r="AZ22" s="92" t="n"/>
-      <c r="BA22" s="92" t="n"/>
-      <c r="BB22" s="92" t="n"/>
-      <c r="BC22" s="92" t="n"/>
-      <c r="BD22" s="93" t="n"/>
+      <c r="B22" s="100" t="n"/>
+      <c r="C22" s="100" t="n"/>
+      <c r="D22" s="100" t="n"/>
+      <c r="E22" s="100" t="n"/>
+      <c r="F22" s="100" t="n"/>
+      <c r="G22" s="100" t="n"/>
+      <c r="H22" s="100" t="n"/>
+      <c r="I22" s="100" t="n"/>
+      <c r="J22" s="100" t="n"/>
+      <c r="K22" s="100" t="n"/>
+      <c r="L22" s="100" t="n"/>
+      <c r="M22" s="100" t="n"/>
+      <c r="N22" s="100" t="n"/>
+      <c r="O22" s="100" t="n"/>
+      <c r="P22" s="100" t="n"/>
+      <c r="Q22" s="100" t="n"/>
+      <c r="R22" s="100" t="n"/>
+      <c r="S22" s="100" t="n"/>
+      <c r="T22" s="100" t="n"/>
+      <c r="U22" s="100" t="n"/>
+      <c r="V22" s="100" t="n"/>
+      <c r="W22" s="100" t="n"/>
+      <c r="X22" s="100" t="n"/>
+      <c r="Y22" s="100" t="n"/>
+      <c r="Z22" s="100" t="n"/>
+      <c r="AA22" s="100" t="n"/>
+      <c r="AB22" s="100" t="n"/>
+      <c r="AC22" s="100" t="n"/>
+      <c r="AD22" s="100" t="n"/>
+      <c r="AE22" s="100" t="n"/>
+      <c r="AF22" s="100" t="n"/>
+      <c r="AG22" s="100" t="n"/>
+      <c r="AH22" s="100" t="n"/>
+      <c r="AI22" s="100" t="n"/>
+      <c r="AJ22" s="100" t="n"/>
+      <c r="AK22" s="100" t="n"/>
+      <c r="AL22" s="100" t="n"/>
+      <c r="AM22" s="100" t="n"/>
+      <c r="AN22" s="100" t="n"/>
+      <c r="AO22" s="100" t="n"/>
+      <c r="AP22" s="100" t="n"/>
+      <c r="AQ22" s="100" t="n"/>
+      <c r="AR22" s="100" t="n"/>
+      <c r="AS22" s="100" t="n"/>
+      <c r="AT22" s="100" t="n"/>
+      <c r="AU22" s="100" t="n"/>
+      <c r="AV22" s="100" t="n"/>
+      <c r="AW22" s="100" t="n"/>
+      <c r="AX22" s="100" t="n"/>
+      <c r="AY22" s="100" t="n"/>
+      <c r="AZ22" s="100" t="n"/>
+      <c r="BA22" s="100" t="n"/>
+      <c r="BB22" s="100" t="n"/>
+      <c r="BC22" s="100" t="n"/>
+      <c r="BD22" s="101" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/04-Bieu-Mau/08-FRM-800/FRM-801_Training_Plan.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-801_Training_Plan.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM801_TrainPlan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM801_Targets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM801_Targets" sheetId="2" state="veryHidden" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM801_Evidence" sheetId="3" state="veryHidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="zLISTS" sheetId="4" state="veryHidden" r:id="rId4"/>
   </sheets>

--- a/04-Bieu-Mau/08-FRM-800/FRM-801_Training_Plan.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-801_Training_Plan.xlsx
@@ -26,10 +26,657 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
+  <si>
+    <t>  1. CONTROLLED LOOKUP LISTS</t>
+  </si>
+  <si>
+    <t>  1. REFERENCE INFORMATION</t>
+  </si>
+  <si>
+    <t>  2. COMPETENCE GAP / TARGET</t>
+  </si>
+  <si>
+    <t>  3. SCHEDULE / RESOURCE</t>
+  </si>
+  <si>
+    <t>  4. DECISION / REVIEW</t>
+  </si>
+  <si>
+    <t>  5. APPROVAL / SIGN-OFF</t>
+  </si>
+  <si>
+    <t>  REFERENCE / SOURCE CONTEXT</t>
+  </si>
+  <si>
+    <t>  SUPPORT TABLE</t>
+  </si>
+  <si>
+    <t>  TARGET POPULATION / SKILL PLAN</t>
+  </si>
+  <si>
+    <t>ABSENT</t>
+  </si>
+  <si>
+    <t>ACCEPT</t>
+  </si>
+  <si>
+    <t>ACCEPT WITH ACTION</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>ATTENDANCE_STATUS</t>
+  </si>
+  <si>
+    <t>AUTHORIZATION_STATUS</t>
+  </si>
+  <si>
+    <t>AUTHORIZED</t>
+  </si>
+  <si>
+    <t>AWARE</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Approved By</t>
+  </si>
+  <si>
+    <t>Authorized By</t>
+  </si>
+  <si>
+    <t>Boundary / SoR</t>
+  </si>
+  <si>
+    <t>CERTIFICATION BODY</t>
+  </si>
+  <si>
+    <t>CERT_STATUS</t>
+  </si>
+  <si>
+    <t>CLASSROOM</t>
+  </si>
+  <si>
+    <t>CLIMATE_SCENARIO</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>COACHING</t>
+  </si>
+  <si>
+    <t>COMBINED</t>
+  </si>
+  <si>
+    <t>COMMUNITY</t>
+  </si>
+  <si>
+    <t>COMPETENCY_LEVEL</t>
+  </si>
+  <si>
+    <t>COMPLIANCE</t>
+  </si>
+  <si>
+    <t>CONDITIONAL</t>
+  </si>
+  <si>
+    <t>CONTEXT_CLASS</t>
+  </si>
+  <si>
+    <t>CONTRACTUAL</t>
+  </si>
+  <si>
+    <t>COPY_ACTION</t>
+  </si>
+  <si>
+    <t>CRITICAL</t>
+  </si>
+  <si>
+    <t>CSR_CLASS</t>
+  </si>
+  <si>
+    <t>CURRENCY</t>
+  </si>
+  <si>
+    <t>CUSTOMER</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Current Gap</t>
+  </si>
+  <si>
+    <t>Current Level</t>
+  </si>
+  <si>
+    <t>Cycle</t>
+  </si>
+  <si>
+    <t>DECISION</t>
+  </si>
+  <si>
+    <t>DELIVERY</t>
+  </si>
+  <si>
+    <t>DEPT</t>
+  </si>
+  <si>
+    <t>DESTROY</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT_PRIORITY</t>
+  </si>
+  <si>
+    <t>DOC_STATUS</t>
+  </si>
+  <si>
+    <t>DRAFT</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <t>Department / Role</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Due Date</t>
+  </si>
+  <si>
+    <t>EFFECTIVE</t>
+  </si>
+  <si>
+    <t>EMPLOYEE</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>ENVIRONMENT</t>
+  </si>
+  <si>
+    <t>ENVIRONMENTAL</t>
+  </si>
+  <si>
+    <t>ESG</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>EXCUSED</t>
+  </si>
+  <si>
+    <t>EXPIRED</t>
+  </si>
+  <si>
+    <t>EXPIRING</t>
+  </si>
+  <si>
+    <t>EXTERNAL COURSE</t>
+  </si>
+  <si>
+    <t>Eff. Date</t>
+  </si>
+  <si>
+    <t>Evidence Folder Ref</t>
+  </si>
+  <si>
+    <t>Evidence ID</t>
+  </si>
+  <si>
+    <t>Evidence Ref</t>
+  </si>
+  <si>
+    <t>Expected Evidence</t>
+  </si>
+  <si>
+    <t>FACILITY</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>FINANCE</t>
+  </si>
+  <si>
+    <t>FRM-801</t>
+  </si>
+  <si>
+    <t>Follow-Up Date</t>
+  </si>
+  <si>
+    <t>Form Code</t>
+  </si>
+  <si>
+    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>HR + Department Manager</t>
+  </si>
+  <si>
+    <t>HSE</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
+    <t>INCIDENT_CLASS</t>
+  </si>
+  <si>
+    <t>INDEPENDENT</t>
+  </si>
+  <si>
+    <t>INSPECTION</t>
+  </si>
+  <si>
+    <t>INSURANCE</t>
+  </si>
+  <si>
+    <t>INTERNAL</t>
+  </si>
+  <si>
+    <t>ISSUE</t>
+  </si>
+  <si>
+    <t>ISSUE_ACTION</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>JPY</t>
+  </si>
+  <si>
+    <t>LATE</t>
+  </si>
+  <si>
+    <t>LEGAL</t>
+  </si>
+  <si>
+    <t>LIGHTING_AREA</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>M365 evidence / shared workbook</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>MEETING ROOM</t>
+  </si>
+  <si>
+    <t>MGT</t>
+  </si>
+  <si>
+    <t>MONITORING</t>
+  </si>
+  <si>
+    <t>Material / Resource</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>NOT AUTHORIZED</t>
+  </si>
+  <si>
+    <t>NOT TRAINED</t>
+  </si>
+  <si>
+    <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
+  </si>
+  <si>
+    <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
+  </si>
+  <si>
+    <t>NOTICE: Controlled support sheet. Keep one row per controlled reference item and maintain traceable owner, date and evidence linkage.</t>
+  </si>
+  <si>
+    <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
+  </si>
+  <si>
+    <t>NOTICE: Training plans shall state the required skill, current gap, target level, method, trainer, schedule, expected evidence and follow-up date; do not plan training without a clear competence outcome.</t>
+  </si>
+  <si>
+    <t>Name / Signature / Date</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>OBSERVATION</t>
+  </si>
+  <si>
+    <t>OBSOLETE</t>
+  </si>
+  <si>
+    <t>OFFICE</t>
+  </si>
+  <si>
+    <t>OJT</t>
+  </si>
+  <si>
+    <t>OJT / Test / Observation Method</t>
+  </si>
+  <si>
+    <t>ON HOLD</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>OTHER</t>
+  </si>
+  <si>
+    <t>OUTDOOR</t>
+  </si>
+  <si>
+    <t>OWNER</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Owner / Manager</t>
+  </si>
+  <si>
+    <t>PACKAGING</t>
+  </si>
+  <si>
+    <t>PARTY_TYPE</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>PESTLE</t>
+  </si>
+  <si>
+    <t>PHYSICAL ACUTE</t>
+  </si>
+  <si>
+    <t>PHYSICAL CHRONIC</t>
+  </si>
+  <si>
+    <t>PLANNED</t>
+  </si>
+  <si>
+    <t>PLANNING</t>
+  </si>
+  <si>
+    <t>PRESENT</t>
+  </si>
+  <si>
+    <t>PROD</t>
+  </si>
+  <si>
+    <t>Per authority matrix</t>
+  </si>
+  <si>
+    <t>Person or Group</t>
+  </si>
+  <si>
+    <t>Plan Status</t>
+  </si>
+  <si>
+    <t>Prepared By</t>
+  </si>
+  <si>
+    <t>Prepared Date</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>QMS</t>
+  </si>
+  <si>
+    <t>QUALITY</t>
+  </si>
+  <si>
+    <t>Quality Management System · Controlled Document</t>
+  </si>
+  <si>
+    <t>READ-AND-UNDERSTAND</t>
+  </si>
+  <si>
+    <t>RECALL</t>
+  </si>
+  <si>
+    <t>REGULATOR</t>
+  </si>
+  <si>
+    <t>REJECT</t>
+  </si>
+  <si>
+    <t>REJECTED</t>
+  </si>
+  <si>
+    <t>REPLACE</t>
+  </si>
+  <si>
+    <t>REQUIREMENT_CLASS</t>
+  </si>
+  <si>
+    <t>RESULT</t>
+  </si>
+  <si>
+    <t>RETURN</t>
+  </si>
+  <si>
+    <t>REVIEW_OUTCOME</t>
+  </si>
+  <si>
+    <t>REVISE</t>
+  </si>
+  <si>
+    <t>RISK</t>
+  </si>
+  <si>
+    <t>Record traceable evidence references only; do not duplicate system-owned master data.</t>
+  </si>
+  <si>
+    <t>Reference Path or Link</t>
+  </si>
+  <si>
+    <t>Related Record</t>
+  </si>
+  <si>
+    <t>Required Skill</t>
+  </si>
+  <si>
+    <t>Review Status</t>
+  </si>
+  <si>
+    <t>Reviewed By</t>
+  </si>
+  <si>
+    <t>Revision</t>
+  </si>
+  <si>
+    <t>SAFETY</t>
+  </si>
+  <si>
+    <t>SALES</t>
+  </si>
+  <si>
+    <t>SECURITY</t>
+  </si>
+  <si>
+    <t>SHAREHOLDER</t>
+  </si>
+  <si>
+    <t>SHOP FLOOR</t>
+  </si>
+  <si>
+    <t>SOCIAL</t>
+  </si>
+  <si>
+    <t>SOP-801; WI-801 / WI-804; ANNEX-HR-001 + ANNEX-QMS-027 / 028</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>STRATEGIC</t>
+  </si>
+  <si>
+    <t>SUPERSEDED</t>
+  </si>
+  <si>
+    <t>SUPERVISED</t>
+  </si>
+  <si>
+    <t>SUPPLIER</t>
+  </si>
+  <si>
+    <t>SUSPENDED</t>
+  </si>
+  <si>
+    <t>SWOT</t>
+  </si>
+  <si>
+    <t>Scheduled Date</t>
+  </si>
+  <si>
+    <t>Source Links</t>
+  </si>
+  <si>
+    <t>Source System</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Structured training plan + schedule / resource table</t>
+  </si>
+  <si>
+    <t>TEST</t>
+  </si>
+  <si>
+    <t>TRACEABILITY</t>
+  </si>
+  <si>
+    <t>TRAINING PLAN</t>
+  </si>
+  <si>
+    <t>TRAINING PLAN — CONTROLLED LOOKUP LISTS</t>
+  </si>
+  <si>
+    <t>TRAINING PLAN — EVIDENCE REFERENCE REGISTER</t>
+  </si>
+  <si>
+    <t>TRAINING PLAN — TARGETS / RESOURCES</t>
+  </si>
+  <si>
+    <t>TRAINING_METHOD</t>
+  </si>
+  <si>
+    <t>TRANSITION CUSTOMER</t>
+  </si>
+  <si>
+    <t>TRANSITION MARKET</t>
+  </si>
+  <si>
+    <t>TRANSITION REGULATORY</t>
+  </si>
+  <si>
+    <t>Target ID</t>
+  </si>
+  <si>
+    <t>Target Level</t>
+  </si>
+  <si>
+    <t>Target Population</t>
+  </si>
+  <si>
+    <t>Trainer</t>
+  </si>
+  <si>
+    <t>Training Method</t>
+  </si>
+  <si>
+    <t>Training Plan ID</t>
+  </si>
+  <si>
+    <t>Training-plan event defines who must be trained and when; intentionally separate from attendance, OJT, competence, certification and skills matrices.</t>
+  </si>
+  <si>
+    <t>UNDER REVIEW</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>V0</t>
+  </si>
+  <si>
+    <t>VALID</t>
+  </si>
+  <si>
+    <t>VND</t>
+  </si>
+  <si>
+    <t>VOID</t>
+  </si>
+  <si>
+    <t>WAREHOUSE</t>
+  </si>
+  <si>
+    <t>WHS</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>YES_NO</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -140,8 +787,13 @@
       <color rgb="001B3A6B"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007B4F00"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -198,8 +850,13 @@
         <fgColor rgb="000C2D48"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="145">
+  <borders count="148">
     <border>
       <left/>
       <right/>
@@ -1757,11 +2414,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="333">
+  <cellXfs count="336">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2622,6 +3313,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="128" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4764,67 +5464,67 @@
       <c r="BC26" s="241" t="n"/>
       <c r="BD26" s="241" t="n"/>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="287" t="inlineStr">
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="333" t="inlineStr">
         <is>
           <t>NOTICE: Training plans shall state the required skill, current gap, target level, method, trainer, schedule, expected evidence and follow-up date; do not plan training without a clear competence outcome.</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="6" t="n"/>
-      <c r="K27" s="6" t="n"/>
-      <c r="L27" s="6" t="n"/>
-      <c r="M27" s="6" t="n"/>
-      <c r="N27" s="6" t="n"/>
-      <c r="O27" s="6" t="n"/>
-      <c r="P27" s="6" t="n"/>
-      <c r="Q27" s="6" t="n"/>
-      <c r="R27" s="6" t="n"/>
-      <c r="S27" s="6" t="n"/>
-      <c r="T27" s="6" t="n"/>
-      <c r="U27" s="6" t="n"/>
-      <c r="V27" s="6" t="n"/>
-      <c r="W27" s="6" t="n"/>
-      <c r="X27" s="6" t="n"/>
-      <c r="Y27" s="6" t="n"/>
-      <c r="Z27" s="6" t="n"/>
-      <c r="AA27" s="6" t="n"/>
-      <c r="AB27" s="6" t="n"/>
-      <c r="AC27" s="6" t="n"/>
-      <c r="AD27" s="6" t="n"/>
-      <c r="AE27" s="6" t="n"/>
-      <c r="AF27" s="6" t="n"/>
-      <c r="AG27" s="6" t="n"/>
-      <c r="AH27" s="6" t="n"/>
-      <c r="AI27" s="6" t="n"/>
-      <c r="AJ27" s="6" t="n"/>
-      <c r="AK27" s="6" t="n"/>
-      <c r="AL27" s="6" t="n"/>
-      <c r="AM27" s="6" t="n"/>
-      <c r="AN27" s="6" t="n"/>
-      <c r="AO27" s="6" t="n"/>
-      <c r="AP27" s="6" t="n"/>
-      <c r="AQ27" s="6" t="n"/>
-      <c r="AR27" s="6" t="n"/>
-      <c r="AS27" s="6" t="n"/>
-      <c r="AT27" s="6" t="n"/>
-      <c r="AU27" s="6" t="n"/>
-      <c r="AV27" s="6" t="n"/>
-      <c r="AW27" s="6" t="n"/>
-      <c r="AX27" s="6" t="n"/>
-      <c r="AY27" s="6" t="n"/>
-      <c r="AZ27" s="6" t="n"/>
-      <c r="BA27" s="6" t="n"/>
-      <c r="BB27" s="6" t="n"/>
-      <c r="BC27" s="6" t="n"/>
-      <c r="BD27" s="7" t="n"/>
+      <c r="B27" s="334" t="n"/>
+      <c r="C27" s="334" t="n"/>
+      <c r="D27" s="334" t="n"/>
+      <c r="E27" s="334" t="n"/>
+      <c r="F27" s="334" t="n"/>
+      <c r="G27" s="334" t="n"/>
+      <c r="H27" s="334" t="n"/>
+      <c r="I27" s="334" t="n"/>
+      <c r="J27" s="334" t="n"/>
+      <c r="K27" s="334" t="n"/>
+      <c r="L27" s="334" t="n"/>
+      <c r="M27" s="334" t="n"/>
+      <c r="N27" s="334" t="n"/>
+      <c r="O27" s="334" t="n"/>
+      <c r="P27" s="334" t="n"/>
+      <c r="Q27" s="334" t="n"/>
+      <c r="R27" s="334" t="n"/>
+      <c r="S27" s="334" t="n"/>
+      <c r="T27" s="334" t="n"/>
+      <c r="U27" s="334" t="n"/>
+      <c r="V27" s="334" t="n"/>
+      <c r="W27" s="334" t="n"/>
+      <c r="X27" s="334" t="n"/>
+      <c r="Y27" s="334" t="n"/>
+      <c r="Z27" s="334" t="n"/>
+      <c r="AA27" s="334" t="n"/>
+      <c r="AB27" s="334" t="n"/>
+      <c r="AC27" s="334" t="n"/>
+      <c r="AD27" s="334" t="n"/>
+      <c r="AE27" s="334" t="n"/>
+      <c r="AF27" s="334" t="n"/>
+      <c r="AG27" s="334" t="n"/>
+      <c r="AH27" s="334" t="n"/>
+      <c r="AI27" s="334" t="n"/>
+      <c r="AJ27" s="334" t="n"/>
+      <c r="AK27" s="334" t="n"/>
+      <c r="AL27" s="334" t="n"/>
+      <c r="AM27" s="334" t="n"/>
+      <c r="AN27" s="334" t="n"/>
+      <c r="AO27" s="334" t="n"/>
+      <c r="AP27" s="334" t="n"/>
+      <c r="AQ27" s="334" t="n"/>
+      <c r="AR27" s="334" t="n"/>
+      <c r="AS27" s="334" t="n"/>
+      <c r="AT27" s="334" t="n"/>
+      <c r="AU27" s="334" t="n"/>
+      <c r="AV27" s="334" t="n"/>
+      <c r="AW27" s="334" t="n"/>
+      <c r="AX27" s="334" t="n"/>
+      <c r="AY27" s="334" t="n"/>
+      <c r="AZ27" s="334" t="n"/>
+      <c r="BA27" s="334" t="n"/>
+      <c r="BB27" s="334" t="n"/>
+      <c r="BC27" s="334" t="n"/>
+      <c r="BD27" s="335" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1"/>
     <row r="29" ht="20" customHeight="1"/>

--- a/04-Bieu-Mau/08-FRM-800/FRM-801_Training_Plan.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-801_Training_Plan.xlsx
@@ -856,7 +856,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="148">
+  <borders count="153">
     <border>
       <left/>
       <right/>
@@ -2447,6 +2447,64 @@
       <bottom style="thin">
         <color rgb="00F9A825"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">

--- a/04-Bieu-Mau/08-FRM-800/FRM-801_Training_Plan.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-801_Training_Plan.xlsx
@@ -24,653 +24,6 @@
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="214">
-  <si>
-    <t>  1. CONTROLLED LOOKUP LISTS</t>
-  </si>
-  <si>
-    <t>  1. REFERENCE INFORMATION</t>
-  </si>
-  <si>
-    <t>  2. COMPETENCE GAP / TARGET</t>
-  </si>
-  <si>
-    <t>  3. SCHEDULE / RESOURCE</t>
-  </si>
-  <si>
-    <t>  4. DECISION / REVIEW</t>
-  </si>
-  <si>
-    <t>  5. APPROVAL / SIGN-OFF</t>
-  </si>
-  <si>
-    <t>  REFERENCE / SOURCE CONTEXT</t>
-  </si>
-  <si>
-    <t>  SUPPORT TABLE</t>
-  </si>
-  <si>
-    <t>  TARGET POPULATION / SKILL PLAN</t>
-  </si>
-  <si>
-    <t>ABSENT</t>
-  </si>
-  <si>
-    <t>ACCEPT</t>
-  </si>
-  <si>
-    <t>ACCEPT WITH ACTION</t>
-  </si>
-  <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>ATTENDANCE_STATUS</t>
-  </si>
-  <si>
-    <t>AUTHORIZATION_STATUS</t>
-  </si>
-  <si>
-    <t>AUTHORIZED</t>
-  </si>
-  <si>
-    <t>AWARE</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>Approved By</t>
-  </si>
-  <si>
-    <t>Authorized By</t>
-  </si>
-  <si>
-    <t>Boundary / SoR</t>
-  </si>
-  <si>
-    <t>CERTIFICATION BODY</t>
-  </si>
-  <si>
-    <t>CERT_STATUS</t>
-  </si>
-  <si>
-    <t>CLASSROOM</t>
-  </si>
-  <si>
-    <t>CLIMATE_SCENARIO</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>COACHING</t>
-  </si>
-  <si>
-    <t>COMBINED</t>
-  </si>
-  <si>
-    <t>COMMUNITY</t>
-  </si>
-  <si>
-    <t>COMPETENCY_LEVEL</t>
-  </si>
-  <si>
-    <t>COMPLIANCE</t>
-  </si>
-  <si>
-    <t>CONDITIONAL</t>
-  </si>
-  <si>
-    <t>CONTEXT_CLASS</t>
-  </si>
-  <si>
-    <t>CONTRACTUAL</t>
-  </si>
-  <si>
-    <t>COPY_ACTION</t>
-  </si>
-  <si>
-    <t>CRITICAL</t>
-  </si>
-  <si>
-    <t>CSR_CLASS</t>
-  </si>
-  <si>
-    <t>CURRENCY</t>
-  </si>
-  <si>
-    <t>CUSTOMER</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Current Gap</t>
-  </si>
-  <si>
-    <t>Current Level</t>
-  </si>
-  <si>
-    <t>Cycle</t>
-  </si>
-  <si>
-    <t>DECISION</t>
-  </si>
-  <si>
-    <t>DELIVERY</t>
-  </si>
-  <si>
-    <t>DEPT</t>
-  </si>
-  <si>
-    <t>DESTROY</t>
-  </si>
-  <si>
-    <t>DEVELOPMENT_PRIORITY</t>
-  </si>
-  <si>
-    <t>DOC_STATUS</t>
-  </si>
-  <si>
-    <t>DRAFT</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Decision</t>
-  </si>
-  <si>
-    <t>Department / Role</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Due Date</t>
-  </si>
-  <si>
-    <t>EFFECTIVE</t>
-  </si>
-  <si>
-    <t>EMPLOYEE</t>
-  </si>
-  <si>
-    <t>ENG</t>
-  </si>
-  <si>
-    <t>ENVIRONMENT</t>
-  </si>
-  <si>
-    <t>ENVIRONMENTAL</t>
-  </si>
-  <si>
-    <t>ESG</t>
-  </si>
-  <si>
-    <t>EUR</t>
-  </si>
-  <si>
-    <t>EXCUSED</t>
-  </si>
-  <si>
-    <t>EXPIRED</t>
-  </si>
-  <si>
-    <t>EXPIRING</t>
-  </si>
-  <si>
-    <t>EXTERNAL COURSE</t>
-  </si>
-  <si>
-    <t>Eff. Date</t>
-  </si>
-  <si>
-    <t>Evidence Folder Ref</t>
-  </si>
-  <si>
-    <t>Evidence ID</t>
-  </si>
-  <si>
-    <t>Evidence Ref</t>
-  </si>
-  <si>
-    <t>Expected Evidence</t>
-  </si>
-  <si>
-    <t>FACILITY</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>FINANCE</t>
-  </si>
-  <si>
-    <t>FRM-801</t>
-  </si>
-  <si>
-    <t>Follow-Up Date</t>
-  </si>
-  <si>
-    <t>Form Code</t>
-  </si>
-  <si>
-    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>HOLD</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>HR + Department Manager</t>
-  </si>
-  <si>
-    <t>HSE</t>
-  </si>
-  <si>
-    <t>IN PROGRESS</t>
-  </si>
-  <si>
-    <t>INCIDENT_CLASS</t>
-  </si>
-  <si>
-    <t>INDEPENDENT</t>
-  </si>
-  <si>
-    <t>INSPECTION</t>
-  </si>
-  <si>
-    <t>INSURANCE</t>
-  </si>
-  <si>
-    <t>INTERNAL</t>
-  </si>
-  <si>
-    <t>ISSUE</t>
-  </si>
-  <si>
-    <t>ISSUE_ACTION</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>JPY</t>
-  </si>
-  <si>
-    <t>LATE</t>
-  </si>
-  <si>
-    <t>LEGAL</t>
-  </si>
-  <si>
-    <t>LIGHTING_AREA</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>M365 evidence / shared workbook</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>MEETING ROOM</t>
-  </si>
-  <si>
-    <t>MGT</t>
-  </si>
-  <si>
-    <t>MONITORING</t>
-  </si>
-  <si>
-    <t>Material / Resource</t>
-  </si>
-  <si>
-    <t>Method</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>NOT AUTHORIZED</t>
-  </si>
-  <si>
-    <t>NOT TRAINED</t>
-  </si>
-  <si>
-    <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
-  </si>
-  <si>
-    <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
-  </si>
-  <si>
-    <t>NOTICE: Controlled support sheet. Keep one row per controlled reference item and maintain traceable owner, date and evidence linkage.</t>
-  </si>
-  <si>
-    <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
-  </si>
-  <si>
-    <t>NOTICE: Training plans shall state the required skill, current gap, target level, method, trainer, schedule, expected evidence and follow-up date; do not plan training without a clear competence outcome.</t>
-  </si>
-  <si>
-    <t>Name / Signature / Date</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>OBSERVATION</t>
-  </si>
-  <si>
-    <t>OBSOLETE</t>
-  </si>
-  <si>
-    <t>OFFICE</t>
-  </si>
-  <si>
-    <t>OJT</t>
-  </si>
-  <si>
-    <t>OJT / Test / Observation Method</t>
-  </si>
-  <si>
-    <t>ON HOLD</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>OTHER</t>
-  </si>
-  <si>
-    <t>OUTDOOR</t>
-  </si>
-  <si>
-    <t>OWNER</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>Owner / Manager</t>
-  </si>
-  <si>
-    <t>PACKAGING</t>
-  </si>
-  <si>
-    <t>PARTY_TYPE</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>PESTLE</t>
-  </si>
-  <si>
-    <t>PHYSICAL ACUTE</t>
-  </si>
-  <si>
-    <t>PHYSICAL CHRONIC</t>
-  </si>
-  <si>
-    <t>PLANNED</t>
-  </si>
-  <si>
-    <t>PLANNING</t>
-  </si>
-  <si>
-    <t>PRESENT</t>
-  </si>
-  <si>
-    <t>PROD</t>
-  </si>
-  <si>
-    <t>Per authority matrix</t>
-  </si>
-  <si>
-    <t>Person or Group</t>
-  </si>
-  <si>
-    <t>Plan Status</t>
-  </si>
-  <si>
-    <t>Prepared By</t>
-  </si>
-  <si>
-    <t>Prepared Date</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>QA</t>
-  </si>
-  <si>
-    <t>QMS</t>
-  </si>
-  <si>
-    <t>QUALITY</t>
-  </si>
-  <si>
-    <t>Quality Management System · Controlled Document</t>
-  </si>
-  <si>
-    <t>READ-AND-UNDERSTAND</t>
-  </si>
-  <si>
-    <t>RECALL</t>
-  </si>
-  <si>
-    <t>REGULATOR</t>
-  </si>
-  <si>
-    <t>REJECT</t>
-  </si>
-  <si>
-    <t>REJECTED</t>
-  </si>
-  <si>
-    <t>REPLACE</t>
-  </si>
-  <si>
-    <t>REQUIREMENT_CLASS</t>
-  </si>
-  <si>
-    <t>RESULT</t>
-  </si>
-  <si>
-    <t>RETURN</t>
-  </si>
-  <si>
-    <t>REVIEW_OUTCOME</t>
-  </si>
-  <si>
-    <t>REVISE</t>
-  </si>
-  <si>
-    <t>RISK</t>
-  </si>
-  <si>
-    <t>Record traceable evidence references only; do not duplicate system-owned master data.</t>
-  </si>
-  <si>
-    <t>Reference Path or Link</t>
-  </si>
-  <si>
-    <t>Related Record</t>
-  </si>
-  <si>
-    <t>Required Skill</t>
-  </si>
-  <si>
-    <t>Review Status</t>
-  </si>
-  <si>
-    <t>Reviewed By</t>
-  </si>
-  <si>
-    <t>Revision</t>
-  </si>
-  <si>
-    <t>SAFETY</t>
-  </si>
-  <si>
-    <t>SALES</t>
-  </si>
-  <si>
-    <t>SECURITY</t>
-  </si>
-  <si>
-    <t>SHAREHOLDER</t>
-  </si>
-  <si>
-    <t>SHOP FLOOR</t>
-  </si>
-  <si>
-    <t>SOCIAL</t>
-  </si>
-  <si>
-    <t>SOP-801; WI-801 / WI-804; ANNEX-HR-001 + ANNEX-QMS-027 / 028</t>
-  </si>
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>STRATEGIC</t>
-  </si>
-  <si>
-    <t>SUPERSEDED</t>
-  </si>
-  <si>
-    <t>SUPERVISED</t>
-  </si>
-  <si>
-    <t>SUPPLIER</t>
-  </si>
-  <si>
-    <t>SUSPENDED</t>
-  </si>
-  <si>
-    <t>SWOT</t>
-  </si>
-  <si>
-    <t>Scheduled Date</t>
-  </si>
-  <si>
-    <t>Source Links</t>
-  </si>
-  <si>
-    <t>Source System</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Structured training plan + schedule / resource table</t>
-  </si>
-  <si>
-    <t>TEST</t>
-  </si>
-  <si>
-    <t>TRACEABILITY</t>
-  </si>
-  <si>
-    <t>TRAINING PLAN</t>
-  </si>
-  <si>
-    <t>TRAINING PLAN — CONTROLLED LOOKUP LISTS</t>
-  </si>
-  <si>
-    <t>TRAINING PLAN — EVIDENCE REFERENCE REGISTER</t>
-  </si>
-  <si>
-    <t>TRAINING PLAN — TARGETS / RESOURCES</t>
-  </si>
-  <si>
-    <t>TRAINING_METHOD</t>
-  </si>
-  <si>
-    <t>TRANSITION CUSTOMER</t>
-  </si>
-  <si>
-    <t>TRANSITION MARKET</t>
-  </si>
-  <si>
-    <t>TRANSITION REGULATORY</t>
-  </si>
-  <si>
-    <t>Target ID</t>
-  </si>
-  <si>
-    <t>Target Level</t>
-  </si>
-  <si>
-    <t>Target Population</t>
-  </si>
-  <si>
-    <t>Trainer</t>
-  </si>
-  <si>
-    <t>Training Method</t>
-  </si>
-  <si>
-    <t>Training Plan ID</t>
-  </si>
-  <si>
-    <t>Training-plan event defines who must be trained and when; intentionally separate from attendance, OJT, competence, certification and skills matrices.</t>
-  </si>
-  <si>
-    <t>UNDER REVIEW</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>V0</t>
-  </si>
-  <si>
-    <t>VALID</t>
-  </si>
-  <si>
-    <t>VND</t>
-  </si>
-  <si>
-    <t>VOID</t>
-  </si>
-  <si>
-    <t>WAREHOUSE</t>
-  </si>
-  <si>
-    <t>WHS</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>YES_NO</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -856,7 +209,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="153">
+  <borders count="155">
     <border>
       <left/>
       <right/>
@@ -2506,11 +1859,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="336">
+  <cellXfs count="373">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3380,6 +2757,97 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="116" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3462,11 +2930,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3480,9 +2948,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3495,11 +2960,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3513,9 +2978,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3528,11 +2990,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3546,9 +3008,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3561,11 +3020,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3579,9 +3038,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3939,7 +3395,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="273" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -3951,7 +3407,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
-      <c r="L1" s="188" t="inlineStr">
+      <c r="L1" s="371" t="inlineStr">
         <is>
           <t>TRAINING PLAN</t>
         </is>
@@ -3985,7 +3441,7 @@
       <c r="AM1" s="2" t="n"/>
       <c r="AN1" s="2" t="n"/>
       <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
+      <c r="AP1" s="3" t="n"/>
       <c r="AQ1" s="274" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -4010,279 +3466,392 @@
       <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="AQ2" s="277" t="inlineStr">
+      <c r="A2" s="336" t="n"/>
+      <c r="B2" s="337" t="n"/>
+      <c r="C2" s="337" t="n"/>
+      <c r="D2" s="337" t="n"/>
+      <c r="E2" s="337" t="n"/>
+      <c r="F2" s="337" t="n"/>
+      <c r="G2" s="337" t="n"/>
+      <c r="H2" s="337" t="n"/>
+      <c r="I2" s="337" t="n"/>
+      <c r="J2" s="337" t="n"/>
+      <c r="K2" s="338" t="n"/>
+      <c r="L2" s="337" t="n"/>
+      <c r="M2" s="337" t="n"/>
+      <c r="N2" s="337" t="n"/>
+      <c r="O2" s="337" t="n"/>
+      <c r="P2" s="337" t="n"/>
+      <c r="Q2" s="337" t="n"/>
+      <c r="R2" s="337" t="n"/>
+      <c r="S2" s="337" t="n"/>
+      <c r="T2" s="337" t="n"/>
+      <c r="U2" s="337" t="n"/>
+      <c r="V2" s="337" t="n"/>
+      <c r="W2" s="337" t="n"/>
+      <c r="X2" s="337" t="n"/>
+      <c r="Y2" s="337" t="n"/>
+      <c r="Z2" s="337" t="n"/>
+      <c r="AA2" s="337" t="n"/>
+      <c r="AB2" s="337" t="n"/>
+      <c r="AC2" s="337" t="n"/>
+      <c r="AD2" s="337" t="n"/>
+      <c r="AE2" s="337" t="n"/>
+      <c r="AF2" s="337" t="n"/>
+      <c r="AG2" s="337" t="n"/>
+      <c r="AH2" s="337" t="n"/>
+      <c r="AI2" s="337" t="n"/>
+      <c r="AJ2" s="337" t="n"/>
+      <c r="AK2" s="337" t="n"/>
+      <c r="AL2" s="337" t="n"/>
+      <c r="AM2" s="337" t="n"/>
+      <c r="AN2" s="337" t="n"/>
+      <c r="AO2" s="337" t="n"/>
+      <c r="AP2" s="338" t="n"/>
+      <c r="AQ2" s="339" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="278" t="n"/>
-      <c r="AS2" s="278" t="n"/>
-      <c r="AT2" s="278" t="n"/>
-      <c r="AU2" s="278" t="n"/>
-      <c r="AV2" s="279" t="n"/>
-      <c r="AW2" s="280" t="inlineStr">
+      <c r="AR2" s="340" t="n"/>
+      <c r="AS2" s="340" t="n"/>
+      <c r="AT2" s="340" t="n"/>
+      <c r="AU2" s="340" t="n"/>
+      <c r="AV2" s="341" t="n"/>
+      <c r="AW2" s="342" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="278" t="n"/>
-      <c r="AY2" s="278" t="n"/>
-      <c r="AZ2" s="278" t="n"/>
-      <c r="BA2" s="278" t="n"/>
-      <c r="BB2" s="278" t="n"/>
-      <c r="BC2" s="278" t="n"/>
-      <c r="BD2" s="281" t="n"/>
+      <c r="AX2" s="343" t="n"/>
+      <c r="AY2" s="343" t="n"/>
+      <c r="AZ2" s="343" t="n"/>
+      <c r="BA2" s="343" t="n"/>
+      <c r="BB2" s="343" t="n"/>
+      <c r="BC2" s="343" t="n"/>
+      <c r="BD2" s="344" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="9" t="n"/>
-      <c r="AQ3" s="277" t="inlineStr">
+      <c r="A3" s="345" t="n"/>
+      <c r="B3" s="46" t="n"/>
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="46" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="46" t="n"/>
+      <c r="G3" s="46" t="n"/>
+      <c r="H3" s="46" t="n"/>
+      <c r="I3" s="46" t="n"/>
+      <c r="J3" s="46" t="n"/>
+      <c r="K3" s="346" t="n"/>
+      <c r="L3" s="46" t="n"/>
+      <c r="M3" s="46" t="n"/>
+      <c r="N3" s="46" t="n"/>
+      <c r="O3" s="46" t="n"/>
+      <c r="P3" s="46" t="n"/>
+      <c r="Q3" s="46" t="n"/>
+      <c r="R3" s="46" t="n"/>
+      <c r="S3" s="46" t="n"/>
+      <c r="T3" s="46" t="n"/>
+      <c r="U3" s="46" t="n"/>
+      <c r="V3" s="46" t="n"/>
+      <c r="W3" s="46" t="n"/>
+      <c r="X3" s="46" t="n"/>
+      <c r="Y3" s="46" t="n"/>
+      <c r="Z3" s="46" t="n"/>
+      <c r="AA3" s="46" t="n"/>
+      <c r="AB3" s="46" t="n"/>
+      <c r="AC3" s="46" t="n"/>
+      <c r="AD3" s="46" t="n"/>
+      <c r="AE3" s="46" t="n"/>
+      <c r="AF3" s="46" t="n"/>
+      <c r="AG3" s="46" t="n"/>
+      <c r="AH3" s="46" t="n"/>
+      <c r="AI3" s="46" t="n"/>
+      <c r="AJ3" s="46" t="n"/>
+      <c r="AK3" s="46" t="n"/>
+      <c r="AL3" s="46" t="n"/>
+      <c r="AM3" s="46" t="n"/>
+      <c r="AN3" s="46" t="n"/>
+      <c r="AO3" s="46" t="n"/>
+      <c r="AP3" s="346" t="n"/>
+      <c r="AQ3" s="347" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="278" t="n"/>
-      <c r="AS3" s="278" t="n"/>
-      <c r="AT3" s="278" t="n"/>
-      <c r="AU3" s="278" t="n"/>
-      <c r="AV3" s="279" t="n"/>
-      <c r="AW3" s="280" t="inlineStr">
+      <c r="AR3" s="348" t="n"/>
+      <c r="AS3" s="348" t="n"/>
+      <c r="AT3" s="348" t="n"/>
+      <c r="AU3" s="348" t="n"/>
+      <c r="AV3" s="349" t="n"/>
+      <c r="AW3" s="243" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="278" t="n"/>
-      <c r="AY3" s="278" t="n"/>
-      <c r="AZ3" s="278" t="n"/>
-      <c r="BA3" s="278" t="n"/>
-      <c r="BB3" s="278" t="n"/>
-      <c r="BC3" s="278" t="n"/>
-      <c r="BD3" s="281" t="n"/>
+      <c r="AX3" s="350" t="n"/>
+      <c r="AY3" s="350" t="n"/>
+      <c r="AZ3" s="350" t="n"/>
+      <c r="BA3" s="350" t="n"/>
+      <c r="BB3" s="350" t="n"/>
+      <c r="BC3" s="350" t="n"/>
+      <c r="BD3" s="351" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="200" t="inlineStr">
+      <c r="A4" s="345" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
+      <c r="I4" s="46" t="n"/>
+      <c r="J4" s="46" t="n"/>
+      <c r="K4" s="346" t="n"/>
+      <c r="L4" s="352" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="277" t="inlineStr">
+      <c r="M4" s="46" t="n"/>
+      <c r="N4" s="46" t="n"/>
+      <c r="O4" s="46" t="n"/>
+      <c r="P4" s="46" t="n"/>
+      <c r="Q4" s="46" t="n"/>
+      <c r="R4" s="46" t="n"/>
+      <c r="S4" s="46" t="n"/>
+      <c r="T4" s="46" t="n"/>
+      <c r="U4" s="46" t="n"/>
+      <c r="V4" s="46" t="n"/>
+      <c r="W4" s="46" t="n"/>
+      <c r="X4" s="46" t="n"/>
+      <c r="Y4" s="46" t="n"/>
+      <c r="Z4" s="46" t="n"/>
+      <c r="AA4" s="46" t="n"/>
+      <c r="AB4" s="46" t="n"/>
+      <c r="AC4" s="46" t="n"/>
+      <c r="AD4" s="46" t="n"/>
+      <c r="AE4" s="46" t="n"/>
+      <c r="AF4" s="46" t="n"/>
+      <c r="AG4" s="46" t="n"/>
+      <c r="AH4" s="46" t="n"/>
+      <c r="AI4" s="46" t="n"/>
+      <c r="AJ4" s="46" t="n"/>
+      <c r="AK4" s="46" t="n"/>
+      <c r="AL4" s="46" t="n"/>
+      <c r="AM4" s="46" t="n"/>
+      <c r="AN4" s="46" t="n"/>
+      <c r="AO4" s="46" t="n"/>
+      <c r="AP4" s="346" t="n"/>
+      <c r="AQ4" s="347" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="278" t="n"/>
-      <c r="AS4" s="278" t="n"/>
-      <c r="AT4" s="278" t="n"/>
-      <c r="AU4" s="278" t="n"/>
-      <c r="AV4" s="279" t="n"/>
-      <c r="AW4" s="280" t="inlineStr">
+      <c r="AR4" s="348" t="n"/>
+      <c r="AS4" s="348" t="n"/>
+      <c r="AT4" s="348" t="n"/>
+      <c r="AU4" s="348" t="n"/>
+      <c r="AV4" s="349" t="n"/>
+      <c r="AW4" s="243" t="inlineStr">
         <is>
           <t>HR + Department Manager</t>
         </is>
       </c>
-      <c r="AX4" s="278" t="n"/>
-      <c r="AY4" s="278" t="n"/>
-      <c r="AZ4" s="278" t="n"/>
-      <c r="BA4" s="278" t="n"/>
-      <c r="BB4" s="278" t="n"/>
-      <c r="BC4" s="278" t="n"/>
-      <c r="BD4" s="281" t="n"/>
+      <c r="AX4" s="350" t="n"/>
+      <c r="AY4" s="350" t="n"/>
+      <c r="AZ4" s="350" t="n"/>
+      <c r="BA4" s="350" t="n"/>
+      <c r="BB4" s="350" t="n"/>
+      <c r="BC4" s="350" t="n"/>
+      <c r="BD4" s="351" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="14" t="n"/>
-      <c r="L5" s="42" t="inlineStr">
+      <c r="A5" s="345" t="n"/>
+      <c r="B5" s="46" t="n"/>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+      <c r="E5" s="46" t="n"/>
+      <c r="F5" s="46" t="n"/>
+      <c r="G5" s="46" t="n"/>
+      <c r="H5" s="46" t="n"/>
+      <c r="I5" s="46" t="n"/>
+      <c r="J5" s="46" t="n"/>
+      <c r="K5" s="346" t="n"/>
+      <c r="L5" s="353" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="13" t="n"/>
-      <c r="N5" s="13" t="n"/>
-      <c r="O5" s="13" t="n"/>
-      <c r="P5" s="13" t="n"/>
-      <c r="Q5" s="13" t="n"/>
-      <c r="R5" s="13" t="n"/>
-      <c r="S5" s="13" t="n"/>
-      <c r="T5" s="13" t="n"/>
-      <c r="U5" s="13" t="n"/>
-      <c r="V5" s="13" t="n"/>
-      <c r="W5" s="13" t="n"/>
-      <c r="X5" s="13" t="n"/>
-      <c r="Y5" s="13" t="n"/>
-      <c r="Z5" s="13" t="n"/>
-      <c r="AA5" s="13" t="n"/>
-      <c r="AB5" s="13" t="n"/>
-      <c r="AC5" s="13" t="n"/>
-      <c r="AD5" s="13" t="n"/>
-      <c r="AE5" s="13" t="n"/>
-      <c r="AF5" s="13" t="n"/>
-      <c r="AG5" s="13" t="n"/>
-      <c r="AH5" s="13" t="n"/>
-      <c r="AI5" s="13" t="n"/>
-      <c r="AJ5" s="13" t="n"/>
-      <c r="AK5" s="13" t="n"/>
-      <c r="AL5" s="13" t="n"/>
-      <c r="AM5" s="13" t="n"/>
-      <c r="AN5" s="13" t="n"/>
-      <c r="AO5" s="13" t="n"/>
-      <c r="AP5" s="13" t="n"/>
-      <c r="AQ5" s="282" t="inlineStr">
+      <c r="M5" s="46" t="n"/>
+      <c r="N5" s="46" t="n"/>
+      <c r="O5" s="46" t="n"/>
+      <c r="P5" s="46" t="n"/>
+      <c r="Q5" s="46" t="n"/>
+      <c r="R5" s="46" t="n"/>
+      <c r="S5" s="46" t="n"/>
+      <c r="T5" s="46" t="n"/>
+      <c r="U5" s="46" t="n"/>
+      <c r="V5" s="46" t="n"/>
+      <c r="W5" s="46" t="n"/>
+      <c r="X5" s="46" t="n"/>
+      <c r="Y5" s="46" t="n"/>
+      <c r="Z5" s="46" t="n"/>
+      <c r="AA5" s="46" t="n"/>
+      <c r="AB5" s="46" t="n"/>
+      <c r="AC5" s="46" t="n"/>
+      <c r="AD5" s="46" t="n"/>
+      <c r="AE5" s="46" t="n"/>
+      <c r="AF5" s="46" t="n"/>
+      <c r="AG5" s="46" t="n"/>
+      <c r="AH5" s="46" t="n"/>
+      <c r="AI5" s="46" t="n"/>
+      <c r="AJ5" s="46" t="n"/>
+      <c r="AK5" s="46" t="n"/>
+      <c r="AL5" s="46" t="n"/>
+      <c r="AM5" s="46" t="n"/>
+      <c r="AN5" s="46" t="n"/>
+      <c r="AO5" s="46" t="n"/>
+      <c r="AP5" s="346" t="n"/>
+      <c r="AQ5" s="347" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="283" t="n"/>
-      <c r="AS5" s="283" t="n"/>
-      <c r="AT5" s="283" t="n"/>
-      <c r="AU5" s="283" t="n"/>
-      <c r="AV5" s="284" t="n"/>
-      <c r="AW5" s="285" t="inlineStr">
+      <c r="AR5" s="348" t="n"/>
+      <c r="AS5" s="348" t="n"/>
+      <c r="AT5" s="348" t="n"/>
+      <c r="AU5" s="348" t="n"/>
+      <c r="AV5" s="349" t="n"/>
+      <c r="AW5" s="243" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="283" t="n"/>
-      <c r="AY5" s="283" t="n"/>
-      <c r="AZ5" s="283" t="n"/>
-      <c r="BA5" s="283" t="n"/>
-      <c r="BB5" s="283" t="n"/>
-      <c r="BC5" s="283" t="n"/>
-      <c r="BD5" s="286" t="n"/>
+      <c r="AX5" s="350" t="n"/>
+      <c r="AY5" s="350" t="n"/>
+      <c r="AZ5" s="350" t="n"/>
+      <c r="BA5" s="350" t="n"/>
+      <c r="BB5" s="350" t="n"/>
+      <c r="BC5" s="350" t="n"/>
+      <c r="BD5" s="351" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="209" t="n"/>
-      <c r="B6" s="209" t="n"/>
-      <c r="C6" s="209" t="n"/>
-      <c r="D6" s="209" t="n"/>
-      <c r="E6" s="209" t="n"/>
-      <c r="F6" s="209" t="n"/>
-      <c r="G6" s="209" t="n"/>
-      <c r="H6" s="209" t="n"/>
-      <c r="I6" s="209" t="n"/>
-      <c r="J6" s="209" t="n"/>
-      <c r="K6" s="209" t="n"/>
-      <c r="L6" s="209" t="n"/>
-      <c r="M6" s="209" t="n"/>
-      <c r="N6" s="209" t="n"/>
-      <c r="O6" s="209" t="n"/>
-      <c r="P6" s="209" t="n"/>
-      <c r="Q6" s="209" t="n"/>
-      <c r="R6" s="209" t="n"/>
-      <c r="S6" s="209" t="n"/>
-      <c r="T6" s="209" t="n"/>
-      <c r="U6" s="209" t="n"/>
-      <c r="V6" s="209" t="n"/>
-      <c r="W6" s="209" t="n"/>
-      <c r="X6" s="209" t="n"/>
-      <c r="Y6" s="209" t="n"/>
-      <c r="Z6" s="209" t="n"/>
-      <c r="AA6" s="209" t="n"/>
-      <c r="AB6" s="209" t="n"/>
-      <c r="AC6" s="209" t="n"/>
-      <c r="AD6" s="209" t="n"/>
-      <c r="AE6" s="209" t="n"/>
-      <c r="AF6" s="209" t="n"/>
-      <c r="AG6" s="209" t="n"/>
-      <c r="AH6" s="209" t="n"/>
-      <c r="AI6" s="209" t="n"/>
-      <c r="AJ6" s="209" t="n"/>
-      <c r="AK6" s="209" t="n"/>
-      <c r="AL6" s="209" t="n"/>
-      <c r="AM6" s="209" t="n"/>
-      <c r="AN6" s="209" t="n"/>
-      <c r="AO6" s="209" t="n"/>
-      <c r="AP6" s="209" t="n"/>
-      <c r="AQ6" s="209" t="n"/>
-      <c r="AR6" s="209" t="n"/>
-      <c r="AS6" s="209" t="n"/>
-      <c r="AT6" s="209" t="n"/>
-      <c r="AU6" s="209" t="n"/>
-      <c r="AV6" s="209" t="n"/>
-      <c r="AW6" s="209" t="n"/>
-      <c r="AX6" s="209" t="n"/>
-      <c r="AY6" s="209" t="n"/>
-      <c r="AZ6" s="209" t="n"/>
-      <c r="BA6" s="209" t="n"/>
-      <c r="BB6" s="209" t="n"/>
-      <c r="BC6" s="209" t="n"/>
-      <c r="BD6" s="209" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="354" t="n"/>
+      <c r="B6" s="355" t="n"/>
+      <c r="C6" s="355" t="n"/>
+      <c r="D6" s="355" t="n"/>
+      <c r="E6" s="355" t="n"/>
+      <c r="F6" s="355" t="n"/>
+      <c r="G6" s="355" t="n"/>
+      <c r="H6" s="355" t="n"/>
+      <c r="I6" s="355" t="n"/>
+      <c r="J6" s="355" t="n"/>
+      <c r="K6" s="356" t="n"/>
+      <c r="L6" s="355" t="n"/>
+      <c r="M6" s="355" t="n"/>
+      <c r="N6" s="355" t="n"/>
+      <c r="O6" s="355" t="n"/>
+      <c r="P6" s="355" t="n"/>
+      <c r="Q6" s="355" t="n"/>
+      <c r="R6" s="355" t="n"/>
+      <c r="S6" s="355" t="n"/>
+      <c r="T6" s="355" t="n"/>
+      <c r="U6" s="355" t="n"/>
+      <c r="V6" s="355" t="n"/>
+      <c r="W6" s="355" t="n"/>
+      <c r="X6" s="355" t="n"/>
+      <c r="Y6" s="355" t="n"/>
+      <c r="Z6" s="355" t="n"/>
+      <c r="AA6" s="355" t="n"/>
+      <c r="AB6" s="355" t="n"/>
+      <c r="AC6" s="355" t="n"/>
+      <c r="AD6" s="355" t="n"/>
+      <c r="AE6" s="355" t="n"/>
+      <c r="AF6" s="355" t="n"/>
+      <c r="AG6" s="355" t="n"/>
+      <c r="AH6" s="355" t="n"/>
+      <c r="AI6" s="355" t="n"/>
+      <c r="AJ6" s="355" t="n"/>
+      <c r="AK6" s="355" t="n"/>
+      <c r="AL6" s="355" t="n"/>
+      <c r="AM6" s="355" t="n"/>
+      <c r="AN6" s="355" t="n"/>
+      <c r="AO6" s="355" t="n"/>
+      <c r="AP6" s="356" t="n"/>
+      <c r="AQ6" s="357" t="n"/>
+      <c r="AR6" s="357" t="n"/>
+      <c r="AS6" s="357" t="n"/>
+      <c r="AT6" s="357" t="n"/>
+      <c r="AU6" s="357" t="n"/>
+      <c r="AV6" s="358" t="n"/>
+      <c r="AW6" s="359" t="n"/>
+      <c r="AX6" s="359" t="n"/>
+      <c r="AY6" s="359" t="n"/>
+      <c r="AZ6" s="359" t="n"/>
+      <c r="BA6" s="359" t="n"/>
+      <c r="BB6" s="359" t="n"/>
+      <c r="BC6" s="359" t="n"/>
+      <c r="BD6" s="360" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. REFERENCE INFORMATION</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="6" t="n"/>
-      <c r="R7" s="6" t="n"/>
-      <c r="S7" s="6" t="n"/>
-      <c r="T7" s="6" t="n"/>
-      <c r="U7" s="6" t="n"/>
-      <c r="V7" s="6" t="n"/>
-      <c r="W7" s="6" t="n"/>
-      <c r="X7" s="6" t="n"/>
-      <c r="Y7" s="6" t="n"/>
-      <c r="Z7" s="6" t="n"/>
-      <c r="AA7" s="6" t="n"/>
-      <c r="AB7" s="6" t="n"/>
-      <c r="AC7" s="6" t="n"/>
-      <c r="AD7" s="6" t="n"/>
-      <c r="AE7" s="6" t="n"/>
-      <c r="AF7" s="6" t="n"/>
-      <c r="AG7" s="6" t="n"/>
-      <c r="AH7" s="6" t="n"/>
-      <c r="AI7" s="6" t="n"/>
-      <c r="AJ7" s="6" t="n"/>
-      <c r="AK7" s="6" t="n"/>
-      <c r="AL7" s="6" t="n"/>
-      <c r="AM7" s="6" t="n"/>
-      <c r="AN7" s="6" t="n"/>
-      <c r="AO7" s="6" t="n"/>
-      <c r="AP7" s="6" t="n"/>
-      <c r="AQ7" s="6" t="n"/>
-      <c r="AR7" s="6" t="n"/>
-      <c r="AS7" s="6" t="n"/>
-      <c r="AT7" s="6" t="n"/>
-      <c r="AU7" s="6" t="n"/>
-      <c r="AV7" s="6" t="n"/>
-      <c r="AW7" s="6" t="n"/>
-      <c r="AX7" s="6" t="n"/>
-      <c r="AY7" s="6" t="n"/>
-      <c r="AZ7" s="6" t="n"/>
-      <c r="BA7" s="6" t="n"/>
-      <c r="BB7" s="6" t="n"/>
-      <c r="BC7" s="6" t="n"/>
-      <c r="BD7" s="7" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="361" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n"/>
+      <c r="P7" s="17" t="n"/>
+      <c r="Q7" s="17" t="n"/>
+      <c r="R7" s="17" t="n"/>
+      <c r="S7" s="17" t="n"/>
+      <c r="T7" s="17" t="n"/>
+      <c r="U7" s="17" t="n"/>
+      <c r="V7" s="17" t="n"/>
+      <c r="W7" s="17" t="n"/>
+      <c r="X7" s="17" t="n"/>
+      <c r="Y7" s="17" t="n"/>
+      <c r="Z7" s="17" t="n"/>
+      <c r="AA7" s="17" t="n"/>
+      <c r="AB7" s="17" t="n"/>
+      <c r="AC7" s="17" t="n"/>
+      <c r="AD7" s="17" t="n"/>
+      <c r="AE7" s="17" t="n"/>
+      <c r="AF7" s="17" t="n"/>
+      <c r="AG7" s="17" t="n"/>
+      <c r="AH7" s="17" t="n"/>
+      <c r="AI7" s="17" t="n"/>
+      <c r="AJ7" s="17" t="n"/>
+      <c r="AK7" s="17" t="n"/>
+      <c r="AL7" s="17" t="n"/>
+      <c r="AM7" s="17" t="n"/>
+      <c r="AN7" s="17" t="n"/>
+      <c r="AO7" s="17" t="n"/>
+      <c r="AP7" s="17" t="n"/>
+      <c r="AQ7" s="17" t="n"/>
+      <c r="AR7" s="17" t="n"/>
+      <c r="AS7" s="17" t="n"/>
+      <c r="AT7" s="17" t="n"/>
+      <c r="AU7" s="17" t="n"/>
+      <c r="AV7" s="17" t="n"/>
+      <c r="AW7" s="17" t="n"/>
+      <c r="AX7" s="17" t="n"/>
+      <c r="AY7" s="17" t="n"/>
+      <c r="AZ7" s="17" t="n"/>
+      <c r="BA7" s="17" t="n"/>
+      <c r="BB7" s="17" t="n"/>
+      <c r="BC7" s="17" t="n"/>
+      <c r="BD7" s="17" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="288" t="inlineStr">
@@ -5523,66 +5092,66 @@
       <c r="BD26" s="241" t="n"/>
     </row>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="333" t="inlineStr">
+      <c r="A27" s="263" t="inlineStr">
         <is>
           <t>NOTICE: Training plans shall state the required skill, current gap, target level, method, trainer, schedule, expected evidence and follow-up date; do not plan training without a clear competence outcome.</t>
         </is>
       </c>
-      <c r="B27" s="334" t="n"/>
-      <c r="C27" s="334" t="n"/>
-      <c r="D27" s="334" t="n"/>
-      <c r="E27" s="334" t="n"/>
-      <c r="F27" s="334" t="n"/>
-      <c r="G27" s="334" t="n"/>
-      <c r="H27" s="334" t="n"/>
-      <c r="I27" s="334" t="n"/>
-      <c r="J27" s="334" t="n"/>
-      <c r="K27" s="334" t="n"/>
-      <c r="L27" s="334" t="n"/>
-      <c r="M27" s="334" t="n"/>
-      <c r="N27" s="334" t="n"/>
-      <c r="O27" s="334" t="n"/>
-      <c r="P27" s="334" t="n"/>
-      <c r="Q27" s="334" t="n"/>
-      <c r="R27" s="334" t="n"/>
-      <c r="S27" s="334" t="n"/>
-      <c r="T27" s="334" t="n"/>
-      <c r="U27" s="334" t="n"/>
-      <c r="V27" s="334" t="n"/>
-      <c r="W27" s="334" t="n"/>
-      <c r="X27" s="334" t="n"/>
-      <c r="Y27" s="334" t="n"/>
-      <c r="Z27" s="334" t="n"/>
-      <c r="AA27" s="334" t="n"/>
-      <c r="AB27" s="334" t="n"/>
-      <c r="AC27" s="334" t="n"/>
-      <c r="AD27" s="334" t="n"/>
-      <c r="AE27" s="334" t="n"/>
-      <c r="AF27" s="334" t="n"/>
-      <c r="AG27" s="334" t="n"/>
-      <c r="AH27" s="334" t="n"/>
-      <c r="AI27" s="334" t="n"/>
-      <c r="AJ27" s="334" t="n"/>
-      <c r="AK27" s="334" t="n"/>
-      <c r="AL27" s="334" t="n"/>
-      <c r="AM27" s="334" t="n"/>
-      <c r="AN27" s="334" t="n"/>
-      <c r="AO27" s="334" t="n"/>
-      <c r="AP27" s="334" t="n"/>
-      <c r="AQ27" s="334" t="n"/>
-      <c r="AR27" s="334" t="n"/>
-      <c r="AS27" s="334" t="n"/>
-      <c r="AT27" s="334" t="n"/>
-      <c r="AU27" s="334" t="n"/>
-      <c r="AV27" s="334" t="n"/>
-      <c r="AW27" s="334" t="n"/>
-      <c r="AX27" s="334" t="n"/>
-      <c r="AY27" s="334" t="n"/>
-      <c r="AZ27" s="334" t="n"/>
-      <c r="BA27" s="334" t="n"/>
-      <c r="BB27" s="334" t="n"/>
-      <c r="BC27" s="334" t="n"/>
-      <c r="BD27" s="335" t="n"/>
+      <c r="B27" s="362" t="n"/>
+      <c r="C27" s="362" t="n"/>
+      <c r="D27" s="362" t="n"/>
+      <c r="E27" s="362" t="n"/>
+      <c r="F27" s="362" t="n"/>
+      <c r="G27" s="362" t="n"/>
+      <c r="H27" s="362" t="n"/>
+      <c r="I27" s="362" t="n"/>
+      <c r="J27" s="362" t="n"/>
+      <c r="K27" s="362" t="n"/>
+      <c r="L27" s="362" t="n"/>
+      <c r="M27" s="362" t="n"/>
+      <c r="N27" s="362" t="n"/>
+      <c r="O27" s="362" t="n"/>
+      <c r="P27" s="362" t="n"/>
+      <c r="Q27" s="362" t="n"/>
+      <c r="R27" s="362" t="n"/>
+      <c r="S27" s="362" t="n"/>
+      <c r="T27" s="362" t="n"/>
+      <c r="U27" s="362" t="n"/>
+      <c r="V27" s="362" t="n"/>
+      <c r="W27" s="362" t="n"/>
+      <c r="X27" s="362" t="n"/>
+      <c r="Y27" s="362" t="n"/>
+      <c r="Z27" s="362" t="n"/>
+      <c r="AA27" s="362" t="n"/>
+      <c r="AB27" s="362" t="n"/>
+      <c r="AC27" s="362" t="n"/>
+      <c r="AD27" s="362" t="n"/>
+      <c r="AE27" s="362" t="n"/>
+      <c r="AF27" s="362" t="n"/>
+      <c r="AG27" s="362" t="n"/>
+      <c r="AH27" s="362" t="n"/>
+      <c r="AI27" s="362" t="n"/>
+      <c r="AJ27" s="362" t="n"/>
+      <c r="AK27" s="362" t="n"/>
+      <c r="AL27" s="362" t="n"/>
+      <c r="AM27" s="362" t="n"/>
+      <c r="AN27" s="362" t="n"/>
+      <c r="AO27" s="362" t="n"/>
+      <c r="AP27" s="362" t="n"/>
+      <c r="AQ27" s="362" t="n"/>
+      <c r="AR27" s="362" t="n"/>
+      <c r="AS27" s="362" t="n"/>
+      <c r="AT27" s="362" t="n"/>
+      <c r="AU27" s="362" t="n"/>
+      <c r="AV27" s="362" t="n"/>
+      <c r="AW27" s="362" t="n"/>
+      <c r="AX27" s="362" t="n"/>
+      <c r="AY27" s="362" t="n"/>
+      <c r="AZ27" s="362" t="n"/>
+      <c r="BA27" s="362" t="n"/>
+      <c r="BB27" s="362" t="n"/>
+      <c r="BC27" s="362" t="n"/>
+      <c r="BD27" s="363" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1"/>
     <row r="29" ht="20" customHeight="1"/>
@@ -5937,7 +5506,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="273" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -5949,7 +5518,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
-      <c r="L1" s="188" t="inlineStr">
+      <c r="L1" s="371" t="inlineStr">
         <is>
           <t>TRAINING PLAN — TARGETS / RESOURCES</t>
         </is>
@@ -5983,7 +5552,7 @@
       <c r="AM1" s="2" t="n"/>
       <c r="AN1" s="2" t="n"/>
       <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
+      <c r="AP1" s="3" t="n"/>
       <c r="AQ1" s="274" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -6008,279 +5577,392 @@
       <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="AQ2" s="277" t="inlineStr">
+      <c r="A2" s="336" t="n"/>
+      <c r="B2" s="337" t="n"/>
+      <c r="C2" s="337" t="n"/>
+      <c r="D2" s="337" t="n"/>
+      <c r="E2" s="337" t="n"/>
+      <c r="F2" s="337" t="n"/>
+      <c r="G2" s="337" t="n"/>
+      <c r="H2" s="337" t="n"/>
+      <c r="I2" s="337" t="n"/>
+      <c r="J2" s="337" t="n"/>
+      <c r="K2" s="338" t="n"/>
+      <c r="L2" s="337" t="n"/>
+      <c r="M2" s="337" t="n"/>
+      <c r="N2" s="337" t="n"/>
+      <c r="O2" s="337" t="n"/>
+      <c r="P2" s="337" t="n"/>
+      <c r="Q2" s="337" t="n"/>
+      <c r="R2" s="337" t="n"/>
+      <c r="S2" s="337" t="n"/>
+      <c r="T2" s="337" t="n"/>
+      <c r="U2" s="337" t="n"/>
+      <c r="V2" s="337" t="n"/>
+      <c r="W2" s="337" t="n"/>
+      <c r="X2" s="337" t="n"/>
+      <c r="Y2" s="337" t="n"/>
+      <c r="Z2" s="337" t="n"/>
+      <c r="AA2" s="337" t="n"/>
+      <c r="AB2" s="337" t="n"/>
+      <c r="AC2" s="337" t="n"/>
+      <c r="AD2" s="337" t="n"/>
+      <c r="AE2" s="337" t="n"/>
+      <c r="AF2" s="337" t="n"/>
+      <c r="AG2" s="337" t="n"/>
+      <c r="AH2" s="337" t="n"/>
+      <c r="AI2" s="337" t="n"/>
+      <c r="AJ2" s="337" t="n"/>
+      <c r="AK2" s="337" t="n"/>
+      <c r="AL2" s="337" t="n"/>
+      <c r="AM2" s="337" t="n"/>
+      <c r="AN2" s="337" t="n"/>
+      <c r="AO2" s="337" t="n"/>
+      <c r="AP2" s="338" t="n"/>
+      <c r="AQ2" s="339" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="278" t="n"/>
-      <c r="AS2" s="278" t="n"/>
-      <c r="AT2" s="278" t="n"/>
-      <c r="AU2" s="278" t="n"/>
-      <c r="AV2" s="279" t="n"/>
-      <c r="AW2" s="280" t="inlineStr">
+      <c r="AR2" s="340" t="n"/>
+      <c r="AS2" s="340" t="n"/>
+      <c r="AT2" s="340" t="n"/>
+      <c r="AU2" s="340" t="n"/>
+      <c r="AV2" s="341" t="n"/>
+      <c r="AW2" s="342" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="278" t="n"/>
-      <c r="AY2" s="278" t="n"/>
-      <c r="AZ2" s="278" t="n"/>
-      <c r="BA2" s="278" t="n"/>
-      <c r="BB2" s="278" t="n"/>
-      <c r="BC2" s="278" t="n"/>
-      <c r="BD2" s="281" t="n"/>
+      <c r="AX2" s="343" t="n"/>
+      <c r="AY2" s="343" t="n"/>
+      <c r="AZ2" s="343" t="n"/>
+      <c r="BA2" s="343" t="n"/>
+      <c r="BB2" s="343" t="n"/>
+      <c r="BC2" s="343" t="n"/>
+      <c r="BD2" s="344" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="9" t="n"/>
-      <c r="AQ3" s="277" t="inlineStr">
+      <c r="A3" s="345" t="n"/>
+      <c r="B3" s="46" t="n"/>
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="46" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="46" t="n"/>
+      <c r="G3" s="46" t="n"/>
+      <c r="H3" s="46" t="n"/>
+      <c r="I3" s="46" t="n"/>
+      <c r="J3" s="46" t="n"/>
+      <c r="K3" s="346" t="n"/>
+      <c r="L3" s="46" t="n"/>
+      <c r="M3" s="46" t="n"/>
+      <c r="N3" s="46" t="n"/>
+      <c r="O3" s="46" t="n"/>
+      <c r="P3" s="46" t="n"/>
+      <c r="Q3" s="46" t="n"/>
+      <c r="R3" s="46" t="n"/>
+      <c r="S3" s="46" t="n"/>
+      <c r="T3" s="46" t="n"/>
+      <c r="U3" s="46" t="n"/>
+      <c r="V3" s="46" t="n"/>
+      <c r="W3" s="46" t="n"/>
+      <c r="X3" s="46" t="n"/>
+      <c r="Y3" s="46" t="n"/>
+      <c r="Z3" s="46" t="n"/>
+      <c r="AA3" s="46" t="n"/>
+      <c r="AB3" s="46" t="n"/>
+      <c r="AC3" s="46" t="n"/>
+      <c r="AD3" s="46" t="n"/>
+      <c r="AE3" s="46" t="n"/>
+      <c r="AF3" s="46" t="n"/>
+      <c r="AG3" s="46" t="n"/>
+      <c r="AH3" s="46" t="n"/>
+      <c r="AI3" s="46" t="n"/>
+      <c r="AJ3" s="46" t="n"/>
+      <c r="AK3" s="46" t="n"/>
+      <c r="AL3" s="46" t="n"/>
+      <c r="AM3" s="46" t="n"/>
+      <c r="AN3" s="46" t="n"/>
+      <c r="AO3" s="46" t="n"/>
+      <c r="AP3" s="346" t="n"/>
+      <c r="AQ3" s="347" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="278" t="n"/>
-      <c r="AS3" s="278" t="n"/>
-      <c r="AT3" s="278" t="n"/>
-      <c r="AU3" s="278" t="n"/>
-      <c r="AV3" s="279" t="n"/>
-      <c r="AW3" s="280" t="inlineStr">
+      <c r="AR3" s="348" t="n"/>
+      <c r="AS3" s="348" t="n"/>
+      <c r="AT3" s="348" t="n"/>
+      <c r="AU3" s="348" t="n"/>
+      <c r="AV3" s="349" t="n"/>
+      <c r="AW3" s="243" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="278" t="n"/>
-      <c r="AY3" s="278" t="n"/>
-      <c r="AZ3" s="278" t="n"/>
-      <c r="BA3" s="278" t="n"/>
-      <c r="BB3" s="278" t="n"/>
-      <c r="BC3" s="278" t="n"/>
-      <c r="BD3" s="281" t="n"/>
+      <c r="AX3" s="350" t="n"/>
+      <c r="AY3" s="350" t="n"/>
+      <c r="AZ3" s="350" t="n"/>
+      <c r="BA3" s="350" t="n"/>
+      <c r="BB3" s="350" t="n"/>
+      <c r="BC3" s="350" t="n"/>
+      <c r="BD3" s="351" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="200" t="inlineStr">
+      <c r="A4" s="345" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
+      <c r="I4" s="46" t="n"/>
+      <c r="J4" s="46" t="n"/>
+      <c r="K4" s="346" t="n"/>
+      <c r="L4" s="352" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="277" t="inlineStr">
+      <c r="M4" s="46" t="n"/>
+      <c r="N4" s="46" t="n"/>
+      <c r="O4" s="46" t="n"/>
+      <c r="P4" s="46" t="n"/>
+      <c r="Q4" s="46" t="n"/>
+      <c r="R4" s="46" t="n"/>
+      <c r="S4" s="46" t="n"/>
+      <c r="T4" s="46" t="n"/>
+      <c r="U4" s="46" t="n"/>
+      <c r="V4" s="46" t="n"/>
+      <c r="W4" s="46" t="n"/>
+      <c r="X4" s="46" t="n"/>
+      <c r="Y4" s="46" t="n"/>
+      <c r="Z4" s="46" t="n"/>
+      <c r="AA4" s="46" t="n"/>
+      <c r="AB4" s="46" t="n"/>
+      <c r="AC4" s="46" t="n"/>
+      <c r="AD4" s="46" t="n"/>
+      <c r="AE4" s="46" t="n"/>
+      <c r="AF4" s="46" t="n"/>
+      <c r="AG4" s="46" t="n"/>
+      <c r="AH4" s="46" t="n"/>
+      <c r="AI4" s="46" t="n"/>
+      <c r="AJ4" s="46" t="n"/>
+      <c r="AK4" s="46" t="n"/>
+      <c r="AL4" s="46" t="n"/>
+      <c r="AM4" s="46" t="n"/>
+      <c r="AN4" s="46" t="n"/>
+      <c r="AO4" s="46" t="n"/>
+      <c r="AP4" s="346" t="n"/>
+      <c r="AQ4" s="347" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="278" t="n"/>
-      <c r="AS4" s="278" t="n"/>
-      <c r="AT4" s="278" t="n"/>
-      <c r="AU4" s="278" t="n"/>
-      <c r="AV4" s="279" t="n"/>
-      <c r="AW4" s="280" t="inlineStr">
+      <c r="AR4" s="348" t="n"/>
+      <c r="AS4" s="348" t="n"/>
+      <c r="AT4" s="348" t="n"/>
+      <c r="AU4" s="348" t="n"/>
+      <c r="AV4" s="349" t="n"/>
+      <c r="AW4" s="243" t="inlineStr">
         <is>
           <t>HR + Department Manager</t>
         </is>
       </c>
-      <c r="AX4" s="278" t="n"/>
-      <c r="AY4" s="278" t="n"/>
-      <c r="AZ4" s="278" t="n"/>
-      <c r="BA4" s="278" t="n"/>
-      <c r="BB4" s="278" t="n"/>
-      <c r="BC4" s="278" t="n"/>
-      <c r="BD4" s="281" t="n"/>
+      <c r="AX4" s="350" t="n"/>
+      <c r="AY4" s="350" t="n"/>
+      <c r="AZ4" s="350" t="n"/>
+      <c r="BA4" s="350" t="n"/>
+      <c r="BB4" s="350" t="n"/>
+      <c r="BC4" s="350" t="n"/>
+      <c r="BD4" s="351" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="14" t="n"/>
-      <c r="L5" s="42" t="inlineStr">
+      <c r="A5" s="345" t="n"/>
+      <c r="B5" s="46" t="n"/>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+      <c r="E5" s="46" t="n"/>
+      <c r="F5" s="46" t="n"/>
+      <c r="G5" s="46" t="n"/>
+      <c r="H5" s="46" t="n"/>
+      <c r="I5" s="46" t="n"/>
+      <c r="J5" s="46" t="n"/>
+      <c r="K5" s="346" t="n"/>
+      <c r="L5" s="353" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="13" t="n"/>
-      <c r="N5" s="13" t="n"/>
-      <c r="O5" s="13" t="n"/>
-      <c r="P5" s="13" t="n"/>
-      <c r="Q5" s="13" t="n"/>
-      <c r="R5" s="13" t="n"/>
-      <c r="S5" s="13" t="n"/>
-      <c r="T5" s="13" t="n"/>
-      <c r="U5" s="13" t="n"/>
-      <c r="V5" s="13" t="n"/>
-      <c r="W5" s="13" t="n"/>
-      <c r="X5" s="13" t="n"/>
-      <c r="Y5" s="13" t="n"/>
-      <c r="Z5" s="13" t="n"/>
-      <c r="AA5" s="13" t="n"/>
-      <c r="AB5" s="13" t="n"/>
-      <c r="AC5" s="13" t="n"/>
-      <c r="AD5" s="13" t="n"/>
-      <c r="AE5" s="13" t="n"/>
-      <c r="AF5" s="13" t="n"/>
-      <c r="AG5" s="13" t="n"/>
-      <c r="AH5" s="13" t="n"/>
-      <c r="AI5" s="13" t="n"/>
-      <c r="AJ5" s="13" t="n"/>
-      <c r="AK5" s="13" t="n"/>
-      <c r="AL5" s="13" t="n"/>
-      <c r="AM5" s="13" t="n"/>
-      <c r="AN5" s="13" t="n"/>
-      <c r="AO5" s="13" t="n"/>
-      <c r="AP5" s="13" t="n"/>
-      <c r="AQ5" s="282" t="inlineStr">
+      <c r="M5" s="46" t="n"/>
+      <c r="N5" s="46" t="n"/>
+      <c r="O5" s="46" t="n"/>
+      <c r="P5" s="46" t="n"/>
+      <c r="Q5" s="46" t="n"/>
+      <c r="R5" s="46" t="n"/>
+      <c r="S5" s="46" t="n"/>
+      <c r="T5" s="46" t="n"/>
+      <c r="U5" s="46" t="n"/>
+      <c r="V5" s="46" t="n"/>
+      <c r="W5" s="46" t="n"/>
+      <c r="X5" s="46" t="n"/>
+      <c r="Y5" s="46" t="n"/>
+      <c r="Z5" s="46" t="n"/>
+      <c r="AA5" s="46" t="n"/>
+      <c r="AB5" s="46" t="n"/>
+      <c r="AC5" s="46" t="n"/>
+      <c r="AD5" s="46" t="n"/>
+      <c r="AE5" s="46" t="n"/>
+      <c r="AF5" s="46" t="n"/>
+      <c r="AG5" s="46" t="n"/>
+      <c r="AH5" s="46" t="n"/>
+      <c r="AI5" s="46" t="n"/>
+      <c r="AJ5" s="46" t="n"/>
+      <c r="AK5" s="46" t="n"/>
+      <c r="AL5" s="46" t="n"/>
+      <c r="AM5" s="46" t="n"/>
+      <c r="AN5" s="46" t="n"/>
+      <c r="AO5" s="46" t="n"/>
+      <c r="AP5" s="346" t="n"/>
+      <c r="AQ5" s="347" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="283" t="n"/>
-      <c r="AS5" s="283" t="n"/>
-      <c r="AT5" s="283" t="n"/>
-      <c r="AU5" s="283" t="n"/>
-      <c r="AV5" s="284" t="n"/>
-      <c r="AW5" s="285" t="inlineStr">
+      <c r="AR5" s="348" t="n"/>
+      <c r="AS5" s="348" t="n"/>
+      <c r="AT5" s="348" t="n"/>
+      <c r="AU5" s="348" t="n"/>
+      <c r="AV5" s="349" t="n"/>
+      <c r="AW5" s="243" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="283" t="n"/>
-      <c r="AY5" s="283" t="n"/>
-      <c r="AZ5" s="283" t="n"/>
-      <c r="BA5" s="283" t="n"/>
-      <c r="BB5" s="283" t="n"/>
-      <c r="BC5" s="283" t="n"/>
-      <c r="BD5" s="286" t="n"/>
+      <c r="AX5" s="350" t="n"/>
+      <c r="AY5" s="350" t="n"/>
+      <c r="AZ5" s="350" t="n"/>
+      <c r="BA5" s="350" t="n"/>
+      <c r="BB5" s="350" t="n"/>
+      <c r="BC5" s="350" t="n"/>
+      <c r="BD5" s="351" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="209" t="n"/>
-      <c r="B6" s="209" t="n"/>
-      <c r="C6" s="209" t="n"/>
-      <c r="D6" s="209" t="n"/>
-      <c r="E6" s="209" t="n"/>
-      <c r="F6" s="209" t="n"/>
-      <c r="G6" s="209" t="n"/>
-      <c r="H6" s="209" t="n"/>
-      <c r="I6" s="209" t="n"/>
-      <c r="J6" s="209" t="n"/>
-      <c r="K6" s="209" t="n"/>
-      <c r="L6" s="209" t="n"/>
-      <c r="M6" s="209" t="n"/>
-      <c r="N6" s="209" t="n"/>
-      <c r="O6" s="209" t="n"/>
-      <c r="P6" s="209" t="n"/>
-      <c r="Q6" s="209" t="n"/>
-      <c r="R6" s="209" t="n"/>
-      <c r="S6" s="209" t="n"/>
-      <c r="T6" s="209" t="n"/>
-      <c r="U6" s="209" t="n"/>
-      <c r="V6" s="209" t="n"/>
-      <c r="W6" s="209" t="n"/>
-      <c r="X6" s="209" t="n"/>
-      <c r="Y6" s="209" t="n"/>
-      <c r="Z6" s="209" t="n"/>
-      <c r="AA6" s="209" t="n"/>
-      <c r="AB6" s="209" t="n"/>
-      <c r="AC6" s="209" t="n"/>
-      <c r="AD6" s="209" t="n"/>
-      <c r="AE6" s="209" t="n"/>
-      <c r="AF6" s="209" t="n"/>
-      <c r="AG6" s="209" t="n"/>
-      <c r="AH6" s="209" t="n"/>
-      <c r="AI6" s="209" t="n"/>
-      <c r="AJ6" s="209" t="n"/>
-      <c r="AK6" s="209" t="n"/>
-      <c r="AL6" s="209" t="n"/>
-      <c r="AM6" s="209" t="n"/>
-      <c r="AN6" s="209" t="n"/>
-      <c r="AO6" s="209" t="n"/>
-      <c r="AP6" s="209" t="n"/>
-      <c r="AQ6" s="209" t="n"/>
-      <c r="AR6" s="209" t="n"/>
-      <c r="AS6" s="209" t="n"/>
-      <c r="AT6" s="209" t="n"/>
-      <c r="AU6" s="209" t="n"/>
-      <c r="AV6" s="209" t="n"/>
-      <c r="AW6" s="209" t="n"/>
-      <c r="AX6" s="209" t="n"/>
-      <c r="AY6" s="209" t="n"/>
-      <c r="AZ6" s="209" t="n"/>
-      <c r="BA6" s="209" t="n"/>
-      <c r="BB6" s="209" t="n"/>
-      <c r="BC6" s="209" t="n"/>
-      <c r="BD6" s="209" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="354" t="n"/>
+      <c r="B6" s="355" t="n"/>
+      <c r="C6" s="355" t="n"/>
+      <c r="D6" s="355" t="n"/>
+      <c r="E6" s="355" t="n"/>
+      <c r="F6" s="355" t="n"/>
+      <c r="G6" s="355" t="n"/>
+      <c r="H6" s="355" t="n"/>
+      <c r="I6" s="355" t="n"/>
+      <c r="J6" s="355" t="n"/>
+      <c r="K6" s="356" t="n"/>
+      <c r="L6" s="355" t="n"/>
+      <c r="M6" s="355" t="n"/>
+      <c r="N6" s="355" t="n"/>
+      <c r="O6" s="355" t="n"/>
+      <c r="P6" s="355" t="n"/>
+      <c r="Q6" s="355" t="n"/>
+      <c r="R6" s="355" t="n"/>
+      <c r="S6" s="355" t="n"/>
+      <c r="T6" s="355" t="n"/>
+      <c r="U6" s="355" t="n"/>
+      <c r="V6" s="355" t="n"/>
+      <c r="W6" s="355" t="n"/>
+      <c r="X6" s="355" t="n"/>
+      <c r="Y6" s="355" t="n"/>
+      <c r="Z6" s="355" t="n"/>
+      <c r="AA6" s="355" t="n"/>
+      <c r="AB6" s="355" t="n"/>
+      <c r="AC6" s="355" t="n"/>
+      <c r="AD6" s="355" t="n"/>
+      <c r="AE6" s="355" t="n"/>
+      <c r="AF6" s="355" t="n"/>
+      <c r="AG6" s="355" t="n"/>
+      <c r="AH6" s="355" t="n"/>
+      <c r="AI6" s="355" t="n"/>
+      <c r="AJ6" s="355" t="n"/>
+      <c r="AK6" s="355" t="n"/>
+      <c r="AL6" s="355" t="n"/>
+      <c r="AM6" s="355" t="n"/>
+      <c r="AN6" s="355" t="n"/>
+      <c r="AO6" s="355" t="n"/>
+      <c r="AP6" s="356" t="n"/>
+      <c r="AQ6" s="357" t="n"/>
+      <c r="AR6" s="357" t="n"/>
+      <c r="AS6" s="357" t="n"/>
+      <c r="AT6" s="357" t="n"/>
+      <c r="AU6" s="357" t="n"/>
+      <c r="AV6" s="358" t="n"/>
+      <c r="AW6" s="359" t="n"/>
+      <c r="AX6" s="359" t="n"/>
+      <c r="AY6" s="359" t="n"/>
+      <c r="AZ6" s="359" t="n"/>
+      <c r="BA6" s="359" t="n"/>
+      <c r="BB6" s="359" t="n"/>
+      <c r="BC6" s="359" t="n"/>
+      <c r="BD6" s="360" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="6" t="n"/>
-      <c r="R7" s="6" t="n"/>
-      <c r="S7" s="6" t="n"/>
-      <c r="T7" s="6" t="n"/>
-      <c r="U7" s="6" t="n"/>
-      <c r="V7" s="6" t="n"/>
-      <c r="W7" s="6" t="n"/>
-      <c r="X7" s="6" t="n"/>
-      <c r="Y7" s="6" t="n"/>
-      <c r="Z7" s="6" t="n"/>
-      <c r="AA7" s="6" t="n"/>
-      <c r="AB7" s="6" t="n"/>
-      <c r="AC7" s="6" t="n"/>
-      <c r="AD7" s="6" t="n"/>
-      <c r="AE7" s="6" t="n"/>
-      <c r="AF7" s="6" t="n"/>
-      <c r="AG7" s="6" t="n"/>
-      <c r="AH7" s="6" t="n"/>
-      <c r="AI7" s="6" t="n"/>
-      <c r="AJ7" s="6" t="n"/>
-      <c r="AK7" s="6" t="n"/>
-      <c r="AL7" s="6" t="n"/>
-      <c r="AM7" s="6" t="n"/>
-      <c r="AN7" s="6" t="n"/>
-      <c r="AO7" s="6" t="n"/>
-      <c r="AP7" s="6" t="n"/>
-      <c r="AQ7" s="6" t="n"/>
-      <c r="AR7" s="6" t="n"/>
-      <c r="AS7" s="6" t="n"/>
-      <c r="AT7" s="6" t="n"/>
-      <c r="AU7" s="6" t="n"/>
-      <c r="AV7" s="6" t="n"/>
-      <c r="AW7" s="6" t="n"/>
-      <c r="AX7" s="6" t="n"/>
-      <c r="AY7" s="6" t="n"/>
-      <c r="AZ7" s="6" t="n"/>
-      <c r="BA7" s="6" t="n"/>
-      <c r="BB7" s="6" t="n"/>
-      <c r="BC7" s="6" t="n"/>
-      <c r="BD7" s="7" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="361" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n"/>
+      <c r="P7" s="17" t="n"/>
+      <c r="Q7" s="17" t="n"/>
+      <c r="R7" s="17" t="n"/>
+      <c r="S7" s="17" t="n"/>
+      <c r="T7" s="17" t="n"/>
+      <c r="U7" s="17" t="n"/>
+      <c r="V7" s="17" t="n"/>
+      <c r="W7" s="17" t="n"/>
+      <c r="X7" s="17" t="n"/>
+      <c r="Y7" s="17" t="n"/>
+      <c r="Z7" s="17" t="n"/>
+      <c r="AA7" s="17" t="n"/>
+      <c r="AB7" s="17" t="n"/>
+      <c r="AC7" s="17" t="n"/>
+      <c r="AD7" s="17" t="n"/>
+      <c r="AE7" s="17" t="n"/>
+      <c r="AF7" s="17" t="n"/>
+      <c r="AG7" s="17" t="n"/>
+      <c r="AH7" s="17" t="n"/>
+      <c r="AI7" s="17" t="n"/>
+      <c r="AJ7" s="17" t="n"/>
+      <c r="AK7" s="17" t="n"/>
+      <c r="AL7" s="17" t="n"/>
+      <c r="AM7" s="17" t="n"/>
+      <c r="AN7" s="17" t="n"/>
+      <c r="AO7" s="17" t="n"/>
+      <c r="AP7" s="17" t="n"/>
+      <c r="AQ7" s="17" t="n"/>
+      <c r="AR7" s="17" t="n"/>
+      <c r="AS7" s="17" t="n"/>
+      <c r="AT7" s="17" t="n"/>
+      <c r="AU7" s="17" t="n"/>
+      <c r="AV7" s="17" t="n"/>
+      <c r="AW7" s="17" t="n"/>
+      <c r="AX7" s="17" t="n"/>
+      <c r="AY7" s="17" t="n"/>
+      <c r="AZ7" s="17" t="n"/>
+      <c r="BA7" s="17" t="n"/>
+      <c r="BB7" s="17" t="n"/>
+      <c r="BC7" s="17" t="n"/>
+      <c r="BD7" s="17" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="288" t="inlineStr">
@@ -7158,67 +6840,67 @@
       <c r="BC21" s="241" t="n"/>
       <c r="BD21" s="241" t="n"/>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="287" t="inlineStr">
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="263" t="inlineStr">
         <is>
           <t>NOTICE: Controlled support sheet. Keep one row per controlled reference item and maintain traceable owner, date and evidence linkage.</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
-      <c r="M22" s="6" t="n"/>
-      <c r="N22" s="6" t="n"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="6" t="n"/>
-      <c r="Q22" s="6" t="n"/>
-      <c r="R22" s="6" t="n"/>
-      <c r="S22" s="6" t="n"/>
-      <c r="T22" s="6" t="n"/>
-      <c r="U22" s="6" t="n"/>
-      <c r="V22" s="6" t="n"/>
-      <c r="W22" s="6" t="n"/>
-      <c r="X22" s="6" t="n"/>
-      <c r="Y22" s="6" t="n"/>
-      <c r="Z22" s="6" t="n"/>
-      <c r="AA22" s="6" t="n"/>
-      <c r="AB22" s="6" t="n"/>
-      <c r="AC22" s="6" t="n"/>
-      <c r="AD22" s="6" t="n"/>
-      <c r="AE22" s="6" t="n"/>
-      <c r="AF22" s="6" t="n"/>
-      <c r="AG22" s="6" t="n"/>
-      <c r="AH22" s="6" t="n"/>
-      <c r="AI22" s="6" t="n"/>
-      <c r="AJ22" s="6" t="n"/>
-      <c r="AK22" s="6" t="n"/>
-      <c r="AL22" s="6" t="n"/>
-      <c r="AM22" s="6" t="n"/>
-      <c r="AN22" s="6" t="n"/>
-      <c r="AO22" s="6" t="n"/>
-      <c r="AP22" s="6" t="n"/>
-      <c r="AQ22" s="6" t="n"/>
-      <c r="AR22" s="6" t="n"/>
-      <c r="AS22" s="6" t="n"/>
-      <c r="AT22" s="6" t="n"/>
-      <c r="AU22" s="6" t="n"/>
-      <c r="AV22" s="6" t="n"/>
-      <c r="AW22" s="6" t="n"/>
-      <c r="AX22" s="6" t="n"/>
-      <c r="AY22" s="6" t="n"/>
-      <c r="AZ22" s="6" t="n"/>
-      <c r="BA22" s="6" t="n"/>
-      <c r="BB22" s="6" t="n"/>
-      <c r="BC22" s="6" t="n"/>
-      <c r="BD22" s="7" t="n"/>
+      <c r="B22" s="362" t="n"/>
+      <c r="C22" s="362" t="n"/>
+      <c r="D22" s="362" t="n"/>
+      <c r="E22" s="362" t="n"/>
+      <c r="F22" s="362" t="n"/>
+      <c r="G22" s="362" t="n"/>
+      <c r="H22" s="362" t="n"/>
+      <c r="I22" s="362" t="n"/>
+      <c r="J22" s="362" t="n"/>
+      <c r="K22" s="362" t="n"/>
+      <c r="L22" s="362" t="n"/>
+      <c r="M22" s="362" t="n"/>
+      <c r="N22" s="362" t="n"/>
+      <c r="O22" s="362" t="n"/>
+      <c r="P22" s="362" t="n"/>
+      <c r="Q22" s="362" t="n"/>
+      <c r="R22" s="362" t="n"/>
+      <c r="S22" s="362" t="n"/>
+      <c r="T22" s="362" t="n"/>
+      <c r="U22" s="362" t="n"/>
+      <c r="V22" s="362" t="n"/>
+      <c r="W22" s="362" t="n"/>
+      <c r="X22" s="362" t="n"/>
+      <c r="Y22" s="362" t="n"/>
+      <c r="Z22" s="362" t="n"/>
+      <c r="AA22" s="362" t="n"/>
+      <c r="AB22" s="362" t="n"/>
+      <c r="AC22" s="362" t="n"/>
+      <c r="AD22" s="362" t="n"/>
+      <c r="AE22" s="362" t="n"/>
+      <c r="AF22" s="362" t="n"/>
+      <c r="AG22" s="362" t="n"/>
+      <c r="AH22" s="362" t="n"/>
+      <c r="AI22" s="362" t="n"/>
+      <c r="AJ22" s="362" t="n"/>
+      <c r="AK22" s="362" t="n"/>
+      <c r="AL22" s="362" t="n"/>
+      <c r="AM22" s="362" t="n"/>
+      <c r="AN22" s="362" t="n"/>
+      <c r="AO22" s="362" t="n"/>
+      <c r="AP22" s="362" t="n"/>
+      <c r="AQ22" s="362" t="n"/>
+      <c r="AR22" s="362" t="n"/>
+      <c r="AS22" s="362" t="n"/>
+      <c r="AT22" s="362" t="n"/>
+      <c r="AU22" s="362" t="n"/>
+      <c r="AV22" s="362" t="n"/>
+      <c r="AW22" s="362" t="n"/>
+      <c r="AX22" s="362" t="n"/>
+      <c r="AY22" s="362" t="n"/>
+      <c r="AZ22" s="362" t="n"/>
+      <c r="BA22" s="362" t="n"/>
+      <c r="BB22" s="362" t="n"/>
+      <c r="BC22" s="362" t="n"/>
+      <c r="BD22" s="363" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1"/>
     <row r="24" ht="20" customHeight="1"/>
@@ -7616,7 +7298,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="273" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -7628,7 +7310,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
-      <c r="L1" s="188" t="inlineStr">
+      <c r="L1" s="371" t="inlineStr">
         <is>
           <t>TRAINING PLAN — EVIDENCE REFERENCE REGISTER</t>
         </is>
@@ -7662,7 +7344,7 @@
       <c r="AM1" s="2" t="n"/>
       <c r="AN1" s="2" t="n"/>
       <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
+      <c r="AP1" s="3" t="n"/>
       <c r="AQ1" s="274" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -7687,279 +7369,392 @@
       <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="AQ2" s="277" t="inlineStr">
+      <c r="A2" s="336" t="n"/>
+      <c r="B2" s="337" t="n"/>
+      <c r="C2" s="337" t="n"/>
+      <c r="D2" s="337" t="n"/>
+      <c r="E2" s="337" t="n"/>
+      <c r="F2" s="337" t="n"/>
+      <c r="G2" s="337" t="n"/>
+      <c r="H2" s="337" t="n"/>
+      <c r="I2" s="337" t="n"/>
+      <c r="J2" s="337" t="n"/>
+      <c r="K2" s="338" t="n"/>
+      <c r="L2" s="337" t="n"/>
+      <c r="M2" s="337" t="n"/>
+      <c r="N2" s="337" t="n"/>
+      <c r="O2" s="337" t="n"/>
+      <c r="P2" s="337" t="n"/>
+      <c r="Q2" s="337" t="n"/>
+      <c r="R2" s="337" t="n"/>
+      <c r="S2" s="337" t="n"/>
+      <c r="T2" s="337" t="n"/>
+      <c r="U2" s="337" t="n"/>
+      <c r="V2" s="337" t="n"/>
+      <c r="W2" s="337" t="n"/>
+      <c r="X2" s="337" t="n"/>
+      <c r="Y2" s="337" t="n"/>
+      <c r="Z2" s="337" t="n"/>
+      <c r="AA2" s="337" t="n"/>
+      <c r="AB2" s="337" t="n"/>
+      <c r="AC2" s="337" t="n"/>
+      <c r="AD2" s="337" t="n"/>
+      <c r="AE2" s="337" t="n"/>
+      <c r="AF2" s="337" t="n"/>
+      <c r="AG2" s="337" t="n"/>
+      <c r="AH2" s="337" t="n"/>
+      <c r="AI2" s="337" t="n"/>
+      <c r="AJ2" s="337" t="n"/>
+      <c r="AK2" s="337" t="n"/>
+      <c r="AL2" s="337" t="n"/>
+      <c r="AM2" s="337" t="n"/>
+      <c r="AN2" s="337" t="n"/>
+      <c r="AO2" s="337" t="n"/>
+      <c r="AP2" s="338" t="n"/>
+      <c r="AQ2" s="339" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="278" t="n"/>
-      <c r="AS2" s="278" t="n"/>
-      <c r="AT2" s="278" t="n"/>
-      <c r="AU2" s="278" t="n"/>
-      <c r="AV2" s="279" t="n"/>
-      <c r="AW2" s="280" t="inlineStr">
+      <c r="AR2" s="340" t="n"/>
+      <c r="AS2" s="340" t="n"/>
+      <c r="AT2" s="340" t="n"/>
+      <c r="AU2" s="340" t="n"/>
+      <c r="AV2" s="341" t="n"/>
+      <c r="AW2" s="342" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="278" t="n"/>
-      <c r="AY2" s="278" t="n"/>
-      <c r="AZ2" s="278" t="n"/>
-      <c r="BA2" s="278" t="n"/>
-      <c r="BB2" s="278" t="n"/>
-      <c r="BC2" s="278" t="n"/>
-      <c r="BD2" s="281" t="n"/>
+      <c r="AX2" s="343" t="n"/>
+      <c r="AY2" s="343" t="n"/>
+      <c r="AZ2" s="343" t="n"/>
+      <c r="BA2" s="343" t="n"/>
+      <c r="BB2" s="343" t="n"/>
+      <c r="BC2" s="343" t="n"/>
+      <c r="BD2" s="344" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="9" t="n"/>
-      <c r="AQ3" s="277" t="inlineStr">
+      <c r="A3" s="345" t="n"/>
+      <c r="B3" s="46" t="n"/>
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="46" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="46" t="n"/>
+      <c r="G3" s="46" t="n"/>
+      <c r="H3" s="46" t="n"/>
+      <c r="I3" s="46" t="n"/>
+      <c r="J3" s="46" t="n"/>
+      <c r="K3" s="346" t="n"/>
+      <c r="L3" s="46" t="n"/>
+      <c r="M3" s="46" t="n"/>
+      <c r="N3" s="46" t="n"/>
+      <c r="O3" s="46" t="n"/>
+      <c r="P3" s="46" t="n"/>
+      <c r="Q3" s="46" t="n"/>
+      <c r="R3" s="46" t="n"/>
+      <c r="S3" s="46" t="n"/>
+      <c r="T3" s="46" t="n"/>
+      <c r="U3" s="46" t="n"/>
+      <c r="V3" s="46" t="n"/>
+      <c r="W3" s="46" t="n"/>
+      <c r="X3" s="46" t="n"/>
+      <c r="Y3" s="46" t="n"/>
+      <c r="Z3" s="46" t="n"/>
+      <c r="AA3" s="46" t="n"/>
+      <c r="AB3" s="46" t="n"/>
+      <c r="AC3" s="46" t="n"/>
+      <c r="AD3" s="46" t="n"/>
+      <c r="AE3" s="46" t="n"/>
+      <c r="AF3" s="46" t="n"/>
+      <c r="AG3" s="46" t="n"/>
+      <c r="AH3" s="46" t="n"/>
+      <c r="AI3" s="46" t="n"/>
+      <c r="AJ3" s="46" t="n"/>
+      <c r="AK3" s="46" t="n"/>
+      <c r="AL3" s="46" t="n"/>
+      <c r="AM3" s="46" t="n"/>
+      <c r="AN3" s="46" t="n"/>
+      <c r="AO3" s="46" t="n"/>
+      <c r="AP3" s="346" t="n"/>
+      <c r="AQ3" s="347" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="278" t="n"/>
-      <c r="AS3" s="278" t="n"/>
-      <c r="AT3" s="278" t="n"/>
-      <c r="AU3" s="278" t="n"/>
-      <c r="AV3" s="279" t="n"/>
-      <c r="AW3" s="280" t="inlineStr">
+      <c r="AR3" s="348" t="n"/>
+      <c r="AS3" s="348" t="n"/>
+      <c r="AT3" s="348" t="n"/>
+      <c r="AU3" s="348" t="n"/>
+      <c r="AV3" s="349" t="n"/>
+      <c r="AW3" s="243" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="278" t="n"/>
-      <c r="AY3" s="278" t="n"/>
-      <c r="AZ3" s="278" t="n"/>
-      <c r="BA3" s="278" t="n"/>
-      <c r="BB3" s="278" t="n"/>
-      <c r="BC3" s="278" t="n"/>
-      <c r="BD3" s="281" t="n"/>
+      <c r="AX3" s="350" t="n"/>
+      <c r="AY3" s="350" t="n"/>
+      <c r="AZ3" s="350" t="n"/>
+      <c r="BA3" s="350" t="n"/>
+      <c r="BB3" s="350" t="n"/>
+      <c r="BC3" s="350" t="n"/>
+      <c r="BD3" s="351" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="200" t="inlineStr">
+      <c r="A4" s="345" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
+      <c r="I4" s="46" t="n"/>
+      <c r="J4" s="46" t="n"/>
+      <c r="K4" s="346" t="n"/>
+      <c r="L4" s="352" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="277" t="inlineStr">
+      <c r="M4" s="46" t="n"/>
+      <c r="N4" s="46" t="n"/>
+      <c r="O4" s="46" t="n"/>
+      <c r="P4" s="46" t="n"/>
+      <c r="Q4" s="46" t="n"/>
+      <c r="R4" s="46" t="n"/>
+      <c r="S4" s="46" t="n"/>
+      <c r="T4" s="46" t="n"/>
+      <c r="U4" s="46" t="n"/>
+      <c r="V4" s="46" t="n"/>
+      <c r="W4" s="46" t="n"/>
+      <c r="X4" s="46" t="n"/>
+      <c r="Y4" s="46" t="n"/>
+      <c r="Z4" s="46" t="n"/>
+      <c r="AA4" s="46" t="n"/>
+      <c r="AB4" s="46" t="n"/>
+      <c r="AC4" s="46" t="n"/>
+      <c r="AD4" s="46" t="n"/>
+      <c r="AE4" s="46" t="n"/>
+      <c r="AF4" s="46" t="n"/>
+      <c r="AG4" s="46" t="n"/>
+      <c r="AH4" s="46" t="n"/>
+      <c r="AI4" s="46" t="n"/>
+      <c r="AJ4" s="46" t="n"/>
+      <c r="AK4" s="46" t="n"/>
+      <c r="AL4" s="46" t="n"/>
+      <c r="AM4" s="46" t="n"/>
+      <c r="AN4" s="46" t="n"/>
+      <c r="AO4" s="46" t="n"/>
+      <c r="AP4" s="346" t="n"/>
+      <c r="AQ4" s="347" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="278" t="n"/>
-      <c r="AS4" s="278" t="n"/>
-      <c r="AT4" s="278" t="n"/>
-      <c r="AU4" s="278" t="n"/>
-      <c r="AV4" s="279" t="n"/>
-      <c r="AW4" s="280" t="inlineStr">
+      <c r="AR4" s="348" t="n"/>
+      <c r="AS4" s="348" t="n"/>
+      <c r="AT4" s="348" t="n"/>
+      <c r="AU4" s="348" t="n"/>
+      <c r="AV4" s="349" t="n"/>
+      <c r="AW4" s="243" t="inlineStr">
         <is>
           <t>HR + Department Manager</t>
         </is>
       </c>
-      <c r="AX4" s="278" t="n"/>
-      <c r="AY4" s="278" t="n"/>
-      <c r="AZ4" s="278" t="n"/>
-      <c r="BA4" s="278" t="n"/>
-      <c r="BB4" s="278" t="n"/>
-      <c r="BC4" s="278" t="n"/>
-      <c r="BD4" s="281" t="n"/>
+      <c r="AX4" s="350" t="n"/>
+      <c r="AY4" s="350" t="n"/>
+      <c r="AZ4" s="350" t="n"/>
+      <c r="BA4" s="350" t="n"/>
+      <c r="BB4" s="350" t="n"/>
+      <c r="BC4" s="350" t="n"/>
+      <c r="BD4" s="351" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="14" t="n"/>
-      <c r="L5" s="42" t="inlineStr">
+      <c r="A5" s="345" t="n"/>
+      <c r="B5" s="46" t="n"/>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+      <c r="E5" s="46" t="n"/>
+      <c r="F5" s="46" t="n"/>
+      <c r="G5" s="46" t="n"/>
+      <c r="H5" s="46" t="n"/>
+      <c r="I5" s="46" t="n"/>
+      <c r="J5" s="46" t="n"/>
+      <c r="K5" s="346" t="n"/>
+      <c r="L5" s="353" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="13" t="n"/>
-      <c r="N5" s="13" t="n"/>
-      <c r="O5" s="13" t="n"/>
-      <c r="P5" s="13" t="n"/>
-      <c r="Q5" s="13" t="n"/>
-      <c r="R5" s="13" t="n"/>
-      <c r="S5" s="13" t="n"/>
-      <c r="T5" s="13" t="n"/>
-      <c r="U5" s="13" t="n"/>
-      <c r="V5" s="13" t="n"/>
-      <c r="W5" s="13" t="n"/>
-      <c r="X5" s="13" t="n"/>
-      <c r="Y5" s="13" t="n"/>
-      <c r="Z5" s="13" t="n"/>
-      <c r="AA5" s="13" t="n"/>
-      <c r="AB5" s="13" t="n"/>
-      <c r="AC5" s="13" t="n"/>
-      <c r="AD5" s="13" t="n"/>
-      <c r="AE5" s="13" t="n"/>
-      <c r="AF5" s="13" t="n"/>
-      <c r="AG5" s="13" t="n"/>
-      <c r="AH5" s="13" t="n"/>
-      <c r="AI5" s="13" t="n"/>
-      <c r="AJ5" s="13" t="n"/>
-      <c r="AK5" s="13" t="n"/>
-      <c r="AL5" s="13" t="n"/>
-      <c r="AM5" s="13" t="n"/>
-      <c r="AN5" s="13" t="n"/>
-      <c r="AO5" s="13" t="n"/>
-      <c r="AP5" s="13" t="n"/>
-      <c r="AQ5" s="282" t="inlineStr">
+      <c r="M5" s="46" t="n"/>
+      <c r="N5" s="46" t="n"/>
+      <c r="O5" s="46" t="n"/>
+      <c r="P5" s="46" t="n"/>
+      <c r="Q5" s="46" t="n"/>
+      <c r="R5" s="46" t="n"/>
+      <c r="S5" s="46" t="n"/>
+      <c r="T5" s="46" t="n"/>
+      <c r="U5" s="46" t="n"/>
+      <c r="V5" s="46" t="n"/>
+      <c r="W5" s="46" t="n"/>
+      <c r="X5" s="46" t="n"/>
+      <c r="Y5" s="46" t="n"/>
+      <c r="Z5" s="46" t="n"/>
+      <c r="AA5" s="46" t="n"/>
+      <c r="AB5" s="46" t="n"/>
+      <c r="AC5" s="46" t="n"/>
+      <c r="AD5" s="46" t="n"/>
+      <c r="AE5" s="46" t="n"/>
+      <c r="AF5" s="46" t="n"/>
+      <c r="AG5" s="46" t="n"/>
+      <c r="AH5" s="46" t="n"/>
+      <c r="AI5" s="46" t="n"/>
+      <c r="AJ5" s="46" t="n"/>
+      <c r="AK5" s="46" t="n"/>
+      <c r="AL5" s="46" t="n"/>
+      <c r="AM5" s="46" t="n"/>
+      <c r="AN5" s="46" t="n"/>
+      <c r="AO5" s="46" t="n"/>
+      <c r="AP5" s="346" t="n"/>
+      <c r="AQ5" s="347" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="283" t="n"/>
-      <c r="AS5" s="283" t="n"/>
-      <c r="AT5" s="283" t="n"/>
-      <c r="AU5" s="283" t="n"/>
-      <c r="AV5" s="284" t="n"/>
-      <c r="AW5" s="285" t="inlineStr">
+      <c r="AR5" s="348" t="n"/>
+      <c r="AS5" s="348" t="n"/>
+      <c r="AT5" s="348" t="n"/>
+      <c r="AU5" s="348" t="n"/>
+      <c r="AV5" s="349" t="n"/>
+      <c r="AW5" s="243" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="283" t="n"/>
-      <c r="AY5" s="283" t="n"/>
-      <c r="AZ5" s="283" t="n"/>
-      <c r="BA5" s="283" t="n"/>
-      <c r="BB5" s="283" t="n"/>
-      <c r="BC5" s="283" t="n"/>
-      <c r="BD5" s="286" t="n"/>
+      <c r="AX5" s="350" t="n"/>
+      <c r="AY5" s="350" t="n"/>
+      <c r="AZ5" s="350" t="n"/>
+      <c r="BA5" s="350" t="n"/>
+      <c r="BB5" s="350" t="n"/>
+      <c r="BC5" s="350" t="n"/>
+      <c r="BD5" s="351" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="209" t="n"/>
-      <c r="B6" s="209" t="n"/>
-      <c r="C6" s="209" t="n"/>
-      <c r="D6" s="209" t="n"/>
-      <c r="E6" s="209" t="n"/>
-      <c r="F6" s="209" t="n"/>
-      <c r="G6" s="209" t="n"/>
-      <c r="H6" s="209" t="n"/>
-      <c r="I6" s="209" t="n"/>
-      <c r="J6" s="209" t="n"/>
-      <c r="K6" s="209" t="n"/>
-      <c r="L6" s="209" t="n"/>
-      <c r="M6" s="209" t="n"/>
-      <c r="N6" s="209" t="n"/>
-      <c r="O6" s="209" t="n"/>
-      <c r="P6" s="209" t="n"/>
-      <c r="Q6" s="209" t="n"/>
-      <c r="R6" s="209" t="n"/>
-      <c r="S6" s="209" t="n"/>
-      <c r="T6" s="209" t="n"/>
-      <c r="U6" s="209" t="n"/>
-      <c r="V6" s="209" t="n"/>
-      <c r="W6" s="209" t="n"/>
-      <c r="X6" s="209" t="n"/>
-      <c r="Y6" s="209" t="n"/>
-      <c r="Z6" s="209" t="n"/>
-      <c r="AA6" s="209" t="n"/>
-      <c r="AB6" s="209" t="n"/>
-      <c r="AC6" s="209" t="n"/>
-      <c r="AD6" s="209" t="n"/>
-      <c r="AE6" s="209" t="n"/>
-      <c r="AF6" s="209" t="n"/>
-      <c r="AG6" s="209" t="n"/>
-      <c r="AH6" s="209" t="n"/>
-      <c r="AI6" s="209" t="n"/>
-      <c r="AJ6" s="209" t="n"/>
-      <c r="AK6" s="209" t="n"/>
-      <c r="AL6" s="209" t="n"/>
-      <c r="AM6" s="209" t="n"/>
-      <c r="AN6" s="209" t="n"/>
-      <c r="AO6" s="209" t="n"/>
-      <c r="AP6" s="209" t="n"/>
-      <c r="AQ6" s="209" t="n"/>
-      <c r="AR6" s="209" t="n"/>
-      <c r="AS6" s="209" t="n"/>
-      <c r="AT6" s="209" t="n"/>
-      <c r="AU6" s="209" t="n"/>
-      <c r="AV6" s="209" t="n"/>
-      <c r="AW6" s="209" t="n"/>
-      <c r="AX6" s="209" t="n"/>
-      <c r="AY6" s="209" t="n"/>
-      <c r="AZ6" s="209" t="n"/>
-      <c r="BA6" s="209" t="n"/>
-      <c r="BB6" s="209" t="n"/>
-      <c r="BC6" s="209" t="n"/>
-      <c r="BD6" s="209" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="354" t="n"/>
+      <c r="B6" s="355" t="n"/>
+      <c r="C6" s="355" t="n"/>
+      <c r="D6" s="355" t="n"/>
+      <c r="E6" s="355" t="n"/>
+      <c r="F6" s="355" t="n"/>
+      <c r="G6" s="355" t="n"/>
+      <c r="H6" s="355" t="n"/>
+      <c r="I6" s="355" t="n"/>
+      <c r="J6" s="355" t="n"/>
+      <c r="K6" s="356" t="n"/>
+      <c r="L6" s="355" t="n"/>
+      <c r="M6" s="355" t="n"/>
+      <c r="N6" s="355" t="n"/>
+      <c r="O6" s="355" t="n"/>
+      <c r="P6" s="355" t="n"/>
+      <c r="Q6" s="355" t="n"/>
+      <c r="R6" s="355" t="n"/>
+      <c r="S6" s="355" t="n"/>
+      <c r="T6" s="355" t="n"/>
+      <c r="U6" s="355" t="n"/>
+      <c r="V6" s="355" t="n"/>
+      <c r="W6" s="355" t="n"/>
+      <c r="X6" s="355" t="n"/>
+      <c r="Y6" s="355" t="n"/>
+      <c r="Z6" s="355" t="n"/>
+      <c r="AA6" s="355" t="n"/>
+      <c r="AB6" s="355" t="n"/>
+      <c r="AC6" s="355" t="n"/>
+      <c r="AD6" s="355" t="n"/>
+      <c r="AE6" s="355" t="n"/>
+      <c r="AF6" s="355" t="n"/>
+      <c r="AG6" s="355" t="n"/>
+      <c r="AH6" s="355" t="n"/>
+      <c r="AI6" s="355" t="n"/>
+      <c r="AJ6" s="355" t="n"/>
+      <c r="AK6" s="355" t="n"/>
+      <c r="AL6" s="355" t="n"/>
+      <c r="AM6" s="355" t="n"/>
+      <c r="AN6" s="355" t="n"/>
+      <c r="AO6" s="355" t="n"/>
+      <c r="AP6" s="356" t="n"/>
+      <c r="AQ6" s="357" t="n"/>
+      <c r="AR6" s="357" t="n"/>
+      <c r="AS6" s="357" t="n"/>
+      <c r="AT6" s="357" t="n"/>
+      <c r="AU6" s="357" t="n"/>
+      <c r="AV6" s="358" t="n"/>
+      <c r="AW6" s="359" t="n"/>
+      <c r="AX6" s="359" t="n"/>
+      <c r="AY6" s="359" t="n"/>
+      <c r="AZ6" s="359" t="n"/>
+      <c r="BA6" s="359" t="n"/>
+      <c r="BB6" s="359" t="n"/>
+      <c r="BC6" s="359" t="n"/>
+      <c r="BD6" s="360" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="6" t="n"/>
-      <c r="R7" s="6" t="n"/>
-      <c r="S7" s="6" t="n"/>
-      <c r="T7" s="6" t="n"/>
-      <c r="U7" s="6" t="n"/>
-      <c r="V7" s="6" t="n"/>
-      <c r="W7" s="6" t="n"/>
-      <c r="X7" s="6" t="n"/>
-      <c r="Y7" s="6" t="n"/>
-      <c r="Z7" s="6" t="n"/>
-      <c r="AA7" s="6" t="n"/>
-      <c r="AB7" s="6" t="n"/>
-      <c r="AC7" s="6" t="n"/>
-      <c r="AD7" s="6" t="n"/>
-      <c r="AE7" s="6" t="n"/>
-      <c r="AF7" s="6" t="n"/>
-      <c r="AG7" s="6" t="n"/>
-      <c r="AH7" s="6" t="n"/>
-      <c r="AI7" s="6" t="n"/>
-      <c r="AJ7" s="6" t="n"/>
-      <c r="AK7" s="6" t="n"/>
-      <c r="AL7" s="6" t="n"/>
-      <c r="AM7" s="6" t="n"/>
-      <c r="AN7" s="6" t="n"/>
-      <c r="AO7" s="6" t="n"/>
-      <c r="AP7" s="6" t="n"/>
-      <c r="AQ7" s="6" t="n"/>
-      <c r="AR7" s="6" t="n"/>
-      <c r="AS7" s="6" t="n"/>
-      <c r="AT7" s="6" t="n"/>
-      <c r="AU7" s="6" t="n"/>
-      <c r="AV7" s="6" t="n"/>
-      <c r="AW7" s="6" t="n"/>
-      <c r="AX7" s="6" t="n"/>
-      <c r="AY7" s="6" t="n"/>
-      <c r="AZ7" s="6" t="n"/>
-      <c r="BA7" s="6" t="n"/>
-      <c r="BB7" s="6" t="n"/>
-      <c r="BC7" s="6" t="n"/>
-      <c r="BD7" s="7" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="361" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n"/>
+      <c r="P7" s="17" t="n"/>
+      <c r="Q7" s="17" t="n"/>
+      <c r="R7" s="17" t="n"/>
+      <c r="S7" s="17" t="n"/>
+      <c r="T7" s="17" t="n"/>
+      <c r="U7" s="17" t="n"/>
+      <c r="V7" s="17" t="n"/>
+      <c r="W7" s="17" t="n"/>
+      <c r="X7" s="17" t="n"/>
+      <c r="Y7" s="17" t="n"/>
+      <c r="Z7" s="17" t="n"/>
+      <c r="AA7" s="17" t="n"/>
+      <c r="AB7" s="17" t="n"/>
+      <c r="AC7" s="17" t="n"/>
+      <c r="AD7" s="17" t="n"/>
+      <c r="AE7" s="17" t="n"/>
+      <c r="AF7" s="17" t="n"/>
+      <c r="AG7" s="17" t="n"/>
+      <c r="AH7" s="17" t="n"/>
+      <c r="AI7" s="17" t="n"/>
+      <c r="AJ7" s="17" t="n"/>
+      <c r="AK7" s="17" t="n"/>
+      <c r="AL7" s="17" t="n"/>
+      <c r="AM7" s="17" t="n"/>
+      <c r="AN7" s="17" t="n"/>
+      <c r="AO7" s="17" t="n"/>
+      <c r="AP7" s="17" t="n"/>
+      <c r="AQ7" s="17" t="n"/>
+      <c r="AR7" s="17" t="n"/>
+      <c r="AS7" s="17" t="n"/>
+      <c r="AT7" s="17" t="n"/>
+      <c r="AU7" s="17" t="n"/>
+      <c r="AV7" s="17" t="n"/>
+      <c r="AW7" s="17" t="n"/>
+      <c r="AX7" s="17" t="n"/>
+      <c r="AY7" s="17" t="n"/>
+      <c r="AZ7" s="17" t="n"/>
+      <c r="BA7" s="17" t="n"/>
+      <c r="BB7" s="17" t="n"/>
+      <c r="BC7" s="17" t="n"/>
+      <c r="BD7" s="17" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="288" t="inlineStr">
@@ -8775,67 +8570,67 @@
       <c r="BC20" s="241" t="n"/>
       <c r="BD20" s="241" t="n"/>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="287" t="inlineStr">
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="263" t="inlineStr">
         <is>
           <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
-      <c r="M21" s="6" t="n"/>
-      <c r="N21" s="6" t="n"/>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="6" t="n"/>
-      <c r="Q21" s="6" t="n"/>
-      <c r="R21" s="6" t="n"/>
-      <c r="S21" s="6" t="n"/>
-      <c r="T21" s="6" t="n"/>
-      <c r="U21" s="6" t="n"/>
-      <c r="V21" s="6" t="n"/>
-      <c r="W21" s="6" t="n"/>
-      <c r="X21" s="6" t="n"/>
-      <c r="Y21" s="6" t="n"/>
-      <c r="Z21" s="6" t="n"/>
-      <c r="AA21" s="6" t="n"/>
-      <c r="AB21" s="6" t="n"/>
-      <c r="AC21" s="6" t="n"/>
-      <c r="AD21" s="6" t="n"/>
-      <c r="AE21" s="6" t="n"/>
-      <c r="AF21" s="6" t="n"/>
-      <c r="AG21" s="6" t="n"/>
-      <c r="AH21" s="6" t="n"/>
-      <c r="AI21" s="6" t="n"/>
-      <c r="AJ21" s="6" t="n"/>
-      <c r="AK21" s="6" t="n"/>
-      <c r="AL21" s="6" t="n"/>
-      <c r="AM21" s="6" t="n"/>
-      <c r="AN21" s="6" t="n"/>
-      <c r="AO21" s="6" t="n"/>
-      <c r="AP21" s="6" t="n"/>
-      <c r="AQ21" s="6" t="n"/>
-      <c r="AR21" s="6" t="n"/>
-      <c r="AS21" s="6" t="n"/>
-      <c r="AT21" s="6" t="n"/>
-      <c r="AU21" s="6" t="n"/>
-      <c r="AV21" s="6" t="n"/>
-      <c r="AW21" s="6" t="n"/>
-      <c r="AX21" s="6" t="n"/>
-      <c r="AY21" s="6" t="n"/>
-      <c r="AZ21" s="6" t="n"/>
-      <c r="BA21" s="6" t="n"/>
-      <c r="BB21" s="6" t="n"/>
-      <c r="BC21" s="6" t="n"/>
-      <c r="BD21" s="7" t="n"/>
+      <c r="B21" s="362" t="n"/>
+      <c r="C21" s="362" t="n"/>
+      <c r="D21" s="362" t="n"/>
+      <c r="E21" s="362" t="n"/>
+      <c r="F21" s="362" t="n"/>
+      <c r="G21" s="362" t="n"/>
+      <c r="H21" s="362" t="n"/>
+      <c r="I21" s="362" t="n"/>
+      <c r="J21" s="362" t="n"/>
+      <c r="K21" s="362" t="n"/>
+      <c r="L21" s="362" t="n"/>
+      <c r="M21" s="362" t="n"/>
+      <c r="N21" s="362" t="n"/>
+      <c r="O21" s="362" t="n"/>
+      <c r="P21" s="362" t="n"/>
+      <c r="Q21" s="362" t="n"/>
+      <c r="R21" s="362" t="n"/>
+      <c r="S21" s="362" t="n"/>
+      <c r="T21" s="362" t="n"/>
+      <c r="U21" s="362" t="n"/>
+      <c r="V21" s="362" t="n"/>
+      <c r="W21" s="362" t="n"/>
+      <c r="X21" s="362" t="n"/>
+      <c r="Y21" s="362" t="n"/>
+      <c r="Z21" s="362" t="n"/>
+      <c r="AA21" s="362" t="n"/>
+      <c r="AB21" s="362" t="n"/>
+      <c r="AC21" s="362" t="n"/>
+      <c r="AD21" s="362" t="n"/>
+      <c r="AE21" s="362" t="n"/>
+      <c r="AF21" s="362" t="n"/>
+      <c r="AG21" s="362" t="n"/>
+      <c r="AH21" s="362" t="n"/>
+      <c r="AI21" s="362" t="n"/>
+      <c r="AJ21" s="362" t="n"/>
+      <c r="AK21" s="362" t="n"/>
+      <c r="AL21" s="362" t="n"/>
+      <c r="AM21" s="362" t="n"/>
+      <c r="AN21" s="362" t="n"/>
+      <c r="AO21" s="362" t="n"/>
+      <c r="AP21" s="362" t="n"/>
+      <c r="AQ21" s="362" t="n"/>
+      <c r="AR21" s="362" t="n"/>
+      <c r="AS21" s="362" t="n"/>
+      <c r="AT21" s="362" t="n"/>
+      <c r="AU21" s="362" t="n"/>
+      <c r="AV21" s="362" t="n"/>
+      <c r="AW21" s="362" t="n"/>
+      <c r="AX21" s="362" t="n"/>
+      <c r="AY21" s="362" t="n"/>
+      <c r="AZ21" s="362" t="n"/>
+      <c r="BA21" s="362" t="n"/>
+      <c r="BB21" s="362" t="n"/>
+      <c r="BC21" s="362" t="n"/>
+      <c r="BD21" s="363" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1"/>
     <row r="23" ht="20" customHeight="1"/>
@@ -9187,7 +8982,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="273" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -9199,7 +8994,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
-      <c r="L1" s="255" t="inlineStr">
+      <c r="L1" s="372" t="inlineStr">
         <is>
           <t>TRAINING PLAN — CONTROLLED LOOKUP LISTS</t>
         </is>
@@ -9233,7 +9028,7 @@
       <c r="AM1" s="2" t="n"/>
       <c r="AN1" s="2" t="n"/>
       <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
+      <c r="AP1" s="3" t="n"/>
       <c r="AQ1" s="327" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -9258,286 +9053,454 @@
       <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="AQ2" s="329" t="inlineStr">
+      <c r="A2" s="336" t="n"/>
+      <c r="B2" s="337" t="n"/>
+      <c r="C2" s="337" t="n"/>
+      <c r="D2" s="337" t="n"/>
+      <c r="E2" s="337" t="n"/>
+      <c r="F2" s="337" t="n"/>
+      <c r="G2" s="337" t="n"/>
+      <c r="H2" s="337" t="n"/>
+      <c r="I2" s="337" t="n"/>
+      <c r="J2" s="337" t="n"/>
+      <c r="K2" s="338" t="n"/>
+      <c r="L2" s="337" t="n"/>
+      <c r="M2" s="337" t="n"/>
+      <c r="N2" s="337" t="n"/>
+      <c r="O2" s="337" t="n"/>
+      <c r="P2" s="337" t="n"/>
+      <c r="Q2" s="337" t="n"/>
+      <c r="R2" s="337" t="n"/>
+      <c r="S2" s="337" t="n"/>
+      <c r="T2" s="337" t="n"/>
+      <c r="U2" s="337" t="n"/>
+      <c r="V2" s="337" t="n"/>
+      <c r="W2" s="337" t="n"/>
+      <c r="X2" s="337" t="n"/>
+      <c r="Y2" s="337" t="n"/>
+      <c r="Z2" s="337" t="n"/>
+      <c r="AA2" s="337" t="n"/>
+      <c r="AB2" s="337" t="n"/>
+      <c r="AC2" s="337" t="n"/>
+      <c r="AD2" s="337" t="n"/>
+      <c r="AE2" s="337" t="n"/>
+      <c r="AF2" s="337" t="n"/>
+      <c r="AG2" s="337" t="n"/>
+      <c r="AH2" s="337" t="n"/>
+      <c r="AI2" s="337" t="n"/>
+      <c r="AJ2" s="337" t="n"/>
+      <c r="AK2" s="337" t="n"/>
+      <c r="AL2" s="337" t="n"/>
+      <c r="AM2" s="337" t="n"/>
+      <c r="AN2" s="337" t="n"/>
+      <c r="AO2" s="337" t="n"/>
+      <c r="AP2" s="338" t="n"/>
+      <c r="AQ2" s="339" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="278" t="n"/>
-      <c r="AS2" s="278" t="n"/>
-      <c r="AT2" s="278" t="n"/>
-      <c r="AU2" s="278" t="n"/>
-      <c r="AV2" s="279" t="n"/>
-      <c r="AW2" s="330" t="inlineStr">
+      <c r="AR2" s="340" t="n"/>
+      <c r="AS2" s="340" t="n"/>
+      <c r="AT2" s="340" t="n"/>
+      <c r="AU2" s="340" t="n"/>
+      <c r="AV2" s="341" t="n"/>
+      <c r="AW2" s="342" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="278" t="n"/>
-      <c r="AY2" s="278" t="n"/>
-      <c r="AZ2" s="278" t="n"/>
-      <c r="BA2" s="278" t="n"/>
-      <c r="BB2" s="278" t="n"/>
-      <c r="BC2" s="278" t="n"/>
-      <c r="BD2" s="281" t="n"/>
+      <c r="AX2" s="343" t="n"/>
+      <c r="AY2" s="343" t="n"/>
+      <c r="AZ2" s="343" t="n"/>
+      <c r="BA2" s="343" t="n"/>
+      <c r="BB2" s="343" t="n"/>
+      <c r="BC2" s="343" t="n"/>
+      <c r="BD2" s="344" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="9" t="n"/>
-      <c r="AQ3" s="329" t="inlineStr">
+      <c r="A3" s="345" t="n"/>
+      <c r="B3" s="46" t="n"/>
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="46" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="46" t="n"/>
+      <c r="G3" s="46" t="n"/>
+      <c r="H3" s="46" t="n"/>
+      <c r="I3" s="46" t="n"/>
+      <c r="J3" s="46" t="n"/>
+      <c r="K3" s="346" t="n"/>
+      <c r="L3" s="46" t="n"/>
+      <c r="M3" s="46" t="n"/>
+      <c r="N3" s="46" t="n"/>
+      <c r="O3" s="46" t="n"/>
+      <c r="P3" s="46" t="n"/>
+      <c r="Q3" s="46" t="n"/>
+      <c r="R3" s="46" t="n"/>
+      <c r="S3" s="46" t="n"/>
+      <c r="T3" s="46" t="n"/>
+      <c r="U3" s="46" t="n"/>
+      <c r="V3" s="46" t="n"/>
+      <c r="W3" s="46" t="n"/>
+      <c r="X3" s="46" t="n"/>
+      <c r="Y3" s="46" t="n"/>
+      <c r="Z3" s="46" t="n"/>
+      <c r="AA3" s="46" t="n"/>
+      <c r="AB3" s="46" t="n"/>
+      <c r="AC3" s="46" t="n"/>
+      <c r="AD3" s="46" t="n"/>
+      <c r="AE3" s="46" t="n"/>
+      <c r="AF3" s="46" t="n"/>
+      <c r="AG3" s="46" t="n"/>
+      <c r="AH3" s="46" t="n"/>
+      <c r="AI3" s="46" t="n"/>
+      <c r="AJ3" s="46" t="n"/>
+      <c r="AK3" s="46" t="n"/>
+      <c r="AL3" s="46" t="n"/>
+      <c r="AM3" s="46" t="n"/>
+      <c r="AN3" s="46" t="n"/>
+      <c r="AO3" s="46" t="n"/>
+      <c r="AP3" s="346" t="n"/>
+      <c r="AQ3" s="347" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="278" t="n"/>
-      <c r="AS3" s="278" t="n"/>
-      <c r="AT3" s="278" t="n"/>
-      <c r="AU3" s="278" t="n"/>
-      <c r="AV3" s="279" t="n"/>
-      <c r="AW3" s="330" t="inlineStr">
+      <c r="AR3" s="348" t="n"/>
+      <c r="AS3" s="348" t="n"/>
+      <c r="AT3" s="348" t="n"/>
+      <c r="AU3" s="348" t="n"/>
+      <c r="AV3" s="349" t="n"/>
+      <c r="AW3" s="243" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="278" t="n"/>
-      <c r="AY3" s="278" t="n"/>
-      <c r="AZ3" s="278" t="n"/>
-      <c r="BA3" s="278" t="n"/>
-      <c r="BB3" s="278" t="n"/>
-      <c r="BC3" s="278" t="n"/>
-      <c r="BD3" s="281" t="n"/>
+      <c r="AX3" s="350" t="n"/>
+      <c r="AY3" s="350" t="n"/>
+      <c r="AZ3" s="350" t="n"/>
+      <c r="BA3" s="350" t="n"/>
+      <c r="BB3" s="350" t="n"/>
+      <c r="BC3" s="350" t="n"/>
+      <c r="BD3" s="351" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="41" t="inlineStr">
+      <c r="A4" s="345" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
+      <c r="I4" s="46" t="n"/>
+      <c r="J4" s="46" t="n"/>
+      <c r="K4" s="346" t="n"/>
+      <c r="L4" s="352" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="329" t="inlineStr">
+      <c r="M4" s="46" t="n"/>
+      <c r="N4" s="46" t="n"/>
+      <c r="O4" s="46" t="n"/>
+      <c r="P4" s="46" t="n"/>
+      <c r="Q4" s="46" t="n"/>
+      <c r="R4" s="46" t="n"/>
+      <c r="S4" s="46" t="n"/>
+      <c r="T4" s="46" t="n"/>
+      <c r="U4" s="46" t="n"/>
+      <c r="V4" s="46" t="n"/>
+      <c r="W4" s="46" t="n"/>
+      <c r="X4" s="46" t="n"/>
+      <c r="Y4" s="46" t="n"/>
+      <c r="Z4" s="46" t="n"/>
+      <c r="AA4" s="46" t="n"/>
+      <c r="AB4" s="46" t="n"/>
+      <c r="AC4" s="46" t="n"/>
+      <c r="AD4" s="46" t="n"/>
+      <c r="AE4" s="46" t="n"/>
+      <c r="AF4" s="46" t="n"/>
+      <c r="AG4" s="46" t="n"/>
+      <c r="AH4" s="46" t="n"/>
+      <c r="AI4" s="46" t="n"/>
+      <c r="AJ4" s="46" t="n"/>
+      <c r="AK4" s="46" t="n"/>
+      <c r="AL4" s="46" t="n"/>
+      <c r="AM4" s="46" t="n"/>
+      <c r="AN4" s="46" t="n"/>
+      <c r="AO4" s="46" t="n"/>
+      <c r="AP4" s="346" t="n"/>
+      <c r="AQ4" s="347" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="278" t="n"/>
-      <c r="AS4" s="278" t="n"/>
-      <c r="AT4" s="278" t="n"/>
-      <c r="AU4" s="278" t="n"/>
-      <c r="AV4" s="279" t="n"/>
-      <c r="AW4" s="330" t="inlineStr">
+      <c r="AR4" s="348" t="n"/>
+      <c r="AS4" s="348" t="n"/>
+      <c r="AT4" s="348" t="n"/>
+      <c r="AU4" s="348" t="n"/>
+      <c r="AV4" s="349" t="n"/>
+      <c r="AW4" s="243" t="inlineStr">
         <is>
           <t>HR + Department Manager</t>
         </is>
       </c>
-      <c r="AX4" s="278" t="n"/>
-      <c r="AY4" s="278" t="n"/>
-      <c r="AZ4" s="278" t="n"/>
-      <c r="BA4" s="278" t="n"/>
-      <c r="BB4" s="278" t="n"/>
-      <c r="BC4" s="278" t="n"/>
-      <c r="BD4" s="281" t="n"/>
+      <c r="AX4" s="350" t="n"/>
+      <c r="AY4" s="350" t="n"/>
+      <c r="AZ4" s="350" t="n"/>
+      <c r="BA4" s="350" t="n"/>
+      <c r="BB4" s="350" t="n"/>
+      <c r="BC4" s="350" t="n"/>
+      <c r="BD4" s="351" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="14" t="n"/>
-      <c r="L5" s="42" t="inlineStr">
+      <c r="A5" s="345" t="n"/>
+      <c r="B5" s="46" t="n"/>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+      <c r="E5" s="46" t="n"/>
+      <c r="F5" s="46" t="n"/>
+      <c r="G5" s="46" t="n"/>
+      <c r="H5" s="46" t="n"/>
+      <c r="I5" s="46" t="n"/>
+      <c r="J5" s="46" t="n"/>
+      <c r="K5" s="346" t="n"/>
+      <c r="L5" s="353" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="13" t="n"/>
-      <c r="N5" s="13" t="n"/>
-      <c r="O5" s="13" t="n"/>
-      <c r="P5" s="13" t="n"/>
-      <c r="Q5" s="13" t="n"/>
-      <c r="R5" s="13" t="n"/>
-      <c r="S5" s="13" t="n"/>
-      <c r="T5" s="13" t="n"/>
-      <c r="U5" s="13" t="n"/>
-      <c r="V5" s="13" t="n"/>
-      <c r="W5" s="13" t="n"/>
-      <c r="X5" s="13" t="n"/>
-      <c r="Y5" s="13" t="n"/>
-      <c r="Z5" s="13" t="n"/>
-      <c r="AA5" s="13" t="n"/>
-      <c r="AB5" s="13" t="n"/>
-      <c r="AC5" s="13" t="n"/>
-      <c r="AD5" s="13" t="n"/>
-      <c r="AE5" s="13" t="n"/>
-      <c r="AF5" s="13" t="n"/>
-      <c r="AG5" s="13" t="n"/>
-      <c r="AH5" s="13" t="n"/>
-      <c r="AI5" s="13" t="n"/>
-      <c r="AJ5" s="13" t="n"/>
-      <c r="AK5" s="13" t="n"/>
-      <c r="AL5" s="13" t="n"/>
-      <c r="AM5" s="13" t="n"/>
-      <c r="AN5" s="13" t="n"/>
-      <c r="AO5" s="13" t="n"/>
-      <c r="AP5" s="13" t="n"/>
-      <c r="AQ5" s="331" t="inlineStr">
+      <c r="M5" s="46" t="n"/>
+      <c r="N5" s="46" t="n"/>
+      <c r="O5" s="46" t="n"/>
+      <c r="P5" s="46" t="n"/>
+      <c r="Q5" s="46" t="n"/>
+      <c r="R5" s="46" t="n"/>
+      <c r="S5" s="46" t="n"/>
+      <c r="T5" s="46" t="n"/>
+      <c r="U5" s="46" t="n"/>
+      <c r="V5" s="46" t="n"/>
+      <c r="W5" s="46" t="n"/>
+      <c r="X5" s="46" t="n"/>
+      <c r="Y5" s="46" t="n"/>
+      <c r="Z5" s="46" t="n"/>
+      <c r="AA5" s="46" t="n"/>
+      <c r="AB5" s="46" t="n"/>
+      <c r="AC5" s="46" t="n"/>
+      <c r="AD5" s="46" t="n"/>
+      <c r="AE5" s="46" t="n"/>
+      <c r="AF5" s="46" t="n"/>
+      <c r="AG5" s="46" t="n"/>
+      <c r="AH5" s="46" t="n"/>
+      <c r="AI5" s="46" t="n"/>
+      <c r="AJ5" s="46" t="n"/>
+      <c r="AK5" s="46" t="n"/>
+      <c r="AL5" s="46" t="n"/>
+      <c r="AM5" s="46" t="n"/>
+      <c r="AN5" s="46" t="n"/>
+      <c r="AO5" s="46" t="n"/>
+      <c r="AP5" s="346" t="n"/>
+      <c r="AQ5" s="347" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="283" t="n"/>
-      <c r="AS5" s="283" t="n"/>
-      <c r="AT5" s="283" t="n"/>
-      <c r="AU5" s="283" t="n"/>
-      <c r="AV5" s="284" t="n"/>
-      <c r="AW5" s="332" t="inlineStr">
+      <c r="AR5" s="348" t="n"/>
+      <c r="AS5" s="348" t="n"/>
+      <c r="AT5" s="348" t="n"/>
+      <c r="AU5" s="348" t="n"/>
+      <c r="AV5" s="349" t="n"/>
+      <c r="AW5" s="243" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="283" t="n"/>
-      <c r="AY5" s="283" t="n"/>
-      <c r="AZ5" s="283" t="n"/>
-      <c r="BA5" s="283" t="n"/>
-      <c r="BB5" s="283" t="n"/>
-      <c r="BC5" s="283" t="n"/>
-      <c r="BD5" s="286" t="n"/>
+      <c r="AX5" s="350" t="n"/>
+      <c r="AY5" s="350" t="n"/>
+      <c r="AZ5" s="350" t="n"/>
+      <c r="BA5" s="350" t="n"/>
+      <c r="BB5" s="350" t="n"/>
+      <c r="BC5" s="350" t="n"/>
+      <c r="BD5" s="351" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="241" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="354" t="n"/>
+      <c r="B6" s="364" t="n"/>
+      <c r="C6" s="364" t="n"/>
+      <c r="D6" s="364" t="n"/>
+      <c r="E6" s="364" t="n"/>
+      <c r="F6" s="364" t="n"/>
+      <c r="G6" s="364" t="n"/>
+      <c r="H6" s="364" t="n"/>
+      <c r="I6" s="364" t="n"/>
+      <c r="J6" s="364" t="n"/>
+      <c r="K6" s="365" t="n"/>
+      <c r="L6" s="364" t="n"/>
+      <c r="M6" s="364" t="n"/>
+      <c r="N6" s="364" t="n"/>
+      <c r="O6" s="364" t="n"/>
+      <c r="P6" s="364" t="n"/>
+      <c r="Q6" s="364" t="n"/>
+      <c r="R6" s="364" t="n"/>
+      <c r="S6" s="364" t="n"/>
+      <c r="T6" s="364" t="n"/>
+      <c r="U6" s="364" t="n"/>
+      <c r="V6" s="364" t="n"/>
+      <c r="W6" s="364" t="n"/>
+      <c r="X6" s="364" t="n"/>
+      <c r="Y6" s="364" t="n"/>
+      <c r="Z6" s="364" t="n"/>
+      <c r="AA6" s="364" t="n"/>
+      <c r="AB6" s="364" t="n"/>
+      <c r="AC6" s="364" t="n"/>
+      <c r="AD6" s="364" t="n"/>
+      <c r="AE6" s="364" t="n"/>
+      <c r="AF6" s="364" t="n"/>
+      <c r="AG6" s="364" t="n"/>
+      <c r="AH6" s="364" t="n"/>
+      <c r="AI6" s="364" t="n"/>
+      <c r="AJ6" s="364" t="n"/>
+      <c r="AK6" s="364" t="n"/>
+      <c r="AL6" s="364" t="n"/>
+      <c r="AM6" s="364" t="n"/>
+      <c r="AN6" s="364" t="n"/>
+      <c r="AO6" s="364" t="n"/>
+      <c r="AP6" s="365" t="n"/>
+      <c r="AQ6" s="366" t="n"/>
+      <c r="AR6" s="366" t="n"/>
+      <c r="AS6" s="366" t="n"/>
+      <c r="AT6" s="366" t="n"/>
+      <c r="AU6" s="366" t="n"/>
+      <c r="AV6" s="367" t="n"/>
+      <c r="AW6" s="368" t="n"/>
+      <c r="AX6" s="368" t="n"/>
+      <c r="AY6" s="368" t="n"/>
+      <c r="AZ6" s="368" t="n"/>
+      <c r="BA6" s="368" t="n"/>
+      <c r="BB6" s="368" t="n"/>
+      <c r="BC6" s="368" t="n"/>
+      <c r="BD6" s="369" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. CONTROLLED LOOKUP LISTS</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="6" t="n"/>
-      <c r="R7" s="6" t="n"/>
-      <c r="S7" s="6" t="n"/>
-      <c r="T7" s="6" t="n"/>
-      <c r="U7" s="6" t="n"/>
-      <c r="V7" s="6" t="n"/>
-      <c r="W7" s="6" t="n"/>
-      <c r="X7" s="6" t="n"/>
-      <c r="Y7" s="6" t="n"/>
-      <c r="Z7" s="6" t="n"/>
-      <c r="AA7" s="6" t="n"/>
-      <c r="AB7" s="6" t="n"/>
-      <c r="AC7" s="6" t="n"/>
-      <c r="AD7" s="6" t="n"/>
-      <c r="AE7" s="6" t="n"/>
-      <c r="AF7" s="6" t="n"/>
-      <c r="AG7" s="6" t="n"/>
-      <c r="AH7" s="6" t="n"/>
-      <c r="AI7" s="6" t="n"/>
-      <c r="AJ7" s="6" t="n"/>
-      <c r="AK7" s="6" t="n"/>
-      <c r="AL7" s="6" t="n"/>
-      <c r="AM7" s="6" t="n"/>
-      <c r="AN7" s="6" t="n"/>
-      <c r="AO7" s="6" t="n"/>
-      <c r="AP7" s="6" t="n"/>
-      <c r="AQ7" s="6" t="n"/>
-      <c r="AR7" s="6" t="n"/>
-      <c r="AS7" s="6" t="n"/>
-      <c r="AT7" s="6" t="n"/>
-      <c r="AU7" s="6" t="n"/>
-      <c r="AV7" s="6" t="n"/>
-      <c r="AW7" s="6" t="n"/>
-      <c r="AX7" s="6" t="n"/>
-      <c r="AY7" s="6" t="n"/>
-      <c r="AZ7" s="6" t="n"/>
-      <c r="BA7" s="6" t="n"/>
-      <c r="BB7" s="6" t="n"/>
-      <c r="BC7" s="6" t="n"/>
-      <c r="BD7" s="7" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="370" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n"/>
+      <c r="P7" s="17" t="n"/>
+      <c r="Q7" s="17" t="n"/>
+      <c r="R7" s="17" t="n"/>
+      <c r="S7" s="17" t="n"/>
+      <c r="T7" s="17" t="n"/>
+      <c r="U7" s="17" t="n"/>
+      <c r="V7" s="17" t="n"/>
+      <c r="W7" s="17" t="n"/>
+      <c r="X7" s="17" t="n"/>
+      <c r="Y7" s="17" t="n"/>
+      <c r="Z7" s="17" t="n"/>
+      <c r="AA7" s="17" t="n"/>
+      <c r="AB7" s="17" t="n"/>
+      <c r="AC7" s="17" t="n"/>
+      <c r="AD7" s="17" t="n"/>
+      <c r="AE7" s="17" t="n"/>
+      <c r="AF7" s="17" t="n"/>
+      <c r="AG7" s="17" t="n"/>
+      <c r="AH7" s="17" t="n"/>
+      <c r="AI7" s="17" t="n"/>
+      <c r="AJ7" s="17" t="n"/>
+      <c r="AK7" s="17" t="n"/>
+      <c r="AL7" s="17" t="n"/>
+      <c r="AM7" s="17" t="n"/>
+      <c r="AN7" s="17" t="n"/>
+      <c r="AO7" s="17" t="n"/>
+      <c r="AP7" s="17" t="n"/>
+      <c r="AQ7" s="17" t="n"/>
+      <c r="AR7" s="17" t="n"/>
+      <c r="AS7" s="17" t="n"/>
+      <c r="AT7" s="17" t="n"/>
+      <c r="AU7" s="17" t="n"/>
+      <c r="AV7" s="17" t="n"/>
+      <c r="AW7" s="17" t="n"/>
+      <c r="AX7" s="17" t="n"/>
+      <c r="AY7" s="17" t="n"/>
+      <c r="AZ7" s="17" t="n"/>
+      <c r="BA7" s="17" t="n"/>
+      <c r="BB7" s="17" t="n"/>
+      <c r="BC7" s="17" t="n"/>
+      <c r="BD7" s="17" t="n"/>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="263" t="inlineStr">
         <is>
           <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="6" t="n"/>
-      <c r="O8" s="6" t="n"/>
-      <c r="P8" s="6" t="n"/>
-      <c r="Q8" s="6" t="n"/>
-      <c r="R8" s="6" t="n"/>
-      <c r="S8" s="6" t="n"/>
-      <c r="T8" s="6" t="n"/>
-      <c r="U8" s="6" t="n"/>
-      <c r="V8" s="6" t="n"/>
-      <c r="W8" s="6" t="n"/>
-      <c r="X8" s="6" t="n"/>
-      <c r="Y8" s="6" t="n"/>
-      <c r="Z8" s="6" t="n"/>
-      <c r="AA8" s="6" t="n"/>
-      <c r="AB8" s="6" t="n"/>
-      <c r="AC8" s="6" t="n"/>
-      <c r="AD8" s="6" t="n"/>
-      <c r="AE8" s="6" t="n"/>
-      <c r="AF8" s="6" t="n"/>
-      <c r="AG8" s="6" t="n"/>
-      <c r="AH8" s="6" t="n"/>
-      <c r="AI8" s="6" t="n"/>
-      <c r="AJ8" s="6" t="n"/>
-      <c r="AK8" s="6" t="n"/>
-      <c r="AL8" s="6" t="n"/>
-      <c r="AM8" s="6" t="n"/>
-      <c r="AN8" s="6" t="n"/>
-      <c r="AO8" s="6" t="n"/>
-      <c r="AP8" s="6" t="n"/>
-      <c r="AQ8" s="6" t="n"/>
-      <c r="AR8" s="6" t="n"/>
-      <c r="AS8" s="6" t="n"/>
-      <c r="AT8" s="6" t="n"/>
-      <c r="AU8" s="6" t="n"/>
-      <c r="AV8" s="6" t="n"/>
-      <c r="AW8" s="6" t="n"/>
-      <c r="AX8" s="6" t="n"/>
-      <c r="AY8" s="6" t="n"/>
-      <c r="AZ8" s="6" t="n"/>
-      <c r="BA8" s="6" t="n"/>
-      <c r="BB8" s="6" t="n"/>
-      <c r="BC8" s="6" t="n"/>
-      <c r="BD8" s="7" t="n"/>
+      <c r="B8" s="362" t="n"/>
+      <c r="C8" s="362" t="n"/>
+      <c r="D8" s="362" t="n"/>
+      <c r="E8" s="362" t="n"/>
+      <c r="F8" s="362" t="n"/>
+      <c r="G8" s="362" t="n"/>
+      <c r="H8" s="362" t="n"/>
+      <c r="I8" s="362" t="n"/>
+      <c r="J8" s="362" t="n"/>
+      <c r="K8" s="362" t="n"/>
+      <c r="L8" s="362" t="n"/>
+      <c r="M8" s="362" t="n"/>
+      <c r="N8" s="362" t="n"/>
+      <c r="O8" s="362" t="n"/>
+      <c r="P8" s="362" t="n"/>
+      <c r="Q8" s="362" t="n"/>
+      <c r="R8" s="362" t="n"/>
+      <c r="S8" s="362" t="n"/>
+      <c r="T8" s="362" t="n"/>
+      <c r="U8" s="362" t="n"/>
+      <c r="V8" s="362" t="n"/>
+      <c r="W8" s="362" t="n"/>
+      <c r="X8" s="362" t="n"/>
+      <c r="Y8" s="362" t="n"/>
+      <c r="Z8" s="362" t="n"/>
+      <c r="AA8" s="362" t="n"/>
+      <c r="AB8" s="362" t="n"/>
+      <c r="AC8" s="362" t="n"/>
+      <c r="AD8" s="362" t="n"/>
+      <c r="AE8" s="362" t="n"/>
+      <c r="AF8" s="362" t="n"/>
+      <c r="AG8" s="362" t="n"/>
+      <c r="AH8" s="362" t="n"/>
+      <c r="AI8" s="362" t="n"/>
+      <c r="AJ8" s="362" t="n"/>
+      <c r="AK8" s="362" t="n"/>
+      <c r="AL8" s="362" t="n"/>
+      <c r="AM8" s="362" t="n"/>
+      <c r="AN8" s="362" t="n"/>
+      <c r="AO8" s="362" t="n"/>
+      <c r="AP8" s="362" t="n"/>
+      <c r="AQ8" s="362" t="n"/>
+      <c r="AR8" s="362" t="n"/>
+      <c r="AS8" s="362" t="n"/>
+      <c r="AT8" s="362" t="n"/>
+      <c r="AU8" s="362" t="n"/>
+      <c r="AV8" s="362" t="n"/>
+      <c r="AW8" s="362" t="n"/>
+      <c r="AX8" s="362" t="n"/>
+      <c r="AY8" s="362" t="n"/>
+      <c r="AZ8" s="362" t="n"/>
+      <c r="BA8" s="362" t="n"/>
+      <c r="BB8" s="362" t="n"/>
+      <c r="BC8" s="362" t="n"/>
+      <c r="BD8" s="363" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="246" t="inlineStr">
@@ -10909,67 +10872,67 @@
       <c r="BC21" s="271" t="n"/>
       <c r="BD21" s="272" t="n"/>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="23" t="inlineStr">
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="263" t="inlineStr">
         <is>
           <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
-      <c r="M22" s="6" t="n"/>
-      <c r="N22" s="6" t="n"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="6" t="n"/>
-      <c r="Q22" s="6" t="n"/>
-      <c r="R22" s="6" t="n"/>
-      <c r="S22" s="6" t="n"/>
-      <c r="T22" s="6" t="n"/>
-      <c r="U22" s="6" t="n"/>
-      <c r="V22" s="6" t="n"/>
-      <c r="W22" s="6" t="n"/>
-      <c r="X22" s="6" t="n"/>
-      <c r="Y22" s="6" t="n"/>
-      <c r="Z22" s="6" t="n"/>
-      <c r="AA22" s="6" t="n"/>
-      <c r="AB22" s="6" t="n"/>
-      <c r="AC22" s="6" t="n"/>
-      <c r="AD22" s="6" t="n"/>
-      <c r="AE22" s="6" t="n"/>
-      <c r="AF22" s="6" t="n"/>
-      <c r="AG22" s="6" t="n"/>
-      <c r="AH22" s="6" t="n"/>
-      <c r="AI22" s="6" t="n"/>
-      <c r="AJ22" s="6" t="n"/>
-      <c r="AK22" s="6" t="n"/>
-      <c r="AL22" s="6" t="n"/>
-      <c r="AM22" s="6" t="n"/>
-      <c r="AN22" s="6" t="n"/>
-      <c r="AO22" s="6" t="n"/>
-      <c r="AP22" s="6" t="n"/>
-      <c r="AQ22" s="6" t="n"/>
-      <c r="AR22" s="6" t="n"/>
-      <c r="AS22" s="6" t="n"/>
-      <c r="AT22" s="6" t="n"/>
-      <c r="AU22" s="6" t="n"/>
-      <c r="AV22" s="6" t="n"/>
-      <c r="AW22" s="6" t="n"/>
-      <c r="AX22" s="6" t="n"/>
-      <c r="AY22" s="6" t="n"/>
-      <c r="AZ22" s="6" t="n"/>
-      <c r="BA22" s="6" t="n"/>
-      <c r="BB22" s="6" t="n"/>
-      <c r="BC22" s="6" t="n"/>
-      <c r="BD22" s="7" t="n"/>
+      <c r="B22" s="362" t="n"/>
+      <c r="C22" s="362" t="n"/>
+      <c r="D22" s="362" t="n"/>
+      <c r="E22" s="362" t="n"/>
+      <c r="F22" s="362" t="n"/>
+      <c r="G22" s="362" t="n"/>
+      <c r="H22" s="362" t="n"/>
+      <c r="I22" s="362" t="n"/>
+      <c r="J22" s="362" t="n"/>
+      <c r="K22" s="362" t="n"/>
+      <c r="L22" s="362" t="n"/>
+      <c r="M22" s="362" t="n"/>
+      <c r="N22" s="362" t="n"/>
+      <c r="O22" s="362" t="n"/>
+      <c r="P22" s="362" t="n"/>
+      <c r="Q22" s="362" t="n"/>
+      <c r="R22" s="362" t="n"/>
+      <c r="S22" s="362" t="n"/>
+      <c r="T22" s="362" t="n"/>
+      <c r="U22" s="362" t="n"/>
+      <c r="V22" s="362" t="n"/>
+      <c r="W22" s="362" t="n"/>
+      <c r="X22" s="362" t="n"/>
+      <c r="Y22" s="362" t="n"/>
+      <c r="Z22" s="362" t="n"/>
+      <c r="AA22" s="362" t="n"/>
+      <c r="AB22" s="362" t="n"/>
+      <c r="AC22" s="362" t="n"/>
+      <c r="AD22" s="362" t="n"/>
+      <c r="AE22" s="362" t="n"/>
+      <c r="AF22" s="362" t="n"/>
+      <c r="AG22" s="362" t="n"/>
+      <c r="AH22" s="362" t="n"/>
+      <c r="AI22" s="362" t="n"/>
+      <c r="AJ22" s="362" t="n"/>
+      <c r="AK22" s="362" t="n"/>
+      <c r="AL22" s="362" t="n"/>
+      <c r="AM22" s="362" t="n"/>
+      <c r="AN22" s="362" t="n"/>
+      <c r="AO22" s="362" t="n"/>
+      <c r="AP22" s="362" t="n"/>
+      <c r="AQ22" s="362" t="n"/>
+      <c r="AR22" s="362" t="n"/>
+      <c r="AS22" s="362" t="n"/>
+      <c r="AT22" s="362" t="n"/>
+      <c r="AU22" s="362" t="n"/>
+      <c r="AV22" s="362" t="n"/>
+      <c r="AW22" s="362" t="n"/>
+      <c r="AX22" s="362" t="n"/>
+      <c r="AY22" s="362" t="n"/>
+      <c r="AZ22" s="362" t="n"/>
+      <c r="BA22" s="362" t="n"/>
+      <c r="BB22" s="362" t="n"/>
+      <c r="BC22" s="362" t="n"/>
+      <c r="BD22" s="363" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/04-Bieu-Mau/08-FRM-800/FRM-801_Training_Plan.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-801_Training_Plan.xlsx
@@ -826,6 +826,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2973,7 +2976,6 @@
     <row r="198" ht="20" customHeight="1"/>
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="75">
     <mergeCell ref="L4:AP4"/>
     <mergeCell ref="AC10:AL10"/>
@@ -4587,7 +4589,6 @@
     <row r="198" ht="20" customHeight="1"/>
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="105">
     <mergeCell ref="AT13:AX13"/>
     <mergeCell ref="AO17:AS17"/>
@@ -6178,7 +6179,6 @@
     <row r="198" ht="20" customHeight="1"/>
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="88">
     <mergeCell ref="N19:W19"/>
     <mergeCell ref="AW2:BD2"/>

--- a/04-Bieu-Mau/08-FRM-800/FRM-801_Training_Plan.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-801_Training_Plan.xlsx
@@ -1357,7 +1357,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>HR + Department Manager</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -1427,7 +1427,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -3327,7 +3327,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>HR + Department Manager</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -3397,7 +3397,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -4978,7 +4978,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>HR + Department Manager</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -5048,7 +5048,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -6521,7 +6521,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>HR + Department Manager</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -6591,7 +6591,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>

--- a/04-Bieu-Mau/08-FRM-800/FRM-801_Training_Plan.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-801_Training_Plan.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM801_TrainPlan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM801_Targets" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM801_Targets" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM801_Evidence" sheetId="3" state="veryHidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="zLISTS" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REV_HISTORY" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'FRM801_TrainPlan'!$1:$6</definedName>
@@ -812,7 +814,7 @@
       <row>0</row>
       <rowOff>257175</rowOff>
     </from>
-    <ext cx="1552575" cy="438150"/>
+    <ext cx="5238750" cy="1514475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1271,7 +1273,7 @@
       <c r="AV2" s="37" t="n"/>
       <c r="AW2" s="38" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="AX2" s="36" t="n"/>
@@ -1327,7 +1329,7 @@
       <c r="AV3" s="37" t="n"/>
       <c r="AW3" s="38" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AX3" s="36" t="n"/>
@@ -1357,7 +1359,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + Department Manager</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -1427,7 +1429,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -1638,7 +1640,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>Target Population</t>
+          <t>Linked FRM-807</t>
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
@@ -1670,7 +1672,7 @@
       <c r="AB10" s="27" t="n"/>
       <c r="AC10" s="19" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Ref: SOP-801</t>
         </is>
       </c>
       <c r="AD10" s="6" t="n"/>
@@ -1682,7 +1684,11 @@
       <c r="AJ10" s="6" t="n"/>
       <c r="AK10" s="6" t="n"/>
       <c r="AL10" s="7" t="n"/>
-      <c r="AM10" s="20" t="n"/>
+      <c r="AM10" s="20" t="inlineStr">
+        <is>
+          <t>Retain: 5 years per QMS schedule</t>
+        </is>
+      </c>
       <c r="AN10" s="26" t="n"/>
       <c r="AO10" s="26" t="n"/>
       <c r="AP10" s="26" t="n"/>
@@ -2976,6 +2982,7 @@
     <row r="198" ht="20" customHeight="1"/>
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="75">
     <mergeCell ref="L4:AP4"/>
     <mergeCell ref="AC10:AL10"/>
@@ -3327,7 +3334,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + Department Manager</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -3397,7 +3404,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -4589,6 +4596,7 @@
     <row r="198" ht="20" customHeight="1"/>
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="105">
     <mergeCell ref="AT13:AX13"/>
     <mergeCell ref="AO17:AS17"/>
@@ -4978,7 +4986,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + Department Manager</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -5048,7 +5056,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -6179,6 +6187,7 @@
     <row r="198" ht="20" customHeight="1"/>
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="88">
     <mergeCell ref="N19:W19"/>
     <mergeCell ref="AW2:BD2"/>
@@ -6521,7 +6530,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + Department Manager</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -6591,7 +6600,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -7895,4 +7904,97 @@
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial release</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QMS Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cross-ref: FRM-807; Parent ref: SOP-801</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QMS Upgrade</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/04-Bieu-Mau/08-FRM-800/FRM-801_Training_Plan.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-801_Training_Plan.xlsx
@@ -4969,6 +4969,83 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>Năm / Kỳ kế hoạch
+Ví dụ: FY2026.</t>
+      </text>
+    </comment>
+    <comment ref="AC9" authorId="0" shapeId="0">
+      <text>
+        <t>Người chuẩn bị
+HR Manager.</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t>Bộ phận
+Áp dụng cho bộ phận hoặc toàn công ty.</t>
+      </text>
+    </comment>
+    <comment ref="AC10" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Ngày phê duyệt
+</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>Lịch đào tạo
+ISO 9001 cl.7.2 — xác định năng lực cần thiết và đào tạo.
+Ghi từng chủ đề, đối tượng, ngày dự kiến, trạng thái.</t>
+      </text>
+    </comment>
+    <comment ref="H14" authorId="0" shapeId="0">
+      <text>
+        <t>Nhận thức ISO
+Đào tạo cơ bản về ISO 9001 / AS9100D cho toàn bộ nhân viên.</t>
+      </text>
+    </comment>
+    <comment ref="H15" authorId="0" shapeId="0">
+      <text>
+        <t>Chính sách chất lượng
+Truyền đạt chính sách và mục tiêu QMS.</t>
+      </text>
+    </comment>
+    <comment ref="H16" authorId="0" shapeId="0">
+      <text>
+        <t>Kỹ năng chuyên môn
+CNC operation, inspection, programming — theo skill matrix.</t>
+      </text>
+    </comment>
+    <comment ref="H17" authorId="0" shapeId="0">
+      <text>
+        <t>An toàn
+Sơ cứu, PCCC, sơ tán, PPE.</t>
+      </text>
+    </comment>
+    <comment ref="H18" authorId="0" shapeId="0">
+      <text>
+        <t>Đào tạo nhân viên mới
+Orientation: QMS, safety, quy định nội bộ.</t>
+      </text>
+    </comment>
+    <comment ref="H19" authorId="0" shapeId="0">
+      <text>
+        <t>CSR
+Customer-Specific Requirements: yêu cầu riêng của từng khách hàng.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6059,8 +6136,9 @@
       <c r="BD13" s="479" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="264">
-      <c r="A14" s="490" t="n">
-        <v>1</v>
+      <c r="A14" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B14" s="491" t="n"/>
       <c r="C14" s="492" t="n"/>
@@ -6131,8 +6209,9 @@
       <c r="BD14" s="498" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="264">
-      <c r="A15" s="490" t="n">
-        <v>2</v>
+      <c r="A15" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B15" s="491" t="n"/>
       <c r="C15" s="492" t="n"/>
@@ -6203,8 +6282,9 @@
       <c r="BD15" s="498" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="264">
-      <c r="A16" s="490" t="n">
-        <v>3</v>
+      <c r="A16" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B16" s="491" t="n"/>
       <c r="C16" s="492" t="n"/>
@@ -6218,7 +6298,7 @@
       <c r="G16" s="492" t="n"/>
       <c r="H16" s="494" t="inlineStr">
         <is>
-          <t>Job-specific skills (CNC, inspection, etc.).</t>
+          <t>Job-specific skills (CNC, inspection).</t>
         </is>
       </c>
       <c r="I16" s="491" t="n"/>
@@ -6275,8 +6355,9 @@
       <c r="BD16" s="498" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="264">
-      <c r="A17" s="490" t="n">
-        <v>4</v>
+      <c r="A17" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B17" s="491" t="n"/>
       <c r="C17" s="492" t="n"/>
@@ -6347,8 +6428,9 @@
       <c r="BD17" s="498" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="264">
-      <c r="A18" s="490" t="n">
-        <v>5</v>
+      <c r="A18" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B18" s="491" t="n"/>
       <c r="C18" s="492" t="n"/>
@@ -6419,8 +6501,9 @@
       <c r="BD18" s="498" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="264">
-      <c r="A19" s="490" t="n">
-        <v>6</v>
+      <c r="A19" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B19" s="491" t="n"/>
       <c r="C19" s="492" t="n"/>
@@ -6434,7 +6517,7 @@
       <c r="G19" s="492" t="n"/>
       <c r="H19" s="499" t="inlineStr">
         <is>
-          <t>Customer-specific requirements (CSR).</t>
+          <t>Customer-specific requirements.</t>
         </is>
       </c>
       <c r="I19" s="491" t="n"/>
@@ -6491,8 +6574,9 @@
       <c r="BD19" s="498" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="264">
-      <c r="A20" s="490" t="n">
-        <v>7</v>
+      <c r="A20" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B20" s="491" t="n"/>
       <c r="C20" s="492" t="n"/>
@@ -6551,8 +6635,9 @@
       <c r="BD20" s="498" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="264">
-      <c r="A21" s="490" t="n">
-        <v>8</v>
+      <c r="A21" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B21" s="491" t="n"/>
       <c r="C21" s="492" t="n"/>
@@ -6611,8 +6696,9 @@
       <c r="BD21" s="498" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="264">
-      <c r="A22" s="490" t="n">
-        <v>9</v>
+      <c r="A22" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B22" s="491" t="n"/>
       <c r="C22" s="492" t="n"/>
@@ -6671,8 +6757,9 @@
       <c r="BD22" s="498" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="264">
-      <c r="A23" s="490" t="n">
-        <v>10</v>
+      <c r="A23" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B23" s="491" t="n"/>
       <c r="C23" s="492" t="n"/>
@@ -6731,8 +6818,9 @@
       <c r="BD23" s="498" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1" s="264">
-      <c r="A24" s="490" t="n">
-        <v>11</v>
+      <c r="A24" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B24" s="491" t="n"/>
       <c r="C24" s="492" t="n"/>
@@ -6791,8 +6879,9 @@
       <c r="BD24" s="498" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1" s="264">
-      <c r="A25" s="504" t="n">
-        <v>12</v>
+      <c r="A25" s="504">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B25" s="481" t="n"/>
       <c r="C25" s="482" t="n"/>
@@ -7227,7 +7316,7 @@
     <row r="33" ht="24" customHeight="1" s="264">
       <c r="A33" s="516" t="inlineStr">
         <is>
-          <t>NOTICE — Annual plan. Ref: SOP-801. Retain: 5 years.</t>
+          <t>NOTICE — Annual plan. Track completion. Review at Management Review. Ref: SOP-801. Retain: 5 years.</t>
         </is>
       </c>
       <c r="B33" s="471" t="n"/>
@@ -7401,25 +7490,26 @@
     <mergeCell ref="A32:BD32"/>
     <mergeCell ref="AR23:AW23"/>
   </mergeCells>
-  <conditionalFormatting sqref="AF14:AF25">
+  <conditionalFormatting sqref="AR14:AR25">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
-      <formula>"PASS"</formula>
+      <formula>"CLOSED"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
-      <formula>"HOLD"</formula>
+      <formula>"IN PROGRESS"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
-      <formula>"FAIL"</formula>
+      <formula>"OPEN"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="AF14 AF15 AF16 AF17 AF18 AF19 AF20 AF21 AF22 AF23 AF24 AF25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>=LISTS!$A$2:$A$5</formula1>
+    <dataValidation sqref="AR14 AR15 AR16 AR17 AR18 AR19 AR20 AR21 AR22 AR23 AR24 AR25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>=LISTS!$C$2:$C$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
